--- a/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
+++ b/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00-使用说明" sheetId="1" r:id="Ref95c552b72344b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01-需求" sheetId="2" r:id="R38d36df26be74440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-子需求" sheetId="3" r:id="Rdce652d6205340fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-SOW主表" sheetId="4" r:id="Red87a1a08a6d4d79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-验收条件" sheetId="5" r:id="R7714d93cbbd04f44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05-任务明细" sheetId="6" r:id="R221abea5730348e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06-集成点" sheetId="7" r:id="R2ae0700585df4a21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-假设清单" sheetId="8" r:id="R746d8eb9189a40c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20-项目汇总" sheetId="9" r:id="R97672f45155f4368"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90-系统现状" sheetId="10" r:id="R4ab59e14b277468a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="91-项目参数" sheetId="11" r:id="R2bfef2b75b4e420f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="92-基础人天" sheetId="12" r:id="Rc2b9c209301e487a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00-使用说明" sheetId="1" r:id="R79fa3a44a61c466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01-需求" sheetId="2" r:id="R4b155fce7ad344c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-子需求" sheetId="3" r:id="R0e11e9e421d943d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-SOW主表" sheetId="4" r:id="R8f909793b4bd477a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-验收条件" sheetId="5" r:id="Re89c4710e0794387"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05-任务明细" sheetId="6" r:id="R9ba8af3ddebd4b77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06-集成点" sheetId="7" r:id="Raef57dc55099472c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-假设清单" sheetId="8" r:id="R417833d062064b2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20-项目汇总" sheetId="9" r:id="Rbcb1ddf84c1248e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90-系统现状" sheetId="10" r:id="Ra48c463e92a14453"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="91-项目参数" sheetId="11" r:id="R8de3c243240949b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="92-基础人天" sheetId="12" r:id="R600174cc391f414d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -322,7 +322,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="107">
+  <x:fills count="108">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -854,6 +854,11 @@
         <x:fgColor rgb="FFFFF5E3"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF5E3"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="38">
     <x:border/>
@@ -1364,7 +1369,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="666">
+  <x:cellXfs count="675">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -3100,6 +3105,33 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="107" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="107" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="44" fillId="107" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="44" fillId="107" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="44" fillId="107" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="44" fillId="107" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="44" fillId="107" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="44" fillId="107" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="44" fillId="107" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -5473,8 +5505,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23908f8eb74b49d1"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb630f32d9524410"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcabeb4cbf93e4926"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7d6f0ceb36f44f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5795,7 +5827,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8e6dff07d1c49b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba0859d1e85e4460"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8596,7 +8628,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf36eb22e7b54bdd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76636dbf87314b72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9646,7 +9678,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23b6002d81f64196"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5c6f53b828b420b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9846,28 +9878,28 @@
       <x:c r="J6"/>
       <x:c r="K6"/>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="604" t="str">
+    <x:row r="7" ht="34" customHeight="1">
+      <x:c r="A7" s="672" t="str">
         <x:v>feature-production-scope</x:v>
       </x:c>
-      <x:c r="B7" s="604" t="str">
+      <x:c r="B7" s="672" t="str">
         <x:v>epic-platform</x:v>
       </x:c>
-      <x:c r="C7" s="604" t="str">
+      <x:c r="C7" s="672" t="str">
         <x:v>平台边界</x:v>
       </x:c>
-      <x:c r="D7" s="604" t="str">
+      <x:c r="D7" s="672" t="str">
         <x:v>生产上线范围</x:v>
       </x:c>
-      <x:c r="E7" s="604" t="str">
+      <x:c r="E7" s="672" t="str">
         <x:v>明确客户档案能力的生产上线与运营移交责任边界。</x:v>
       </x:c>
-      <x:c r="F7" s="604" t="str"/>
-      <x:c r="G7" s="604" t="str"/>
-      <x:c r="H7" s="607" t="str">
+      <x:c r="F7" s="672" t="str"/>
+      <x:c r="G7" s="672" t="str"/>
+      <x:c r="H7" s="673" t="str">
         <x:v>SOURCE_INPUT</x:v>
       </x:c>
-      <x:c r="I7" s="604" t="str"/>
+      <x:c r="I7" s="672" t="str"/>
       <x:c r="J7"/>
       <x:c r="K7"/>
     </x:row>
@@ -11147,7 +11179,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a8fb71980094c53"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra58bd4ad2b9b44c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11287,11 +11319,11 @@
       </x:c>
       <x:c r="E5" s="608" t="str">
         <x:f>IF(C5="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C5,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</x:f>
-        <x:v>来源未匹配</x:v>
+        <x:v>客户管理</x:v>
       </x:c>
       <x:c r="F5" s="608" t="str">
         <x:f>IF(C5="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C5,FeatureTable[Feature ID],0)),"来源未匹配"))</x:f>
-        <x:v>来源未匹配</x:v>
+        <x:v>创建并查看客户档案</x:v>
       </x:c>
       <x:c r="G5" s="608" t="str">
         <x:f>IF(A5="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A5,"")),""))</x:f>
@@ -11336,11 +11368,11 @@
       </x:c>
       <x:c r="E6" s="608" t="str">
         <x:f>IF(C6="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C6,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</x:f>
-        <x:v>来源未匹配</x:v>
+        <x:v>平台边界</x:v>
       </x:c>
       <x:c r="F6" s="608" t="str">
         <x:f>IF(C6="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C6,FeatureTable[Feature ID],0)),"来源未匹配"))</x:f>
-        <x:v>来源未匹配</x:v>
+        <x:v>客户档案操作 API</x:v>
       </x:c>
       <x:c r="G6" s="608" t="str">
         <x:f>IF(A6="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A6,"")),""))</x:f>
@@ -11383,11 +11415,11 @@
       </x:c>
       <x:c r="E7" s="608" t="str">
         <x:f>IF(C7="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C7,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</x:f>
-        <x:v>来源未匹配</x:v>
+        <x:v>平台边界</x:v>
       </x:c>
       <x:c r="F7" s="608" t="str">
         <x:f>IF(C7="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C7,FeatureTable[Feature ID],0)),"来源未匹配"))</x:f>
-        <x:v>来源未匹配</x:v>
+        <x:v>客户档案操作 API</x:v>
       </x:c>
       <x:c r="G7" s="608" t="str">
         <x:f>IF(A7="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A7,"")),""))</x:f>
@@ -12688,7 +12720,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R528714014ea745c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dd8a18c0aaa46ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13403,7 +13435,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R921776aa153d4ba4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R364ccd1f1abc4a0a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22241,7 +22273,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93b75909c2ea44cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dfdfeeac3374651"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23936,7 +23968,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4b3d40832e844ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ac0997c71f84b81"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25226,7 +25258,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2ebe03e598e4da0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ea3d7cc8a5e4f5f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25597,7 +25629,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R449bd7dcba304f1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3f8a2d95b8c4b97"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
+++ b/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
@@ -6323,7 +6323,11 @@
       </c>
     </row>
     <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="618" t="inlineStr"/>
+      <c r="A44" s="618" t="inlineStr">
+        <is>
+          <t>Feature覆盖</t>
+        </is>
+      </c>
       <c r="B44" s="618" t="inlineStr">
         <is>
           <t>COVERAGE</t>
@@ -6358,7 +6362,11 @@
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="618" t="inlineStr"/>
+      <c r="A45" s="618" t="inlineStr">
+        <is>
+          <t>Feature覆盖</t>
+        </is>
+      </c>
       <c r="B45" s="618" t="inlineStr">
         <is>
           <t>COVERAGE</t>
@@ -6393,7 +6401,11 @@
       </c>
     </row>
     <row r="46" ht="45" customHeight="1">
-      <c r="A46" s="618" t="inlineStr"/>
+      <c r="A46" s="618" t="inlineStr">
+        <is>
+          <t>Feature覆盖</t>
+        </is>
+      </c>
       <c r="B46" s="618" t="inlineStr">
         <is>
           <t>COVERAGE</t>
@@ -6428,7 +6440,11 @@
       </c>
     </row>
     <row r="47" ht="45" customHeight="1">
-      <c r="A47" s="618" t="inlineStr"/>
+      <c r="A47" s="618" t="inlineStr">
+        <is>
+          <t>Feature覆盖</t>
+        </is>
+      </c>
       <c r="B47" s="618" t="inlineStr">
         <is>
           <t>COVERAGE</t>
@@ -6463,7 +6479,11 @@
       </c>
     </row>
     <row r="48" ht="45" customHeight="1">
-      <c r="A48" s="618" t="inlineStr"/>
+      <c r="A48" s="618" t="inlineStr">
+        <is>
+          <t>Feature覆盖</t>
+        </is>
+      </c>
       <c r="B48" s="618" t="inlineStr">
         <is>
           <t>COVERAGE</t>
@@ -6498,7 +6518,11 @@
       </c>
     </row>
     <row r="49" ht="60" customHeight="1">
-      <c r="A49" s="618" t="inlineStr"/>
+      <c r="A49" s="618" t="inlineStr">
+        <is>
+          <t>Feature覆盖</t>
+        </is>
+      </c>
       <c r="B49" s="618" t="inlineStr">
         <is>
           <t>COVERAGE</t>
@@ -6533,7 +6557,11 @@
       </c>
     </row>
     <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="618" t="inlineStr"/>
+      <c r="A50" s="618" t="inlineStr">
+        <is>
+          <t>Feature覆盖</t>
+        </is>
+      </c>
       <c r="B50" s="618" t="inlineStr">
         <is>
           <t>COVERAGE</t>
@@ -6568,7 +6596,11 @@
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
-      <c r="A51" s="618" t="inlineStr"/>
+      <c r="A51" s="618" t="inlineStr">
+        <is>
+          <t>Feature覆盖</t>
+        </is>
+      </c>
       <c r="B51" s="618" t="inlineStr">
         <is>
           <t>COVERAGE</t>
@@ -6603,7 +6635,11 @@
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="618" t="inlineStr"/>
+      <c r="A52" s="618" t="inlineStr">
+        <is>
+          <t>Feature覆盖</t>
+        </is>
+      </c>
       <c r="B52" s="618" t="inlineStr">
         <is>
           <t>COVERAGE</t>
@@ -6638,7 +6674,11 @@
       </c>
     </row>
     <row r="53" ht="45" customHeight="1">
-      <c r="A53" s="618" t="inlineStr"/>
+      <c r="A53" s="618" t="inlineStr">
+        <is>
+          <t>Feature覆盖</t>
+        </is>
+      </c>
       <c r="B53" s="618" t="inlineStr">
         <is>
           <t>COVERAGE</t>
@@ -6673,7 +6713,11 @@
       </c>
     </row>
     <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="618" t="inlineStr"/>
+      <c r="A54" s="618" t="inlineStr">
+        <is>
+          <t>Feature覆盖</t>
+        </is>
+      </c>
       <c r="B54" s="618" t="inlineStr">
         <is>
           <t>COVERAGE</t>
@@ -6708,7 +6752,11 @@
       </c>
     </row>
     <row r="55" ht="36" customHeight="1">
-      <c r="A55" s="618" t="inlineStr"/>
+      <c r="A55" s="618" t="inlineStr">
+        <is>
+          <t>Feature覆盖</t>
+        </is>
+      </c>
       <c r="B55" s="618" t="inlineStr">
         <is>
           <t>COVERAGE</t>

--- a/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
+++ b/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="54">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -320,8 +320,19 @@
       <color rgb="FF667680"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FF315F61"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <color rgb="FF334155"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="107">
+  <fills count="110">
     <fill>
       <patternFill/>
     </fill>
@@ -853,6 +864,21 @@
         <fgColor rgb="FFFFF5E3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26465F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F1F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="38">
     <border/>
@@ -1363,7 +1389,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="655">
+  <cellXfs count="669">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -3022,6 +3048,30 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="107" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="107" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="107" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="108" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="108" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="108" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="108" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="109" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="109" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="109" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3059,7 +3109,13 @@
     <xf numFmtId="164" fontId="47" fillId="103" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="104" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="44" fillId="108" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="109" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="109" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="50" fillId="97" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3119,7 +3175,7 @@
     <cellStyle name="40% - Accent6" xfId="47"/>
     <cellStyle name="60% - Accent6" xfId="48"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="37">
     <dxf>
       <font>
         <b val="1"/>
@@ -3396,6 +3452,106 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
@@ -3680,7 +3836,7 @@
     <tableColumn id="7" name="状态"/>
     <tableColumn id="8" name="处理方式"/>
     <tableColumn id="9" name="关联 Story 人天">
-      <calculatedColumnFormula>IF(OR(E5="",G5&lt;&gt;"待确认"),0,IFERROR(INDEX(SOWStoryTable[人天],MATCH(E5,SOWStoryTable[Story ID],0)),0))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(OR(E5="",G5&lt;&gt;"待确认"),0,SUMPRODUCT(SOWStoryTable[人天]*--ISNUMBER(SEARCH("、"&amp;SOWStoryTable[Story ID]&amp;"、","、"&amp;SUBSTITUTE(E5," ","")&amp;"、"))))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3934,13 +4090,13 @@
           <t>SOW估算与生成模板 v1.3</t>
         </is>
       </c>
-      <c r="B1" s="635" t="n"/>
-      <c r="C1" s="635" t="n"/>
-      <c r="D1" s="635" t="n"/>
-      <c r="E1" s="635" t="n"/>
-      <c r="F1" s="635" t="n"/>
-      <c r="G1" s="635" t="n"/>
-      <c r="H1" s="635" t="n"/>
+      <c r="B1" s="647" t="n"/>
+      <c r="C1" s="647" t="n"/>
+      <c r="D1" s="647" t="n"/>
+      <c r="E1" s="647" t="n"/>
+      <c r="F1" s="647" t="n"/>
+      <c r="G1" s="647" t="n"/>
+      <c r="H1" s="647" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="400" t="inlineStr">
@@ -3948,13 +4104,13 @@
           <t>稳定 JSON 是业务事实源；XLSX 是参数、公式、取整和最终人天的唯一计算权威；本文件为 fill-only 生产模板</t>
         </is>
       </c>
-      <c r="B2" s="636" t="n"/>
-      <c r="C2" s="636" t="n"/>
-      <c r="D2" s="636" t="n"/>
-      <c r="E2" s="636" t="n"/>
-      <c r="F2" s="636" t="n"/>
-      <c r="G2" s="636" t="n"/>
-      <c r="H2" s="636" t="n"/>
+      <c r="B2" s="648" t="n"/>
+      <c r="C2" s="648" t="n"/>
+      <c r="D2" s="648" t="n"/>
+      <c r="E2" s="648" t="n"/>
+      <c r="F2" s="648" t="n"/>
+      <c r="G2" s="648" t="n"/>
+      <c r="H2" s="648" t="n"/>
     </row>
     <row r="3" ht="9" customHeight="1">
       <c r="A3" s="404" t="n"/>
@@ -3972,13 +4128,13 @@
           <t>使用顺序</t>
         </is>
       </c>
-      <c r="B4" s="637" t="n"/>
-      <c r="C4" s="637" t="n"/>
-      <c r="D4" s="637" t="n"/>
-      <c r="E4" s="637" t="n"/>
-      <c r="F4" s="637" t="n"/>
-      <c r="G4" s="637" t="n"/>
-      <c r="H4" s="638" t="n"/>
+      <c r="B4" s="649" t="n"/>
+      <c r="C4" s="649" t="n"/>
+      <c r="D4" s="649" t="n"/>
+      <c r="E4" s="649" t="n"/>
+      <c r="F4" s="649" t="n"/>
+      <c r="G4" s="649" t="n"/>
+      <c r="H4" s="650" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="448" t="n">
@@ -3989,12 +4145,12 @@
           <t>确认需求与子需求，形成稳定 ID 和来源追溯。</t>
         </is>
       </c>
-      <c r="C5" s="639" t="n"/>
-      <c r="D5" s="639" t="n"/>
-      <c r="E5" s="639" t="n"/>
-      <c r="F5" s="639" t="n"/>
-      <c r="G5" s="639" t="n"/>
-      <c r="H5" s="640" t="n"/>
+      <c r="C5" s="651" t="n"/>
+      <c r="D5" s="651" t="n"/>
+      <c r="E5" s="651" t="n"/>
+      <c r="F5" s="651" t="n"/>
+      <c r="G5" s="651" t="n"/>
+      <c r="H5" s="652" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="448" t="n">
@@ -4005,12 +4161,12 @@
           <t>确认 As-Is、有效起点、目标设计与范围裁决。</t>
         </is>
       </c>
-      <c r="C6" s="639" t="n"/>
-      <c r="D6" s="639" t="n"/>
-      <c r="E6" s="639" t="n"/>
-      <c r="F6" s="639" t="n"/>
-      <c r="G6" s="639" t="n"/>
-      <c r="H6" s="640" t="n"/>
+      <c r="C6" s="651" t="n"/>
+      <c r="D6" s="651" t="n"/>
+      <c r="E6" s="651" t="n"/>
+      <c r="F6" s="651" t="n"/>
+      <c r="G6" s="651" t="n"/>
+      <c r="H6" s="652" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="448" t="n">
@@ -4021,12 +4177,12 @@
           <t>形成 Delivery Gap、无类型 Story、独立验收条件，并登记有证据支持的顶层 Integration。</t>
         </is>
       </c>
-      <c r="C7" s="639" t="n"/>
-      <c r="D7" s="639" t="n"/>
-      <c r="E7" s="639" t="n"/>
-      <c r="F7" s="639" t="n"/>
-      <c r="G7" s="639" t="n"/>
-      <c r="H7" s="640" t="n"/>
+      <c r="C7" s="651" t="n"/>
+      <c r="D7" s="651" t="n"/>
+      <c r="E7" s="651" t="n"/>
+      <c r="F7" s="651" t="n"/>
+      <c r="G7" s="651" t="n"/>
+      <c r="H7" s="652" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="448" t="n">
@@ -4037,12 +4193,12 @@
           <t>登记假设/风险；类型只分类，状态仅限已明确/待确认。</t>
         </is>
       </c>
-      <c r="C8" s="639" t="n"/>
-      <c r="D8" s="639" t="n"/>
-      <c r="E8" s="639" t="n"/>
-      <c r="F8" s="639" t="n"/>
-      <c r="G8" s="639" t="n"/>
-      <c r="H8" s="640" t="n"/>
+      <c r="C8" s="651" t="n"/>
+      <c r="D8" s="651" t="n"/>
+      <c r="E8" s="651" t="n"/>
+      <c r="F8" s="651" t="n"/>
+      <c r="G8" s="651" t="n"/>
+      <c r="H8" s="652" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="448" t="n">
@@ -4053,12 +4209,12 @@
           <t>按一个基础单元实例拆分一条 Task；选择基础单元、工作模式和复杂度，并填写相应理由。</t>
         </is>
       </c>
-      <c r="C9" s="639" t="n"/>
-      <c r="D9" s="639" t="n"/>
-      <c r="E9" s="639" t="n"/>
-      <c r="F9" s="639" t="n"/>
-      <c r="G9" s="639" t="n"/>
-      <c r="H9" s="640" t="n"/>
+      <c r="C9" s="651" t="n"/>
+      <c r="D9" s="651" t="n"/>
+      <c r="E9" s="651" t="n"/>
+      <c r="F9" s="651" t="n"/>
+      <c r="G9" s="651" t="n"/>
+      <c r="H9" s="652" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="448" t="n">
@@ -4069,12 +4225,12 @@
           <t>在 92-基础人天 的同一行选择基础单元，并按工作模式读取对应 M 档人天；S/L 必须说明偏离 M 的具体事实。</t>
         </is>
       </c>
-      <c r="C10" s="639" t="n"/>
-      <c r="D10" s="639" t="n"/>
-      <c r="E10" s="639" t="n"/>
-      <c r="F10" s="639" t="n"/>
-      <c r="G10" s="639" t="n"/>
-      <c r="H10" s="640" t="n"/>
+      <c r="C10" s="651" t="n"/>
+      <c r="D10" s="651" t="n"/>
+      <c r="E10" s="651" t="n"/>
+      <c r="F10" s="651" t="n"/>
+      <c r="G10" s="651" t="n"/>
+      <c r="H10" s="652" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="448" t="n">
@@ -4085,12 +4241,12 @@
           <t>generate-sow 只填充 Table、复制公式原型、对账并打包，不执行公式。</t>
         </is>
       </c>
-      <c r="C11" s="639" t="n"/>
-      <c r="D11" s="639" t="n"/>
-      <c r="E11" s="639" t="n"/>
-      <c r="F11" s="639" t="n"/>
-      <c r="G11" s="639" t="n"/>
-      <c r="H11" s="640" t="n"/>
+      <c r="C11" s="651" t="n"/>
+      <c r="D11" s="651" t="n"/>
+      <c r="E11" s="651" t="n"/>
+      <c r="F11" s="651" t="n"/>
+      <c r="G11" s="651" t="n"/>
+      <c r="H11" s="652" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="448" t="n">
@@ -4101,12 +4257,12 @@
           <t>在电子表格应用中打开工作簿，由模板计算并核对项目汇总。</t>
         </is>
       </c>
-      <c r="C12" s="639" t="n"/>
-      <c r="D12" s="639" t="n"/>
-      <c r="E12" s="639" t="n"/>
-      <c r="F12" s="639" t="n"/>
-      <c r="G12" s="639" t="n"/>
-      <c r="H12" s="640" t="n"/>
+      <c r="C12" s="651" t="n"/>
+      <c r="D12" s="651" t="n"/>
+      <c r="E12" s="651" t="n"/>
+      <c r="F12" s="651" t="n"/>
+      <c r="G12" s="651" t="n"/>
+      <c r="H12" s="652" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="404" t="n"/>
@@ -4124,13 +4280,13 @@
           <t>v1.3 计算合同</t>
         </is>
       </c>
-      <c r="B14" s="637" t="n"/>
-      <c r="C14" s="637" t="n"/>
-      <c r="D14" s="637" t="n"/>
-      <c r="E14" s="637" t="n"/>
-      <c r="F14" s="637" t="n"/>
-      <c r="G14" s="637" t="n"/>
-      <c r="H14" s="638" t="n"/>
+      <c r="B14" s="649" t="n"/>
+      <c r="C14" s="649" t="n"/>
+      <c r="D14" s="649" t="n"/>
+      <c r="E14" s="649" t="n"/>
+      <c r="F14" s="649" t="n"/>
+      <c r="G14" s="649" t="n"/>
+      <c r="H14" s="650" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="450" t="inlineStr">
@@ -4143,12 +4299,12 @@
           <t>基础单元：37 项；工作模式：新建/调整/接入复用；复杂度：S/M/L（X 只用于拆分或澄清）。</t>
         </is>
       </c>
-      <c r="C15" s="639" t="n"/>
-      <c r="D15" s="639" t="n"/>
-      <c r="E15" s="639" t="n"/>
-      <c r="F15" s="639" t="n"/>
-      <c r="G15" s="639" t="n"/>
-      <c r="H15" s="640" t="n"/>
+      <c r="C15" s="651" t="n"/>
+      <c r="D15" s="651" t="n"/>
+      <c r="E15" s="651" t="n"/>
+      <c r="F15" s="651" t="n"/>
+      <c r="G15" s="651" t="n"/>
+      <c r="H15" s="652" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="450" t="inlineStr">
@@ -4161,12 +4317,12 @@
           <t>基础单元目录直接提供新建/调整/接入复用三列 M 档人天；❌ 组合不得进入正式估算。</t>
         </is>
       </c>
-      <c r="C16" s="639" t="n"/>
-      <c r="D16" s="639" t="n"/>
-      <c r="E16" s="639" t="n"/>
-      <c r="F16" s="639" t="n"/>
-      <c r="G16" s="639" t="n"/>
-      <c r="H16" s="640" t="n"/>
+      <c r="C16" s="651" t="n"/>
+      <c r="D16" s="651" t="n"/>
+      <c r="E16" s="651" t="n"/>
+      <c r="F16" s="651" t="n"/>
+      <c r="G16" s="651" t="n"/>
+      <c r="H16" s="652" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="450" t="inlineStr">
@@ -4179,12 +4335,12 @@
           <t>同 Story 的 Task 小计求和后，向上取整至 ROUND_STORY。</t>
         </is>
       </c>
-      <c r="C17" s="639" t="n"/>
-      <c r="D17" s="639" t="n"/>
-      <c r="E17" s="639" t="n"/>
-      <c r="F17" s="639" t="n"/>
-      <c r="G17" s="639" t="n"/>
-      <c r="H17" s="640" t="n"/>
+      <c r="C17" s="651" t="n"/>
+      <c r="D17" s="651" t="n"/>
+      <c r="E17" s="651" t="n"/>
+      <c r="F17" s="651" t="n"/>
+      <c r="G17" s="651" t="n"/>
+      <c r="H17" s="652" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="450" t="inlineStr">
@@ -4197,12 +4353,12 @@
           <t>内部/外部系统对接 Task 触发 SIT；UAT 仅汇总显式标记为适用的 Story。</t>
         </is>
       </c>
-      <c r="C18" s="639" t="n"/>
-      <c r="D18" s="639" t="n"/>
-      <c r="E18" s="639" t="n"/>
-      <c r="F18" s="639" t="n"/>
-      <c r="G18" s="639" t="n"/>
-      <c r="H18" s="640" t="n"/>
+      <c r="C18" s="651" t="n"/>
+      <c r="D18" s="651" t="n"/>
+      <c r="E18" s="651" t="n"/>
+      <c r="F18" s="651" t="n"/>
+      <c r="G18" s="651" t="n"/>
+      <c r="H18" s="652" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="450" t="inlineStr">
@@ -4215,12 +4371,12 @@
           <t>状态为待确认的关联 Story 按 Story 去重；同一 Story 多条待确认项只计一次。</t>
         </is>
       </c>
-      <c r="C19" s="639" t="n"/>
-      <c r="D19" s="639" t="n"/>
-      <c r="E19" s="639" t="n"/>
-      <c r="F19" s="639" t="n"/>
-      <c r="G19" s="639" t="n"/>
-      <c r="H19" s="640" t="n"/>
+      <c r="C19" s="651" t="n"/>
+      <c r="D19" s="651" t="n"/>
+      <c r="E19" s="651" t="n"/>
+      <c r="F19" s="651" t="n"/>
+      <c r="G19" s="651" t="n"/>
+      <c r="H19" s="652" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="450" t="inlineStr">
@@ -4233,12 +4389,12 @@
           <t>直接开发 + SIT + UAT + 待确认风险人天；所有计算结果只存在于 XLSX。</t>
         </is>
       </c>
-      <c r="C20" s="639" t="n"/>
-      <c r="D20" s="639" t="n"/>
-      <c r="E20" s="639" t="n"/>
-      <c r="F20" s="639" t="n"/>
-      <c r="G20" s="639" t="n"/>
-      <c r="H20" s="640" t="n"/>
+      <c r="C20" s="651" t="n"/>
+      <c r="D20" s="651" t="n"/>
+      <c r="E20" s="651" t="n"/>
+      <c r="F20" s="651" t="n"/>
+      <c r="G20" s="651" t="n"/>
+      <c r="H20" s="652" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="404" t="n"/>
@@ -4256,13 +4412,13 @@
           <t>工作表职责</t>
         </is>
       </c>
-      <c r="B22" s="637" t="n"/>
-      <c r="C22" s="637" t="n"/>
-      <c r="D22" s="637" t="n"/>
-      <c r="E22" s="637" t="n"/>
-      <c r="F22" s="637" t="n"/>
-      <c r="G22" s="637" t="n"/>
-      <c r="H22" s="638" t="n"/>
+      <c r="B22" s="649" t="n"/>
+      <c r="C22" s="649" t="n"/>
+      <c r="D22" s="649" t="n"/>
+      <c r="E22" s="649" t="n"/>
+      <c r="F22" s="649" t="n"/>
+      <c r="G22" s="649" t="n"/>
+      <c r="H22" s="650" t="n"/>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="453" t="inlineStr">
@@ -4732,13 +4888,85 @@
     <row r="40" ht="68" customHeight="1"/>
     <row r="41" ht="68" customHeight="1"/>
     <row r="42" ht="68" customHeight="1"/>
-    <row r="43"/>
-    <row r="44" ht="42" customHeight="1"/>
-    <row r="45" ht="42" customHeight="1"/>
-    <row r="46" ht="42" customHeight="1"/>
-    <row r="47" ht="42" customHeight="1"/>
-    <row r="48" ht="42" customHeight="1"/>
-    <row r="49" ht="42" customHeight="1"/>
+    <row r="43">
+      <c r="A43" s="638" t="inlineStr">
+        <is>
+          <t>稳定输入 SHA-256</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="642" t="inlineStr">
+        <is>
+          <t>sourceRequirements</t>
+        </is>
+      </c>
+      <c r="B44" s="646" t="inlineStr">
+        <is>
+          <t>702d8cfc3a0d1bba8c3766b3018bea9a3c2597c7d80155b2714e0e837d157c63</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="642" t="inlineStr">
+        <is>
+          <t>asis</t>
+        </is>
+      </c>
+      <c r="B45" s="646" t="inlineStr">
+        <is>
+          <t>179cb9c44d398f2b6741d655c7698e675ac2e722e1849ae5c87b3bdad3261d55</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="642" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="B46" s="646" t="inlineStr">
+        <is>
+          <t>b98ffa53f534f1584040707fc60bf646e39dc8a77972a9935b8f8d7d1458eefb</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="642" t="inlineStr">
+        <is>
+          <t>derivedRequirements</t>
+        </is>
+      </c>
+      <c r="B47" s="646" t="inlineStr">
+        <is>
+          <t>16d678a745213634f4b9e0b027e9b271233f60af4c91e27b25dd1b14cae002a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="642" t="inlineStr">
+        <is>
+          <t>delivery</t>
+        </is>
+      </c>
+      <c r="B48" s="646" t="inlineStr">
+        <is>
+          <t>913f98721c96db021fb423460db0dd04e2c2e86de0d7560dbeccec4ea6bc240c</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="642" t="inlineStr">
+        <is>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="B49" s="646" t="inlineStr">
+        <is>
+          <t>3f494630e386223f0d085c8b60307508d8fec3034a4a44b4212774c23baf7d9a</t>
+        </is>
+      </c>
+    </row>
     <row r="50" ht="42" customHeight="1"/>
     <row r="51" ht="42" customHeight="1"/>
   </sheetData>
@@ -4803,14 +5031,14 @@
           <t>系统现状 / As-Is</t>
         </is>
       </c>
-      <c r="B1" s="635" t="n"/>
-      <c r="C1" s="635" t="n"/>
-      <c r="D1" s="635" t="n"/>
-      <c r="E1" s="635" t="n"/>
-      <c r="F1" s="635" t="n"/>
-      <c r="G1" s="635" t="n"/>
-      <c r="H1" s="635" t="n"/>
-      <c r="I1" s="635" t="n"/>
+      <c r="B1" s="647" t="n"/>
+      <c r="C1" s="647" t="n"/>
+      <c r="D1" s="647" t="n"/>
+      <c r="E1" s="647" t="n"/>
+      <c r="F1" s="647" t="n"/>
+      <c r="G1" s="647" t="n"/>
+      <c r="H1" s="647" t="n"/>
+      <c r="I1" s="647" t="n"/>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="400" t="inlineStr">
@@ -4818,14 +5046,14 @@
           <t>模式：BROWNFIELD | As-of：2026-08-19 | Repo：customer-portal@0123456789ab | 排除范围：上线后驻场支持、旧系统退役、ERP 库存核算改造、总账系统改造</t>
         </is>
       </c>
-      <c r="B2" s="636" t="n"/>
-      <c r="C2" s="636" t="n"/>
-      <c r="D2" s="636" t="n"/>
-      <c r="E2" s="636" t="n"/>
-      <c r="F2" s="636" t="n"/>
-      <c r="G2" s="636" t="n"/>
-      <c r="H2" s="636" t="n"/>
-      <c r="I2" s="636" t="n"/>
+      <c r="B2" s="648" t="n"/>
+      <c r="C2" s="648" t="n"/>
+      <c r="D2" s="648" t="n"/>
+      <c r="E2" s="648" t="n"/>
+      <c r="F2" s="648" t="n"/>
+      <c r="G2" s="648" t="n"/>
+      <c r="H2" s="648" t="n"/>
+      <c r="I2" s="648" t="n"/>
     </row>
     <row r="3" ht="9" customHeight="1"/>
     <row r="4" ht="38" customHeight="1">
@@ -4866,263 +5094,263 @@
       </c>
     </row>
     <row r="5" ht="75" customHeight="1">
-      <c r="A5" s="620" t="inlineStr">
+      <c r="A5" s="663" t="inlineStr">
         <is>
           <t>系统边界与参与方</t>
         </is>
       </c>
-      <c r="B5" s="620" t="inlineStr">
+      <c r="B5" s="663" t="inlineStr">
         <is>
           <t>ASSESSED</t>
         </is>
       </c>
-      <c r="C5" s="619" t="inlineStr">
+      <c r="C5" s="664" t="inlineStr">
         <is>
           <t>会员门户、门店工作台和订单服务承载渠道交易，ERP、支付与发票平台保持系统责任边界。</t>
         </is>
       </c>
-      <c r="D5" s="651" t="n">
+      <c r="D5" s="665" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="651" t="n">
+      <c r="E5" s="665" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="651" t="n">
+      <c r="F5" s="665" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="651" t="n">
+      <c r="G5" s="665" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="75" customHeight="1">
-      <c r="A6" s="620" t="inlineStr">
+      <c r="A6" s="663" t="inlineStr">
         <is>
           <t>能力与流程</t>
         </is>
       </c>
-      <c r="B6" s="620" t="inlineStr">
+      <c r="B6" s="663" t="inlineStr">
         <is>
           <t>ASSESSED</t>
         </is>
       </c>
-      <c r="C6" s="619" t="inlineStr">
+      <c r="C6" s="664" t="inlineStr">
         <is>
           <t>客户档案、订单服务和通知具备基础能力，会员等级、退货退款、对账与开票需要补齐。</t>
         </is>
       </c>
-      <c r="D6" s="651" t="n">
+      <c r="D6" s="665" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="651" t="n">
+      <c r="E6" s="665" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="651" t="n">
+      <c r="F6" s="665" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="651" t="n">
+      <c r="G6" s="665" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="620" t="inlineStr">
+      <c r="A7" s="663" t="inlineStr">
         <is>
           <t>应用与组件</t>
         </is>
       </c>
-      <c r="B7" s="620" t="inlineStr">
+      <c r="B7" s="663" t="inlineStr">
         <is>
           <t>ASSESSED</t>
         </is>
       </c>
-      <c r="C7" s="619" t="inlineStr">
+      <c r="C7" s="664" t="inlineStr">
         <is>
           <t>现有客户档案组件、订单服务和门店菜单入口可作为调整与续建起点。</t>
         </is>
       </c>
-      <c r="D7" s="651" t="n">
+      <c r="D7" s="665" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="651" t="n">
+      <c r="E7" s="665" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="651" t="n">
+      <c r="F7" s="665" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="651" t="n">
+      <c r="G7" s="665" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="75" customHeight="1">
-      <c r="A8" s="620" t="inlineStr">
+      <c r="A8" s="663" t="inlineStr">
         <is>
           <t>集成与外部依赖</t>
         </is>
       </c>
-      <c r="B8" s="620" t="inlineStr">
+      <c r="B8" s="663" t="inlineStr">
         <is>
           <t>ASSESSED</t>
         </is>
       </c>
-      <c r="C8" s="619" t="inlineStr">
+      <c r="C8" s="664" t="inlineStr">
         <is>
           <t>ERP、支付网关和电子发票通道均已企业级接入，本项目承担租户内映射、适配和专项验证。</t>
         </is>
       </c>
-      <c r="D8" s="651" t="n">
+      <c r="D8" s="665" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="651" t="n">
+      <c r="E8" s="665" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="651" t="n">
+      <c r="F8" s="665" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="651" t="n">
+      <c r="G8" s="665" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="620" t="inlineStr">
+      <c r="A9" s="663" t="inlineStr">
         <is>
           <t>数据与存储</t>
         </is>
       </c>
-      <c r="B9" s="620" t="inlineStr">
+      <c r="B9" s="663" t="inlineStr">
         <is>
           <t>ASSESSED</t>
         </is>
       </c>
-      <c r="C9" s="619" t="inlineStr">
+      <c r="C9" s="664" t="inlineStr">
         <is>
           <t>会员主数据和订单库已有稳定结构，历史订单映射与对账指标需要新增。</t>
         </is>
       </c>
-      <c r="D9" s="651" t="n">
+      <c r="D9" s="665" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="651" t="n">
+      <c r="E9" s="665" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="651" t="n">
+      <c r="F9" s="665" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="651" t="n">
+      <c r="G9" s="665" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="620" t="inlineStr">
+      <c r="A10" s="663" t="inlineStr">
         <is>
           <t>平台、环境与部署</t>
         </is>
       </c>
-      <c r="B10" s="620" t="inlineStr">
+      <c r="B10" s="663" t="inlineStr">
         <is>
           <t>ASSESSED</t>
         </is>
       </c>
-      <c r="C10" s="619" t="inlineStr">
+      <c r="C10" s="664" t="inlineStr">
         <is>
           <t>保留 Kubernetes 生产环境与 CI/CD 流水线，新增应用配置和切换清单。</t>
         </is>
       </c>
-      <c r="D10" s="651" t="n">
+      <c r="D10" s="665" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="651" t="n">
+      <c r="E10" s="665" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="651" t="n">
+      <c r="F10" s="665" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="651" t="n">
+      <c r="G10" s="665" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="620" t="inlineStr">
+      <c r="A11" s="663" t="inlineStr">
         <is>
           <t>安全与合规</t>
         </is>
       </c>
-      <c r="B11" s="620" t="inlineStr">
+      <c r="B11" s="663" t="inlineStr">
         <is>
           <t>ASSESSED</t>
         </is>
       </c>
-      <c r="C11" s="619" t="inlineStr">
+      <c r="C11" s="664" t="inlineStr">
         <is>
           <t>统一身份控制与授权中心可复用，新增功能遵循最小权限和审计留痕要求。</t>
         </is>
       </c>
-      <c r="D11" s="651" t="n">
+      <c r="D11" s="665" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="651" t="n">
+      <c r="E11" s="665" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="651" t="n">
+      <c r="F11" s="665" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="651" t="n">
+      <c r="G11" s="665" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="620" t="inlineStr">
+      <c r="A12" s="663" t="inlineStr">
         <is>
           <t>运维与质量</t>
         </is>
       </c>
-      <c r="B12" s="620" t="inlineStr">
+      <c r="B12" s="663" t="inlineStr">
         <is>
           <t>INSUFFICIENT_EVIDENCE</t>
         </is>
       </c>
-      <c r="C12" s="619" t="inlineStr">
+      <c r="C12" s="664" t="inlineStr">
         <is>
           <t>统一监控和回归资产可复用，但生产告警最终通知渠道尚待上线前确认。</t>
         </is>
       </c>
-      <c r="D12" s="651" t="n">
+      <c r="D12" s="665" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="651" t="n">
+      <c r="E12" s="665" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="651" t="n">
+      <c r="F12" s="665" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="651" t="n">
+      <c r="G12" s="665" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="620" t="inlineStr">
+      <c r="A13" s="663" t="inlineStr">
         <is>
           <t>交付与约束</t>
         </is>
       </c>
-      <c r="B13" s="620" t="inlineStr">
+      <c r="B13" s="663" t="inlineStr">
         <is>
           <t>ASSESSED</t>
         </is>
       </c>
-      <c r="C13" s="619" t="inlineStr">
+      <c r="C13" s="664" t="inlineStr">
         <is>
           <t>数据迁移、生产切换、验证、交接和培训纳入本期；驻场支持与旧系统退役明确排除。</t>
         </is>
       </c>
-      <c r="D13" s="651" t="n">
+      <c r="D13" s="665" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="651" t="n">
+      <c r="E13" s="665" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="651" t="n">
+      <c r="F13" s="665" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="651" t="n">
+      <c r="G13" s="665" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5215,7 +5443,7 @@
       </c>
       <c r="I18" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/profile.ts#L12</t>
+          <t>customer-portal:src/profile.ts#L12</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5486,7 @@
       </c>
       <c r="I19" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/profile.ts#L12</t>
+          <t>customer-portal:src/profile.ts#L12</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5529,7 @@
       </c>
       <c r="I20" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/order/state-machine.ts#L20</t>
+          <t>customer-portal:src/order/state-machine.ts#L20</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5576,7 @@
       </c>
       <c r="I21" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/erp-inventory-v2.yaml#reserve</t>
+          <t>customer-portal:contracts/erp-inventory-v2.yaml#reserve</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5623,7 @@
       </c>
       <c r="I22" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/payment-refund-v1.yaml#refund</t>
+          <t>customer-portal:contracts/payment-refund-v1.yaml#refund</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5670,7 @@
       </c>
       <c r="I23" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/einvoice-v1.yaml#issue</t>
+          <t>customer-portal:contracts/einvoice-v1.yaml#issue</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5713,7 @@
       </c>
       <c r="I24" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/deploy/production/values.yaml#application</t>
+          <t>customer-portal:deploy/production/values.yaml#application</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5756,7 @@
       </c>
       <c r="I25" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/deploy/production/values.yaml#application</t>
+          <t>customer-portal:deploy/production/values.yaml#application</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5799,7 @@
       </c>
       <c r="I26" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/deploy/production/values.yaml#application</t>
+          <t>customer-portal:deploy/production/values.yaml#application</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5842,7 @@
       </c>
       <c r="I27" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/docs/operations-and-test-assets.md#baseline</t>
+          <t>repositories/customer-portal/docs/operations-and-test-assets.md#baseline</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5885,7 @@
       </c>
       <c r="I28" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/docs/operations-and-test-assets.md#baseline</t>
+          <t>repositories/customer-portal/docs/operations-and-test-assets.md#baseline</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5932,7 @@
       </c>
       <c r="I29" s="618" t="inlineStr">
         <is>
-          <t>sow-phase-one#Profile!A12、customer-portal/src/profile.ts#L12</t>
+          <t>sow-phase-one#Profile!A12、customer-portal:src/profile.ts#L12</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5979,7 @@
       </c>
       <c r="I30" s="618" t="inlineStr">
         <is>
-          <t>sow-phase-one#StoreOrder!B9、customer-portal/src/order/state-machine.ts#L20</t>
+          <t>sow-phase-one#StoreOrder!B9、customer-portal:src/order/state-machine.ts#L20</t>
         </is>
       </c>
     </row>
@@ -5798,7 +6026,7 @@
       </c>
       <c r="I31" s="618" t="inlineStr">
         <is>
-          <t>sow-phase-one#Profile!A18、customer-portal/deploy/production/values.yaml#application</t>
+          <t>sow-phase-one#Profile!A18、customer-portal:deploy/production/values.yaml#application</t>
         </is>
       </c>
     </row>
@@ -5845,7 +6073,7 @@
       </c>
       <c r="I32" s="618" t="inlineStr">
         <is>
-          <t>sow-phase-one#Delivery-baseline、customer-portal/src/order/state-machine.ts#L20</t>
+          <t>sow-phase-one#Delivery-baseline、customer-portal:src/order/state-machine.ts#L20</t>
         </is>
       </c>
     </row>
@@ -5888,7 +6116,7 @@
       </c>
       <c r="I33" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/profile.ts#L12</t>
+          <t>customer-portal:src/profile.ts#L12</t>
         </is>
       </c>
     </row>
@@ -5931,7 +6159,7 @@
       </c>
       <c r="I34" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/profile.ts#L12</t>
+          <t>customer-portal:src/profile.ts#L12</t>
         </is>
       </c>
     </row>
@@ -5974,7 +6202,7 @@
       </c>
       <c r="I35" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/order/state-machine.ts#L20</t>
+          <t>customer-portal:src/order/state-machine.ts#L20</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6245,7 @@
       </c>
       <c r="I36" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/erp-inventory-v2.yaml#reserve</t>
+          <t>customer-portal:contracts/erp-inventory-v2.yaml#reserve</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6288,7 @@
       </c>
       <c r="I37" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/payment-refund-v1.yaml#refund</t>
+          <t>customer-portal:contracts/payment-refund-v1.yaml#refund</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6331,7 @@
       </c>
       <c r="I38" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/einvoice-v1.yaml#issue</t>
+          <t>customer-portal:contracts/einvoice-v1.yaml#issue</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6374,7 @@
       </c>
       <c r="I39" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/deploy/production/values.yaml#application</t>
+          <t>customer-portal:deploy/production/values.yaml#application</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6417,7 @@
       </c>
       <c r="I40" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/deploy/production/values.yaml#application</t>
+          <t>customer-portal:deploy/production/values.yaml#application</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6460,7 @@
       </c>
       <c r="I41" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/deploy/production/values.yaml#application</t>
+          <t>customer-portal:deploy/production/values.yaml#application</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6503,7 @@
       </c>
       <c r="I42" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/docs/operations-and-test-assets.md#baseline</t>
+          <t>repositories/customer-portal/docs/operations-and-test-assets.md#baseline</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6546,7 @@
       </c>
       <c r="I43" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/docs/operations-and-test-assets.md#baseline</t>
+          <t>repositories/customer-portal/docs/operations-and-test-assets.md#baseline</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6585,7 @@
       </c>
       <c r="I44" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/profile.ts#L12</t>
+          <t>customer-portal:src/profile.ts#L12</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6624,7 @@
       </c>
       <c r="I45" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/profile.ts#L12</t>
+          <t>customer-portal:src/profile.ts#L12</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6663,7 @@
       </c>
       <c r="I46" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/deploy/production/values.yaml#application</t>
+          <t>customer-portal:deploy/production/values.yaml#application</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6702,7 @@
       </c>
       <c r="I47" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/order/state-machine.ts#L20</t>
+          <t>customer-portal:src/order/state-machine.ts#L20</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6741,7 @@
       </c>
       <c r="I48" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/erp-inventory-v2.yaml#reserve</t>
+          <t>customer-portal:contracts/erp-inventory-v2.yaml#reserve</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6780,7 @@
       </c>
       <c r="I49" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/payment-refund-v1.yaml#refund</t>
+          <t>customer-portal:contracts/payment-refund-v1.yaml#refund</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6819,7 @@
       </c>
       <c r="I50" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/order/state-machine.ts#L20</t>
+          <t>customer-portal:src/order/state-machine.ts#L20</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6858,7 @@
       </c>
       <c r="I51" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/order/state-machine.ts#L20</t>
+          <t>customer-portal:src/order/state-machine.ts#L20</t>
         </is>
       </c>
     </row>
@@ -6669,7 +6897,7 @@
       </c>
       <c r="I52" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/deploy/production/values.yaml#application</t>
+          <t>customer-portal:deploy/production/values.yaml#application</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6936,7 @@
       </c>
       <c r="I53" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/payment-refund-v1.yaml#refund</t>
+          <t>customer-portal:contracts/payment-refund-v1.yaml#refund</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6975,7 @@
       </c>
       <c r="I54" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/einvoice-v1.yaml#issue</t>
+          <t>customer-portal:contracts/einvoice-v1.yaml#issue</t>
         </is>
       </c>
     </row>
@@ -6786,7 +7014,7 @@
       </c>
       <c r="I55" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/order/state-machine.ts#L20</t>
+          <t>customer-portal:src/order/state-machine.ts#L20</t>
         </is>
       </c>
     </row>
@@ -6833,7 +7061,7 @@
       </c>
       <c r="I56" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/docs/operations-and-test-assets.md#baseline</t>
+          <t>repositories/customer-portal/docs/operations-and-test-assets.md#baseline</t>
         </is>
       </c>
     </row>
@@ -6880,7 +7108,7 @@
       </c>
       <c r="I57" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/erp-inventory-v2.yaml#reserve</t>
+          <t>customer-portal:contracts/erp-inventory-v2.yaml#reserve</t>
         </is>
       </c>
     </row>
@@ -6927,7 +7155,7 @@
       </c>
       <c r="I58" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/payment-refund-v1.yaml#refund</t>
+          <t>customer-portal:contracts/payment-refund-v1.yaml#refund</t>
         </is>
       </c>
     </row>
@@ -6974,7 +7202,7 @@
       </c>
       <c r="I59" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/einvoice-v1.yaml#issue</t>
+          <t>customer-portal:contracts/einvoice-v1.yaml#issue</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7229,7 @@
       </c>
       <c r="E60" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/profile.ts#L12</t>
+          <t>customer-portal:src/profile.ts#L12</t>
         </is>
       </c>
       <c r="F60" s="618" t="inlineStr">
@@ -7017,7 +7245,7 @@
       </c>
       <c r="I60" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/profile.ts#L12</t>
+          <t>customer-portal:src/profile.ts#L12</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7272,7 @@
       </c>
       <c r="E61" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/order/state-machine.ts#L20</t>
+          <t>customer-portal:src/order/state-machine.ts#L20</t>
         </is>
       </c>
       <c r="F61" s="618" t="inlineStr">
@@ -7060,7 +7288,7 @@
       </c>
       <c r="I61" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/src/order/state-machine.ts#L20</t>
+          <t>customer-portal:src/order/state-machine.ts#L20</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7315,7 @@
       </c>
       <c r="E62" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/erp-inventory-v2.yaml#reserve</t>
+          <t>customer-portal:contracts/erp-inventory-v2.yaml#reserve</t>
         </is>
       </c>
       <c r="F62" s="618" t="inlineStr">
@@ -7103,7 +7331,7 @@
       </c>
       <c r="I62" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/erp-inventory-v2.yaml#reserve</t>
+          <t>customer-portal:contracts/erp-inventory-v2.yaml#reserve</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7358,7 @@
       </c>
       <c r="E63" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/payment-refund-v1.yaml#refund</t>
+          <t>customer-portal:contracts/payment-refund-v1.yaml#refund</t>
         </is>
       </c>
       <c r="F63" s="618" t="inlineStr">
@@ -7146,7 +7374,7 @@
       </c>
       <c r="I63" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/payment-refund-v1.yaml#refund</t>
+          <t>customer-portal:contracts/payment-refund-v1.yaml#refund</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7401,7 @@
       </c>
       <c r="E64" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/einvoice-v1.yaml#issue</t>
+          <t>customer-portal:contracts/einvoice-v1.yaml#issue</t>
         </is>
       </c>
       <c r="F64" s="618" t="inlineStr">
@@ -7189,7 +7417,7 @@
       </c>
       <c r="I64" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/contracts/einvoice-v1.yaml#issue</t>
+          <t>customer-portal:contracts/einvoice-v1.yaml#issue</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7444,7 @@
       </c>
       <c r="E65" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/deploy/production/values.yaml#application</t>
+          <t>customer-portal:deploy/production/values.yaml#application</t>
         </is>
       </c>
       <c r="F65" s="618" t="inlineStr">
@@ -7232,7 +7460,7 @@
       </c>
       <c r="I65" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/deploy/production/values.yaml#application</t>
+          <t>customer-portal:deploy/production/values.yaml#application</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7487,7 @@
       </c>
       <c r="E66" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/docs/operations-and-test-assets.md#baseline</t>
+          <t>repositories/customer-portal/docs/operations-and-test-assets.md#baseline</t>
         </is>
       </c>
       <c r="F66" s="618" t="inlineStr">
@@ -7275,7 +7503,7 @@
       </c>
       <c r="I66" s="618" t="inlineStr">
         <is>
-          <t>customer-portal/docs/operations-and-test-assets.md#baseline</t>
+          <t>repositories/customer-portal/docs/operations-and-test-assets.md#baseline</t>
         </is>
       </c>
     </row>
@@ -7315,11 +7543,11 @@
           <t>项目参数</t>
         </is>
       </c>
-      <c r="B1" s="635" t="n"/>
-      <c r="C1" s="635" t="n"/>
-      <c r="D1" s="635" t="n"/>
-      <c r="E1" s="635" t="n"/>
-      <c r="F1" s="635" t="n"/>
+      <c r="B1" s="647" t="n"/>
+      <c r="C1" s="647" t="n"/>
+      <c r="D1" s="647" t="n"/>
+      <c r="E1" s="647" t="n"/>
+      <c r="F1" s="647" t="n"/>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="400" t="inlineStr">
@@ -7327,11 +7555,11 @@
           <t>全部项目级公式引用本表；包含 Task 复杂度系数、UAT/SIT 支持参数和取整规则，不包含敏捷或非 Dev 角色人天。</t>
         </is>
       </c>
-      <c r="B2" s="636" t="n"/>
-      <c r="C2" s="636" t="n"/>
-      <c r="D2" s="636" t="n"/>
-      <c r="E2" s="636" t="n"/>
-      <c r="F2" s="636" t="n"/>
+      <c r="B2" s="648" t="n"/>
+      <c r="C2" s="648" t="n"/>
+      <c r="D2" s="648" t="n"/>
+      <c r="E2" s="648" t="n"/>
+      <c r="F2" s="648" t="n"/>
     </row>
     <row r="3" ht="9" customHeight="1"/>
     <row r="4" ht="38" customHeight="1">
@@ -7377,7 +7605,7 @@
           <t>S档复杂度系数</t>
         </is>
       </c>
-      <c r="C5" s="652" t="n">
+      <c r="C5" s="666" t="n">
         <v>0.6</v>
       </c>
       <c r="D5" s="598" t="inlineStr">
@@ -7407,7 +7635,7 @@
           <t>M档复杂度系数</t>
         </is>
       </c>
-      <c r="C6" s="652" t="n">
+      <c r="C6" s="666" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="598" t="inlineStr">
@@ -7437,7 +7665,7 @@
           <t>L档复杂度系数</t>
         </is>
       </c>
-      <c r="C7" s="652" t="n">
+      <c r="C7" s="666" t="n">
         <v>1.5</v>
       </c>
       <c r="D7" s="598" t="inlineStr">
@@ -7467,7 +7695,7 @@
           <t>UAT支持系数</t>
         </is>
       </c>
-      <c r="C8" s="652" t="n">
+      <c r="C8" s="666" t="n">
         <v>0.05</v>
       </c>
       <c r="D8" s="598" t="inlineStr">
@@ -7497,7 +7725,7 @@
           <t>内部集成点SIT支持</t>
         </is>
       </c>
-      <c r="C9" s="652" t="n">
+      <c r="C9" s="666" t="n">
         <v>0.5</v>
       </c>
       <c r="D9" s="598" t="inlineStr">
@@ -7527,7 +7755,7 @@
           <t>外部集成点SIT支持</t>
         </is>
       </c>
-      <c r="C10" s="652" t="n">
+      <c r="C10" s="666" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="598" t="inlineStr">
@@ -7557,7 +7785,7 @@
           <t>Story取整粒度</t>
         </is>
       </c>
-      <c r="C11" s="652" t="n">
+      <c r="C11" s="666" t="n">
         <v>0.5</v>
       </c>
       <c r="D11" s="598" t="inlineStr">
@@ -7587,7 +7815,7 @@
           <t>项目级取整粒度</t>
         </is>
       </c>
-      <c r="C12" s="652" t="n">
+      <c r="C12" s="666" t="n">
         <v>0.5</v>
       </c>
       <c r="D12" s="598" t="inlineStr">
@@ -7657,19 +7885,19 @@
           <t>基础单元与估算标准</t>
         </is>
       </c>
-      <c r="B1" s="635" t="n"/>
-      <c r="C1" s="635" t="n"/>
-      <c r="D1" s="635" t="n"/>
-      <c r="E1" s="635" t="n"/>
-      <c r="F1" s="635" t="n"/>
-      <c r="G1" s="635" t="n"/>
-      <c r="H1" s="635" t="n"/>
-      <c r="I1" s="635" t="n"/>
-      <c r="J1" s="635" t="n"/>
-      <c r="K1" s="635" t="n"/>
-      <c r="L1" s="635" t="n"/>
-      <c r="M1" s="635" t="n"/>
-      <c r="N1" s="635" t="n"/>
+      <c r="B1" s="647" t="n"/>
+      <c r="C1" s="647" t="n"/>
+      <c r="D1" s="647" t="n"/>
+      <c r="E1" s="647" t="n"/>
+      <c r="F1" s="647" t="n"/>
+      <c r="G1" s="647" t="n"/>
+      <c r="H1" s="647" t="n"/>
+      <c r="I1" s="647" t="n"/>
+      <c r="J1" s="647" t="n"/>
+      <c r="K1" s="647" t="n"/>
+      <c r="L1" s="647" t="n"/>
+      <c r="M1" s="647" t="n"/>
+      <c r="N1" s="647" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="400" t="inlineStr">
@@ -7677,19 +7905,19 @@
           <t>一行一个基础单元；新建、调整、接入复用三列直接给出 M 档基础人天；❌ 表示该组合不适用。S/M/L/X 标准用于判断和拆分，不另设重复配置表。</t>
         </is>
       </c>
-      <c r="B2" s="636" t="n"/>
-      <c r="C2" s="636" t="n"/>
-      <c r="D2" s="636" t="n"/>
-      <c r="E2" s="636" t="n"/>
-      <c r="F2" s="636" t="n"/>
-      <c r="G2" s="636" t="n"/>
-      <c r="H2" s="636" t="n"/>
-      <c r="I2" s="636" t="n"/>
-      <c r="J2" s="636" t="n"/>
-      <c r="K2" s="636" t="n"/>
-      <c r="L2" s="636" t="n"/>
-      <c r="M2" s="636" t="n"/>
-      <c r="N2" s="636" t="n"/>
+      <c r="B2" s="648" t="n"/>
+      <c r="C2" s="648" t="n"/>
+      <c r="D2" s="648" t="n"/>
+      <c r="E2" s="648" t="n"/>
+      <c r="F2" s="648" t="n"/>
+      <c r="G2" s="648" t="n"/>
+      <c r="H2" s="648" t="n"/>
+      <c r="I2" s="648" t="n"/>
+      <c r="J2" s="648" t="n"/>
+      <c r="K2" s="648" t="n"/>
+      <c r="L2" s="648" t="n"/>
+      <c r="M2" s="648" t="n"/>
+      <c r="N2" s="648" t="n"/>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="570" t="inlineStr">
@@ -7697,31 +7925,31 @@
           <t>分类与标识</t>
         </is>
       </c>
-      <c r="B3" s="653" t="n"/>
-      <c r="C3" s="653" t="n"/>
-      <c r="D3" s="654" t="n"/>
+      <c r="B3" s="667" t="n"/>
+      <c r="C3" s="667" t="n"/>
+      <c r="D3" s="668" t="n"/>
       <c r="E3" s="573" t="inlineStr">
         <is>
           <t>计数与工作边界</t>
         </is>
       </c>
-      <c r="F3" s="653" t="n"/>
-      <c r="G3" s="654" t="n"/>
+      <c r="F3" s="667" t="n"/>
+      <c r="G3" s="668" t="n"/>
       <c r="H3" s="576" t="inlineStr">
         <is>
           <t>M档基础人天（按工作模式）</t>
         </is>
       </c>
-      <c r="I3" s="653" t="n"/>
-      <c r="J3" s="654" t="n"/>
+      <c r="I3" s="667" t="n"/>
+      <c r="J3" s="668" t="n"/>
       <c r="K3" s="579" t="inlineStr">
         <is>
           <t>复杂度判定标准</t>
         </is>
       </c>
-      <c r="L3" s="653" t="n"/>
-      <c r="M3" s="653" t="n"/>
-      <c r="N3" s="654" t="n"/>
+      <c r="L3" s="667" t="n"/>
+      <c r="M3" s="667" t="n"/>
+      <c r="N3" s="668" t="n"/>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="453" t="inlineStr">
@@ -10516,12 +10744,12 @@
           <t>需求（Epic）</t>
         </is>
       </c>
-      <c r="B1" s="635" t="n"/>
-      <c r="C1" s="635" t="n"/>
-      <c r="D1" s="635" t="n"/>
-      <c r="E1" s="635" t="n"/>
-      <c r="F1" s="635" t="n"/>
-      <c r="G1" s="635" t="n"/>
+      <c r="B1" s="647" t="n"/>
+      <c r="C1" s="647" t="n"/>
+      <c r="D1" s="647" t="n"/>
+      <c r="E1" s="647" t="n"/>
+      <c r="F1" s="647" t="n"/>
+      <c r="G1" s="647" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="400" t="inlineStr">
@@ -10529,12 +10757,12 @@
           <t>业务与技术 Epic 使用同一结构；输入归一化是内部中间产物，不进入工作簿</t>
         </is>
       </c>
-      <c r="B2" s="636" t="n"/>
-      <c r="C2" s="636" t="n"/>
-      <c r="D2" s="636" t="n"/>
-      <c r="E2" s="636" t="n"/>
-      <c r="F2" s="636" t="n"/>
-      <c r="G2" s="636" t="n"/>
+      <c r="B2" s="648" t="n"/>
+      <c r="C2" s="648" t="n"/>
+      <c r="D2" s="648" t="n"/>
+      <c r="E2" s="648" t="n"/>
+      <c r="F2" s="648" t="n"/>
+      <c r="G2" s="648" t="n"/>
     </row>
     <row r="3" ht="9" customHeight="1"/>
     <row r="4" ht="38" customHeight="1">
@@ -10575,222 +10803,222 @@
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="641" t="inlineStr">
+      <c r="A5" s="653" t="inlineStr">
         <is>
           <t>epic-customer-management</t>
         </is>
       </c>
-      <c r="B5" s="642" t="inlineStr">
+      <c r="B5" s="654" t="inlineStr">
         <is>
           <t>BUSINESS</t>
         </is>
       </c>
-      <c r="C5" s="641" t="inlineStr">
+      <c r="C5" s="653" t="inlineStr">
         <is>
           <t>会员与客户管理</t>
         </is>
       </c>
-      <c r="D5" s="641" t="inlineStr">
+      <c r="D5" s="653" t="inlineStr">
         <is>
           <t>统一会员身份、档案、等级与授权边界。</t>
         </is>
       </c>
-      <c r="E5" s="641" t="inlineStr">
+      <c r="E5" s="653" t="inlineStr">
         <is>
           <t>会员门户、会员主数据、授权中心 / customer_profile、member_tier</t>
         </is>
       </c>
-      <c r="F5" s="641" t="inlineStr">
+      <c r="F5" s="653" t="inlineStr">
         <is>
           <t>会员信息跨渠道一致，等级与授权过程可追溯</t>
         </is>
       </c>
-      <c r="G5" s="641" t="inlineStr">
+      <c r="G5" s="653" t="inlineStr">
         <is>
           <t>不迁移授权主数据，不改造现有授权中心</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="641" t="inlineStr">
+      <c r="A6" s="653" t="inlineStr">
         <is>
           <t>epic-order-fulfillment</t>
         </is>
       </c>
-      <c r="B6" s="642" t="inlineStr">
+      <c r="B6" s="654" t="inlineStr">
         <is>
           <t>BUSINESS</t>
         </is>
       </c>
-      <c r="C6" s="641" t="inlineStr">
+      <c r="C6" s="653" t="inlineStr">
         <is>
           <t>订单与履约</t>
         </is>
       </c>
-      <c r="D6" s="641" t="inlineStr">
+      <c r="D6" s="653" t="inlineStr">
         <is>
           <t>统一订单受理、库存预占、状态流转与退货退款。</t>
         </is>
       </c>
-      <c r="E6" s="641" t="inlineStr">
+      <c r="E6" s="653" t="inlineStr">
         <is>
           <t>订单服务、ERP、支付网关 / order、inventory_reservation、refund</t>
         </is>
       </c>
-      <c r="F6" s="641" t="inlineStr">
+      <c r="F6" s="653" t="inlineStr">
         <is>
           <t>门店与线上订单按同一规则履约且异常可恢复</t>
         </is>
       </c>
-      <c r="G6" s="641" t="inlineStr">
+      <c r="G6" s="653" t="inlineStr">
         <is>
           <t>不替换 ERP 库存核算与支付清算能力</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="641" t="inlineStr">
+      <c r="A7" s="653" t="inlineStr">
         <is>
           <t>epic-omnichannel-operations</t>
         </is>
       </c>
-      <c r="B7" s="642" t="inlineStr">
+      <c r="B7" s="654" t="inlineStr">
         <is>
           <t>BUSINESS</t>
         </is>
       </c>
-      <c r="C7" s="641" t="inlineStr">
+      <c r="C7" s="653" t="inlineStr">
         <is>
           <t>全渠道运营</t>
         </is>
       </c>
-      <c r="D7" s="641" t="inlineStr">
+      <c r="D7" s="653" t="inlineStr">
         <is>
           <t>为门店、顾客和客服提供一致的订单操作与信息。</t>
         </is>
       </c>
-      <c r="E7" s="641" t="inlineStr">
+      <c r="E7" s="653" t="inlineStr">
         <is>
           <t>门店工作台、会员门户、消息中心 / store_order、order_timeline</t>
         </is>
       </c>
-      <c r="F7" s="641" t="inlineStr">
+      <c r="F7" s="653" t="inlineStr">
         <is>
           <t>门店处理效率与顾客订单可视性提升</t>
         </is>
       </c>
-      <c r="G7" s="641" t="inlineStr">
+      <c r="G7" s="653" t="inlineStr">
         <is>
           <t>不改造消息中心通道策略与营销触达规则</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="641" t="inlineStr">
+      <c r="A8" s="653" t="inlineStr">
         <is>
           <t>epic-finance-settlement</t>
         </is>
       </c>
-      <c r="B8" s="642" t="inlineStr">
+      <c r="B8" s="654" t="inlineStr">
         <is>
           <t>BUSINESS</t>
         </is>
       </c>
-      <c r="C8" s="641" t="inlineStr">
+      <c r="C8" s="653" t="inlineStr">
         <is>
           <t>财务结算与经营分析</t>
         </is>
       </c>
-      <c r="D8" s="641" t="inlineStr">
+      <c r="D8" s="653" t="inlineStr">
         <is>
           <t>建立支付、退款、发票和经营指标的日结闭环。</t>
         </is>
       </c>
-      <c r="E8" s="641" t="inlineStr">
+      <c r="E8" s="653" t="inlineStr">
         <is>
           <t>订单服务、支付网关、电子发票平台、财务数据集市</t>
         </is>
       </c>
-      <c r="F8" s="641" t="inlineStr">
+      <c r="F8" s="653" t="inlineStr">
         <is>
           <t>财务差异可定位、发票可追踪、经营指标口径一致</t>
         </is>
       </c>
-      <c r="G8" s="641" t="inlineStr">
+      <c r="G8" s="653" t="inlineStr">
         <is>
           <t>不改造总账系统，不包含税务筹划与历史会计调整</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="641" t="inlineStr">
+      <c r="A9" s="653" t="inlineStr">
         <is>
           <t>epic-platform</t>
         </is>
       </c>
-      <c r="B9" s="642" t="inlineStr">
+      <c r="B9" s="654" t="inlineStr">
         <is>
           <t>TECHNICAL</t>
         </is>
       </c>
-      <c r="C9" s="641" t="inlineStr">
+      <c r="C9" s="653" t="inlineStr">
         <is>
           <t>平台与服务边界</t>
         </is>
       </c>
-      <c r="D9" s="641" t="inlineStr">
+      <c r="D9" s="653" t="inlineStr">
         <is>
           <t>明确会员、订单与生产发布所需的稳定技术边界。</t>
         </is>
       </c>
-      <c r="E9" s="641" t="inlineStr">
+      <c r="E9" s="653" t="inlineStr">
         <is>
           <t>会员门户、订单服务、API 网关、生产平台</t>
         </is>
       </c>
-      <c r="F9" s="641" t="inlineStr">
+      <c r="F9" s="653" t="inlineStr">
         <is>
           <t>服务职责清晰、发布可回滚、生产范围可签署</t>
         </is>
       </c>
-      <c r="G9" s="641" t="inlineStr">
+      <c r="G9" s="653" t="inlineStr">
         <is>
           <t>不替换企业级网关、Kubernetes 平台与 CI/CD 产品</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="641" t="inlineStr">
+      <c r="A10" s="653" t="inlineStr">
         <is>
           <t>epic-delivery-assurance</t>
         </is>
       </c>
-      <c r="B10" s="642" t="inlineStr">
+      <c r="B10" s="654" t="inlineStr">
         <is>
           <t>TECHNICAL</t>
         </is>
       </c>
-      <c r="C10" s="641" t="inlineStr">
+      <c r="C10" s="653" t="inlineStr">
         <is>
           <t>上线与质量保障</t>
         </is>
       </c>
-      <c r="D10" s="641" t="inlineStr">
+      <c r="D10" s="653" t="inlineStr">
         <is>
           <t>将数据迁移、监控运维、质量验证和责任边界纳入可估算交付。</t>
         </is>
       </c>
-      <c r="E10" s="641" t="inlineStr">
+      <c r="E10" s="653" t="inlineStr">
         <is>
           <t>迁移作业、统一监控平台、测试资产、运维知识库</t>
         </is>
       </c>
-      <c r="F10" s="641" t="inlineStr">
+      <c r="F10" s="653" t="inlineStr">
         <is>
           <t>上线过程可验证、可回退、可运维并可审计</t>
         </is>
       </c>
-      <c r="G10" s="641" t="inlineStr">
+      <c r="G10" s="653" t="inlineStr">
         <is>
           <t>不包含上线后驻场支持和旧系统退役实施</t>
         </is>
@@ -10935,14 +11163,14 @@
           <t>子需求（Feature）</t>
         </is>
       </c>
-      <c r="B1" s="635" t="n"/>
-      <c r="C1" s="635" t="n"/>
-      <c r="D1" s="635" t="n"/>
-      <c r="E1" s="635" t="n"/>
-      <c r="F1" s="635" t="n"/>
-      <c r="G1" s="635" t="n"/>
-      <c r="H1" s="635" t="n"/>
-      <c r="I1" s="635" t="n"/>
+      <c r="B1" s="647" t="n"/>
+      <c r="C1" s="647" t="n"/>
+      <c r="D1" s="647" t="n"/>
+      <c r="E1" s="647" t="n"/>
+      <c r="F1" s="647" t="n"/>
+      <c r="G1" s="647" t="n"/>
+      <c r="H1" s="647" t="n"/>
+      <c r="I1" s="647" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="400" t="inlineStr">
@@ -10950,14 +11178,14 @@
           <t>Feature 是范围与交付的最小稳定需求实体；业务与技术 Feature 使用同一结构</t>
         </is>
       </c>
-      <c r="B2" s="636" t="n"/>
-      <c r="C2" s="636" t="n"/>
-      <c r="D2" s="636" t="n"/>
-      <c r="E2" s="636" t="n"/>
-      <c r="F2" s="636" t="n"/>
-      <c r="G2" s="636" t="n"/>
-      <c r="H2" s="636" t="n"/>
-      <c r="I2" s="636" t="n"/>
+      <c r="B2" s="648" t="n"/>
+      <c r="C2" s="648" t="n"/>
+      <c r="D2" s="648" t="n"/>
+      <c r="E2" s="648" t="n"/>
+      <c r="F2" s="648" t="n"/>
+      <c r="G2" s="648" t="n"/>
+      <c r="H2" s="648" t="n"/>
+      <c r="I2" s="648" t="n"/>
     </row>
     <row r="3" ht="9" customHeight="1"/>
     <row r="4" ht="38" customHeight="1">
@@ -11008,782 +11236,782 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="641" t="inlineStr">
+      <c r="A5" s="653" t="inlineStr">
         <is>
           <t>feature-customer-profile</t>
         </is>
       </c>
-      <c r="B5" s="641" t="inlineStr">
+      <c r="B5" s="653" t="inlineStr">
         <is>
           <t>epic-customer-management</t>
         </is>
       </c>
-      <c r="C5" s="641" t="inlineStr">
+      <c r="C5" s="653" t="inlineStr">
         <is>
           <t>会员与客户管理</t>
         </is>
       </c>
-      <c r="D5" s="641" t="inlineStr">
+      <c r="D5" s="653" t="inlineStr">
         <is>
           <t>创建并查看客户档案</t>
         </is>
       </c>
-      <c r="E5" s="641" t="inlineStr">
+      <c r="E5" s="653" t="inlineStr">
         <is>
           <t>用户创建或维护客户档案后，各渠道可查看授权范围内的最新信息。</t>
         </is>
       </c>
-      <c r="F5" s="641" t="inlineStr">
+      <c r="F5" s="653" t="inlineStr">
         <is>
           <t>会员门户、会员主数据 / customer_profile</t>
         </is>
       </c>
-      <c r="G5" s="641" t="inlineStr">
+      <c r="G5" s="653" t="inlineStr">
         <is>
           <t>档案查询 P95 小于 300ms；敏感字段按角色脱敏</t>
         </is>
       </c>
-      <c r="H5" s="642" t="inlineStr">
+      <c r="H5" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I5" s="641" t="inlineStr"/>
+      <c r="I5" s="653" t="inlineStr"/>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="641" t="inlineStr">
+      <c r="A6" s="653" t="inlineStr">
         <is>
           <t>feature-member-tier</t>
         </is>
       </c>
-      <c r="B6" s="641" t="inlineStr">
+      <c r="B6" s="653" t="inlineStr">
         <is>
           <t>epic-customer-management</t>
         </is>
       </c>
-      <c r="C6" s="641" t="inlineStr">
+      <c r="C6" s="653" t="inlineStr">
         <is>
           <t>会员与客户管理</t>
         </is>
       </c>
-      <c r="D6" s="641" t="inlineStr">
+      <c r="D6" s="653" t="inlineStr">
         <is>
           <t>会员等级计算与版本</t>
         </is>
       </c>
-      <c r="E6" s="641" t="inlineStr">
+      <c r="E6" s="653" t="inlineStr">
         <is>
           <t>按有效消费额计算等级，并记录规则版本、生效日和调整原因。</t>
         </is>
       </c>
-      <c r="F6" s="641" t="inlineStr">
+      <c r="F6" s="653" t="inlineStr">
         <is>
           <t>会员主数据、订单服务 / member_tier_rule、member_tier_history</t>
         </is>
       </c>
-      <c r="G6" s="641" t="inlineStr">
+      <c r="G6" s="653" t="inlineStr">
         <is>
           <t>同一会员同一时点仅有一个生效等级</t>
         </is>
       </c>
-      <c r="H6" s="642" t="inlineStr">
+      <c r="H6" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I6" s="641" t="inlineStr"/>
+      <c r="I6" s="653" t="inlineStr"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="641" t="inlineStr">
+      <c r="A7" s="653" t="inlineStr">
         <is>
           <t>feature-customer-consent</t>
         </is>
       </c>
-      <c r="B7" s="641" t="inlineStr">
+      <c r="B7" s="653" t="inlineStr">
         <is>
           <t>epic-customer-management</t>
         </is>
       </c>
-      <c r="C7" s="641" t="inlineStr">
+      <c r="C7" s="653" t="inlineStr">
         <is>
           <t>会员与客户管理</t>
         </is>
       </c>
-      <c r="D7" s="641" t="inlineStr">
+      <c r="D7" s="653" t="inlineStr">
         <is>
           <t>会员授权与撤回复用</t>
         </is>
       </c>
-      <c r="E7" s="641" t="inlineStr">
+      <c r="E7" s="653" t="inlineStr">
         <is>
           <t>复用授权中心的授权、撤回与查询能力。</t>
         </is>
       </c>
-      <c r="F7" s="641" t="inlineStr">
+      <c r="F7" s="653" t="inlineStr">
         <is>
           <t>授权中心 / consent_record、consent_audit</t>
         </is>
       </c>
-      <c r="G7" s="641" t="inlineStr">
+      <c r="G7" s="653" t="inlineStr">
         <is>
           <t>渠道不复制授权主数据，查询留痕保存 36 个月</t>
         </is>
       </c>
-      <c r="H7" s="642" t="inlineStr">
+      <c r="H7" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I7" s="641" t="inlineStr"/>
+      <c r="I7" s="653" t="inlineStr"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="641" t="inlineStr">
+      <c r="A8" s="653" t="inlineStr">
         <is>
           <t>feature-order-orchestration</t>
         </is>
       </c>
-      <c r="B8" s="641" t="inlineStr">
+      <c r="B8" s="653" t="inlineStr">
         <is>
           <t>epic-order-fulfillment</t>
         </is>
       </c>
-      <c r="C8" s="641" t="inlineStr">
+      <c r="C8" s="653" t="inlineStr">
         <is>
           <t>订单与履约</t>
         </is>
       </c>
-      <c r="D8" s="641" t="inlineStr">
+      <c r="D8" s="653" t="inlineStr">
         <is>
           <t>统一订单编排与状态机</t>
         </is>
       </c>
-      <c r="E8" s="641" t="inlineStr">
+      <c r="E8" s="653" t="inlineStr">
         <is>
           <t>接收门店与线上订单，执行价格、权益和履约校验并驱动状态流转。</t>
         </is>
       </c>
-      <c r="F8" s="641" t="inlineStr">
+      <c r="F8" s="653" t="inlineStr">
         <is>
           <t>订单服务、门店工作台、会员门户 / order、order_state</t>
         </is>
       </c>
-      <c r="G8" s="641" t="inlineStr">
+      <c r="G8" s="653" t="inlineStr">
         <is>
           <t>订单状态变更幂等且全链路可追踪</t>
         </is>
       </c>
-      <c r="H8" s="642" t="inlineStr">
+      <c r="H8" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I8" s="641" t="inlineStr"/>
+      <c r="I8" s="653" t="inlineStr"/>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="641" t="inlineStr">
+      <c r="A9" s="653" t="inlineStr">
         <is>
           <t>feature-inventory-reservation</t>
         </is>
       </c>
-      <c r="B9" s="641" t="inlineStr">
+      <c r="B9" s="653" t="inlineStr">
         <is>
           <t>epic-order-fulfillment</t>
         </is>
       </c>
-      <c r="C9" s="641" t="inlineStr">
+      <c r="C9" s="653" t="inlineStr">
         <is>
           <t>订单与履约</t>
         </is>
       </c>
-      <c r="D9" s="641" t="inlineStr">
+      <c r="D9" s="653" t="inlineStr">
         <is>
           <t>库存预占与释放</t>
         </is>
       </c>
-      <c r="E9" s="641" t="inlineStr">
+      <c r="E9" s="653" t="inlineStr">
         <is>
           <t>订单确认前通过 ERP 预占库存，取消或超时后释放。</t>
         </is>
       </c>
-      <c r="F9" s="641" t="inlineStr">
+      <c r="F9" s="653" t="inlineStr">
         <is>
           <t>订单服务、ERP / inventory_reservation</t>
         </is>
       </c>
-      <c r="G9" s="641" t="inlineStr">
+      <c r="G9" s="653" t="inlineStr">
         <is>
           <t>接口重试不得重复预占；调用超时 3 秒</t>
         </is>
       </c>
-      <c r="H9" s="642" t="inlineStr">
+      <c r="H9" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I9" s="641" t="inlineStr"/>
+      <c r="I9" s="653" t="inlineStr"/>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="641" t="inlineStr">
+      <c r="A10" s="653" t="inlineStr">
         <is>
           <t>feature-return-refund</t>
         </is>
       </c>
-      <c r="B10" s="641" t="inlineStr">
+      <c r="B10" s="653" t="inlineStr">
         <is>
           <t>epic-order-fulfillment</t>
         </is>
       </c>
-      <c r="C10" s="641" t="inlineStr">
+      <c r="C10" s="653" t="inlineStr">
         <is>
           <t>订单与履约</t>
         </is>
       </c>
-      <c r="D10" s="641" t="inlineStr">
+      <c r="D10" s="653" t="inlineStr">
         <is>
           <t>退货退款闭环</t>
         </is>
       </c>
-      <c r="E10" s="641" t="inlineStr">
+      <c r="E10" s="653" t="inlineStr">
         <is>
           <t>核验可退数量，生成退货单并调用支付网关退款。</t>
         </is>
       </c>
-      <c r="F10" s="641" t="inlineStr">
+      <c r="F10" s="653" t="inlineStr">
         <is>
           <t>门店工作台、订单服务、支付网关 / return_order、refund</t>
         </is>
       </c>
-      <c r="G10" s="641" t="inlineStr">
+      <c r="G10" s="653" t="inlineStr">
         <is>
           <t>退款请求幂等，支付结果与订单差异可审计</t>
         </is>
       </c>
-      <c r="H10" s="642" t="inlineStr">
+      <c r="H10" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I10" s="641" t="inlineStr"/>
+      <c r="I10" s="653" t="inlineStr"/>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="641" t="inlineStr">
+      <c r="A11" s="653" t="inlineStr">
         <is>
           <t>feature-store-order</t>
         </is>
       </c>
-      <c r="B11" s="641" t="inlineStr">
+      <c r="B11" s="653" t="inlineStr">
         <is>
           <t>epic-omnichannel-operations</t>
         </is>
       </c>
-      <c r="C11" s="641" t="inlineStr">
+      <c r="C11" s="653" t="inlineStr">
         <is>
           <t>全渠道运营</t>
         </is>
       </c>
-      <c r="D11" s="641" t="inlineStr">
+      <c r="D11" s="653" t="inlineStr">
         <is>
           <t>门店接单工作台</t>
         </is>
       </c>
-      <c r="E11" s="641" t="inlineStr">
+      <c r="E11" s="653" t="inlineStr">
         <is>
           <t>展示待处理订单、缺货替代与交接信息并按门店权限操作。</t>
         </is>
       </c>
-      <c r="F11" s="641" t="inlineStr">
+      <c r="F11" s="653" t="inlineStr">
         <is>
           <t>门店工作台、订单服务 / store_order_queue</t>
         </is>
       </c>
-      <c r="G11" s="641" t="inlineStr">
+      <c r="G11" s="653" t="inlineStr">
         <is>
           <t>仅授权门店可查看和操作本店订单</t>
         </is>
       </c>
-      <c r="H11" s="642" t="inlineStr">
+      <c r="H11" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I11" s="641" t="inlineStr"/>
+      <c r="I11" s="653" t="inlineStr"/>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="641" t="inlineStr">
+      <c r="A12" s="653" t="inlineStr">
         <is>
           <t>feature-order-visibility</t>
         </is>
       </c>
-      <c r="B12" s="641" t="inlineStr">
+      <c r="B12" s="653" t="inlineStr">
         <is>
           <t>epic-omnichannel-operations</t>
         </is>
       </c>
-      <c r="C12" s="641" t="inlineStr">
+      <c r="C12" s="653" t="inlineStr">
         <is>
           <t>全渠道运营</t>
         </is>
       </c>
-      <c r="D12" s="641" t="inlineStr">
+      <c r="D12" s="653" t="inlineStr">
         <is>
           <t>订单状态与履约轨迹</t>
         </is>
       </c>
-      <c r="E12" s="641" t="inlineStr">
+      <c r="E12" s="653" t="inlineStr">
         <is>
           <t>顾客和客服查看一致的状态、履约节点与异常原因。</t>
         </is>
       </c>
-      <c r="F12" s="641" t="inlineStr">
+      <c r="F12" s="653" t="inlineStr">
         <is>
           <t>会员门户、客服工作台、订单服务 / order_timeline</t>
         </is>
       </c>
-      <c r="G12" s="641" t="inlineStr">
+      <c r="G12" s="653" t="inlineStr">
         <is>
           <t>关键状态变更 60 秒内可见</t>
         </is>
       </c>
-      <c r="H12" s="642" t="inlineStr">
+      <c r="H12" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I12" s="641" t="inlineStr"/>
+      <c r="I12" s="653" t="inlineStr"/>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="641" t="inlineStr">
+      <c r="A13" s="653" t="inlineStr">
         <is>
           <t>feature-customer-notification</t>
         </is>
       </c>
-      <c r="B13" s="641" t="inlineStr">
+      <c r="B13" s="653" t="inlineStr">
         <is>
           <t>epic-omnichannel-operations</t>
         </is>
       </c>
-      <c r="C13" s="641" t="inlineStr">
+      <c r="C13" s="653" t="inlineStr">
         <is>
           <t>全渠道运营</t>
         </is>
       </c>
-      <c r="D13" s="641" t="inlineStr">
+      <c r="D13" s="653" t="inlineStr">
         <is>
           <t>订单节点通知复用</t>
         </is>
       </c>
-      <c r="E13" s="641" t="inlineStr">
+      <c r="E13" s="653" t="inlineStr">
         <is>
           <t>复用消息中心消费标准订单事件并发送通知。</t>
         </is>
       </c>
-      <c r="F13" s="641" t="inlineStr">
+      <c r="F13" s="653" t="inlineStr">
         <is>
           <t>消息中心、订单事件总线 / notification_event</t>
         </is>
       </c>
-      <c r="G13" s="641" t="inlineStr">
+      <c r="G13" s="653" t="inlineStr">
         <is>
           <t>不新增通知渠道和营销模板</t>
         </is>
       </c>
-      <c r="H13" s="642" t="inlineStr">
+      <c r="H13" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I13" s="641" t="inlineStr"/>
+      <c r="I13" s="653" t="inlineStr"/>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="641" t="inlineStr">
+      <c r="A14" s="653" t="inlineStr">
         <is>
           <t>feature-payment-reconciliation</t>
         </is>
       </c>
-      <c r="B14" s="641" t="inlineStr">
+      <c r="B14" s="653" t="inlineStr">
         <is>
           <t>epic-finance-settlement</t>
         </is>
       </c>
-      <c r="C14" s="641" t="inlineStr">
+      <c r="C14" s="653" t="inlineStr">
         <is>
           <t>财务结算与经营分析</t>
         </is>
       </c>
-      <c r="D14" s="641" t="inlineStr">
+      <c r="D14" s="653" t="inlineStr">
         <is>
           <t>支付退款日结对账</t>
         </is>
       </c>
-      <c r="E14" s="641" t="inlineStr">
+      <c r="E14" s="653" t="inlineStr">
         <is>
           <t>按渠道、门店和订单核对实收、退款与手续费差异。</t>
         </is>
       </c>
-      <c r="F14" s="641" t="inlineStr">
+      <c r="F14" s="653" t="inlineStr">
         <is>
           <t>订单服务、支付网关、财务数据集市 / payment_reconciliation</t>
         </is>
       </c>
-      <c r="G14" s="641" t="inlineStr">
+      <c r="G14" s="653" t="inlineStr">
         <is>
           <t>每日 07:00 前完成前一自然日对账</t>
         </is>
       </c>
-      <c r="H14" s="642" t="inlineStr">
+      <c r="H14" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I14" s="641" t="inlineStr"/>
+      <c r="I14" s="653" t="inlineStr"/>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="641" t="inlineStr">
+      <c r="A15" s="653" t="inlineStr">
         <is>
           <t>feature-einvoice</t>
         </is>
       </c>
-      <c r="B15" s="641" t="inlineStr">
+      <c r="B15" s="653" t="inlineStr">
         <is>
           <t>epic-finance-settlement</t>
         </is>
       </c>
-      <c r="C15" s="641" t="inlineStr">
+      <c r="C15" s="653" t="inlineStr">
         <is>
           <t>财务结算与经营分析</t>
         </is>
       </c>
-      <c r="D15" s="641" t="inlineStr">
+      <c r="D15" s="653" t="inlineStr">
         <is>
           <t>电子发票申请与状态</t>
         </is>
       </c>
-      <c r="E15" s="641" t="inlineStr">
+      <c r="E15" s="653" t="inlineStr">
         <is>
           <t>调用电子发票平台开票并保存号码、状态和失败原因。</t>
         </is>
       </c>
-      <c r="F15" s="641" t="inlineStr">
+      <c r="F15" s="653" t="inlineStr">
         <is>
           <t>订单服务、电子发票平台 / invoice_application</t>
         </is>
       </c>
-      <c r="G15" s="641" t="inlineStr">
+      <c r="G15" s="653" t="inlineStr">
         <is>
           <t>开票失败可重试且不得重复开票</t>
         </is>
       </c>
-      <c r="H15" s="642" t="inlineStr">
+      <c r="H15" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I15" s="641" t="inlineStr"/>
+      <c r="I15" s="653" t="inlineStr"/>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="641" t="inlineStr">
+      <c r="A16" s="653" t="inlineStr">
         <is>
           <t>feature-finance-report</t>
         </is>
       </c>
-      <c r="B16" s="641" t="inlineStr">
+      <c r="B16" s="653" t="inlineStr">
         <is>
           <t>epic-finance-settlement</t>
         </is>
       </c>
-      <c r="C16" s="641" t="inlineStr">
+      <c r="C16" s="653" t="inlineStr">
         <is>
           <t>财务结算与经营分析</t>
         </is>
       </c>
-      <c r="D16" s="641" t="inlineStr">
+      <c r="D16" s="653" t="inlineStr">
         <is>
           <t>财务经营报表</t>
         </is>
       </c>
-      <c r="E16" s="641" t="inlineStr">
+      <c r="E16" s="653" t="inlineStr">
         <is>
           <t>按日、区域和渠道展示销售、退款、优惠与未对账金额。</t>
         </is>
       </c>
-      <c r="F16" s="641" t="inlineStr">
+      <c r="F16" s="653" t="inlineStr">
         <is>
           <t>财务数据集市 / finance_daily_metric</t>
         </is>
       </c>
-      <c r="G16" s="641" t="inlineStr">
+      <c r="G16" s="653" t="inlineStr">
         <is>
           <t>指标与对账规则同源，支持追溯到订单</t>
         </is>
       </c>
-      <c r="H16" s="642" t="inlineStr">
+      <c r="H16" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I16" s="641" t="inlineStr"/>
+      <c r="I16" s="653" t="inlineStr"/>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="641" t="inlineStr">
+      <c r="A17" s="653" t="inlineStr">
         <is>
           <t>feature-profile-api</t>
         </is>
       </c>
-      <c r="B17" s="641" t="inlineStr">
+      <c r="B17" s="653" t="inlineStr">
         <is>
           <t>epic-platform</t>
         </is>
       </c>
-      <c r="C17" s="641" t="inlineStr">
+      <c r="C17" s="653" t="inlineStr">
         <is>
           <t>平台与服务边界</t>
         </is>
       </c>
-      <c r="D17" s="641" t="inlineStr">
+      <c r="D17" s="653" t="inlineStr">
         <is>
           <t>客户档案操作 API</t>
         </is>
       </c>
-      <c r="E17" s="641" t="inlineStr">
+      <c r="E17" s="653" t="inlineStr">
         <is>
           <t>通过稳定 API 创建、维护和检索客户档案，并隔离渠道与会员主数据。</t>
         </is>
       </c>
-      <c r="F17" s="641" t="inlineStr">
+      <c r="F17" s="653" t="inlineStr">
         <is>
           <t>会员门户、会员主数据 / customer-profile-api</t>
         </is>
       </c>
-      <c r="G17" s="641" t="inlineStr">
+      <c r="G17" s="653" t="inlineStr">
         <is>
           <t>API P95 小于 300ms；写操作使用幂等键；敏感字段按权限返回</t>
         </is>
       </c>
-      <c r="H17" s="642" t="inlineStr">
+      <c r="H17" s="654" t="inlineStr">
         <is>
           <t>DESIGN_DERIVED</t>
         </is>
       </c>
-      <c r="I17" s="641" t="inlineStr">
+      <c r="I17" s="653" t="inlineStr">
         <is>
           <t>设计决策/Decision: decision-profile-api 使用专用 API 边界处理客户档案操作；产生原因/Cause: 客户档案操作 API 需要为会员门户与未来渠道提供统一操作边界；不交付影响/Non-delivery impact: 接口/API | 星云会员门户 -&gt; 无法通过统一边界创建或检索客户档案</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="641" t="inlineStr">
+      <c r="A18" s="653" t="inlineStr">
         <is>
           <t>feature-production-scope</t>
         </is>
       </c>
-      <c r="B18" s="641" t="inlineStr">
+      <c r="B18" s="653" t="inlineStr">
         <is>
           <t>epic-platform</t>
         </is>
       </c>
-      <c r="C18" s="641" t="inlineStr">
+      <c r="C18" s="653" t="inlineStr">
         <is>
           <t>平台与服务边界</t>
         </is>
       </c>
-      <c r="D18" s="641" t="inlineStr">
+      <c r="D18" s="653" t="inlineStr">
         <is>
           <t>生产准备、切换与验证</t>
         </is>
       </c>
-      <c r="E18" s="641" t="inlineStr">
+      <c r="E18" s="653" t="inlineStr">
         <is>
           <t>完成环境配置、发布清单、切换回滚和生产验证，并形成签署证据。</t>
         </is>
       </c>
-      <c r="F18" s="641" t="inlineStr">
+      <c r="F18" s="653" t="inlineStr">
         <is>
           <t>Kubernetes 生产环境、CI/CD、功能开关、发布清单</t>
         </is>
       </c>
-      <c r="G18" s="641" t="inlineStr">
+      <c r="G18" s="653" t="inlineStr">
         <is>
           <t>业务中断不超过 15 分钟；回滚路径在切换前完成演练</t>
         </is>
       </c>
-      <c r="H18" s="642" t="inlineStr">
+      <c r="H18" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I18" s="641" t="inlineStr"/>
+      <c r="I18" s="653" t="inlineStr"/>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="641" t="inlineStr">
+      <c r="A19" s="653" t="inlineStr">
         <is>
           <t>feature-legacy-retirement</t>
         </is>
       </c>
-      <c r="B19" s="641" t="inlineStr">
+      <c r="B19" s="653" t="inlineStr">
         <is>
           <t>epic-platform</t>
         </is>
       </c>
-      <c r="C19" s="641" t="inlineStr">
+      <c r="C19" s="653" t="inlineStr">
         <is>
           <t>平台与服务边界</t>
         </is>
       </c>
-      <c r="D19" s="641" t="inlineStr">
+      <c r="D19" s="653" t="inlineStr">
         <is>
           <t>上线后支持与旧系统退役边界</t>
         </is>
       </c>
-      <c r="E19" s="641" t="inlineStr">
+      <c r="E19" s="653" t="inlineStr">
         <is>
           <t>明确上线后驻场支持和旧系统退役不在本期固定范围内。</t>
         </is>
       </c>
-      <c r="F19" s="641" t="inlineStr">
+      <c r="F19" s="653" t="inlineStr">
         <is>
           <t>旧会员门户、旧订单查询服务</t>
         </is>
       </c>
-      <c r="G19" s="641" t="inlineStr">
+      <c r="G19" s="653" t="inlineStr">
         <is>
           <t>如需实施必须单独立项并重新确认基线</t>
         </is>
       </c>
-      <c r="H19" s="642" t="inlineStr">
+      <c r="H19" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I19" s="641" t="inlineStr"/>
+      <c r="I19" s="653" t="inlineStr"/>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="641" t="inlineStr">
+      <c r="A20" s="653" t="inlineStr">
         <is>
           <t>feature-data-migration</t>
         </is>
       </c>
-      <c r="B20" s="641" t="inlineStr">
+      <c r="B20" s="653" t="inlineStr">
         <is>
           <t>epic-delivery-assurance</t>
         </is>
       </c>
-      <c r="C20" s="641" t="inlineStr">
+      <c r="C20" s="653" t="inlineStr">
         <is>
           <t>上线与质量保障</t>
         </is>
       </c>
-      <c r="D20" s="641" t="inlineStr">
+      <c r="D20" s="653" t="inlineStr">
         <is>
           <t>会员与订单数据迁移</t>
         </is>
       </c>
-      <c r="E20" s="641" t="inlineStr">
+      <c r="E20" s="653" t="inlineStr">
         <is>
           <t>迁移会员扩展字段与两年内历史订单，执行校验、补偿与留痕。</t>
         </is>
       </c>
-      <c r="F20" s="641" t="inlineStr">
+      <c r="F20" s="653" t="inlineStr">
         <is>
           <t>会员主数据、订单库 / customer_profile、order、order_item</t>
         </is>
       </c>
-      <c r="G20" s="641" t="inlineStr">
+      <c r="G20" s="653" t="inlineStr">
         <is>
           <t>迁移前后关键字段一致率 100%，业务主键重复为 0</t>
         </is>
       </c>
-      <c r="H20" s="642" t="inlineStr">
+      <c r="H20" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I20" s="641" t="inlineStr"/>
+      <c r="I20" s="653" t="inlineStr"/>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="641" t="inlineStr">
+      <c r="A21" s="653" t="inlineStr">
         <is>
           <t>feature-observability-ops</t>
         </is>
       </c>
-      <c r="B21" s="641" t="inlineStr">
+      <c r="B21" s="653" t="inlineStr">
         <is>
           <t>epic-delivery-assurance</t>
         </is>
       </c>
-      <c r="C21" s="641" t="inlineStr">
+      <c r="C21" s="653" t="inlineStr">
         <is>
           <t>上线与质量保障</t>
         </is>
       </c>
-      <c r="D21" s="641" t="inlineStr">
+      <c r="D21" s="653" t="inlineStr">
         <is>
           <t>监控、运维交接与用户赋能</t>
         </is>
       </c>
-      <c r="E21" s="641" t="inlineStr">
+      <c r="E21" s="653" t="inlineStr">
         <is>
           <t>建设关键指标和告警，完成运维手册、交接演练与业务用户培训。</t>
         </is>
       </c>
-      <c r="F21" s="641" t="inlineStr">
+      <c r="F21" s="653" t="inlineStr">
         <is>
           <t>统一监控平台、运维知识库、培训材料</t>
         </is>
       </c>
-      <c r="G21" s="641" t="inlineStr">
+      <c r="G21" s="653" t="inlineStr">
         <is>
           <t>核心交易告警 5 分钟内触发；交接与培训均需签到和验收记录</t>
         </is>
       </c>
-      <c r="H21" s="642" t="inlineStr">
+      <c r="H21" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I21" s="641" t="inlineStr"/>
+      <c r="I21" s="653" t="inlineStr"/>
     </row>
     <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="641" t="inlineStr">
+      <c r="A22" s="653" t="inlineStr">
         <is>
           <t>feature-test-quality</t>
         </is>
       </c>
-      <c r="B22" s="641" t="inlineStr">
+      <c r="B22" s="653" t="inlineStr">
         <is>
           <t>epic-delivery-assurance</t>
         </is>
       </c>
-      <c r="C22" s="641" t="inlineStr">
+      <c r="C22" s="653" t="inlineStr">
         <is>
           <t>上线与质量保障</t>
         </is>
       </c>
-      <c r="D22" s="641" t="inlineStr">
+      <c r="D22" s="653" t="inlineStr">
         <is>
           <t>自动化、性能与生产质量验证</t>
         </is>
       </c>
-      <c r="E22" s="641" t="inlineStr">
+      <c r="E22" s="653" t="inlineStr">
         <is>
           <t>调整既有测试资产，覆盖回归、性能、安全、兼容性和生产烟测。</t>
         </is>
       </c>
-      <c r="F22" s="641" t="inlineStr">
+      <c r="F22" s="653" t="inlineStr">
         <is>
           <t>API 自动化框架、测试用例库、负载模型、兼容矩阵</t>
         </is>
       </c>
-      <c r="G22" s="641" t="inlineStr">
+      <c r="G22" s="653" t="inlineStr">
         <is>
           <t>P0/P1 用例通过率 100%，核心查询峰值 500 TPS</t>
         </is>
       </c>
-      <c r="H22" s="642" t="inlineStr">
+      <c r="H22" s="654" t="inlineStr">
         <is>
           <t>SOURCE_INPUT</t>
         </is>
       </c>
-      <c r="I22" s="641" t="inlineStr"/>
+      <c r="I22" s="653" t="inlineStr"/>
     </row>
     <row r="23"/>
     <row r="24"/>
@@ -11916,16 +12144,16 @@
           <t>SOW主表 / SowStory</t>
         </is>
       </c>
-      <c r="B1" s="635" t="n"/>
-      <c r="C1" s="635" t="n"/>
-      <c r="D1" s="635" t="n"/>
-      <c r="E1" s="635" t="n"/>
-      <c r="F1" s="635" t="n"/>
-      <c r="G1" s="635" t="n"/>
-      <c r="H1" s="635" t="n"/>
-      <c r="I1" s="635" t="n"/>
-      <c r="J1" s="635" t="n"/>
-      <c r="K1" s="635" t="n"/>
+      <c r="B1" s="647" t="n"/>
+      <c r="C1" s="647" t="n"/>
+      <c r="D1" s="647" t="n"/>
+      <c r="E1" s="647" t="n"/>
+      <c r="F1" s="647" t="n"/>
+      <c r="G1" s="647" t="n"/>
+      <c r="H1" s="647" t="n"/>
+      <c r="I1" s="647" t="n"/>
+      <c r="J1" s="647" t="n"/>
+      <c r="K1" s="647" t="n"/>
       <c r="L1" s="390" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
@@ -11934,16 +12162,16 @@
           <t>Story 无类型字段；每个 Story 来源于一个 Feature；UAT 适用性显式记录；任务与人天由 Task 表汇总。</t>
         </is>
       </c>
-      <c r="B2" s="636" t="n"/>
-      <c r="C2" s="636" t="n"/>
-      <c r="D2" s="636" t="n"/>
-      <c r="E2" s="636" t="n"/>
-      <c r="F2" s="636" t="n"/>
-      <c r="G2" s="636" t="n"/>
-      <c r="H2" s="636" t="n"/>
-      <c r="I2" s="636" t="n"/>
-      <c r="J2" s="636" t="n"/>
-      <c r="K2" s="636" t="n"/>
+      <c r="B2" s="648" t="n"/>
+      <c r="C2" s="648" t="n"/>
+      <c r="D2" s="648" t="n"/>
+      <c r="E2" s="648" t="n"/>
+      <c r="F2" s="648" t="n"/>
+      <c r="G2" s="648" t="n"/>
+      <c r="H2" s="648" t="n"/>
+      <c r="I2" s="648" t="n"/>
+      <c r="J2" s="648" t="n"/>
+      <c r="K2" s="648" t="n"/>
       <c r="L2" s="400" t="n"/>
     </row>
     <row r="3" ht="9" customHeight="1"/>
@@ -12005,1151 +12233,1151 @@
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="641" t="inlineStr">
+      <c r="A5" s="653" t="inlineStr">
         <is>
           <t>story-customer-profile</t>
         </is>
       </c>
-      <c r="B5" s="641" t="inlineStr">
+      <c r="B5" s="653" t="inlineStr">
         <is>
           <t>创建并查看客户档案</t>
         </is>
       </c>
-      <c r="C5" s="641" t="inlineStr">
+      <c r="C5" s="653" t="inlineStr">
         <is>
           <t>feature-customer-profile</t>
         </is>
       </c>
-      <c r="D5" s="642" t="inlineStr">
+      <c r="D5" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E5" s="643">
+      <c r="E5" s="655">
         <f>IF(C5="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C5,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F5" s="643">
+      <c r="F5" s="655">
         <f>IF(C5="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C5,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G5" s="643">
+      <c r="G5" s="655">
         <f>IF(A5="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A5,"")),""))</f>
         <v/>
       </c>
-      <c r="H5" s="644">
+      <c r="H5" s="656">
         <f>IF(A5="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A5,"")),""))</f>
         <v/>
       </c>
-      <c r="I5" s="645">
+      <c r="I5" s="657">
         <f>IF(A5="","",CEILING(SUMIF(TaskTable[Story ID],A5,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J5" s="643">
+      <c r="J5" s="655">
         <f>IF(A5="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A5&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K5" s="646">
+      <c r="K5" s="658">
         <f>IF(A5="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A5&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="641" t="inlineStr">
+      <c r="A6" s="653" t="inlineStr">
         <is>
           <t>story-profile-api</t>
         </is>
       </c>
-      <c r="B6" s="641" t="inlineStr">
+      <c r="B6" s="653" t="inlineStr">
         <is>
           <t>提供客户档案操作</t>
         </is>
       </c>
-      <c r="C6" s="641" t="inlineStr">
+      <c r="C6" s="653" t="inlineStr">
         <is>
           <t>feature-profile-api</t>
         </is>
       </c>
-      <c r="D6" s="642" t="inlineStr">
+      <c r="D6" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E6" s="643">
+      <c r="E6" s="655">
         <f>IF(C6="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C6,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F6" s="643">
+      <c r="F6" s="655">
         <f>IF(C6="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C6,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G6" s="643">
+      <c r="G6" s="655">
         <f>IF(A6="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A6,"")),""))</f>
         <v/>
       </c>
-      <c r="H6" s="644">
+      <c r="H6" s="656">
         <f>IF(A6="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A6,"")),""))</f>
         <v/>
       </c>
-      <c r="I6" s="645">
+      <c r="I6" s="657">
         <f>IF(A6="","",CEILING(SUMIF(TaskTable[Story ID],A6,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J6" s="643">
+      <c r="J6" s="655">
         <f>IF(A6="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A6&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K6" s="646">
+      <c r="K6" s="658">
         <f>IF(A6="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A6&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="641" t="inlineStr">
+      <c r="A7" s="653" t="inlineStr">
         <is>
           <t>story-profile-integration</t>
         </is>
       </c>
-      <c r="B7" s="641" t="inlineStr">
+      <c r="B7" s="653" t="inlineStr">
         <is>
           <t>集成会员主数据查询</t>
         </is>
       </c>
-      <c r="C7" s="641" t="inlineStr">
+      <c r="C7" s="653" t="inlineStr">
         <is>
           <t>feature-profile-api</t>
         </is>
       </c>
-      <c r="D7" s="642" t="inlineStr">
+      <c r="D7" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E7" s="643">
+      <c r="E7" s="655">
         <f>IF(C7="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C7,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F7" s="643">
+      <c r="F7" s="655">
         <f>IF(C7="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C7,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G7" s="643">
+      <c r="G7" s="655">
         <f>IF(A7="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A7,"")),""))</f>
         <v/>
       </c>
-      <c r="H7" s="644">
+      <c r="H7" s="656">
         <f>IF(A7="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A7,"")),""))</f>
         <v/>
       </c>
-      <c r="I7" s="645">
+      <c r="I7" s="657">
         <f>IF(A7="","",CEILING(SUMIF(TaskTable[Story ID],A7,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J7" s="643">
+      <c r="J7" s="655">
         <f>IF(A7="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A7&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K7" s="646">
+      <c r="K7" s="658">
         <f>IF(A7="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A7&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="641" t="inlineStr">
+      <c r="A8" s="653" t="inlineStr">
         <is>
           <t>story-member-tier</t>
         </is>
       </c>
-      <c r="B8" s="641" t="inlineStr">
+      <c r="B8" s="653" t="inlineStr">
         <is>
           <t>计算并追溯会员等级</t>
         </is>
       </c>
-      <c r="C8" s="641" t="inlineStr">
+      <c r="C8" s="653" t="inlineStr">
         <is>
           <t>feature-member-tier</t>
         </is>
       </c>
-      <c r="D8" s="642" t="inlineStr">
+      <c r="D8" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E8" s="643">
+      <c r="E8" s="655">
         <f>IF(C8="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C8,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F8" s="643">
+      <c r="F8" s="655">
         <f>IF(C8="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C8,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G8" s="643">
+      <c r="G8" s="655">
         <f>IF(A8="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A8,"")),""))</f>
         <v/>
       </c>
-      <c r="H8" s="644">
+      <c r="H8" s="656">
         <f>IF(A8="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A8,"")),""))</f>
         <v/>
       </c>
-      <c r="I8" s="645">
+      <c r="I8" s="657">
         <f>IF(A8="","",CEILING(SUMIF(TaskTable[Story ID],A8,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J8" s="643">
+      <c r="J8" s="655">
         <f>IF(A8="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A8&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K8" s="646">
+      <c r="K8" s="658">
         <f>IF(A8="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A8&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="641" t="inlineStr">
+      <c r="A9" s="653" t="inlineStr">
         <is>
           <t>story-order-create</t>
         </is>
       </c>
-      <c r="B9" s="641" t="inlineStr">
+      <c r="B9" s="653" t="inlineStr">
         <is>
           <t>统一创建全渠道订单</t>
         </is>
       </c>
-      <c r="C9" s="641" t="inlineStr">
+      <c r="C9" s="653" t="inlineStr">
         <is>
           <t>feature-order-orchestration</t>
         </is>
       </c>
-      <c r="D9" s="642" t="inlineStr">
+      <c r="D9" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E9" s="643">
+      <c r="E9" s="655">
         <f>IF(C9="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C9,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F9" s="643">
+      <c r="F9" s="655">
         <f>IF(C9="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C9,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G9" s="643">
+      <c r="G9" s="655">
         <f>IF(A9="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A9,"")),""))</f>
         <v/>
       </c>
-      <c r="H9" s="644">
+      <c r="H9" s="656">
         <f>IF(A9="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A9,"")),""))</f>
         <v/>
       </c>
-      <c r="I9" s="645">
+      <c r="I9" s="657">
         <f>IF(A9="","",CEILING(SUMIF(TaskTable[Story ID],A9,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J9" s="643">
+      <c r="J9" s="655">
         <f>IF(A9="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A9&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K9" s="646">
+      <c r="K9" s="658">
         <f>IF(A9="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A9&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="641" t="inlineStr">
+      <c r="A10" s="653" t="inlineStr">
         <is>
           <t>story-order-state</t>
         </is>
       </c>
-      <c r="B10" s="641" t="inlineStr">
+      <c r="B10" s="653" t="inlineStr">
         <is>
           <t>驱动订单状态与事件</t>
         </is>
       </c>
-      <c r="C10" s="641" t="inlineStr">
+      <c r="C10" s="653" t="inlineStr">
         <is>
           <t>feature-order-orchestration</t>
         </is>
       </c>
-      <c r="D10" s="642" t="inlineStr">
+      <c r="D10" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E10" s="643">
+      <c r="E10" s="655">
         <f>IF(C10="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C10,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F10" s="643">
+      <c r="F10" s="655">
         <f>IF(C10="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C10,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G10" s="643">
+      <c r="G10" s="655">
         <f>IF(A10="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A10,"")),""))</f>
         <v/>
       </c>
-      <c r="H10" s="644">
+      <c r="H10" s="656">
         <f>IF(A10="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A10,"")),""))</f>
         <v/>
       </c>
-      <c r="I10" s="645">
+      <c r="I10" s="657">
         <f>IF(A10="","",CEILING(SUMIF(TaskTable[Story ID],A10,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J10" s="643">
+      <c r="J10" s="655">
         <f>IF(A10="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A10&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K10" s="646">
+      <c r="K10" s="658">
         <f>IF(A10="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A10&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="641" t="inlineStr">
+      <c r="A11" s="653" t="inlineStr">
         <is>
           <t>story-inventory-reservation</t>
         </is>
       </c>
-      <c r="B11" s="641" t="inlineStr">
+      <c r="B11" s="653" t="inlineStr">
         <is>
           <t>预占和释放 ERP 库存</t>
         </is>
       </c>
-      <c r="C11" s="641" t="inlineStr">
+      <c r="C11" s="653" t="inlineStr">
         <is>
           <t>feature-inventory-reservation</t>
         </is>
       </c>
-      <c r="D11" s="642" t="inlineStr">
+      <c r="D11" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E11" s="643">
+      <c r="E11" s="655">
         <f>IF(C11="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C11,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F11" s="643">
+      <c r="F11" s="655">
         <f>IF(C11="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C11,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G11" s="643">
+      <c r="G11" s="655">
         <f>IF(A11="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A11,"")),""))</f>
         <v/>
       </c>
-      <c r="H11" s="644">
+      <c r="H11" s="656">
         <f>IF(A11="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A11,"")),""))</f>
         <v/>
       </c>
-      <c r="I11" s="645">
+      <c r="I11" s="657">
         <f>IF(A11="","",CEILING(SUMIF(TaskTable[Story ID],A11,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J11" s="643">
+      <c r="J11" s="655">
         <f>IF(A11="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A11&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K11" s="646">
+      <c r="K11" s="658">
         <f>IF(A11="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A11&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="641" t="inlineStr">
+      <c r="A12" s="653" t="inlineStr">
         <is>
           <t>story-return-request</t>
         </is>
       </c>
-      <c r="B12" s="641" t="inlineStr">
+      <c r="B12" s="653" t="inlineStr">
         <is>
           <t>提交并审核退货申请</t>
         </is>
       </c>
-      <c r="C12" s="641" t="inlineStr">
+      <c r="C12" s="653" t="inlineStr">
         <is>
           <t>feature-return-refund</t>
         </is>
       </c>
-      <c r="D12" s="642" t="inlineStr">
+      <c r="D12" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E12" s="643">
+      <c r="E12" s="655">
         <f>IF(C12="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C12,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F12" s="643">
+      <c r="F12" s="655">
         <f>IF(C12="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C12,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G12" s="643">
+      <c r="G12" s="655">
         <f>IF(A12="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A12,"")),""))</f>
         <v/>
       </c>
-      <c r="H12" s="644">
+      <c r="H12" s="656">
         <f>IF(A12="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A12,"")),""))</f>
         <v/>
       </c>
-      <c r="I12" s="645">
+      <c r="I12" s="657">
         <f>IF(A12="","",CEILING(SUMIF(TaskTable[Story ID],A12,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J12" s="643">
+      <c r="J12" s="655">
         <f>IF(A12="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A12&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K12" s="646">
+      <c r="K12" s="658">
         <f>IF(A12="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A12&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="641" t="inlineStr">
+      <c r="A13" s="653" t="inlineStr">
         <is>
           <t>story-refund-payment</t>
         </is>
       </c>
-      <c r="B13" s="641" t="inlineStr">
+      <c r="B13" s="653" t="inlineStr">
         <is>
           <t>发起退款并回写结果</t>
         </is>
       </c>
-      <c r="C13" s="641" t="inlineStr">
+      <c r="C13" s="653" t="inlineStr">
         <is>
           <t>feature-return-refund</t>
         </is>
       </c>
-      <c r="D13" s="642" t="inlineStr">
+      <c r="D13" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E13" s="643">
+      <c r="E13" s="655">
         <f>IF(C13="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C13,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F13" s="643">
+      <c r="F13" s="655">
         <f>IF(C13="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C13,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G13" s="643">
+      <c r="G13" s="655">
         <f>IF(A13="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A13,"")),""))</f>
         <v/>
       </c>
-      <c r="H13" s="644">
+      <c r="H13" s="656">
         <f>IF(A13="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A13,"")),""))</f>
         <v/>
       </c>
-      <c r="I13" s="645">
+      <c r="I13" s="657">
         <f>IF(A13="","",CEILING(SUMIF(TaskTable[Story ID],A13,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J13" s="643">
+      <c r="J13" s="655">
         <f>IF(A13="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A13&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K13" s="646">
+      <c r="K13" s="658">
         <f>IF(A13="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A13&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="641" t="inlineStr">
+      <c r="A14" s="653" t="inlineStr">
         <is>
           <t>story-store-order</t>
         </is>
       </c>
-      <c r="B14" s="641" t="inlineStr">
+      <c r="B14" s="653" t="inlineStr">
         <is>
           <t>门店处理订单与交接</t>
         </is>
       </c>
-      <c r="C14" s="641" t="inlineStr">
+      <c r="C14" s="653" t="inlineStr">
         <is>
           <t>feature-store-order</t>
         </is>
       </c>
-      <c r="D14" s="642" t="inlineStr">
+      <c r="D14" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E14" s="643">
+      <c r="E14" s="655">
         <f>IF(C14="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C14,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F14" s="643">
+      <c r="F14" s="655">
         <f>IF(C14="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C14,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G14" s="643">
+      <c r="G14" s="655">
         <f>IF(A14="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A14,"")),""))</f>
         <v/>
       </c>
-      <c r="H14" s="644">
+      <c r="H14" s="656">
         <f>IF(A14="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A14,"")),""))</f>
         <v/>
       </c>
-      <c r="I14" s="645">
+      <c r="I14" s="657">
         <f>IF(A14="","",CEILING(SUMIF(TaskTable[Story ID],A14,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J14" s="643">
+      <c r="J14" s="655">
         <f>IF(A14="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A14&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K14" s="646">
+      <c r="K14" s="658">
         <f>IF(A14="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A14&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="641" t="inlineStr">
+      <c r="A15" s="653" t="inlineStr">
         <is>
           <t>story-order-visibility</t>
         </is>
       </c>
-      <c r="B15" s="641" t="inlineStr">
+      <c r="B15" s="653" t="inlineStr">
         <is>
           <t>查看统一履约轨迹</t>
         </is>
       </c>
-      <c r="C15" s="641" t="inlineStr">
+      <c r="C15" s="653" t="inlineStr">
         <is>
           <t>feature-order-visibility</t>
         </is>
       </c>
-      <c r="D15" s="642" t="inlineStr">
+      <c r="D15" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E15" s="643">
+      <c r="E15" s="655">
         <f>IF(C15="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C15,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F15" s="643">
+      <c r="F15" s="655">
         <f>IF(C15="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C15,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G15" s="643">
+      <c r="G15" s="655">
         <f>IF(A15="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A15,"")),""))</f>
         <v/>
       </c>
-      <c r="H15" s="644">
+      <c r="H15" s="656">
         <f>IF(A15="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A15,"")),""))</f>
         <v/>
       </c>
-      <c r="I15" s="645">
+      <c r="I15" s="657">
         <f>IF(A15="","",CEILING(SUMIF(TaskTable[Story ID],A15,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J15" s="643">
+      <c r="J15" s="655">
         <f>IF(A15="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A15&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K15" s="646">
+      <c r="K15" s="658">
         <f>IF(A15="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A15&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="641" t="inlineStr">
+      <c r="A16" s="653" t="inlineStr">
         <is>
           <t>story-payment-reconciliation</t>
         </is>
       </c>
-      <c r="B16" s="641" t="inlineStr">
+      <c r="B16" s="653" t="inlineStr">
         <is>
           <t>执行支付退款日结对账</t>
         </is>
       </c>
-      <c r="C16" s="641" t="inlineStr">
+      <c r="C16" s="653" t="inlineStr">
         <is>
           <t>feature-payment-reconciliation</t>
         </is>
       </c>
-      <c r="D16" s="642" t="inlineStr">
+      <c r="D16" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E16" s="643">
+      <c r="E16" s="655">
         <f>IF(C16="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C16,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F16" s="643">
+      <c r="F16" s="655">
         <f>IF(C16="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C16,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G16" s="643">
+      <c r="G16" s="655">
         <f>IF(A16="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A16,"")),""))</f>
         <v/>
       </c>
-      <c r="H16" s="644">
+      <c r="H16" s="656">
         <f>IF(A16="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A16,"")),""))</f>
         <v/>
       </c>
-      <c r="I16" s="645">
+      <c r="I16" s="657">
         <f>IF(A16="","",CEILING(SUMIF(TaskTable[Story ID],A16,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J16" s="643">
+      <c r="J16" s="655">
         <f>IF(A16="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A16&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K16" s="646">
+      <c r="K16" s="658">
         <f>IF(A16="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A16&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="641" t="inlineStr">
+      <c r="A17" s="653" t="inlineStr">
         <is>
           <t>story-einvoice</t>
         </is>
       </c>
-      <c r="B17" s="641" t="inlineStr">
+      <c r="B17" s="653" t="inlineStr">
         <is>
           <t>申请并追踪电子发票</t>
         </is>
       </c>
-      <c r="C17" s="641" t="inlineStr">
+      <c r="C17" s="653" t="inlineStr">
         <is>
           <t>feature-einvoice</t>
         </is>
       </c>
-      <c r="D17" s="642" t="inlineStr">
+      <c r="D17" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E17" s="643">
+      <c r="E17" s="655">
         <f>IF(C17="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C17,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F17" s="643">
+      <c r="F17" s="655">
         <f>IF(C17="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C17,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G17" s="643">
+      <c r="G17" s="655">
         <f>IF(A17="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A17,"")),""))</f>
         <v/>
       </c>
-      <c r="H17" s="644">
+      <c r="H17" s="656">
         <f>IF(A17="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A17,"")),""))</f>
         <v/>
       </c>
-      <c r="I17" s="645">
+      <c r="I17" s="657">
         <f>IF(A17="","",CEILING(SUMIF(TaskTable[Story ID],A17,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J17" s="643">
+      <c r="J17" s="655">
         <f>IF(A17="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A17&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K17" s="646">
+      <c r="K17" s="658">
         <f>IF(A17="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A17&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="641" t="inlineStr">
+      <c r="A18" s="653" t="inlineStr">
         <is>
           <t>story-finance-report</t>
         </is>
       </c>
-      <c r="B18" s="641" t="inlineStr">
+      <c r="B18" s="653" t="inlineStr">
         <is>
           <t>查看财务经营日报</t>
         </is>
       </c>
-      <c r="C18" s="641" t="inlineStr">
+      <c r="C18" s="653" t="inlineStr">
         <is>
           <t>feature-finance-report</t>
         </is>
       </c>
-      <c r="D18" s="642" t="inlineStr">
+      <c r="D18" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E18" s="643">
+      <c r="E18" s="655">
         <f>IF(C18="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C18,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F18" s="643">
+      <c r="F18" s="655">
         <f>IF(C18="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C18,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G18" s="643">
+      <c r="G18" s="655">
         <f>IF(A18="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A18,"")),""))</f>
         <v/>
       </c>
-      <c r="H18" s="644">
+      <c r="H18" s="656">
         <f>IF(A18="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A18,"")),""))</f>
         <v/>
       </c>
-      <c r="I18" s="645">
+      <c r="I18" s="657">
         <f>IF(A18="","",CEILING(SUMIF(TaskTable[Story ID],A18,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J18" s="643">
+      <c r="J18" s="655">
         <f>IF(A18="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A18&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K18" s="646">
+      <c r="K18" s="658">
         <f>IF(A18="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A18&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="641" t="inlineStr">
+      <c r="A19" s="653" t="inlineStr">
         <is>
           <t>story-production-preparation</t>
         </is>
       </c>
-      <c r="B19" s="641" t="inlineStr">
+      <c r="B19" s="653" t="inlineStr">
         <is>
           <t>准备生产环境和发布流水线</t>
         </is>
       </c>
-      <c r="C19" s="641" t="inlineStr">
+      <c r="C19" s="653" t="inlineStr">
         <is>
           <t>feature-production-scope</t>
         </is>
       </c>
-      <c r="D19" s="642" t="inlineStr">
+      <c r="D19" s="654" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E19" s="643">
+      <c r="E19" s="655">
         <f>IF(C19="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C19,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F19" s="643">
+      <c r="F19" s="655">
         <f>IF(C19="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C19,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G19" s="643">
+      <c r="G19" s="655">
         <f>IF(A19="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A19,"")),""))</f>
         <v/>
       </c>
-      <c r="H19" s="644">
+      <c r="H19" s="656">
         <f>IF(A19="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A19,"")),""))</f>
         <v/>
       </c>
-      <c r="I19" s="645">
+      <c r="I19" s="657">
         <f>IF(A19="","",CEILING(SUMIF(TaskTable[Story ID],A19,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J19" s="643">
+      <c r="J19" s="655">
         <f>IF(A19="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A19&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K19" s="646">
+      <c r="K19" s="658">
         <f>IF(A19="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A19&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="641" t="inlineStr">
+      <c r="A20" s="653" t="inlineStr">
         <is>
           <t>story-production-cutover</t>
         </is>
       </c>
-      <c r="B20" s="641" t="inlineStr">
+      <c r="B20" s="653" t="inlineStr">
         <is>
           <t>执行生产切换与回滚演练</t>
         </is>
       </c>
-      <c r="C20" s="641" t="inlineStr">
+      <c r="C20" s="653" t="inlineStr">
         <is>
           <t>feature-production-scope</t>
         </is>
       </c>
-      <c r="D20" s="642" t="inlineStr">
+      <c r="D20" s="654" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E20" s="643">
+      <c r="E20" s="655">
         <f>IF(C20="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C20,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F20" s="643">
+      <c r="F20" s="655">
         <f>IF(C20="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C20,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G20" s="643">
+      <c r="G20" s="655">
         <f>IF(A20="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A20,"")),""))</f>
         <v/>
       </c>
-      <c r="H20" s="644">
+      <c r="H20" s="656">
         <f>IF(A20="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A20,"")),""))</f>
         <v/>
       </c>
-      <c r="I20" s="645">
+      <c r="I20" s="657">
         <f>IF(A20="","",CEILING(SUMIF(TaskTable[Story ID],A20,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J20" s="643">
+      <c r="J20" s="655">
         <f>IF(A20="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A20&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K20" s="646">
+      <c r="K20" s="658">
         <f>IF(A20="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A20&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="641" t="inlineStr">
+      <c r="A21" s="653" t="inlineStr">
         <is>
           <t>story-production-validation</t>
         </is>
       </c>
-      <c r="B21" s="641" t="inlineStr">
+      <c r="B21" s="653" t="inlineStr">
         <is>
           <t>完成生产烟测与业务确认</t>
         </is>
       </c>
-      <c r="C21" s="641" t="inlineStr">
+      <c r="C21" s="653" t="inlineStr">
         <is>
           <t>feature-production-scope</t>
         </is>
       </c>
-      <c r="D21" s="642" t="inlineStr">
+      <c r="D21" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E21" s="643">
+      <c r="E21" s="655">
         <f>IF(C21="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C21,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F21" s="643">
+      <c r="F21" s="655">
         <f>IF(C21="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C21,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G21" s="643">
+      <c r="G21" s="655">
         <f>IF(A21="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A21,"")),""))</f>
         <v/>
       </c>
-      <c r="H21" s="644">
+      <c r="H21" s="656">
         <f>IF(A21="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A21,"")),""))</f>
         <v/>
       </c>
-      <c r="I21" s="645">
+      <c r="I21" s="657">
         <f>IF(A21="","",CEILING(SUMIF(TaskTable[Story ID],A21,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J21" s="643">
+      <c r="J21" s="655">
         <f>IF(A21="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A21&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K21" s="646">
+      <c r="K21" s="658">
         <f>IF(A21="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A21&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="641" t="inlineStr">
+      <c r="A22" s="653" t="inlineStr">
         <is>
           <t>story-data-migration</t>
         </is>
       </c>
-      <c r="B22" s="641" t="inlineStr">
+      <c r="B22" s="653" t="inlineStr">
         <is>
           <t>迁移会员与历史订单数据</t>
         </is>
       </c>
-      <c r="C22" s="641" t="inlineStr">
+      <c r="C22" s="653" t="inlineStr">
         <is>
           <t>feature-data-migration</t>
         </is>
       </c>
-      <c r="D22" s="642" t="inlineStr">
+      <c r="D22" s="654" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E22" s="643">
+      <c r="E22" s="655">
         <f>IF(C22="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C22,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F22" s="643">
+      <c r="F22" s="655">
         <f>IF(C22="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C22,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G22" s="643">
+      <c r="G22" s="655">
         <f>IF(A22="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A22,"")),""))</f>
         <v/>
       </c>
-      <c r="H22" s="644">
+      <c r="H22" s="656">
         <f>IF(A22="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A22,"")),""))</f>
         <v/>
       </c>
-      <c r="I22" s="645">
+      <c r="I22" s="657">
         <f>IF(A22="","",CEILING(SUMIF(TaskTable[Story ID],A22,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J22" s="643">
+      <c r="J22" s="655">
         <f>IF(A22="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A22&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K22" s="646">
+      <c r="K22" s="658">
         <f>IF(A22="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A22&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="641" t="inlineStr">
+      <c r="A23" s="653" t="inlineStr">
         <is>
           <t>story-observability</t>
         </is>
       </c>
-      <c r="B23" s="641" t="inlineStr">
+      <c r="B23" s="653" t="inlineStr">
         <is>
           <t>监控核心交易与财务作业</t>
         </is>
       </c>
-      <c r="C23" s="641" t="inlineStr">
+      <c r="C23" s="653" t="inlineStr">
         <is>
           <t>feature-observability-ops</t>
         </is>
       </c>
-      <c r="D23" s="642" t="inlineStr">
+      <c r="D23" s="654" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E23" s="643">
+      <c r="E23" s="655">
         <f>IF(C23="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C23,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F23" s="643">
+      <c r="F23" s="655">
         <f>IF(C23="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C23,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G23" s="643">
+      <c r="G23" s="655">
         <f>IF(A23="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A23,"")),""))</f>
         <v/>
       </c>
-      <c r="H23" s="644">
+      <c r="H23" s="656">
         <f>IF(A23="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A23,"")),""))</f>
         <v/>
       </c>
-      <c r="I23" s="645">
+      <c r="I23" s="657">
         <f>IF(A23="","",CEILING(SUMIF(TaskTable[Story ID],A23,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J23" s="643">
+      <c r="J23" s="655">
         <f>IF(A23="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A23&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K23" s="646">
+      <c r="K23" s="658">
         <f>IF(A23="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A23&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="641" t="inlineStr">
+      <c r="A24" s="653" t="inlineStr">
         <is>
           <t>story-ops-handover</t>
         </is>
       </c>
-      <c r="B24" s="641" t="inlineStr">
+      <c r="B24" s="653" t="inlineStr">
         <is>
           <t>完成运维交接与演练</t>
         </is>
       </c>
-      <c r="C24" s="641" t="inlineStr">
+      <c r="C24" s="653" t="inlineStr">
         <is>
           <t>feature-observability-ops</t>
         </is>
       </c>
-      <c r="D24" s="642" t="inlineStr">
+      <c r="D24" s="654" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E24" s="643">
+      <c r="E24" s="655">
         <f>IF(C24="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C24,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F24" s="643">
+      <c r="F24" s="655">
         <f>IF(C24="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C24,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G24" s="643">
+      <c r="G24" s="655">
         <f>IF(A24="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A24,"")),""))</f>
         <v/>
       </c>
-      <c r="H24" s="644">
+      <c r="H24" s="656">
         <f>IF(A24="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A24,"")),""))</f>
         <v/>
       </c>
-      <c r="I24" s="645">
+      <c r="I24" s="657">
         <f>IF(A24="","",CEILING(SUMIF(TaskTable[Story ID],A24,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J24" s="643">
+      <c r="J24" s="655">
         <f>IF(A24="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A24&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K24" s="646">
+      <c r="K24" s="658">
         <f>IF(A24="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A24&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="641" t="inlineStr">
+      <c r="A25" s="653" t="inlineStr">
         <is>
           <t>story-user-training</t>
         </is>
       </c>
-      <c r="B25" s="641" t="inlineStr">
+      <c r="B25" s="653" t="inlineStr">
         <is>
           <t>培训门店、客服和财务用户</t>
         </is>
       </c>
-      <c r="C25" s="641" t="inlineStr">
+      <c r="C25" s="653" t="inlineStr">
         <is>
           <t>feature-observability-ops</t>
         </is>
       </c>
-      <c r="D25" s="642" t="inlineStr">
+      <c r="D25" s="654" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E25" s="643">
+      <c r="E25" s="655">
         <f>IF(C25="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C25,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F25" s="643">
+      <c r="F25" s="655">
         <f>IF(C25="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C25,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G25" s="643">
+      <c r="G25" s="655">
         <f>IF(A25="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A25,"")),""))</f>
         <v/>
       </c>
-      <c r="H25" s="644">
+      <c r="H25" s="656">
         <f>IF(A25="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A25,"")),""))</f>
         <v/>
       </c>
-      <c r="I25" s="645">
+      <c r="I25" s="657">
         <f>IF(A25="","",CEILING(SUMIF(TaskTable[Story ID],A25,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J25" s="643">
+      <c r="J25" s="655">
         <f>IF(A25="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A25&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K25" s="646">
+      <c r="K25" s="658">
         <f>IF(A25="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A25&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="641" t="inlineStr">
+      <c r="A26" s="653" t="inlineStr">
         <is>
           <t>story-test-automation</t>
         </is>
       </c>
-      <c r="B26" s="641" t="inlineStr">
+      <c r="B26" s="653" t="inlineStr">
         <is>
           <t>扩展自动化与性能验证</t>
         </is>
       </c>
-      <c r="C26" s="641" t="inlineStr">
+      <c r="C26" s="653" t="inlineStr">
         <is>
           <t>feature-test-quality</t>
         </is>
       </c>
-      <c r="D26" s="642" t="inlineStr">
+      <c r="D26" s="654" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E26" s="643">
+      <c r="E26" s="655">
         <f>IF(C26="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C26,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F26" s="643">
+      <c r="F26" s="655">
         <f>IF(C26="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C26,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G26" s="643">
+      <c r="G26" s="655">
         <f>IF(A26="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A26,"")),""))</f>
         <v/>
       </c>
-      <c r="H26" s="644">
+      <c r="H26" s="656">
         <f>IF(A26="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A26,"")),""))</f>
         <v/>
       </c>
-      <c r="I26" s="645">
+      <c r="I26" s="657">
         <f>IF(A26="","",CEILING(SUMIF(TaskTable[Story ID],A26,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J26" s="643">
+      <c r="J26" s="655">
         <f>IF(A26="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A26&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K26" s="646">
+      <c r="K26" s="658">
         <f>IF(A26="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A26&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="641" t="inlineStr">
+      <c r="A27" s="653" t="inlineStr">
         <is>
           <t>story-test-non-uat</t>
         </is>
       </c>
-      <c r="B27" s="641" t="inlineStr">
+      <c r="B27" s="653" t="inlineStr">
         <is>
           <t>执行兼容性与工程回归</t>
         </is>
       </c>
-      <c r="C27" s="641" t="inlineStr">
+      <c r="C27" s="653" t="inlineStr">
         <is>
           <t>feature-test-quality</t>
         </is>
       </c>
-      <c r="D27" s="642" t="inlineStr">
+      <c r="D27" s="654" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E27" s="643">
+      <c r="E27" s="655">
         <f>IF(C27="","",IFERROR(INDEX(EpicTable[需求名称],MATCH(INDEX(FeatureTable[Epic ID],MATCH(C27,FeatureTable[Feature ID],0)),EpicTable[Epic ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="F27" s="643">
+      <c r="F27" s="655">
         <f>IF(C27="","",IFERROR(INDEX(FeatureTable[子需求名称],MATCH(C27,FeatureTable[Feature ID],0)),"来源未匹配"))</f>
         <v/>
       </c>
-      <c r="G27" s="643">
+      <c r="G27" s="655">
         <f>IF(A27="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[顺序]&amp;"）"&amp;AcceptanceCriterionTable[验收结果],AcceptanceCriterionTable[Story ID]=A27,"")),""))</f>
         <v/>
       </c>
-      <c r="H27" s="644">
+      <c r="H27" s="656">
         <f>IF(A27="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务说明],TaskTable[Story ID]=A27,"")),""))</f>
         <v/>
       </c>
-      <c r="I27" s="645">
+      <c r="I27" s="657">
         <f>IF(A27="","",CEILING(SUMIF(TaskTable[Story ID],A27,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="J27" s="643">
+      <c r="J27" s="655">
         <f>IF(A27="","",IFERROR(_xlfn.TEXTJOIN("、",TRUE,_xlfn._xlws.FILTER(AssumptionRiskTable[假设ID],ISNUMBER(SEARCH("、"&amp;A27&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、")),"")),""))</f>
         <v/>
       </c>
-      <c r="K27" s="646">
+      <c r="K27" s="658">
         <f>IF(A27="","",IF(SUMPRODUCT(ISNUMBER(SEARCH("、"&amp;A27&amp;"、","、"&amp;AssumptionRiskTable[关联 Story ID]&amp;"、"))*(AssumptionRiskTable[状态]="待确认"))&gt;0,"待确认","已明确"))</f>
         <v/>
       </c>
@@ -13236,9 +13464,9 @@
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <conditionalFormatting sqref="L5:L14">
-    <cfRule type="containsText" priority="1" operator="containsText" dxfId="19" text="已明确"/>
-    <cfRule type="containsText" priority="2" operator="containsText" dxfId="20" text="待确认"/>
+  <conditionalFormatting sqref="K5:K104">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="35" text="已明确"/>
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="36" text="待确认"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="C5:C104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -13276,9 +13504,9 @@
           <t>验收条件（AcceptanceCriterion）</t>
         </is>
       </c>
-      <c r="B1" s="635" t="n"/>
-      <c r="C1" s="635" t="n"/>
-      <c r="D1" s="635" t="n"/>
+      <c r="B1" s="647" t="n"/>
+      <c r="C1" s="647" t="n"/>
+      <c r="D1" s="647" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="400" t="inlineStr">
@@ -13286,9 +13514,9 @@
           <t>事实源：每行一条可独立核验的 AC；通过 Story ID 归属一个 Story；SOW 主表只读派生汇总</t>
         </is>
       </c>
-      <c r="B2" s="636" t="n"/>
-      <c r="C2" s="636" t="n"/>
-      <c r="D2" s="636" t="n"/>
+      <c r="B2" s="648" t="n"/>
+      <c r="C2" s="648" t="n"/>
+      <c r="D2" s="648" t="n"/>
     </row>
     <row r="3" ht="9" customHeight="1"/>
     <row r="4" ht="38" customHeight="1">
@@ -13314,620 +13542,620 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="641" t="inlineStr">
+      <c r="A5" s="653" t="inlineStr">
         <is>
           <t>ac-profile-visible</t>
         </is>
       </c>
-      <c r="B5" s="641" t="inlineStr">
+      <c r="B5" s="653" t="inlineStr">
         <is>
           <t>story-customer-profile</t>
         </is>
       </c>
-      <c r="C5" s="647" t="n">
+      <c r="C5" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="641" t="inlineStr">
+      <c r="D5" s="653" t="inlineStr">
         <is>
           <t>用户保存档案后可以查看授权范围内的最新字段。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="641" t="inlineStr">
+      <c r="A6" s="653" t="inlineStr">
         <is>
           <t>ac-profile-audit</t>
         </is>
       </c>
-      <c r="B6" s="641" t="inlineStr">
+      <c r="B6" s="653" t="inlineStr">
         <is>
           <t>story-customer-profile</t>
         </is>
       </c>
-      <c r="C6" s="647" t="n">
+      <c r="C6" s="659" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="641" t="inlineStr">
+      <c r="D6" s="653" t="inlineStr">
         <is>
           <t>档案变更记录包含操作者、时间和变更字段。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="641" t="inlineStr">
+      <c r="A7" s="653" t="inlineStr">
         <is>
           <t>ac-profile-api</t>
         </is>
       </c>
-      <c r="B7" s="641" t="inlineStr">
+      <c r="B7" s="653" t="inlineStr">
         <is>
           <t>story-profile-api</t>
         </is>
       </c>
-      <c r="C7" s="647" t="n">
+      <c r="C7" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="641" t="inlineStr">
+      <c r="D7" s="653" t="inlineStr">
         <is>
           <t>渠道可以通过已发布 API 创建、维护和检索客户档案。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="641" t="inlineStr">
+      <c r="A8" s="653" t="inlineStr">
         <is>
           <t>ac-profile-api-security</t>
         </is>
       </c>
-      <c r="B8" s="641" t="inlineStr">
+      <c r="B8" s="653" t="inlineStr">
         <is>
           <t>story-profile-api</t>
         </is>
       </c>
-      <c r="C8" s="647" t="n">
+      <c r="C8" s="659" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="641" t="inlineStr">
+      <c r="D8" s="653" t="inlineStr">
         <is>
           <t>未授权角色无法读取敏感字段且访问留痕。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="641" t="inlineStr">
+      <c r="A9" s="653" t="inlineStr">
         <is>
           <t>ac-profile-integration</t>
         </is>
       </c>
-      <c r="B9" s="641" t="inlineStr">
+      <c r="B9" s="653" t="inlineStr">
         <is>
           <t>story-profile-integration</t>
         </is>
       </c>
-      <c r="C9" s="647" t="n">
+      <c r="C9" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="641" t="inlineStr">
+      <c r="D9" s="653" t="inlineStr">
         <is>
           <t>星云会员门户可以通过内部接口检索统一会员号和档案。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="641" t="inlineStr">
+      <c r="A10" s="653" t="inlineStr">
         <is>
           <t>ac-member-tier</t>
         </is>
       </c>
-      <c r="B10" s="641" t="inlineStr">
+      <c r="B10" s="653" t="inlineStr">
         <is>
           <t>story-member-tier</t>
         </is>
       </c>
-      <c r="C10" s="647" t="n">
+      <c r="C10" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="641" t="inlineStr">
+      <c r="D10" s="653" t="inlineStr">
         <is>
           <t>会员等级按生效规则计算且可以追溯规则版本。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="641" t="inlineStr">
+      <c r="A11" s="653" t="inlineStr">
         <is>
           <t>ac-member-tier-history</t>
         </is>
       </c>
-      <c r="B11" s="641" t="inlineStr">
+      <c r="B11" s="653" t="inlineStr">
         <is>
           <t>story-member-tier</t>
         </is>
       </c>
-      <c r="C11" s="647" t="n">
+      <c r="C11" s="659" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="641" t="inlineStr">
+      <c r="D11" s="653" t="inlineStr">
         <is>
           <t>等级调整后保留原等级、生效时间和调整原因。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="641" t="inlineStr">
+      <c r="A12" s="653" t="inlineStr">
         <is>
           <t>ac-order-create</t>
         </is>
       </c>
-      <c r="B12" s="641" t="inlineStr">
+      <c r="B12" s="653" t="inlineStr">
         <is>
           <t>story-order-create</t>
         </is>
       </c>
-      <c r="C12" s="647" t="n">
+      <c r="C12" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="641" t="inlineStr">
+      <c r="D12" s="653" t="inlineStr">
         <is>
           <t>门店和线上渠道通过相同校验规则创建订单。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="641" t="inlineStr">
+      <c r="A13" s="653" t="inlineStr">
         <is>
           <t>ac-order-idempotency</t>
         </is>
       </c>
-      <c r="B13" s="641" t="inlineStr">
+      <c r="B13" s="653" t="inlineStr">
         <is>
           <t>story-order-create</t>
         </is>
       </c>
-      <c r="C13" s="647" t="n">
+      <c r="C13" s="659" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="641" t="inlineStr">
+      <c r="D13" s="653" t="inlineStr">
         <is>
           <t>相同幂等键的重复请求不产生重复订单。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="641" t="inlineStr">
+      <c r="A14" s="653" t="inlineStr">
         <is>
           <t>ac-order-state</t>
         </is>
       </c>
-      <c r="B14" s="641" t="inlineStr">
+      <c r="B14" s="653" t="inlineStr">
         <is>
           <t>story-order-state</t>
         </is>
       </c>
-      <c r="C14" s="647" t="n">
+      <c r="C14" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="641" t="inlineStr">
+      <c r="D14" s="653" t="inlineStr">
         <is>
           <t>合法命令驱动状态变化并记录来源、时间和事件编号。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="641" t="inlineStr">
+      <c r="A15" s="653" t="inlineStr">
         <is>
           <t>ac-inventory-reservation</t>
         </is>
       </c>
-      <c r="B15" s="641" t="inlineStr">
+      <c r="B15" s="653" t="inlineStr">
         <is>
           <t>story-inventory-reservation</t>
         </is>
       </c>
-      <c r="C15" s="647" t="n">
+      <c r="C15" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="641" t="inlineStr">
+      <c r="D15" s="653" t="inlineStr">
         <is>
           <t>订单确认和取消分别完成库存预占与释放。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="641" t="inlineStr">
+      <c r="A16" s="653" t="inlineStr">
         <is>
           <t>ac-inventory-retry</t>
         </is>
       </c>
-      <c r="B16" s="641" t="inlineStr">
+      <c r="B16" s="653" t="inlineStr">
         <is>
           <t>story-inventory-reservation</t>
         </is>
       </c>
-      <c r="C16" s="647" t="n">
+      <c r="C16" s="659" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="641" t="inlineStr">
+      <c r="D16" s="653" t="inlineStr">
         <is>
           <t>ERP 超时重试不会产生重复预占。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="641" t="inlineStr">
+      <c r="A17" s="653" t="inlineStr">
         <is>
           <t>ac-return-request</t>
         </is>
       </c>
-      <c r="B17" s="641" t="inlineStr">
+      <c r="B17" s="653" t="inlineStr">
         <is>
           <t>story-return-request</t>
         </is>
       </c>
-      <c r="C17" s="647" t="n">
+      <c r="C17" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="641" t="inlineStr">
+      <c r="D17" s="653" t="inlineStr">
         <is>
           <t>系统拒绝超过可退数量的申请并记录审核结果。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="641" t="inlineStr">
+      <c r="A18" s="653" t="inlineStr">
         <is>
           <t>ac-refund-payment</t>
         </is>
       </c>
-      <c r="B18" s="641" t="inlineStr">
+      <c r="B18" s="653" t="inlineStr">
         <is>
           <t>story-refund-payment</t>
         </is>
       </c>
-      <c r="C18" s="647" t="n">
+      <c r="C18" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="641" t="inlineStr">
+      <c r="D18" s="653" t="inlineStr">
         <is>
           <t>退款结果回写订单且同一退货单不重复退款。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="641" t="inlineStr">
+      <c r="A19" s="653" t="inlineStr">
         <is>
           <t>ac-store-order</t>
         </is>
       </c>
-      <c r="B19" s="641" t="inlineStr">
+      <c r="B19" s="653" t="inlineStr">
         <is>
           <t>story-store-order</t>
         </is>
       </c>
-      <c r="C19" s="647" t="n">
+      <c r="C19" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="641" t="inlineStr">
+      <c r="D19" s="653" t="inlineStr">
         <is>
           <t>授权门店可以处理本店订单并完成交接记录。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="641" t="inlineStr">
+      <c r="A20" s="653" t="inlineStr">
         <is>
           <t>ac-order-visibility</t>
         </is>
       </c>
-      <c r="B20" s="641" t="inlineStr">
+      <c r="B20" s="653" t="inlineStr">
         <is>
           <t>story-order-visibility</t>
         </is>
       </c>
-      <c r="C20" s="647" t="n">
+      <c r="C20" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="641" t="inlineStr">
+      <c r="D20" s="653" t="inlineStr">
         <is>
           <t>顾客和客服看到一致的履约节点与异常原因。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="641" t="inlineStr">
+      <c r="A21" s="653" t="inlineStr">
         <is>
           <t>ac-payment-reconciliation</t>
         </is>
       </c>
-      <c r="B21" s="641" t="inlineStr">
+      <c r="B21" s="653" t="inlineStr">
         <is>
           <t>story-payment-reconciliation</t>
         </is>
       </c>
-      <c r="C21" s="647" t="n">
+      <c r="C21" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="641" t="inlineStr">
+      <c r="D21" s="653" t="inlineStr">
         <is>
           <t>前一自然日交易在 07:00 前完成对账并标识差异。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="641" t="inlineStr">
+      <c r="A22" s="653" t="inlineStr">
         <is>
           <t>ac-payment-trace</t>
         </is>
       </c>
-      <c r="B22" s="641" t="inlineStr">
+      <c r="B22" s="653" t="inlineStr">
         <is>
           <t>story-payment-reconciliation</t>
         </is>
       </c>
-      <c r="C22" s="647" t="n">
+      <c r="C22" s="659" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="641" t="inlineStr">
+      <c r="D22" s="653" t="inlineStr">
         <is>
           <t>每个差异项可以追溯到订单、支付交易和退款记录。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="641" t="inlineStr">
+      <c r="A23" s="653" t="inlineStr">
         <is>
           <t>ac-einvoice</t>
         </is>
       </c>
-      <c r="B23" s="641" t="inlineStr">
+      <c r="B23" s="653" t="inlineStr">
         <is>
           <t>story-einvoice</t>
         </is>
       </c>
-      <c r="C23" s="647" t="n">
+      <c r="C23" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="641" t="inlineStr">
+      <c r="D23" s="653" t="inlineStr">
         <is>
           <t>开票成功后保存发票号码和下载地址，失败时保存失败码。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="641" t="inlineStr">
+      <c r="A24" s="653" t="inlineStr">
         <is>
           <t>ac-einvoice-idempotency</t>
         </is>
       </c>
-      <c r="B24" s="641" t="inlineStr">
+      <c r="B24" s="653" t="inlineStr">
         <is>
           <t>story-einvoice</t>
         </is>
       </c>
-      <c r="C24" s="647" t="n">
+      <c r="C24" s="659" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="641" t="inlineStr">
+      <c r="D24" s="653" t="inlineStr">
         <is>
           <t>重复提交相同开票申请不会重复开票。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="641" t="inlineStr">
+      <c r="A25" s="653" t="inlineStr">
         <is>
           <t>ac-finance-report</t>
         </is>
       </c>
-      <c r="B25" s="641" t="inlineStr">
+      <c r="B25" s="653" t="inlineStr">
         <is>
           <t>story-finance-report</t>
         </is>
       </c>
-      <c r="C25" s="647" t="n">
+      <c r="C25" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="641" t="inlineStr">
+      <c r="D25" s="653" t="inlineStr">
         <is>
           <t>财务可按日期、区域和渠道查看已定义经营指标。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="641" t="inlineStr">
+      <c r="A26" s="653" t="inlineStr">
         <is>
           <t>ac-finance-drilldown</t>
         </is>
       </c>
-      <c r="B26" s="641" t="inlineStr">
+      <c r="B26" s="653" t="inlineStr">
         <is>
           <t>story-finance-report</t>
         </is>
       </c>
-      <c r="C26" s="647" t="n">
+      <c r="C26" s="659" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="641" t="inlineStr">
+      <c r="D26" s="653" t="inlineStr">
         <is>
           <t>报表金额可下钻到构成订单和对账状态。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="641" t="inlineStr">
+      <c r="A27" s="653" t="inlineStr">
         <is>
           <t>ac-production-preparation</t>
         </is>
       </c>
-      <c r="B27" s="641" t="inlineStr">
+      <c r="B27" s="653" t="inlineStr">
         <is>
           <t>story-production-preparation</t>
         </is>
       </c>
-      <c r="C27" s="647" t="n">
+      <c r="C27" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="641" t="inlineStr">
+      <c r="D27" s="653" t="inlineStr">
         <is>
           <t>生产参数、权限、制品和功能开关通过准备检查。</t>
         </is>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="641" t="inlineStr">
+      <c r="A28" s="653" t="inlineStr">
         <is>
           <t>ac-production-cutover</t>
         </is>
       </c>
-      <c r="B28" s="641" t="inlineStr">
+      <c r="B28" s="653" t="inlineStr">
         <is>
           <t>story-production-cutover</t>
         </is>
       </c>
-      <c r="C28" s="647" t="n">
+      <c r="C28" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="641" t="inlineStr">
+      <c r="D28" s="653" t="inlineStr">
         <is>
           <t>切换清单在批准窗口内完成且回滚演练有记录。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="641" t="inlineStr">
+      <c r="A29" s="653" t="inlineStr">
         <is>
           <t>ac-production-validation</t>
         </is>
       </c>
-      <c r="B29" s="641" t="inlineStr">
+      <c r="B29" s="653" t="inlineStr">
         <is>
           <t>story-production-validation</t>
         </is>
       </c>
-      <c r="C29" s="647" t="n">
+      <c r="C29" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="641" t="inlineStr">
+      <c r="D29" s="653" t="inlineStr">
         <is>
           <t>五条关键业务链路烟测通过并由业务负责人确认。</t>
         </is>
       </c>
     </row>
     <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="641" t="inlineStr">
+      <c r="A30" s="653" t="inlineStr">
         <is>
           <t>ac-data-migration</t>
         </is>
       </c>
-      <c r="B30" s="641" t="inlineStr">
+      <c r="B30" s="653" t="inlineStr">
         <is>
           <t>story-data-migration</t>
         </is>
       </c>
-      <c r="C30" s="647" t="n">
+      <c r="C30" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="641" t="inlineStr">
+      <c r="D30" s="653" t="inlineStr">
         <is>
           <t>关键字段迁移前后一致率为 100%，重复业务主键为 0。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="641" t="inlineStr">
+      <c r="A31" s="653" t="inlineStr">
         <is>
           <t>ac-observability</t>
         </is>
       </c>
-      <c r="B31" s="641" t="inlineStr">
+      <c r="B31" s="653" t="inlineStr">
         <is>
           <t>story-observability</t>
         </is>
       </c>
-      <c r="C31" s="647" t="n">
+      <c r="C31" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="641" t="inlineStr">
+      <c r="D31" s="653" t="inlineStr">
         <is>
           <t>核心交易和财务作业指标均配置阈值、渠道与接收人。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="641" t="inlineStr">
+      <c r="A32" s="653" t="inlineStr">
         <is>
           <t>ac-ops-handover</t>
         </is>
       </c>
-      <c r="B32" s="641" t="inlineStr">
+      <c r="B32" s="653" t="inlineStr">
         <is>
           <t>story-ops-handover</t>
         </is>
       </c>
-      <c r="C32" s="647" t="n">
+      <c r="C32" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="641" t="inlineStr">
+      <c r="D32" s="653" t="inlineStr">
         <is>
           <t>运维手册、联系人和故障演练由运维经理签收。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="641" t="inlineStr">
+      <c r="A33" s="653" t="inlineStr">
         <is>
           <t>ac-user-training</t>
         </is>
       </c>
-      <c r="B33" s="641" t="inlineStr">
+      <c r="B33" s="653" t="inlineStr">
         <is>
           <t>story-user-training</t>
         </is>
       </c>
-      <c r="C33" s="647" t="n">
+      <c r="C33" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="641" t="inlineStr">
+      <c r="D33" s="653" t="inlineStr">
         <is>
           <t>门店、客服和财务培训完成并保留材料、签到和反馈。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="641" t="inlineStr">
+      <c r="A34" s="653" t="inlineStr">
         <is>
           <t>ac-test-automation</t>
         </is>
       </c>
-      <c r="B34" s="641" t="inlineStr">
+      <c r="B34" s="653" t="inlineStr">
         <is>
           <t>story-test-automation</t>
         </is>
       </c>
-      <c r="C34" s="647" t="n">
+      <c r="C34" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="641" t="inlineStr">
+      <c r="D34" s="653" t="inlineStr">
         <is>
           <t>P0/P1 自动化用例全部通过且核心查询达到 500 TPS。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="641" t="inlineStr">
+      <c r="A35" s="653" t="inlineStr">
         <is>
           <t>ac-test-non-uat</t>
         </is>
       </c>
-      <c r="B35" s="641" t="inlineStr">
+      <c r="B35" s="653" t="inlineStr">
         <is>
           <t>story-test-non-uat</t>
         </is>
       </c>
-      <c r="C35" s="647" t="n">
+      <c r="C35" s="659" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="641" t="inlineStr">
+      <c r="D35" s="653" t="inlineStr">
         <is>
           <t>支持的浏览器和设备矩阵通过工程回归且无阻断缺陷。</t>
         </is>
@@ -14008,11 +14236,11 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C5:C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole" operator="greaterThanOrEqual">
-      <formula1>1</formula1>
-    </dataValidation>
     <dataValidation sqref="B5:B104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>INDIRECT("'03-SOW主表'!$A$5:$A$104")</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:C104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14054,20 +14282,20 @@
           <t>任务明细（Task）</t>
         </is>
       </c>
-      <c r="B1" s="635" t="n"/>
-      <c r="C1" s="635" t="n"/>
-      <c r="D1" s="635" t="n"/>
-      <c r="E1" s="635" t="n"/>
-      <c r="F1" s="635" t="n"/>
-      <c r="G1" s="635" t="n"/>
-      <c r="H1" s="635" t="n"/>
-      <c r="I1" s="635" t="n"/>
-      <c r="J1" s="635" t="n"/>
-      <c r="K1" s="635" t="n"/>
-      <c r="L1" s="635" t="n"/>
-      <c r="M1" s="635" t="n"/>
-      <c r="N1" s="635" t="n"/>
-      <c r="O1" s="635" t="n"/>
+      <c r="B1" s="647" t="n"/>
+      <c r="C1" s="647" t="n"/>
+      <c r="D1" s="647" t="n"/>
+      <c r="E1" s="647" t="n"/>
+      <c r="F1" s="647" t="n"/>
+      <c r="G1" s="647" t="n"/>
+      <c r="H1" s="647" t="n"/>
+      <c r="I1" s="647" t="n"/>
+      <c r="J1" s="647" t="n"/>
+      <c r="K1" s="647" t="n"/>
+      <c r="L1" s="647" t="n"/>
+      <c r="M1" s="647" t="n"/>
+      <c r="N1" s="647" t="n"/>
+      <c r="O1" s="647" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="400" t="inlineStr">
@@ -14075,20 +14303,20 @@
           <t>一行对应一个基础单元实例；任务族、基础人天、复杂度倍率和人天小计由模板派生；不使用活动、数量或 Story 类型。</t>
         </is>
       </c>
-      <c r="B2" s="636" t="n"/>
-      <c r="C2" s="636" t="n"/>
-      <c r="D2" s="636" t="n"/>
-      <c r="E2" s="636" t="n"/>
-      <c r="F2" s="636" t="n"/>
-      <c r="G2" s="636" t="n"/>
-      <c r="H2" s="636" t="n"/>
-      <c r="I2" s="636" t="n"/>
-      <c r="J2" s="636" t="n"/>
-      <c r="K2" s="636" t="n"/>
-      <c r="L2" s="636" t="n"/>
-      <c r="M2" s="636" t="n"/>
-      <c r="N2" s="636" t="n"/>
-      <c r="O2" s="636" t="n"/>
+      <c r="B2" s="648" t="n"/>
+      <c r="C2" s="648" t="n"/>
+      <c r="D2" s="648" t="n"/>
+      <c r="E2" s="648" t="n"/>
+      <c r="F2" s="648" t="n"/>
+      <c r="G2" s="648" t="n"/>
+      <c r="H2" s="648" t="n"/>
+      <c r="I2" s="648" t="n"/>
+      <c r="J2" s="648" t="n"/>
+      <c r="K2" s="648" t="n"/>
+      <c r="L2" s="648" t="n"/>
+      <c r="M2" s="648" t="n"/>
+      <c r="N2" s="648" t="n"/>
+      <c r="O2" s="648" t="n"/>
     </row>
     <row r="3" ht="9" customHeight="1"/>
     <row r="4" ht="38" customHeight="1">
@@ -14169,2987 +14397,2987 @@
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="641" t="inlineStr">
+      <c r="A5" s="653" t="inlineStr">
         <is>
           <t>task-customer-profile-page</t>
         </is>
       </c>
-      <c r="B5" s="641" t="inlineStr">
+      <c r="B5" s="653" t="inlineStr">
         <is>
           <t>story-customer-profile</t>
         </is>
       </c>
-      <c r="C5" s="641" t="inlineStr">
+      <c r="C5" s="653" t="inlineStr">
         <is>
           <t>调整客户档案页面和状态</t>
         </is>
       </c>
-      <c r="D5" s="641" t="inlineStr">
+      <c r="D5" s="653" t="inlineStr">
         <is>
           <t>BU-UI-INTERACTION</t>
         </is>
       </c>
-      <c r="E5" s="646">
+      <c r="E5" s="658">
         <f>IF(D5="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D5,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F5" s="642" t="inlineStr">
+      <c r="F5" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G5" s="648" t="inlineStr">
+      <c r="G5" s="660" t="inlineStr">
         <is>
           <t>沿用可复用的客户档案框架及其页面入口，修改本次交付范围内的界面状态和校验。</t>
         </is>
       </c>
-      <c r="H5" s="649" t="inlineStr">
+      <c r="H5" s="661" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I5" s="648" t="inlineStr">
+      <c r="I5" s="660" t="inlineStr">
         <is>
           <t>仅一个界面和单一路径，使用成熟组件，无复杂权限或跨界面状态恢复。</t>
         </is>
       </c>
-      <c r="J5" s="648" t="inlineStr"/>
-      <c r="K5" s="648" t="inlineStr">
+      <c r="J5" s="660" t="inlineStr"/>
+      <c r="K5" s="660" t="inlineStr">
         <is>
           <t>effective-start-customer-profile</t>
         </is>
       </c>
-      <c r="L5" s="648" t="inlineStr">
+      <c r="L5" s="660" t="inlineStr">
         <is>
           <t>调整一个可独立验收的客户档案界面实例。</t>
         </is>
       </c>
-      <c r="M5" s="645">
+      <c r="M5" s="657">
         <f>IF(OR(A5="",D5="",F5=""),"",IFERROR(IF(F5="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D5,BaseUnitCatalogTable[基础单元ID],0)),IF(F5="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D5,BaseUnitCatalogTable[基础单元ID],0)),IF(F5="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D5,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N5" s="645">
+      <c r="N5" s="657">
         <f>IF(OR(A5="",H5=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H5,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O5" s="645">
+      <c r="O5" s="657">
         <f>IF(OR(A5="",NOT(ISNUMBER(M5)),NOT(ISNUMBER(N5))),"",ROUND(M5*N5,1))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="641" t="inlineStr">
+      <c r="A6" s="653" t="inlineStr">
         <is>
           <t>task-profile-api</t>
         </is>
       </c>
-      <c r="B6" s="641" t="inlineStr">
+      <c r="B6" s="653" t="inlineStr">
         <is>
           <t>story-profile-api</t>
         </is>
       </c>
-      <c r="C6" s="641" t="inlineStr">
+      <c r="C6" s="653" t="inlineStr">
         <is>
           <t>调整客户档案业务服务与接口</t>
         </is>
       </c>
-      <c r="D6" s="641" t="inlineStr">
+      <c r="D6" s="653" t="inlineStr">
         <is>
           <t>BU-BUSINESS-SERVICE-API</t>
         </is>
       </c>
-      <c r="E6" s="646">
+      <c r="E6" s="658">
         <f>IF(D6="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D6,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F6" s="642" t="inlineStr">
+      <c r="F6" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G6" s="648" t="inlineStr">
+      <c r="G6" s="660" t="inlineStr">
         <is>
           <t>保留可复用的客户档案框架对应的服务边界，扩展创建和检索规则及接口。</t>
         </is>
       </c>
-      <c r="H6" s="649" t="inlineStr">
+      <c r="H6" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I6" s="648" t="inlineStr"/>
-      <c r="J6" s="648" t="inlineStr"/>
-      <c r="K6" s="648" t="inlineStr">
+      <c r="I6" s="660" t="inlineStr"/>
+      <c r="J6" s="660" t="inlineStr"/>
+      <c r="K6" s="660" t="inlineStr">
         <is>
           <t>effective-start-customer-profile</t>
         </is>
       </c>
-      <c r="L6" s="648" t="inlineStr">
+      <c r="L6" s="660" t="inlineStr">
         <is>
           <t>一组围绕客户档案操作的紧密相关接口，符合单实例计数口径。</t>
         </is>
       </c>
-      <c r="M6" s="645">
+      <c r="M6" s="657">
         <f>IF(OR(A6="",D6="",F6=""),"",IFERROR(IF(F6="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D6,BaseUnitCatalogTable[基础单元ID],0)),IF(F6="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D6,BaseUnitCatalogTable[基础单元ID],0)),IF(F6="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D6,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N6" s="645">
+      <c r="N6" s="657">
         <f>IF(OR(A6="",H6=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H6,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O6" s="645">
+      <c r="O6" s="657">
         <f>IF(OR(A6="",NOT(ISNUMBER(M6)),NOT(ISNUMBER(N6))),"",ROUND(M6*N6,1))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="641" t="inlineStr">
+      <c r="A7" s="653" t="inlineStr">
         <is>
           <t>task-profile-integration</t>
         </is>
       </c>
-      <c r="B7" s="641" t="inlineStr">
+      <c r="B7" s="653" t="inlineStr">
         <is>
           <t>story-profile-integration</t>
         </is>
       </c>
-      <c r="C7" s="641" t="inlineStr">
+      <c r="C7" s="653" t="inlineStr">
         <is>
           <t>接入内部客户档案 API</t>
         </is>
       </c>
-      <c r="D7" s="641" t="inlineStr">
+      <c r="D7" s="653" t="inlineStr">
         <is>
           <t>BU-INTERNAL-INTEGRATION</t>
         </is>
       </c>
-      <c r="E7" s="646">
+      <c r="E7" s="658">
         <f>IF(D7="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D7,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F7" s="642" t="inlineStr">
+      <c r="F7" s="654" t="inlineStr">
         <is>
           <t>接入复用</t>
         </is>
       </c>
-      <c r="G7" s="648" t="inlineStr">
+      <c r="G7" s="660" t="inlineStr">
         <is>
           <t>可复用的客户档案框架保持不变；本项目负责并交付：认证、映射、适配。</t>
         </is>
       </c>
-      <c r="H7" s="649" t="inlineStr">
+      <c r="H7" s="661" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I7" s="648" t="inlineStr">
+      <c r="I7" s="660" t="inlineStr">
         <is>
           <t>同组织稳定接口、单向查询和简单字段映射，不涉及对端改造。</t>
         </is>
       </c>
-      <c r="J7" s="648" t="inlineStr">
+      <c r="J7" s="660" t="inlineStr">
         <is>
           <t>integration-profile-api</t>
         </is>
       </c>
-      <c r="K7" s="648" t="inlineStr">
+      <c r="K7" s="660" t="inlineStr">
         <is>
           <t>effective-start-customer-profile</t>
         </is>
       </c>
-      <c r="L7" s="648" t="inlineStr">
+      <c r="L7" s="660" t="inlineStr">
         <is>
           <t>实现一个已登记的内部出站 Integration，不包含另行开展的 SIT。</t>
         </is>
       </c>
-      <c r="M7" s="645">
+      <c r="M7" s="657">
         <f>IF(OR(A7="",D7="",F7=""),"",IFERROR(IF(F7="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D7,BaseUnitCatalogTable[基础单元ID],0)),IF(F7="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D7,BaseUnitCatalogTable[基础单元ID],0)),IF(F7="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D7,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N7" s="645">
+      <c r="N7" s="657">
         <f>IF(OR(A7="",H7=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H7,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O7" s="645">
+      <c r="O7" s="657">
         <f>IF(OR(A7="",NOT(ISNUMBER(M7)),NOT(ISNUMBER(N7))),"",ROUND(M7*N7,1))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="641" t="inlineStr">
+      <c r="A8" s="653" t="inlineStr">
         <is>
           <t>task-customer-profile-model</t>
         </is>
       </c>
-      <c r="B8" s="641" t="inlineStr">
+      <c r="B8" s="653" t="inlineStr">
         <is>
           <t>story-customer-profile</t>
         </is>
       </c>
-      <c r="C8" s="641" t="inlineStr">
+      <c r="C8" s="653" t="inlineStr">
         <is>
           <t>调整可复用的客户档案框架字段模型</t>
         </is>
       </c>
-      <c r="D8" s="641" t="inlineStr">
+      <c r="D8" s="653" t="inlineStr">
         <is>
           <t>BU-DATA-MODEL</t>
         </is>
       </c>
-      <c r="E8" s="646">
+      <c r="E8" s="658">
         <f>IF(D8="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D8,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F8" s="642" t="inlineStr">
+      <c r="F8" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G8" s="648" t="inlineStr">
+      <c r="G8" s="660" t="inlineStr">
         <is>
           <t>在可复用的客户档案框架中增加一期顺延字段、授权标识和变更审计列。</t>
         </is>
       </c>
-      <c r="H8" s="649" t="inlineStr">
+      <c r="H8" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I8" s="648" t="inlineStr"/>
-      <c r="J8" s="648" t="inlineStr"/>
-      <c r="K8" s="648" t="inlineStr">
+      <c r="I8" s="660" t="inlineStr"/>
+      <c r="J8" s="660" t="inlineStr"/>
+      <c r="K8" s="660" t="inlineStr">
         <is>
           <t>effective-start-customer-profile</t>
         </is>
       </c>
-      <c r="L8" s="648" t="inlineStr">
+      <c r="L8" s="660" t="inlineStr">
         <is>
           <t>一个客户档案数据模型实例，覆盖字段、约束和审计列。</t>
         </is>
       </c>
-      <c r="M8" s="645">
+      <c r="M8" s="657">
         <f>IF(OR(A8="",D8="",F8=""),"",IFERROR(IF(F8="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D8,BaseUnitCatalogTable[基础单元ID],0)),IF(F8="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D8,BaseUnitCatalogTable[基础单元ID],0)),IF(F8="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D8,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N8" s="645">
+      <c r="N8" s="657">
         <f>IF(OR(A8="",H8=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H8,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O8" s="645">
+      <c r="O8" s="657">
         <f>IF(OR(A8="",NOT(ISNUMBER(M8)),NOT(ISNUMBER(N8))),"",ROUND(M8*N8,1))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="641" t="inlineStr">
+      <c r="A9" s="653" t="inlineStr">
         <is>
           <t>task-profile-identity</t>
         </is>
       </c>
-      <c r="B9" s="641" t="inlineStr">
+      <c r="B9" s="653" t="inlineStr">
         <is>
           <t>story-profile-api</t>
         </is>
       </c>
-      <c r="C9" s="641" t="inlineStr">
+      <c r="C9" s="653" t="inlineStr">
         <is>
           <t>建立档案 API 身份与字段权限</t>
         </is>
       </c>
-      <c r="D9" s="641" t="inlineStr">
+      <c r="D9" s="653" t="inlineStr">
         <is>
           <t>BU-IDENTITY-ACCESS</t>
         </is>
       </c>
-      <c r="E9" s="646">
+      <c r="E9" s="658">
         <f>IF(D9="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D9,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F9" s="642" t="inlineStr">
+      <c r="F9" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G9" s="648" t="inlineStr">
+      <c r="G9" s="660" t="inlineStr">
         <is>
           <t>为档案 API 新增角色、权限范围和敏感字段过滤规则。</t>
         </is>
       </c>
-      <c r="H9" s="649" t="inlineStr">
+      <c r="H9" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I9" s="648" t="inlineStr"/>
-      <c r="J9" s="648" t="inlineStr"/>
-      <c r="K9" s="648" t="inlineStr"/>
-      <c r="L9" s="648" t="inlineStr">
+      <c r="I9" s="660" t="inlineStr"/>
+      <c r="J9" s="660" t="inlineStr"/>
+      <c r="K9" s="660" t="inlineStr"/>
+      <c r="L9" s="660" t="inlineStr">
         <is>
           <t>一个档案 API 权限控制实例，覆盖门店、客服和会员三类主体。</t>
         </is>
       </c>
-      <c r="M9" s="645">
+      <c r="M9" s="657">
         <f>IF(OR(A9="",D9="",F9=""),"",IFERROR(IF(F9="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D9,BaseUnitCatalogTable[基础单元ID],0)),IF(F9="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D9,BaseUnitCatalogTable[基础单元ID],0)),IF(F9="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D9,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N9" s="645">
+      <c r="N9" s="657">
         <f>IF(OR(A9="",H9=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H9,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O9" s="645">
+      <c r="O9" s="657">
         <f>IF(OR(A9="",NOT(ISNUMBER(M9)),NOT(ISNUMBER(N9))),"",ROUND(M9*N9,1))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="641" t="inlineStr">
+      <c r="A10" s="653" t="inlineStr">
         <is>
           <t>task-member-tier-service</t>
         </is>
       </c>
-      <c r="B10" s="641" t="inlineStr">
+      <c r="B10" s="653" t="inlineStr">
         <is>
           <t>story-member-tier</t>
         </is>
       </c>
-      <c r="C10" s="641" t="inlineStr">
+      <c r="C10" s="653" t="inlineStr">
         <is>
           <t>调整既有会员主数据模型的等级计算服务</t>
         </is>
       </c>
-      <c r="D10" s="641" t="inlineStr">
+      <c r="D10" s="653" t="inlineStr">
         <is>
           <t>BU-BUSINESS-SERVICE-API</t>
         </is>
       </c>
-      <c r="E10" s="646">
+      <c r="E10" s="658">
         <f>IF(D10="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D10,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F10" s="642" t="inlineStr">
+      <c r="F10" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G10" s="648" t="inlineStr">
+      <c r="G10" s="660" t="inlineStr">
         <is>
           <t>基于既有会员主数据模型新增等级试算、生效和查询操作。</t>
         </is>
       </c>
-      <c r="H10" s="649" t="inlineStr">
+      <c r="H10" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I10" s="648" t="inlineStr"/>
-      <c r="J10" s="648" t="inlineStr"/>
-      <c r="K10" s="648" t="inlineStr">
+      <c r="I10" s="660" t="inlineStr"/>
+      <c r="J10" s="660" t="inlineStr"/>
+      <c r="K10" s="660" t="inlineStr">
         <is>
           <t>effective-start-member-master</t>
         </is>
       </c>
-      <c r="L10" s="648" t="inlineStr">
+      <c r="L10" s="660" t="inlineStr">
         <is>
           <t>一组围绕等级规则生效的紧密相关业务操作。</t>
         </is>
       </c>
-      <c r="M10" s="645">
+      <c r="M10" s="657">
         <f>IF(OR(A10="",D10="",F10=""),"",IFERROR(IF(F10="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D10,BaseUnitCatalogTable[基础单元ID],0)),IF(F10="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D10,BaseUnitCatalogTable[基础单元ID],0)),IF(F10="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D10,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N10" s="645">
+      <c r="N10" s="657">
         <f>IF(OR(A10="",H10=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H10,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O10" s="645">
+      <c r="O10" s="657">
         <f>IF(OR(A10="",NOT(ISNUMBER(M10)),NOT(ISNUMBER(N10))),"",ROUND(M10*N10,1))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="641" t="inlineStr">
+      <c r="A11" s="653" t="inlineStr">
         <is>
           <t>task-member-tier-model</t>
         </is>
       </c>
-      <c r="B11" s="641" t="inlineStr">
+      <c r="B11" s="653" t="inlineStr">
         <is>
           <t>story-member-tier</t>
         </is>
       </c>
-      <c r="C11" s="641" t="inlineStr">
+      <c r="C11" s="653" t="inlineStr">
         <is>
           <t>调整既有会员主数据模型的等级历史</t>
         </is>
       </c>
-      <c r="D11" s="641" t="inlineStr">
+      <c r="D11" s="653" t="inlineStr">
         <is>
           <t>BU-DATA-MODEL</t>
         </is>
       </c>
-      <c r="E11" s="646">
+      <c r="E11" s="658">
         <f>IF(D11="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D11,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F11" s="642" t="inlineStr">
+      <c r="F11" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G11" s="648" t="inlineStr">
+      <c r="G11" s="660" t="inlineStr">
         <is>
           <t>扩展既有会员主数据模型，增加规则版本、生效区间和等级变更历史。</t>
         </is>
       </c>
-      <c r="H11" s="649" t="inlineStr">
+      <c r="H11" s="661" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I11" s="648" t="inlineStr">
+      <c r="I11" s="660" t="inlineStr">
         <is>
           <t>新增两张关系清晰的历史表和唯一性约束，不涉及分区或跨库事务。</t>
         </is>
       </c>
-      <c r="J11" s="648" t="inlineStr"/>
-      <c r="K11" s="648" t="inlineStr">
+      <c r="J11" s="660" t="inlineStr"/>
+      <c r="K11" s="660" t="inlineStr">
         <is>
           <t>effective-start-member-master</t>
         </is>
       </c>
-      <c r="L11" s="648" t="inlineStr">
+      <c r="L11" s="660" t="inlineStr">
         <is>
           <t>一个会员等级数据模型实例。</t>
         </is>
       </c>
-      <c r="M11" s="645">
+      <c r="M11" s="657">
         <f>IF(OR(A11="",D11="",F11=""),"",IFERROR(IF(F11="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D11,BaseUnitCatalogTable[基础单元ID],0)),IF(F11="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D11,BaseUnitCatalogTable[基础单元ID],0)),IF(F11="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D11,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N11" s="645">
+      <c r="N11" s="657">
         <f>IF(OR(A11="",H11=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H11,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O11" s="645">
+      <c r="O11" s="657">
         <f>IF(OR(A11="",NOT(ISNUMBER(M11)),NOT(ISNUMBER(N11))),"",ROUND(M11*N11,1))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="641" t="inlineStr">
+      <c r="A12" s="653" t="inlineStr">
         <is>
           <t>task-order-create-page</t>
         </is>
       </c>
-      <c r="B12" s="641" t="inlineStr">
+      <c r="B12" s="653" t="inlineStr">
         <is>
           <t>story-order-create</t>
         </is>
       </c>
-      <c r="C12" s="641" t="inlineStr">
+      <c r="C12" s="653" t="inlineStr">
         <is>
           <t>新建全渠道订单创建交互</t>
         </is>
       </c>
-      <c r="D12" s="641" t="inlineStr">
+      <c r="D12" s="653" t="inlineStr">
         <is>
           <t>BU-UI-INTERACTION</t>
         </is>
       </c>
-      <c r="E12" s="646">
+      <c r="E12" s="658">
         <f>IF(D12="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D12,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F12" s="642" t="inlineStr">
+      <c r="F12" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G12" s="648" t="inlineStr">
+      <c r="G12" s="660" t="inlineStr">
         <is>
           <t>新增门店与线上共用的价格、权益和履约方式校验交互。</t>
         </is>
       </c>
-      <c r="H12" s="649" t="inlineStr">
+      <c r="H12" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I12" s="648" t="inlineStr"/>
-      <c r="J12" s="648" t="inlineStr"/>
-      <c r="K12" s="648" t="inlineStr"/>
-      <c r="L12" s="648" t="inlineStr">
+      <c r="I12" s="660" t="inlineStr"/>
+      <c r="J12" s="660" t="inlineStr"/>
+      <c r="K12" s="660" t="inlineStr"/>
+      <c r="L12" s="660" t="inlineStr">
         <is>
           <t>一个订单创建主流程界面实例，包含统一校验和错误反馈。</t>
         </is>
       </c>
-      <c r="M12" s="645">
+      <c r="M12" s="657">
         <f>IF(OR(A12="",D12="",F12=""),"",IFERROR(IF(F12="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D12,BaseUnitCatalogTable[基础单元ID],0)),IF(F12="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D12,BaseUnitCatalogTable[基础单元ID],0)),IF(F12="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D12,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N12" s="645">
+      <c r="N12" s="657">
         <f>IF(OR(A12="",H12=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H12,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O12" s="645">
+      <c r="O12" s="657">
         <f>IF(OR(A12="",NOT(ISNUMBER(M12)),NOT(ISNUMBER(N12))),"",ROUND(M12*N12,1))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="641" t="inlineStr">
+      <c r="A13" s="653" t="inlineStr">
         <is>
           <t>task-order-create-service</t>
         </is>
       </c>
-      <c r="B13" s="641" t="inlineStr">
+      <c r="B13" s="653" t="inlineStr">
         <is>
           <t>story-order-create</t>
         </is>
       </c>
-      <c r="C13" s="641" t="inlineStr">
+      <c r="C13" s="653" t="inlineStr">
         <is>
           <t>新建全渠道订单创建服务</t>
         </is>
       </c>
-      <c r="D13" s="641" t="inlineStr">
+      <c r="D13" s="653" t="inlineStr">
         <is>
           <t>BU-BUSINESS-SERVICE-API</t>
         </is>
       </c>
-      <c r="E13" s="646">
+      <c r="E13" s="658">
         <f>IF(D13="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D13,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F13" s="642" t="inlineStr">
+      <c r="F13" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G13" s="648" t="inlineStr">
+      <c r="G13" s="660" t="inlineStr">
         <is>
           <t>新增跨渠道订单创建、价格快照、权益核验和幂等控制。</t>
         </is>
       </c>
-      <c r="H13" s="649" t="inlineStr">
+      <c r="H13" s="661" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I13" s="648" t="inlineStr">
+      <c r="I13" s="660" t="inlineStr">
         <is>
           <t>涉及门店与线上两类渠道、四项业务校验、跨域价格权益快照和并发幂等。</t>
         </is>
       </c>
-      <c r="J13" s="648" t="inlineStr"/>
-      <c r="K13" s="648" t="inlineStr"/>
-      <c r="L13" s="648" t="inlineStr">
+      <c r="J13" s="660" t="inlineStr"/>
+      <c r="K13" s="660" t="inlineStr"/>
+      <c r="L13" s="660" t="inlineStr">
         <is>
           <t>一个全渠道订单创建服务实例。</t>
         </is>
       </c>
-      <c r="M13" s="645">
+      <c r="M13" s="657">
         <f>IF(OR(A13="",D13="",F13=""),"",IFERROR(IF(F13="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D13,BaseUnitCatalogTable[基础单元ID],0)),IF(F13="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D13,BaseUnitCatalogTable[基础单元ID],0)),IF(F13="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D13,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N13" s="645">
+      <c r="N13" s="657">
         <f>IF(OR(A13="",H13=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H13,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O13" s="645">
+      <c r="O13" s="657">
         <f>IF(OR(A13="",NOT(ISNUMBER(M13)),NOT(ISNUMBER(N13))),"",ROUND(M13*N13,1))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="641" t="inlineStr">
+      <c r="A14" s="653" t="inlineStr">
         <is>
           <t>task-order-state-service</t>
         </is>
       </c>
-      <c r="B14" s="641" t="inlineStr">
+      <c r="B14" s="653" t="inlineStr">
         <is>
           <t>story-order-state</t>
         </is>
       </c>
-      <c r="C14" s="641" t="inlineStr">
+      <c r="C14" s="653" t="inlineStr">
         <is>
           <t>调整既有订单服务与状态机</t>
         </is>
       </c>
-      <c r="D14" s="641" t="inlineStr">
+      <c r="D14" s="653" t="inlineStr">
         <is>
           <t>BU-BUSINESS-SERVICE-API</t>
         </is>
       </c>
-      <c r="E14" s="646">
+      <c r="E14" s="658">
         <f>IF(D14="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D14,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F14" s="642" t="inlineStr">
+      <c r="F14" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G14" s="648" t="inlineStr">
+      <c r="G14" s="660" t="inlineStr">
         <is>
           <t>扩展既有订单服务与状态机，增加门店接单、退货、退款和开票状态。</t>
         </is>
       </c>
-      <c r="H14" s="649" t="inlineStr">
+      <c r="H14" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I14" s="648" t="inlineStr"/>
-      <c r="J14" s="648" t="inlineStr"/>
-      <c r="K14" s="648" t="inlineStr">
+      <c r="I14" s="660" t="inlineStr"/>
+      <c r="J14" s="660" t="inlineStr"/>
+      <c r="K14" s="660" t="inlineStr">
         <is>
           <t>effective-start-order-service</t>
         </is>
       </c>
-      <c r="L14" s="648" t="inlineStr">
+      <c r="L14" s="660" t="inlineStr">
         <is>
           <t>一个订单状态机调整实例，包含新增状态、命令和合法迁移。</t>
         </is>
       </c>
-      <c r="M14" s="645">
+      <c r="M14" s="657">
         <f>IF(OR(A14="",D14="",F14=""),"",IFERROR(IF(F14="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D14,BaseUnitCatalogTable[基础单元ID],0)),IF(F14="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D14,BaseUnitCatalogTable[基础单元ID],0)),IF(F14="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D14,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N14" s="645">
+      <c r="N14" s="657">
         <f>IF(OR(A14="",H14=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H14,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O14" s="645">
+      <c r="O14" s="657">
         <f>IF(OR(A14="",NOT(ISNUMBER(M14)),NOT(ISNUMBER(N14))),"",ROUND(M14*N14,1))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="641" t="inlineStr">
+      <c r="A15" s="653" t="inlineStr">
         <is>
           <t>task-order-state-events</t>
         </is>
       </c>
-      <c r="B15" s="641" t="inlineStr">
+      <c r="B15" s="653" t="inlineStr">
         <is>
           <t>story-order-state</t>
         </is>
       </c>
-      <c r="C15" s="641" t="inlineStr">
+      <c r="C15" s="653" t="inlineStr">
         <is>
           <t>新建订单状态事件处理</t>
         </is>
       </c>
-      <c r="D15" s="641" t="inlineStr">
+      <c r="D15" s="653" t="inlineStr">
         <is>
           <t>BU-EVENT-MESSAGE</t>
         </is>
       </c>
-      <c r="E15" s="646">
+      <c r="E15" s="658">
         <f>IF(D15="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D15,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F15" s="642" t="inlineStr">
+      <c r="F15" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G15" s="648" t="inlineStr">
+      <c r="G15" s="660" t="inlineStr">
         <is>
           <t>新增带事件编号、业务键和重放保护的订单状态事件。</t>
         </is>
       </c>
-      <c r="H15" s="649" t="inlineStr">
+      <c r="H15" s="661" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I15" s="648" t="inlineStr">
+      <c r="I15" s="660" t="inlineStr">
         <is>
           <t>覆盖九类状态事件、顺序保证、重复消费和失败重放，并被多个下游订阅。</t>
         </is>
       </c>
-      <c r="J15" s="648" t="inlineStr"/>
-      <c r="K15" s="648" t="inlineStr"/>
-      <c r="L15" s="648" t="inlineStr">
+      <c r="J15" s="660" t="inlineStr"/>
+      <c r="K15" s="660" t="inlineStr"/>
+      <c r="L15" s="660" t="inlineStr">
         <is>
           <t>一个订单状态事件主题及其生产消费处理实例。</t>
         </is>
       </c>
-      <c r="M15" s="645">
+      <c r="M15" s="657">
         <f>IF(OR(A15="",D15="",F15=""),"",IFERROR(IF(F15="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D15,BaseUnitCatalogTable[基础单元ID],0)),IF(F15="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D15,BaseUnitCatalogTable[基础单元ID],0)),IF(F15="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D15,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N15" s="645">
+      <c r="N15" s="657">
         <f>IF(OR(A15="",H15=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H15,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O15" s="645">
+      <c r="O15" s="657">
         <f>IF(OR(A15="",NOT(ISNUMBER(M15)),NOT(ISNUMBER(N15))),"",ROUND(M15*N15,1))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="641" t="inlineStr">
+      <c r="A16" s="653" t="inlineStr">
         <is>
           <t>task-erp-reservation-integration</t>
         </is>
       </c>
-      <c r="B16" s="641" t="inlineStr">
+      <c r="B16" s="653" t="inlineStr">
         <is>
           <t>story-inventory-reservation</t>
         </is>
       </c>
-      <c r="C16" s="641" t="inlineStr">
+      <c r="C16" s="653" t="inlineStr">
         <is>
           <t>接入既有 ERP 库存接口</t>
         </is>
       </c>
-      <c r="D16" s="641" t="inlineStr">
+      <c r="D16" s="653" t="inlineStr">
         <is>
           <t>BU-INTERNAL-INTEGRATION</t>
         </is>
       </c>
-      <c r="E16" s="646">
+      <c r="E16" s="658">
         <f>IF(D16="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D16,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F16" s="642" t="inlineStr">
+      <c r="F16" s="654" t="inlineStr">
         <is>
           <t>接入复用</t>
         </is>
       </c>
-      <c r="G16" s="648" t="inlineStr">
+      <c r="G16" s="660" t="inlineStr">
         <is>
           <t>既有 ERP 库存接口保持不变；本项目负责并交付：映射、适配、认证、专项验证。</t>
         </is>
       </c>
-      <c r="H16" s="649" t="inlineStr">
+      <c r="H16" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I16" s="648" t="inlineStr"/>
-      <c r="J16" s="648" t="inlineStr">
+      <c r="I16" s="660" t="inlineStr"/>
+      <c r="J16" s="660" t="inlineStr">
         <is>
           <t>integration-erp-reservation</t>
         </is>
       </c>
-      <c r="K16" s="648" t="inlineStr">
+      <c r="K16" s="660" t="inlineStr">
         <is>
           <t>effective-start-erp-interface</t>
         </is>
       </c>
-      <c r="L16" s="648" t="inlineStr">
+      <c r="L16" s="660" t="inlineStr">
         <is>
           <t>实现一个已登记的内部 ERP 库存 Integration，SIT 人天由集成表公式另计。</t>
         </is>
       </c>
-      <c r="M16" s="645">
+      <c r="M16" s="657">
         <f>IF(OR(A16="",D16="",F16=""),"",IFERROR(IF(F16="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D16,BaseUnitCatalogTable[基础单元ID],0)),IF(F16="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D16,BaseUnitCatalogTable[基础单元ID],0)),IF(F16="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D16,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N16" s="645">
+      <c r="N16" s="657">
         <f>IF(OR(A16="",H16=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H16,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O16" s="645">
+      <c r="O16" s="657">
         <f>IF(OR(A16="",NOT(ISNUMBER(M16)),NOT(ISNUMBER(N16))),"",ROUND(M16*N16,1))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="641" t="inlineStr">
+      <c r="A17" s="653" t="inlineStr">
         <is>
           <t>task-inventory-sit</t>
         </is>
       </c>
-      <c r="B17" s="641" t="inlineStr">
+      <c r="B17" s="653" t="inlineStr">
         <is>
           <t>story-inventory-reservation</t>
         </is>
       </c>
-      <c r="C17" s="641" t="inlineStr">
+      <c r="C17" s="653" t="inlineStr">
         <is>
           <t>验证库存预占幂等与补偿</t>
         </is>
       </c>
-      <c r="D17" s="641" t="inlineStr">
+      <c r="D17" s="653" t="inlineStr">
         <is>
           <t>BU-MANUAL-TESTING</t>
         </is>
       </c>
-      <c r="E17" s="646">
+      <c r="E17" s="658">
         <f>IF(D17="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D17,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F17" s="642" t="inlineStr">
+      <c r="F17" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G17" s="648" t="inlineStr">
+      <c r="G17" s="660" t="inlineStr">
         <is>
           <t>新增 ERP 超时、重试、重复请求和释放失败的人工验证场景。</t>
         </is>
       </c>
-      <c r="H17" s="649" t="inlineStr">
+      <c r="H17" s="661" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I17" s="648" t="inlineStr">
+      <c r="I17" s="660" t="inlineStr">
         <is>
           <t>集中验证四个已定义异常场景，数据准备简单且无需跨设备矩阵。</t>
         </is>
       </c>
-      <c r="J17" s="648" t="inlineStr"/>
-      <c r="K17" s="648" t="inlineStr"/>
-      <c r="L17" s="648" t="inlineStr">
+      <c r="J17" s="660" t="inlineStr"/>
+      <c r="K17" s="660" t="inlineStr"/>
+      <c r="L17" s="660" t="inlineStr">
         <is>
           <t>一个库存集成专项人工测试实例，不替代集成支持 SIT 公式。</t>
         </is>
       </c>
-      <c r="M17" s="645">
+      <c r="M17" s="657">
         <f>IF(OR(A17="",D17="",F17=""),"",IFERROR(IF(F17="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D17,BaseUnitCatalogTable[基础单元ID],0)),IF(F17="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D17,BaseUnitCatalogTable[基础单元ID],0)),IF(F17="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D17,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N17" s="645">
+      <c r="N17" s="657">
         <f>IF(OR(A17="",H17=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H17,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O17" s="645">
+      <c r="O17" s="657">
         <f>IF(OR(A17="",NOT(ISNUMBER(M17)),NOT(ISNUMBER(N17))),"",ROUND(M17*N17,1))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="641" t="inlineStr">
+      <c r="A18" s="653" t="inlineStr">
         <is>
           <t>task-return-page</t>
         </is>
       </c>
-      <c r="B18" s="641" t="inlineStr">
+      <c r="B18" s="653" t="inlineStr">
         <is>
           <t>story-return-request</t>
         </is>
       </c>
-      <c r="C18" s="641" t="inlineStr">
+      <c r="C18" s="653" t="inlineStr">
         <is>
           <t>新建退货申请与审核交互</t>
         </is>
       </c>
-      <c r="D18" s="641" t="inlineStr">
+      <c r="D18" s="653" t="inlineStr">
         <is>
           <t>BU-UI-INTERACTION</t>
         </is>
       </c>
-      <c r="E18" s="646">
+      <c r="E18" s="658">
         <f>IF(D18="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D18,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F18" s="642" t="inlineStr">
+      <c r="F18" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G18" s="648" t="inlineStr">
+      <c r="G18" s="660" t="inlineStr">
         <is>
           <t>新增门店和客服使用的退货明细、可退校验和审核反馈。</t>
         </is>
       </c>
-      <c r="H18" s="649" t="inlineStr">
+      <c r="H18" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I18" s="648" t="inlineStr"/>
-      <c r="J18" s="648" t="inlineStr"/>
-      <c r="K18" s="648" t="inlineStr"/>
-      <c r="L18" s="648" t="inlineStr">
+      <c r="I18" s="660" t="inlineStr"/>
+      <c r="J18" s="660" t="inlineStr"/>
+      <c r="K18" s="660" t="inlineStr"/>
+      <c r="L18" s="660" t="inlineStr">
         <is>
           <t>一个退货申请与审核主流程界面实例。</t>
         </is>
       </c>
-      <c r="M18" s="645">
+      <c r="M18" s="657">
         <f>IF(OR(A18="",D18="",F18=""),"",IFERROR(IF(F18="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D18,BaseUnitCatalogTable[基础单元ID],0)),IF(F18="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D18,BaseUnitCatalogTable[基础单元ID],0)),IF(F18="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D18,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N18" s="645">
+      <c r="N18" s="657">
         <f>IF(OR(A18="",H18=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H18,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O18" s="645">
+      <c r="O18" s="657">
         <f>IF(OR(A18="",NOT(ISNUMBER(M18)),NOT(ISNUMBER(N18))),"",ROUND(M18*N18,1))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="641" t="inlineStr">
+      <c r="A19" s="653" t="inlineStr">
         <is>
           <t>task-return-service</t>
         </is>
       </c>
-      <c r="B19" s="641" t="inlineStr">
+      <c r="B19" s="653" t="inlineStr">
         <is>
           <t>story-return-request</t>
         </is>
       </c>
-      <c r="C19" s="641" t="inlineStr">
+      <c r="C19" s="653" t="inlineStr">
         <is>
           <t>调整既有订单服务与状态机的退货规则</t>
         </is>
       </c>
-      <c r="D19" s="641" t="inlineStr">
+      <c r="D19" s="653" t="inlineStr">
         <is>
           <t>BU-BUSINESS-SERVICE-API</t>
         </is>
       </c>
-      <c r="E19" s="646">
+      <c r="E19" s="658">
         <f>IF(D19="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D19,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F19" s="642" t="inlineStr">
+      <c r="F19" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G19" s="648" t="inlineStr">
+      <c r="G19" s="660" t="inlineStr">
         <is>
           <t>在既有订单服务与状态机中增加可退数量、退货审核和退货单状态。</t>
         </is>
       </c>
-      <c r="H19" s="649" t="inlineStr">
+      <c r="H19" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I19" s="648" t="inlineStr"/>
-      <c r="J19" s="648" t="inlineStr"/>
-      <c r="K19" s="648" t="inlineStr">
+      <c r="I19" s="660" t="inlineStr"/>
+      <c r="J19" s="660" t="inlineStr"/>
+      <c r="K19" s="660" t="inlineStr">
         <is>
           <t>effective-start-order-service</t>
         </is>
       </c>
-      <c r="L19" s="648" t="inlineStr">
+      <c r="L19" s="660" t="inlineStr">
         <is>
           <t>一个退货领域服务调整实例。</t>
         </is>
       </c>
-      <c r="M19" s="645">
+      <c r="M19" s="657">
         <f>IF(OR(A19="",D19="",F19=""),"",IFERROR(IF(F19="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D19,BaseUnitCatalogTable[基础单元ID],0)),IF(F19="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D19,BaseUnitCatalogTable[基础单元ID],0)),IF(F19="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D19,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N19" s="645">
+      <c r="N19" s="657">
         <f>IF(OR(A19="",H19=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H19,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O19" s="645">
+      <c r="O19" s="657">
         <f>IF(OR(A19="",NOT(ISNUMBER(M19)),NOT(ISNUMBER(N19))),"",ROUND(M19*N19,1))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="641" t="inlineStr">
+      <c r="A20" s="653" t="inlineStr">
         <is>
           <t>task-payment-refund-integration</t>
         </is>
       </c>
-      <c r="B20" s="641" t="inlineStr">
+      <c r="B20" s="653" t="inlineStr">
         <is>
           <t>story-refund-payment</t>
         </is>
       </c>
-      <c r="C20" s="641" t="inlineStr">
+      <c r="C20" s="653" t="inlineStr">
         <is>
           <t>接入既有支付网关租户</t>
         </is>
       </c>
-      <c r="D20" s="641" t="inlineStr">
+      <c r="D20" s="653" t="inlineStr">
         <is>
           <t>BU-EXTERNAL-INTEGRATION</t>
         </is>
       </c>
-      <c r="E20" s="646">
+      <c r="E20" s="658">
         <f>IF(D20="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D20,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F20" s="642" t="inlineStr">
+      <c r="F20" s="654" t="inlineStr">
         <is>
           <t>接入复用</t>
         </is>
       </c>
-      <c r="G20" s="648" t="inlineStr">
+      <c r="G20" s="660" t="inlineStr">
         <is>
           <t>既有支付网关租户保持不变；本项目负责并交付：配置、映射、适配、认证、专项验证。</t>
         </is>
       </c>
-      <c r="H20" s="649" t="inlineStr">
+      <c r="H20" s="661" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I20" s="648" t="inlineStr">
+      <c r="I20" s="660" t="inlineStr">
         <is>
           <t>涉及外部认证、同步申请与异步回调、金额幂等、供应商错误码和认证窗口。</t>
         </is>
       </c>
-      <c r="J20" s="648" t="inlineStr">
+      <c r="J20" s="660" t="inlineStr">
         <is>
           <t>integration-payment-gateway</t>
         </is>
       </c>
-      <c r="K20" s="648" t="inlineStr">
+      <c r="K20" s="660" t="inlineStr">
         <is>
           <t>effective-start-payment-gateway</t>
         </is>
       </c>
-      <c r="L20" s="648" t="inlineStr">
+      <c r="L20" s="660" t="inlineStr">
         <is>
           <t>实现一个已登记的外部支付退款 Integration，外部支持成本在集成表单列展示。</t>
         </is>
       </c>
-      <c r="M20" s="645">
+      <c r="M20" s="657">
         <f>IF(OR(A20="",D20="",F20=""),"",IFERROR(IF(F20="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D20,BaseUnitCatalogTable[基础单元ID],0)),IF(F20="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D20,BaseUnitCatalogTable[基础单元ID],0)),IF(F20="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D20,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N20" s="645">
+      <c r="N20" s="657">
         <f>IF(OR(A20="",H20=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H20,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O20" s="645">
+      <c r="O20" s="657">
         <f>IF(OR(A20="",NOT(ISNUMBER(M20)),NOT(ISNUMBER(N20))),"",ROUND(M20*N20,1))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="641" t="inlineStr">
+      <c r="A21" s="653" t="inlineStr">
         <is>
           <t>task-refund-security</t>
         </is>
       </c>
-      <c r="B21" s="641" t="inlineStr">
+      <c r="B21" s="653" t="inlineStr">
         <is>
           <t>story-refund-payment</t>
         </is>
       </c>
-      <c r="C21" s="641" t="inlineStr">
+      <c r="C21" s="653" t="inlineStr">
         <is>
           <t>验证退款签名与隐私保护</t>
         </is>
       </c>
-      <c r="D21" s="641" t="inlineStr">
+      <c r="D21" s="653" t="inlineStr">
         <is>
           <t>BU-SECURITY-PRIVACY-TESTING</t>
         </is>
       </c>
-      <c r="E21" s="646">
+      <c r="E21" s="658">
         <f>IF(D21="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D21,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F21" s="642" t="inlineStr">
+      <c r="F21" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G21" s="648" t="inlineStr">
+      <c r="G21" s="660" t="inlineStr">
         <is>
           <t>新增退款回调签名、重放攻击、敏感字段和越权场景验证。</t>
         </is>
       </c>
-      <c r="H21" s="649" t="inlineStr">
+      <c r="H21" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I21" s="648" t="inlineStr"/>
-      <c r="J21" s="648" t="inlineStr"/>
-      <c r="K21" s="648" t="inlineStr"/>
-      <c r="L21" s="648" t="inlineStr">
+      <c r="I21" s="660" t="inlineStr"/>
+      <c r="J21" s="660" t="inlineStr"/>
+      <c r="K21" s="660" t="inlineStr"/>
+      <c r="L21" s="660" t="inlineStr">
         <is>
           <t>一个退款链路安全与隐私测试实例。</t>
         </is>
       </c>
-      <c r="M21" s="645">
+      <c r="M21" s="657">
         <f>IF(OR(A21="",D21="",F21=""),"",IFERROR(IF(F21="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D21,BaseUnitCatalogTable[基础单元ID],0)),IF(F21="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D21,BaseUnitCatalogTable[基础单元ID],0)),IF(F21="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D21,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N21" s="645">
+      <c r="N21" s="657">
         <f>IF(OR(A21="",H21=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H21,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O21" s="645">
+      <c r="O21" s="657">
         <f>IF(OR(A21="",NOT(ISNUMBER(M21)),NOT(ISNUMBER(N21))),"",ROUND(M21*N21,1))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="641" t="inlineStr">
+      <c r="A22" s="653" t="inlineStr">
         <is>
           <t>task-store-order-page</t>
         </is>
       </c>
-      <c r="B22" s="641" t="inlineStr">
+      <c r="B22" s="653" t="inlineStr">
         <is>
           <t>story-store-order</t>
         </is>
       </c>
-      <c r="C22" s="641" t="inlineStr">
+      <c r="C22" s="653" t="inlineStr">
         <is>
           <t>新建门店订单队列与交接界面</t>
         </is>
       </c>
-      <c r="D22" s="641" t="inlineStr">
+      <c r="D22" s="653" t="inlineStr">
         <is>
           <t>BU-UI-INTERACTION</t>
         </is>
       </c>
-      <c r="E22" s="646">
+      <c r="E22" s="658">
         <f>IF(D22="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D22,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F22" s="642" t="inlineStr">
+      <c r="F22" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G22" s="648" t="inlineStr">
+      <c r="G22" s="660" t="inlineStr">
         <is>
           <t>新增门店待处理队列、缺货替代、备注和班次交接交互。</t>
         </is>
       </c>
-      <c r="H22" s="649" t="inlineStr">
+      <c r="H22" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I22" s="648" t="inlineStr"/>
-      <c r="J22" s="648" t="inlineStr"/>
-      <c r="K22" s="648" t="inlineStr"/>
-      <c r="L22" s="648" t="inlineStr">
+      <c r="I22" s="660" t="inlineStr"/>
+      <c r="J22" s="660" t="inlineStr"/>
+      <c r="K22" s="660" t="inlineStr"/>
+      <c r="L22" s="660" t="inlineStr">
         <is>
           <t>一个门店接单工作台主界面实例。</t>
         </is>
       </c>
-      <c r="M22" s="645">
+      <c r="M22" s="657">
         <f>IF(OR(A22="",D22="",F22=""),"",IFERROR(IF(F22="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D22,BaseUnitCatalogTable[基础单元ID],0)),IF(F22="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D22,BaseUnitCatalogTable[基础单元ID],0)),IF(F22="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D22,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N22" s="645">
+      <c r="N22" s="657">
         <f>IF(OR(A22="",H22=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H22,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O22" s="645">
+      <c r="O22" s="657">
         <f>IF(OR(A22="",NOT(ISNUMBER(M22)),NOT(ISNUMBER(N22))),"",ROUND(M22*N22,1))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="641" t="inlineStr">
+      <c r="A23" s="653" t="inlineStr">
         <is>
           <t>task-store-order-service</t>
         </is>
       </c>
-      <c r="B23" s="641" t="inlineStr">
+      <c r="B23" s="653" t="inlineStr">
         <is>
           <t>story-store-order</t>
         </is>
       </c>
-      <c r="C23" s="641" t="inlineStr">
+      <c r="C23" s="653" t="inlineStr">
         <is>
           <t>新建门店接单与交接服务</t>
         </is>
       </c>
-      <c r="D23" s="641" t="inlineStr">
+      <c r="D23" s="653" t="inlineStr">
         <is>
           <t>BU-BUSINESS-SERVICE-API</t>
         </is>
       </c>
-      <c r="E23" s="646">
+      <c r="E23" s="658">
         <f>IF(D23="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D23,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F23" s="642" t="inlineStr">
+      <c r="F23" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G23" s="648" t="inlineStr">
+      <c r="G23" s="660" t="inlineStr">
         <is>
           <t>交付一期顺延的门店接单、缺货替代、权限校验和交接操作。</t>
         </is>
       </c>
-      <c r="H23" s="649" t="inlineStr">
+      <c r="H23" s="661" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I23" s="648" t="inlineStr">
+      <c r="I23" s="660" t="inlineStr">
         <is>
           <t>涉及门店数据隔离、并发抢单、缺货替代和跨班次交接四类复杂规则。</t>
         </is>
       </c>
-      <c r="J23" s="648" t="inlineStr"/>
-      <c r="K23" s="648" t="inlineStr"/>
-      <c r="L23" s="648" t="inlineStr">
+      <c r="J23" s="660" t="inlineStr"/>
+      <c r="K23" s="660" t="inlineStr"/>
+      <c r="L23" s="660" t="inlineStr">
         <is>
           <t>一个门店接单领域服务实例。</t>
         </is>
       </c>
-      <c r="M23" s="645">
+      <c r="M23" s="657">
         <f>IF(OR(A23="",D23="",F23=""),"",IFERROR(IF(F23="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D23,BaseUnitCatalogTable[基础单元ID],0)),IF(F23="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D23,BaseUnitCatalogTable[基础单元ID],0)),IF(F23="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D23,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N23" s="645">
+      <c r="N23" s="657">
         <f>IF(OR(A23="",H23=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H23,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O23" s="645">
+      <c r="O23" s="657">
         <f>IF(OR(A23="",NOT(ISNUMBER(M23)),NOT(ISNUMBER(N23))),"",ROUND(M23*N23,1))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="641" t="inlineStr">
+      <c r="A24" s="653" t="inlineStr">
         <is>
           <t>task-order-timeline-page</t>
         </is>
       </c>
-      <c r="B24" s="641" t="inlineStr">
+      <c r="B24" s="653" t="inlineStr">
         <is>
           <t>story-order-visibility</t>
         </is>
       </c>
-      <c r="C24" s="641" t="inlineStr">
+      <c r="C24" s="653" t="inlineStr">
         <is>
           <t>新建统一订单履约轨迹</t>
         </is>
       </c>
-      <c r="D24" s="641" t="inlineStr">
+      <c r="D24" s="653" t="inlineStr">
         <is>
           <t>BU-UI-INTERACTION</t>
         </is>
       </c>
-      <c r="E24" s="646">
+      <c r="E24" s="658">
         <f>IF(D24="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D24,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F24" s="642" t="inlineStr">
+      <c r="F24" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G24" s="648" t="inlineStr">
+      <c r="G24" s="660" t="inlineStr">
         <is>
           <t>新增顾客与客服共用的状态、履约节点和异常原因时间轴。</t>
         </is>
       </c>
-      <c r="H24" s="649" t="inlineStr">
+      <c r="H24" s="661" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I24" s="648" t="inlineStr">
+      <c r="I24" s="660" t="inlineStr">
         <is>
           <t>单一只读时间轴，复用现有列表组件且无复杂编辑状态。</t>
         </is>
       </c>
-      <c r="J24" s="648" t="inlineStr"/>
-      <c r="K24" s="648" t="inlineStr"/>
-      <c r="L24" s="648" t="inlineStr">
+      <c r="J24" s="660" t="inlineStr"/>
+      <c r="K24" s="660" t="inlineStr"/>
+      <c r="L24" s="660" t="inlineStr">
         <is>
           <t>一个订单履约轨迹界面实例。</t>
         </is>
       </c>
-      <c r="M24" s="645">
+      <c r="M24" s="657">
         <f>IF(OR(A24="",D24="",F24=""),"",IFERROR(IF(F24="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D24,BaseUnitCatalogTable[基础单元ID],0)),IF(F24="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D24,BaseUnitCatalogTable[基础单元ID],0)),IF(F24="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D24,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N24" s="645">
+      <c r="N24" s="657">
         <f>IF(OR(A24="",H24=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H24,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O24" s="645">
+      <c r="O24" s="657">
         <f>IF(OR(A24="",NOT(ISNUMBER(M24)),NOT(ISNUMBER(N24))),"",ROUND(M24*N24,1))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="641" t="inlineStr">
+      <c r="A25" s="653" t="inlineStr">
         <is>
           <t>task-order-timeline-events</t>
         </is>
       </c>
-      <c r="B25" s="641" t="inlineStr">
+      <c r="B25" s="653" t="inlineStr">
         <is>
           <t>story-order-visibility</t>
         </is>
       </c>
-      <c r="C25" s="641" t="inlineStr">
+      <c r="C25" s="653" t="inlineStr">
         <is>
           <t>新建履约轨迹事件投影</t>
         </is>
       </c>
-      <c r="D25" s="641" t="inlineStr">
+      <c r="D25" s="653" t="inlineStr">
         <is>
           <t>BU-EVENT-MESSAGE</t>
         </is>
       </c>
-      <c r="E25" s="646">
+      <c r="E25" s="658">
         <f>IF(D25="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D25,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F25" s="642" t="inlineStr">
+      <c r="F25" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G25" s="648" t="inlineStr">
+      <c r="G25" s="660" t="inlineStr">
         <is>
           <t>新增订单状态事件到渠道可读轨迹的投影与延迟补偿。</t>
         </is>
       </c>
-      <c r="H25" s="649" t="inlineStr">
+      <c r="H25" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I25" s="648" t="inlineStr"/>
-      <c r="J25" s="648" t="inlineStr"/>
-      <c r="K25" s="648" t="inlineStr"/>
-      <c r="L25" s="648" t="inlineStr">
+      <c r="I25" s="660" t="inlineStr"/>
+      <c r="J25" s="660" t="inlineStr"/>
+      <c r="K25" s="660" t="inlineStr"/>
+      <c r="L25" s="660" t="inlineStr">
         <is>
           <t>一个履约轨迹事件消费和投影实例。</t>
         </is>
       </c>
-      <c r="M25" s="645">
+      <c r="M25" s="657">
         <f>IF(OR(A25="",D25="",F25=""),"",IFERROR(IF(F25="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D25,BaseUnitCatalogTable[基础单元ID],0)),IF(F25="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D25,BaseUnitCatalogTable[基础单元ID],0)),IF(F25="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D25,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N25" s="645">
+      <c r="N25" s="657">
         <f>IF(OR(A25="",H25=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H25,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O25" s="645">
+      <c r="O25" s="657">
         <f>IF(OR(A25="",NOT(ISNUMBER(M25)),NOT(ISNUMBER(N25))),"",ROUND(M25*N25,1))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="641" t="inlineStr">
+      <c r="A26" s="653" t="inlineStr">
         <is>
           <t>task-reconciliation-job</t>
         </is>
       </c>
-      <c r="B26" s="641" t="inlineStr">
+      <c r="B26" s="653" t="inlineStr">
         <is>
           <t>story-payment-reconciliation</t>
         </is>
       </c>
-      <c r="C26" s="641" t="inlineStr">
+      <c r="C26" s="653" t="inlineStr">
         <is>
           <t>新建支付退款日结作业</t>
         </is>
       </c>
-      <c r="D26" s="641" t="inlineStr">
+      <c r="D26" s="653" t="inlineStr">
         <is>
           <t>BU-BACKGROUND-JOB</t>
         </is>
       </c>
-      <c r="E26" s="646">
+      <c r="E26" s="658">
         <f>IF(D26="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D26,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F26" s="642" t="inlineStr">
+      <c r="F26" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G26" s="648" t="inlineStr">
+      <c r="G26" s="660" t="inlineStr">
         <is>
           <t>新增每日交易归集、手续费计算、差异识别和失败重跑作业。</t>
         </is>
       </c>
-      <c r="H26" s="649" t="inlineStr">
+      <c r="H26" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I26" s="648" t="inlineStr"/>
-      <c r="J26" s="648" t="inlineStr"/>
-      <c r="K26" s="648" t="inlineStr"/>
-      <c r="L26" s="648" t="inlineStr">
+      <c r="I26" s="660" t="inlineStr"/>
+      <c r="J26" s="660" t="inlineStr"/>
+      <c r="K26" s="660" t="inlineStr"/>
+      <c r="L26" s="660" t="inlineStr">
         <is>
           <t>一个按自然日调度的支付对账后台作业实例。</t>
         </is>
       </c>
-      <c r="M26" s="645">
+      <c r="M26" s="657">
         <f>IF(OR(A26="",D26="",F26=""),"",IFERROR(IF(F26="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D26,BaseUnitCatalogTable[基础单元ID],0)),IF(F26="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D26,BaseUnitCatalogTable[基础单元ID],0)),IF(F26="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D26,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N26" s="645">
+      <c r="N26" s="657">
         <f>IF(OR(A26="",H26=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H26,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O26" s="645">
+      <c r="O26" s="657">
         <f>IF(OR(A26="",NOT(ISNUMBER(M26)),NOT(ISNUMBER(N26))),"",ROUND(M26*N26,1))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="641" t="inlineStr">
+      <c r="A27" s="653" t="inlineStr">
         <is>
           <t>task-reconciliation-report</t>
         </is>
       </c>
-      <c r="B27" s="641" t="inlineStr">
+      <c r="B27" s="653" t="inlineStr">
         <is>
           <t>story-payment-reconciliation</t>
         </is>
       </c>
-      <c r="C27" s="641" t="inlineStr">
+      <c r="C27" s="653" t="inlineStr">
         <is>
           <t>新建支付差异复核视图</t>
         </is>
       </c>
-      <c r="D27" s="641" t="inlineStr">
+      <c r="D27" s="653" t="inlineStr">
         <is>
           <t>BU-REPORT-METRIC</t>
         </is>
       </c>
-      <c r="E27" s="646">
+      <c r="E27" s="658">
         <f>IF(D27="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D27,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F27" s="642" t="inlineStr">
+      <c r="F27" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G27" s="648" t="inlineStr">
+      <c r="G27" s="660" t="inlineStr">
         <is>
           <t>新增按渠道、门店和订单查看实收、退款与手续费差异的财务视图。</t>
         </is>
       </c>
-      <c r="H27" s="649" t="inlineStr">
+      <c r="H27" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I27" s="648" t="inlineStr"/>
-      <c r="J27" s="648" t="inlineStr"/>
-      <c r="K27" s="648" t="inlineStr"/>
-      <c r="L27" s="648" t="inlineStr">
+      <c r="I27" s="660" t="inlineStr"/>
+      <c r="J27" s="660" t="inlineStr"/>
+      <c r="K27" s="660" t="inlineStr"/>
+      <c r="L27" s="660" t="inlineStr">
         <is>
           <t>一个支付日结差异报表实例。</t>
         </is>
       </c>
-      <c r="M27" s="645">
+      <c r="M27" s="657">
         <f>IF(OR(A27="",D27="",F27=""),"",IFERROR(IF(F27="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D27,BaseUnitCatalogTable[基础单元ID],0)),IF(F27="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D27,BaseUnitCatalogTable[基础单元ID],0)),IF(F27="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D27,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N27" s="645">
+      <c r="N27" s="657">
         <f>IF(OR(A27="",H27=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H27,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O27" s="645">
+      <c r="O27" s="657">
         <f>IF(OR(A27="",NOT(ISNUMBER(M27)),NOT(ISNUMBER(N27))),"",ROUND(M27*N27,1))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="641" t="inlineStr">
+      <c r="A28" s="653" t="inlineStr">
         <is>
           <t>task-einvoice-integration</t>
         </is>
       </c>
-      <c r="B28" s="641" t="inlineStr">
+      <c r="B28" s="653" t="inlineStr">
         <is>
           <t>story-einvoice</t>
         </is>
       </c>
-      <c r="C28" s="641" t="inlineStr">
+      <c r="C28" s="653" t="inlineStr">
         <is>
           <t>接入既有电子发票通道</t>
         </is>
       </c>
-      <c r="D28" s="641" t="inlineStr">
+      <c r="D28" s="653" t="inlineStr">
         <is>
           <t>BU-EXTERNAL-INTEGRATION</t>
         </is>
       </c>
-      <c r="E28" s="646">
+      <c r="E28" s="658">
         <f>IF(D28="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D28,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F28" s="642" t="inlineStr">
+      <c r="F28" s="654" t="inlineStr">
         <is>
           <t>接入复用</t>
         </is>
       </c>
-      <c r="G28" s="648" t="inlineStr">
+      <c r="G28" s="660" t="inlineStr">
         <is>
           <t>既有电子发票通道保持不变；本项目负责并交付：配置、映射、适配、认证、租户设置、专项验证。</t>
         </is>
       </c>
-      <c r="H28" s="649" t="inlineStr">
+      <c r="H28" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I28" s="648" t="inlineStr"/>
-      <c r="J28" s="648" t="inlineStr">
+      <c r="I28" s="660" t="inlineStr"/>
+      <c r="J28" s="660" t="inlineStr">
         <is>
           <t>integration-einvoice</t>
         </is>
       </c>
-      <c r="K28" s="648" t="inlineStr">
+      <c r="K28" s="660" t="inlineStr">
         <is>
           <t>effective-start-invoice-gateway</t>
         </is>
       </c>
-      <c r="L28" s="648" t="inlineStr">
+      <c r="L28" s="660" t="inlineStr">
         <is>
           <t>实现一个已登记的外部电子发票 Integration，并单列外部支持成本。</t>
         </is>
       </c>
-      <c r="M28" s="645">
+      <c r="M28" s="657">
         <f>IF(OR(A28="",D28="",F28=""),"",IFERROR(IF(F28="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D28,BaseUnitCatalogTable[基础单元ID],0)),IF(F28="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D28,BaseUnitCatalogTable[基础单元ID],0)),IF(F28="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D28,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N28" s="645">
+      <c r="N28" s="657">
         <f>IF(OR(A28="",H28=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H28,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O28" s="645">
+      <c r="O28" s="657">
         <f>IF(OR(A28="",NOT(ISNUMBER(M28)),NOT(ISNUMBER(N28))),"",ROUND(M28*N28,1))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="641" t="inlineStr">
+      <c r="A29" s="653" t="inlineStr">
         <is>
           <t>task-einvoice-status-job</t>
         </is>
       </c>
-      <c r="B29" s="641" t="inlineStr">
+      <c r="B29" s="653" t="inlineStr">
         <is>
           <t>story-einvoice</t>
         </is>
       </c>
-      <c r="C29" s="641" t="inlineStr">
+      <c r="C29" s="653" t="inlineStr">
         <is>
           <t>新建发票状态补偿作业</t>
         </is>
       </c>
-      <c r="D29" s="641" t="inlineStr">
+      <c r="D29" s="653" t="inlineStr">
         <is>
           <t>BU-BACKGROUND-JOB</t>
         </is>
       </c>
-      <c r="E29" s="646">
+      <c r="E29" s="658">
         <f>IF(D29="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D29,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F29" s="642" t="inlineStr">
+      <c r="F29" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G29" s="648" t="inlineStr">
+      <c r="G29" s="660" t="inlineStr">
         <is>
           <t>新增开票状态轮询、失败重试、重复申请拦截和结果回写作业。</t>
         </is>
       </c>
-      <c r="H29" s="649" t="inlineStr">
+      <c r="H29" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I29" s="648" t="inlineStr"/>
-      <c r="J29" s="648" t="inlineStr"/>
-      <c r="K29" s="648" t="inlineStr"/>
-      <c r="L29" s="648" t="inlineStr">
+      <c r="I29" s="660" t="inlineStr"/>
+      <c r="J29" s="660" t="inlineStr"/>
+      <c r="K29" s="660" t="inlineStr"/>
+      <c r="L29" s="660" t="inlineStr">
         <is>
           <t>一个电子发票状态补偿后台作业实例。</t>
         </is>
       </c>
-      <c r="M29" s="645">
+      <c r="M29" s="657">
         <f>IF(OR(A29="",D29="",F29=""),"",IFERROR(IF(F29="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D29,BaseUnitCatalogTable[基础单元ID],0)),IF(F29="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D29,BaseUnitCatalogTable[基础单元ID],0)),IF(F29="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D29,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N29" s="645">
+      <c r="N29" s="657">
         <f>IF(OR(A29="",H29=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H29,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O29" s="645">
+      <c r="O29" s="657">
         <f>IF(OR(A29="",NOT(ISNUMBER(M29)),NOT(ISNUMBER(N29))),"",ROUND(M29*N29,1))</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="641" t="inlineStr">
+      <c r="A30" s="653" t="inlineStr">
         <is>
           <t>task-finance-report</t>
         </is>
       </c>
-      <c r="B30" s="641" t="inlineStr">
+      <c r="B30" s="653" t="inlineStr">
         <is>
           <t>story-finance-report</t>
         </is>
       </c>
-      <c r="C30" s="641" t="inlineStr">
+      <c r="C30" s="653" t="inlineStr">
         <is>
           <t>新建财务经营日报</t>
         </is>
       </c>
-      <c r="D30" s="641" t="inlineStr">
+      <c r="D30" s="653" t="inlineStr">
         <is>
           <t>BU-REPORT-METRIC</t>
         </is>
       </c>
-      <c r="E30" s="646">
+      <c r="E30" s="658">
         <f>IF(D30="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D30,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F30" s="642" t="inlineStr">
+      <c r="F30" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G30" s="648" t="inlineStr">
+      <c r="G30" s="660" t="inlineStr">
         <is>
           <t>新增销售、退款、优惠和未对账金额的多维指标与下钻。</t>
         </is>
       </c>
-      <c r="H30" s="649" t="inlineStr">
+      <c r="H30" s="661" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I30" s="648" t="inlineStr">
+      <c r="I30" s="660" t="inlineStr">
         <is>
           <t>包含四类金额、日期区域渠道三维切片、逐笔下钻和财务口径校验。</t>
         </is>
       </c>
-      <c r="J30" s="648" t="inlineStr"/>
-      <c r="K30" s="648" t="inlineStr"/>
-      <c r="L30" s="648" t="inlineStr">
+      <c r="J30" s="660" t="inlineStr"/>
+      <c r="K30" s="660" t="inlineStr"/>
+      <c r="L30" s="660" t="inlineStr">
         <is>
           <t>一个财务经营日报与指标集合实例。</t>
         </is>
       </c>
-      <c r="M30" s="645">
+      <c r="M30" s="657">
         <f>IF(OR(A30="",D30="",F30=""),"",IFERROR(IF(F30="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D30,BaseUnitCatalogTable[基础单元ID],0)),IF(F30="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D30,BaseUnitCatalogTable[基础单元ID],0)),IF(F30="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D30,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N30" s="645">
+      <c r="N30" s="657">
         <f>IF(OR(A30="",H30=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H30,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O30" s="645">
+      <c r="O30" s="657">
         <f>IF(OR(A30="",NOT(ISNUMBER(M30)),NOT(ISNUMBER(N30))),"",ROUND(M30*N30,1))</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="641" t="inlineStr">
+      <c r="A31" s="653" t="inlineStr">
         <is>
           <t>task-finance-pipeline</t>
         </is>
       </c>
-      <c r="B31" s="641" t="inlineStr">
+      <c r="B31" s="653" t="inlineStr">
         <is>
           <t>story-finance-report</t>
         </is>
       </c>
-      <c r="C31" s="641" t="inlineStr">
+      <c r="C31" s="653" t="inlineStr">
         <is>
           <t>新建财务指标处理流程</t>
         </is>
       </c>
-      <c r="D31" s="641" t="inlineStr">
+      <c r="D31" s="653" t="inlineStr">
         <is>
           <t>BU-DATA-PIPELINE</t>
         </is>
       </c>
-      <c r="E31" s="646">
+      <c r="E31" s="658">
         <f>IF(D31="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D31,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F31" s="642" t="inlineStr">
+      <c r="F31" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G31" s="648" t="inlineStr">
+      <c r="G31" s="660" t="inlineStr">
         <is>
           <t>新增订单、支付、退款和发票明细的清洗、关联与日汇总流程。</t>
         </is>
       </c>
-      <c r="H31" s="649" t="inlineStr">
+      <c r="H31" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I31" s="648" t="inlineStr"/>
-      <c r="J31" s="648" t="inlineStr"/>
-      <c r="K31" s="648" t="inlineStr"/>
-      <c r="L31" s="648" t="inlineStr">
+      <c r="I31" s="660" t="inlineStr"/>
+      <c r="J31" s="660" t="inlineStr"/>
+      <c r="K31" s="660" t="inlineStr"/>
+      <c r="L31" s="660" t="inlineStr">
         <is>
           <t>一个财务指标数据处理流程实例。</t>
         </is>
       </c>
-      <c r="M31" s="645">
+      <c r="M31" s="657">
         <f>IF(OR(A31="",D31="",F31=""),"",IFERROR(IF(F31="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D31,BaseUnitCatalogTable[基础单元ID],0)),IF(F31="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D31,BaseUnitCatalogTable[基础单元ID],0)),IF(F31="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D31,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N31" s="645">
+      <c r="N31" s="657">
         <f>IF(OR(A31="",H31=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H31,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O31" s="645">
+      <c r="O31" s="657">
         <f>IF(OR(A31="",NOT(ISNUMBER(M31)),NOT(ISNUMBER(N31))),"",ROUND(M31*N31,1))</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="641" t="inlineStr">
+      <c r="A32" s="653" t="inlineStr">
         <is>
           <t>task-production-env</t>
         </is>
       </c>
-      <c r="B32" s="641" t="inlineStr">
+      <c r="B32" s="653" t="inlineStr">
         <is>
           <t>story-production-preparation</t>
         </is>
       </c>
-      <c r="C32" s="641" t="inlineStr">
+      <c r="C32" s="653" t="inlineStr">
         <is>
           <t>调整既有生产环境与发布流水线的运行配置</t>
         </is>
       </c>
-      <c r="D32" s="641" t="inlineStr">
+      <c r="D32" s="653" t="inlineStr">
         <is>
           <t>BU-RUNTIME-ENV</t>
         </is>
       </c>
-      <c r="E32" s="646">
+      <c r="E32" s="658">
         <f>IF(D32="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D32,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F32" s="642" t="inlineStr">
+      <c r="F32" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G32" s="648" t="inlineStr">
+      <c r="G32" s="660" t="inlineStr">
         <is>
           <t>在既有生产环境与发布流水线中增加会员、订单、批处理和外部证书配置。</t>
         </is>
       </c>
-      <c r="H32" s="649" t="inlineStr">
+      <c r="H32" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I32" s="648" t="inlineStr"/>
-      <c r="J32" s="648" t="inlineStr"/>
-      <c r="K32" s="648" t="inlineStr">
+      <c r="I32" s="660" t="inlineStr"/>
+      <c r="J32" s="660" t="inlineStr"/>
+      <c r="K32" s="660" t="inlineStr">
         <is>
           <t>effective-start-deployment-platform</t>
         </is>
       </c>
-      <c r="L32" s="648" t="inlineStr">
+      <c r="L32" s="660" t="inlineStr">
         <is>
           <t>一个生产运行环境配置实例。</t>
         </is>
       </c>
-      <c r="M32" s="645">
+      <c r="M32" s="657">
         <f>IF(OR(A32="",D32="",F32=""),"",IFERROR(IF(F32="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D32,BaseUnitCatalogTable[基础单元ID],0)),IF(F32="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D32,BaseUnitCatalogTable[基础单元ID],0)),IF(F32="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D32,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N32" s="645">
+      <c r="N32" s="657">
         <f>IF(OR(A32="",H32=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H32,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O32" s="645">
+      <c r="O32" s="657">
         <f>IF(OR(A32="",NOT(ISNUMBER(M32)),NOT(ISNUMBER(N32))),"",ROUND(M32*N32,1))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="641" t="inlineStr">
+      <c r="A33" s="653" t="inlineStr">
         <is>
           <t>task-production-pipeline</t>
         </is>
       </c>
-      <c r="B33" s="641" t="inlineStr">
+      <c r="B33" s="653" t="inlineStr">
         <is>
           <t>story-production-preparation</t>
         </is>
       </c>
-      <c r="C33" s="641" t="inlineStr">
+      <c r="C33" s="653" t="inlineStr">
         <is>
           <t>调整既有生产环境与发布流水线的部署步骤</t>
         </is>
       </c>
-      <c r="D33" s="641" t="inlineStr">
+      <c r="D33" s="653" t="inlineStr">
         <is>
           <t>BU-BUILD-DEPLOY-PIPELINE</t>
         </is>
       </c>
-      <c r="E33" s="646">
+      <c r="E33" s="658">
         <f>IF(D33="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D33,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F33" s="642" t="inlineStr">
+      <c r="F33" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G33" s="648" t="inlineStr">
+      <c r="G33" s="660" t="inlineStr">
         <is>
           <t>扩展既有生产环境与发布流水线，增加迁移前检查、分步发布和验证门禁。</t>
         </is>
       </c>
-      <c r="H33" s="649" t="inlineStr">
+      <c r="H33" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I33" s="648" t="inlineStr"/>
-      <c r="J33" s="648" t="inlineStr"/>
-      <c r="K33" s="648" t="inlineStr">
+      <c r="I33" s="660" t="inlineStr"/>
+      <c r="J33" s="660" t="inlineStr"/>
+      <c r="K33" s="660" t="inlineStr">
         <is>
           <t>effective-start-deployment-platform</t>
         </is>
       </c>
-      <c r="L33" s="648" t="inlineStr">
+      <c r="L33" s="660" t="inlineStr">
         <is>
           <t>一个应用构建与部署流水线调整实例。</t>
         </is>
       </c>
-      <c r="M33" s="645">
+      <c r="M33" s="657">
         <f>IF(OR(A33="",D33="",F33=""),"",IFERROR(IF(F33="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D33,BaseUnitCatalogTable[基础单元ID],0)),IF(F33="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D33,BaseUnitCatalogTable[基础单元ID],0)),IF(F33="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D33,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N33" s="645">
+      <c r="N33" s="657">
         <f>IF(OR(A33="",H33=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H33,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O33" s="645">
+      <c r="O33" s="657">
         <f>IF(OR(A33="",NOT(ISNUMBER(M33)),NOT(ISNUMBER(N33))),"",ROUND(M33*N33,1))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="641" t="inlineStr">
+      <c r="A34" s="653" t="inlineStr">
         <is>
           <t>task-production-feature-flag</t>
         </is>
       </c>
-      <c r="B34" s="641" t="inlineStr">
+      <c r="B34" s="653" t="inlineStr">
         <is>
           <t>story-production-preparation</t>
         </is>
       </c>
-      <c r="C34" s="641" t="inlineStr">
+      <c r="C34" s="653" t="inlineStr">
         <is>
           <t>调整既有生产环境与发布流水线的功能开关</t>
         </is>
       </c>
-      <c r="D34" s="641" t="inlineStr">
+      <c r="D34" s="653" t="inlineStr">
         <is>
           <t>BU-CONFIG-FEATURE-FLAG</t>
         </is>
       </c>
-      <c r="E34" s="646">
+      <c r="E34" s="658">
         <f>IF(D34="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D34,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F34" s="642" t="inlineStr">
+      <c r="F34" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G34" s="648" t="inlineStr">
+      <c r="G34" s="660" t="inlineStr">
         <is>
           <t>在既有生产环境与发布流水线中配置渠道切流、退款和开票功能开关。</t>
         </is>
       </c>
-      <c r="H34" s="649" t="inlineStr">
+      <c r="H34" s="661" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I34" s="648" t="inlineStr">
+      <c r="I34" s="660" t="inlineStr">
         <is>
           <t>三个独立布尔开关及默认值，沿用现有配置中心且无复杂灰度算法。</t>
         </is>
       </c>
-      <c r="J34" s="648" t="inlineStr"/>
-      <c r="K34" s="648" t="inlineStr">
+      <c r="J34" s="660" t="inlineStr"/>
+      <c r="K34" s="660" t="inlineStr">
         <is>
           <t>effective-start-deployment-platform</t>
         </is>
       </c>
-      <c r="L34" s="648" t="inlineStr">
+      <c r="L34" s="660" t="inlineStr">
         <is>
           <t>一个上线功能开关配置实例。</t>
         </is>
       </c>
-      <c r="M34" s="645">
+      <c r="M34" s="657">
         <f>IF(OR(A34="",D34="",F34=""),"",IFERROR(IF(F34="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D34,BaseUnitCatalogTable[基础单元ID],0)),IF(F34="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D34,BaseUnitCatalogTable[基础单元ID],0)),IF(F34="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D34,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N34" s="645">
+      <c r="N34" s="657">
         <f>IF(OR(A34="",H34=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H34,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O34" s="645">
+      <c r="O34" s="657">
         <f>IF(OR(A34="",NOT(ISNUMBER(M34)),NOT(ISNUMBER(N34))),"",ROUND(M34*N34,1))</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="641" t="inlineStr">
+      <c r="A35" s="653" t="inlineStr">
         <is>
           <t>task-production-cutover</t>
         </is>
       </c>
-      <c r="B35" s="641" t="inlineStr">
+      <c r="B35" s="653" t="inlineStr">
         <is>
           <t>story-production-cutover</t>
         </is>
       </c>
-      <c r="C35" s="641" t="inlineStr">
+      <c r="C35" s="653" t="inlineStr">
         <is>
           <t>执行生产切换与回滚</t>
         </is>
       </c>
-      <c r="D35" s="641" t="inlineStr">
+      <c r="D35" s="653" t="inlineStr">
         <is>
           <t>BU-RELEASE-CUTOVER</t>
         </is>
       </c>
-      <c r="E35" s="646">
+      <c r="E35" s="658">
         <f>IF(D35="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D35,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F35" s="642" t="inlineStr">
+      <c r="F35" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G35" s="648" t="inlineStr">
+      <c r="G35" s="660" t="inlineStr">
         <is>
           <t>基于既有生产环境与发布流水线编制并执行分步切流、检查点和回滚清单。</t>
         </is>
       </c>
-      <c r="H35" s="649" t="inlineStr">
+      <c r="H35" s="661" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I35" s="648" t="inlineStr">
+      <c r="I35" s="660" t="inlineStr">
         <is>
           <t>涉及会员、订单、四个集成链路、迁移窗口、三次继续回滚决策和多团队协同。</t>
         </is>
       </c>
-      <c r="J35" s="648" t="inlineStr"/>
-      <c r="K35" s="648" t="inlineStr">
+      <c r="J35" s="660" t="inlineStr"/>
+      <c r="K35" s="660" t="inlineStr">
         <is>
           <t>effective-start-deployment-platform</t>
         </is>
       </c>
-      <c r="L35" s="648" t="inlineStr">
+      <c r="L35" s="660" t="inlineStr">
         <is>
           <t>一个批准上线窗口内的生产发布切换实例。</t>
         </is>
       </c>
-      <c r="M35" s="645">
+      <c r="M35" s="657">
         <f>IF(OR(A35="",D35="",F35=""),"",IFERROR(IF(F35="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D35,BaseUnitCatalogTable[基础单元ID],0)),IF(F35="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D35,BaseUnitCatalogTable[基础单元ID],0)),IF(F35="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D35,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N35" s="645">
+      <c r="N35" s="657">
         <f>IF(OR(A35="",H35=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H35,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O35" s="645">
+      <c r="O35" s="657">
         <f>IF(OR(A35="",NOT(ISNUMBER(M35)),NOT(ISNUMBER(N35))),"",ROUND(M35*N35,1))</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="641" t="inlineStr">
+      <c r="A36" s="653" t="inlineStr">
         <is>
           <t>task-cutover-checklist-test</t>
         </is>
       </c>
-      <c r="B36" s="641" t="inlineStr">
+      <c r="B36" s="653" t="inlineStr">
         <is>
           <t>story-production-cutover</t>
         </is>
       </c>
-      <c r="C36" s="641" t="inlineStr">
+      <c r="C36" s="653" t="inlineStr">
         <is>
           <t>验证切换与回滚检查清单</t>
         </is>
       </c>
-      <c r="D36" s="641" t="inlineStr">
+      <c r="D36" s="653" t="inlineStr">
         <is>
           <t>BU-MANUAL-TESTING</t>
         </is>
       </c>
-      <c r="E36" s="646">
+      <c r="E36" s="658">
         <f>IF(D36="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D36,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F36" s="642" t="inlineStr">
+      <c r="F36" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G36" s="648" t="inlineStr">
+      <c r="G36" s="660" t="inlineStr">
         <is>
           <t>新增切换前置条件、检查点、回滚触发器和联系人桌面演练。</t>
         </is>
       </c>
-      <c r="H36" s="649" t="inlineStr">
+      <c r="H36" s="661" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I36" s="648" t="inlineStr">
+      <c r="I36" s="660" t="inlineStr">
         <is>
           <t>一次桌面演练和一套固定清单，不涉及额外环境或大规模数据准备。</t>
         </is>
       </c>
-      <c r="J36" s="648" t="inlineStr"/>
-      <c r="K36" s="648" t="inlineStr"/>
-      <c r="L36" s="648" t="inlineStr">
+      <c r="J36" s="660" t="inlineStr"/>
+      <c r="K36" s="660" t="inlineStr"/>
+      <c r="L36" s="660" t="inlineStr">
         <is>
           <t>一个切换回滚清单验证实例。</t>
         </is>
       </c>
-      <c r="M36" s="645">
+      <c r="M36" s="657">
         <f>IF(OR(A36="",D36="",F36=""),"",IFERROR(IF(F36="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D36,BaseUnitCatalogTable[基础单元ID],0)),IF(F36="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D36,BaseUnitCatalogTable[基础单元ID],0)),IF(F36="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D36,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N36" s="645">
+      <c r="N36" s="657">
         <f>IF(OR(A36="",H36=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H36,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O36" s="645">
+      <c r="O36" s="657">
         <f>IF(OR(A36="",NOT(ISNUMBER(M36)),NOT(ISNUMBER(N36))),"",ROUND(M36*N36,1))</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="641" t="inlineStr">
+      <c r="A37" s="653" t="inlineStr">
         <is>
           <t>task-production-performance</t>
         </is>
       </c>
-      <c r="B37" s="641" t="inlineStr">
+      <c r="B37" s="653" t="inlineStr">
         <is>
           <t>story-production-validation</t>
         </is>
       </c>
-      <c r="C37" s="641" t="inlineStr">
+      <c r="C37" s="653" t="inlineStr">
         <is>
           <t>执行核心查询性能验证</t>
         </is>
       </c>
-      <c r="D37" s="641" t="inlineStr">
+      <c r="D37" s="653" t="inlineStr">
         <is>
           <t>BU-PERFORMANCE-TESTING</t>
         </is>
       </c>
-      <c r="E37" s="646">
+      <c r="E37" s="658">
         <f>IF(D37="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D37,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F37" s="642" t="inlineStr">
+      <c r="F37" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G37" s="648" t="inlineStr">
+      <c r="G37" s="660" t="inlineStr">
         <is>
           <t>新增档案查询、订单创建和轨迹查询的峰值负载与稳定性验证。</t>
         </is>
       </c>
-      <c r="H37" s="649" t="inlineStr">
+      <c r="H37" s="661" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I37" s="648" t="inlineStr">
+      <c r="I37" s="660" t="inlineStr">
         <is>
           <t>三条核心链路、500 TPS 峰值、两小时稳定性和容量拐点分析需要多轮调优。</t>
         </is>
       </c>
-      <c r="J37" s="648" t="inlineStr"/>
-      <c r="K37" s="648" t="inlineStr"/>
-      <c r="L37" s="648" t="inlineStr">
+      <c r="J37" s="660" t="inlineStr"/>
+      <c r="K37" s="660" t="inlineStr"/>
+      <c r="L37" s="660" t="inlineStr">
         <is>
           <t>一个生产前性能与容量测试实例。</t>
         </is>
       </c>
-      <c r="M37" s="645">
+      <c r="M37" s="657">
         <f>IF(OR(A37="",D37="",F37=""),"",IFERROR(IF(F37="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D37,BaseUnitCatalogTable[基础单元ID],0)),IF(F37="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D37,BaseUnitCatalogTable[基础单元ID],0)),IF(F37="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D37,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N37" s="645">
+      <c r="N37" s="657">
         <f>IF(OR(A37="",H37=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H37,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O37" s="645">
+      <c r="O37" s="657">
         <f>IF(OR(A37="",NOT(ISNUMBER(M37)),NOT(ISNUMBER(N37))),"",ROUND(M37*N37,1))</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="641" t="inlineStr">
+      <c r="A38" s="653" t="inlineStr">
         <is>
           <t>task-production-security</t>
         </is>
       </c>
-      <c r="B38" s="641" t="inlineStr">
+      <c r="B38" s="653" t="inlineStr">
         <is>
           <t>story-production-validation</t>
         </is>
       </c>
-      <c r="C38" s="641" t="inlineStr">
+      <c r="C38" s="653" t="inlineStr">
         <is>
           <t>执行生产权限与证书验证</t>
         </is>
       </c>
-      <c r="D38" s="641" t="inlineStr">
+      <c r="D38" s="653" t="inlineStr">
         <is>
           <t>BU-SECURITY-PRIVACY-TESTING</t>
         </is>
       </c>
-      <c r="E38" s="646">
+      <c r="E38" s="658">
         <f>IF(D38="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D38,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F38" s="642" t="inlineStr">
+      <c r="F38" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G38" s="648" t="inlineStr">
+      <c r="G38" s="660" t="inlineStr">
         <is>
           <t>新增生产角色最小权限、外部证书、密钥轮换和敏感字段脱敏检查。</t>
         </is>
       </c>
-      <c r="H38" s="649" t="inlineStr">
+      <c r="H38" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I38" s="648" t="inlineStr"/>
-      <c r="J38" s="648" t="inlineStr"/>
-      <c r="K38" s="648" t="inlineStr"/>
-      <c r="L38" s="648" t="inlineStr">
+      <c r="I38" s="660" t="inlineStr"/>
+      <c r="J38" s="660" t="inlineStr"/>
+      <c r="K38" s="660" t="inlineStr"/>
+      <c r="L38" s="660" t="inlineStr">
         <is>
           <t>一个生产安全与隐私验证实例。</t>
         </is>
       </c>
-      <c r="M38" s="645">
+      <c r="M38" s="657">
         <f>IF(OR(A38="",D38="",F38=""),"",IFERROR(IF(F38="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D38,BaseUnitCatalogTable[基础单元ID],0)),IF(F38="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D38,BaseUnitCatalogTable[基础单元ID],0)),IF(F38="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D38,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N38" s="645">
+      <c r="N38" s="657">
         <f>IF(OR(A38="",H38=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H38,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O38" s="645">
+      <c r="O38" s="657">
         <f>IF(OR(A38="",NOT(ISNUMBER(M38)),NOT(ISNUMBER(N38))),"",ROUND(M38*N38,1))</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="641" t="inlineStr">
+      <c r="A39" s="653" t="inlineStr">
         <is>
           <t>task-production-smoke</t>
         </is>
       </c>
-      <c r="B39" s="641" t="inlineStr">
+      <c r="B39" s="653" t="inlineStr">
         <is>
           <t>story-production-validation</t>
         </is>
       </c>
-      <c r="C39" s="641" t="inlineStr">
+      <c r="C39" s="653" t="inlineStr">
         <is>
           <t>执行五条生产业务烟测</t>
         </is>
       </c>
-      <c r="D39" s="641" t="inlineStr">
+      <c r="D39" s="653" t="inlineStr">
         <is>
           <t>BU-MANUAL-TESTING</t>
         </is>
       </c>
-      <c r="E39" s="646">
+      <c r="E39" s="658">
         <f>IF(D39="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D39,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F39" s="642" t="inlineStr">
+      <c r="F39" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G39" s="648" t="inlineStr">
+      <c r="G39" s="660" t="inlineStr">
         <is>
           <t>新增档案、下单、退款、开票和对账五条生产烟测并留存证据。</t>
         </is>
       </c>
-      <c r="H39" s="649" t="inlineStr">
+      <c r="H39" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I39" s="648" t="inlineStr"/>
-      <c r="J39" s="648" t="inlineStr"/>
-      <c r="K39" s="648" t="inlineStr"/>
-      <c r="L39" s="648" t="inlineStr">
+      <c r="I39" s="660" t="inlineStr"/>
+      <c r="J39" s="660" t="inlineStr"/>
+      <c r="K39" s="660" t="inlineStr"/>
+      <c r="L39" s="660" t="inlineStr">
         <is>
           <t>一个生产关键业务链路烟测实例。</t>
         </is>
       </c>
-      <c r="M39" s="645">
+      <c r="M39" s="657">
         <f>IF(OR(A39="",D39="",F39=""),"",IFERROR(IF(F39="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D39,BaseUnitCatalogTable[基础单元ID],0)),IF(F39="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D39,BaseUnitCatalogTable[基础单元ID],0)),IF(F39="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D39,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N39" s="645">
+      <c r="N39" s="657">
         <f>IF(OR(A39="",H39=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H39,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O39" s="645">
+      <c r="O39" s="657">
         <f>IF(OR(A39="",NOT(ISNUMBER(M39)),NOT(ISNUMBER(N39))),"",ROUND(M39*N39,1))</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="641" t="inlineStr">
+      <c r="A40" s="653" t="inlineStr">
         <is>
           <t>task-data-migration</t>
         </is>
       </c>
-      <c r="B40" s="641" t="inlineStr">
+      <c r="B40" s="653" t="inlineStr">
         <is>
           <t>story-data-migration</t>
         </is>
       </c>
-      <c r="C40" s="641" t="inlineStr">
+      <c r="C40" s="653" t="inlineStr">
         <is>
           <t>迁移会员与两年历史订单</t>
         </is>
       </c>
-      <c r="D40" s="641" t="inlineStr">
+      <c r="D40" s="653" t="inlineStr">
         <is>
           <t>BU-DATA-MIGRATION</t>
         </is>
       </c>
-      <c r="E40" s="646">
+      <c r="E40" s="658">
         <f>IF(D40="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D40,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F40" s="642" t="inlineStr">
+      <c r="F40" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G40" s="648" t="inlineStr">
+      <c r="G40" s="660" t="inlineStr">
         <is>
           <t>从既有会员主数据模型和既有订单服务与状态机抽取数据，执行映射、加载、校验和补偿。</t>
         </is>
       </c>
-      <c r="H40" s="649" t="inlineStr">
+      <c r="H40" s="661" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I40" s="648" t="inlineStr">
+      <c r="I40" s="660" t="inlineStr">
         <is>
           <t>涉及两类源数据、约 1200 万订单行、历史状态映射、增量窗口和失败补偿。</t>
         </is>
       </c>
-      <c r="J40" s="648" t="inlineStr"/>
-      <c r="K40" s="648" t="inlineStr">
+      <c r="J40" s="660" t="inlineStr"/>
+      <c r="K40" s="660" t="inlineStr">
         <is>
           <t>effective-start-member-master、effective-start-order-service</t>
         </is>
       </c>
-      <c r="L40" s="648" t="inlineStr">
+      <c r="L40" s="660" t="inlineStr">
         <is>
           <t>一个会员与订单迁移批次方案实例，与发布切换分别估算。</t>
         </is>
       </c>
-      <c r="M40" s="645">
+      <c r="M40" s="657">
         <f>IF(OR(A40="",D40="",F40=""),"",IFERROR(IF(F40="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D40,BaseUnitCatalogTable[基础单元ID],0)),IF(F40="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D40,BaseUnitCatalogTable[基础单元ID],0)),IF(F40="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D40,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N40" s="645">
+      <c r="N40" s="657">
         <f>IF(OR(A40="",H40=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H40,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O40" s="645">
+      <c r="O40" s="657">
         <f>IF(OR(A40="",NOT(ISNUMBER(M40)),NOT(ISNUMBER(N40))),"",ROUND(M40*N40,1))</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="641" t="inlineStr">
+      <c r="A41" s="653" t="inlineStr">
         <is>
           <t>task-migration-pipeline</t>
         </is>
       </c>
-      <c r="B41" s="641" t="inlineStr">
+      <c r="B41" s="653" t="inlineStr">
         <is>
           <t>story-data-migration</t>
         </is>
       </c>
-      <c r="C41" s="641" t="inlineStr">
+      <c r="C41" s="653" t="inlineStr">
         <is>
           <t>新建迁移抽取转换流程</t>
         </is>
       </c>
-      <c r="D41" s="641" t="inlineStr">
+      <c r="D41" s="653" t="inlineStr">
         <is>
           <t>BU-DATA-PIPELINE</t>
         </is>
       </c>
-      <c r="E41" s="646">
+      <c r="E41" s="658">
         <f>IF(D41="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D41,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F41" s="642" t="inlineStr">
+      <c r="F41" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G41" s="648" t="inlineStr">
+      <c r="G41" s="660" t="inlineStr">
         <is>
           <t>新增全量与增量抽取、字段标准化、状态映射和失败重放流程。</t>
         </is>
       </c>
-      <c r="H41" s="649" t="inlineStr">
+      <c r="H41" s="661" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I41" s="648" t="inlineStr">
+      <c r="I41" s="660" t="inlineStr">
         <is>
           <t>包含全量与增量两条路径、跨版本状态映射、断点续传和可重复执行控制。</t>
         </is>
       </c>
-      <c r="J41" s="648" t="inlineStr"/>
-      <c r="K41" s="648" t="inlineStr"/>
-      <c r="L41" s="648" t="inlineStr">
+      <c r="J41" s="660" t="inlineStr"/>
+      <c r="K41" s="660" t="inlineStr"/>
+      <c r="L41" s="660" t="inlineStr">
         <is>
           <t>一个可重复执行的数据迁移处理流程实例。</t>
         </is>
       </c>
-      <c r="M41" s="645">
+      <c r="M41" s="657">
         <f>IF(OR(A41="",D41="",F41=""),"",IFERROR(IF(F41="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D41,BaseUnitCatalogTable[基础单元ID],0)),IF(F41="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D41,BaseUnitCatalogTable[基础单元ID],0)),IF(F41="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D41,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N41" s="645">
+      <c r="N41" s="657">
         <f>IF(OR(A41="",H41=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H41,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O41" s="645">
+      <c r="O41" s="657">
         <f>IF(OR(A41="",NOT(ISNUMBER(M41)),NOT(ISNUMBER(N41))),"",ROUND(M41*N41,1))</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="641" t="inlineStr">
+      <c r="A42" s="653" t="inlineStr">
         <is>
           <t>task-migration-reconciliation</t>
         </is>
       </c>
-      <c r="B42" s="641" t="inlineStr">
+      <c r="B42" s="653" t="inlineStr">
         <is>
           <t>story-data-migration</t>
         </is>
       </c>
-      <c r="C42" s="641" t="inlineStr">
+      <c r="C42" s="653" t="inlineStr">
         <is>
           <t>验证迁移数量与关键字段</t>
         </is>
       </c>
-      <c r="D42" s="641" t="inlineStr">
+      <c r="D42" s="653" t="inlineStr">
         <is>
           <t>BU-MANUAL-TESTING</t>
         </is>
       </c>
-      <c r="E42" s="646">
+      <c r="E42" s="658">
         <f>IF(D42="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D42,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F42" s="642" t="inlineStr">
+      <c r="F42" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G42" s="648" t="inlineStr">
+      <c r="G42" s="660" t="inlineStr">
         <is>
           <t>新增数量、金额、业务主键、抽样字段和失败补偿核对场景。</t>
         </is>
       </c>
-      <c r="H42" s="649" t="inlineStr">
+      <c r="H42" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I42" s="648" t="inlineStr"/>
-      <c r="J42" s="648" t="inlineStr"/>
-      <c r="K42" s="648" t="inlineStr"/>
-      <c r="L42" s="648" t="inlineStr">
+      <c r="I42" s="660" t="inlineStr"/>
+      <c r="J42" s="660" t="inlineStr"/>
+      <c r="K42" s="660" t="inlineStr"/>
+      <c r="L42" s="660" t="inlineStr">
         <is>
           <t>一个迁移核对与业务签署测试实例。</t>
         </is>
       </c>
-      <c r="M42" s="645">
+      <c r="M42" s="657">
         <f>IF(OR(A42="",D42="",F42=""),"",IFERROR(IF(F42="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D42,BaseUnitCatalogTable[基础单元ID],0)),IF(F42="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D42,BaseUnitCatalogTable[基础单元ID],0)),IF(F42="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D42,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N42" s="645">
+      <c r="N42" s="657">
         <f>IF(OR(A42="",H42=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H42,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O42" s="645">
+      <c r="O42" s="657">
         <f>IF(OR(A42="",NOT(ISNUMBER(M42)),NOT(ISNUMBER(N42))),"",ROUND(M42*N42,1))</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="641" t="inlineStr">
+      <c r="A43" s="653" t="inlineStr">
         <is>
           <t>task-observability-dashboard</t>
         </is>
       </c>
-      <c r="B43" s="641" t="inlineStr">
+      <c r="B43" s="653" t="inlineStr">
         <is>
           <t>story-observability</t>
         </is>
       </c>
-      <c r="C43" s="641" t="inlineStr">
+      <c r="C43" s="653" t="inlineStr">
         <is>
           <t>调整既有统一监控平台的交易与财务看板</t>
         </is>
       </c>
-      <c r="D43" s="641" t="inlineStr">
+      <c r="D43" s="653" t="inlineStr">
         <is>
           <t>BU-OBSERVABILITY-AUDIT</t>
         </is>
       </c>
-      <c r="E43" s="646">
+      <c r="E43" s="658">
         <f>IF(D43="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D43,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F43" s="642" t="inlineStr">
+      <c r="F43" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G43" s="648" t="inlineStr">
+      <c r="G43" s="660" t="inlineStr">
         <is>
           <t>在既有统一监控平台新增订单成功率、退款失败、开票积压和对账延迟指标。</t>
         </is>
       </c>
-      <c r="H43" s="649" t="inlineStr">
+      <c r="H43" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I43" s="648" t="inlineStr"/>
-      <c r="J43" s="648" t="inlineStr"/>
-      <c r="K43" s="648" t="inlineStr">
+      <c r="I43" s="660" t="inlineStr"/>
+      <c r="J43" s="660" t="inlineStr"/>
+      <c r="K43" s="660" t="inlineStr">
         <is>
           <t>effective-start-monitoring-platform</t>
         </is>
       </c>
-      <c r="L43" s="648" t="inlineStr">
+      <c r="L43" s="660" t="inlineStr">
         <is>
           <t>一个核心交易与财务作业可观测性实例。</t>
         </is>
       </c>
-      <c r="M43" s="645">
+      <c r="M43" s="657">
         <f>IF(OR(A43="",D43="",F43=""),"",IFERROR(IF(F43="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D43,BaseUnitCatalogTable[基础单元ID],0)),IF(F43="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D43,BaseUnitCatalogTable[基础单元ID],0)),IF(F43="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D43,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N43" s="645">
+      <c r="N43" s="657">
         <f>IF(OR(A43="",H43=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H43,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O43" s="645">
+      <c r="O43" s="657">
         <f>IF(OR(A43="",NOT(ISNUMBER(M43)),NOT(ISNUMBER(N43))),"",ROUND(M43*N43,1))</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="38" customHeight="1">
-      <c r="A44" s="641" t="inlineStr">
+      <c r="A44" s="653" t="inlineStr">
         <is>
           <t>task-reliability-controls</t>
         </is>
       </c>
-      <c r="B44" s="641" t="inlineStr">
+      <c r="B44" s="653" t="inlineStr">
         <is>
           <t>story-observability</t>
         </is>
       </c>
-      <c r="C44" s="641" t="inlineStr">
+      <c r="C44" s="653" t="inlineStr">
         <is>
           <t>新建关键链路稳定性控制</t>
         </is>
       </c>
-      <c r="D44" s="641" t="inlineStr">
+      <c r="D44" s="653" t="inlineStr">
         <is>
           <t>BU-PERFORMANCE-RELIABILITY</t>
         </is>
       </c>
-      <c r="E44" s="646">
+      <c r="E44" s="658">
         <f>IF(D44="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D44,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F44" s="642" t="inlineStr">
+      <c r="F44" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G44" s="648" t="inlineStr">
+      <c r="G44" s="660" t="inlineStr">
         <is>
           <t>新增 ERP、支付和发票调用的超时、限流、重试与熔断配置。</t>
         </is>
       </c>
-      <c r="H44" s="649" t="inlineStr">
+      <c r="H44" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I44" s="648" t="inlineStr"/>
-      <c r="J44" s="648" t="inlineStr"/>
-      <c r="K44" s="648" t="inlineStr"/>
-      <c r="L44" s="648" t="inlineStr">
+      <c r="I44" s="660" t="inlineStr"/>
+      <c r="J44" s="660" t="inlineStr"/>
+      <c r="K44" s="660" t="inlineStr"/>
+      <c r="L44" s="660" t="inlineStr">
         <is>
           <t>一个跨外部依赖的性能与稳定性保障实例。</t>
         </is>
       </c>
-      <c r="M44" s="645">
+      <c r="M44" s="657">
         <f>IF(OR(A44="",D44="",F44=""),"",IFERROR(IF(F44="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D44,BaseUnitCatalogTable[基础单元ID],0)),IF(F44="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D44,BaseUnitCatalogTable[基础单元ID],0)),IF(F44="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D44,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N44" s="645">
+      <c r="N44" s="657">
         <f>IF(OR(A44="",H44=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H44,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O44" s="645">
+      <c r="O44" s="657">
         <f>IF(OR(A44="",NOT(ISNUMBER(M44)),NOT(ISNUMBER(N44))),"",ROUND(M44*N44,1))</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="38" customHeight="1">
-      <c r="A45" s="641" t="inlineStr">
+      <c r="A45" s="653" t="inlineStr">
         <is>
           <t>task-ops-handover</t>
         </is>
       </c>
-      <c r="B45" s="641" t="inlineStr">
+      <c r="B45" s="653" t="inlineStr">
         <is>
           <t>story-ops-handover</t>
         </is>
       </c>
-      <c r="C45" s="641" t="inlineStr">
+      <c r="C45" s="653" t="inlineStr">
         <is>
           <t>调整既有统一监控平台的运维手册与交接</t>
         </is>
       </c>
-      <c r="D45" s="641" t="inlineStr">
+      <c r="D45" s="653" t="inlineStr">
         <is>
           <t>BU-OPS-HANDOVER</t>
         </is>
       </c>
-      <c r="E45" s="646">
+      <c r="E45" s="658">
         <f>IF(D45="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D45,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F45" s="642" t="inlineStr">
+      <c r="F45" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G45" s="648" t="inlineStr">
+      <c r="G45" s="660" t="inlineStr">
         <is>
           <t>基于既有统一监控平台补齐指标说明、责任人、通知渠道、排障和升级流程。</t>
         </is>
       </c>
-      <c r="H45" s="649" t="inlineStr">
+      <c r="H45" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I45" s="648" t="inlineStr"/>
-      <c r="J45" s="648" t="inlineStr"/>
-      <c r="K45" s="648" t="inlineStr">
+      <c r="I45" s="660" t="inlineStr"/>
+      <c r="J45" s="660" t="inlineStr"/>
+      <c r="K45" s="660" t="inlineStr">
         <is>
           <t>effective-start-monitoring-platform</t>
         </is>
       </c>
-      <c r="L45" s="648" t="inlineStr">
+      <c r="L45" s="660" t="inlineStr">
         <is>
           <t>一个运维交接包和一次故障演练实例。</t>
         </is>
       </c>
-      <c r="M45" s="645">
+      <c r="M45" s="657">
         <f>IF(OR(A45="",D45="",F45=""),"",IFERROR(IF(F45="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D45,BaseUnitCatalogTable[基础单元ID],0)),IF(F45="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D45,BaseUnitCatalogTable[基础单元ID],0)),IF(F45="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D45,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N45" s="645">
+      <c r="N45" s="657">
         <f>IF(OR(A45="",H45=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H45,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O45" s="645">
+      <c r="O45" s="657">
         <f>IF(OR(A45="",NOT(ISNUMBER(M45)),NOT(ISNUMBER(N45))),"",ROUND(M45*N45,1))</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="38" customHeight="1">
-      <c r="A46" s="641" t="inlineStr">
+      <c r="A46" s="653" t="inlineStr">
         <is>
           <t>task-user-training</t>
         </is>
       </c>
-      <c r="B46" s="641" t="inlineStr">
+      <c r="B46" s="653" t="inlineStr">
         <is>
           <t>story-user-training</t>
         </is>
       </c>
-      <c r="C46" s="641" t="inlineStr">
+      <c r="C46" s="653" t="inlineStr">
         <is>
           <t>交付门店客服财务培训</t>
         </is>
       </c>
-      <c r="D46" s="641" t="inlineStr">
+      <c r="D46" s="653" t="inlineStr">
         <is>
           <t>BU-USER-TRAINING</t>
         </is>
       </c>
-      <c r="E46" s="646">
+      <c r="E46" s="658">
         <f>IF(D46="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D46,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F46" s="642" t="inlineStr">
+      <c r="F46" s="654" t="inlineStr">
         <is>
           <t>新建</t>
         </is>
       </c>
-      <c r="G46" s="648" t="inlineStr">
+      <c r="G46" s="660" t="inlineStr">
         <is>
           <t>新增门店、客服和财务三类角色材料，并组织两场培训和反馈收集。</t>
         </is>
       </c>
-      <c r="H46" s="649" t="inlineStr">
+      <c r="H46" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I46" s="648" t="inlineStr"/>
-      <c r="J46" s="648" t="inlineStr"/>
-      <c r="K46" s="648" t="inlineStr"/>
-      <c r="L46" s="648" t="inlineStr">
+      <c r="I46" s="660" t="inlineStr"/>
+      <c r="J46" s="660" t="inlineStr"/>
+      <c r="K46" s="660" t="inlineStr"/>
+      <c r="L46" s="660" t="inlineStr">
         <is>
           <t>一个角色化用户培训与使用材料交付实例。</t>
         </is>
       </c>
-      <c r="M46" s="645">
+      <c r="M46" s="657">
         <f>IF(OR(A46="",D46="",F46=""),"",IFERROR(IF(F46="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D46,BaseUnitCatalogTable[基础单元ID],0)),IF(F46="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D46,BaseUnitCatalogTable[基础单元ID],0)),IF(F46="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D46,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N46" s="645">
+      <c r="N46" s="657">
         <f>IF(OR(A46="",H46=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H46,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O46" s="645">
+      <c r="O46" s="657">
         <f>IF(OR(A46="",NOT(ISNUMBER(M46)),NOT(ISNUMBER(N46))),"",ROUND(M46*N46,1))</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="38" customHeight="1">
-      <c r="A47" s="641" t="inlineStr">
+      <c r="A47" s="653" t="inlineStr">
         <is>
           <t>task-test-framework</t>
         </is>
       </c>
-      <c r="B47" s="641" t="inlineStr">
+      <c r="B47" s="653" t="inlineStr">
         <is>
           <t>story-test-automation</t>
         </is>
       </c>
-      <c r="C47" s="641" t="inlineStr">
+      <c r="C47" s="653" t="inlineStr">
         <is>
           <t>调整既有回归测试资产的自动化框架</t>
         </is>
       </c>
-      <c r="D47" s="641" t="inlineStr">
+      <c r="D47" s="653" t="inlineStr">
         <is>
           <t>BU-AUTOMATION-FRAMEWORK</t>
         </is>
       </c>
-      <c r="E47" s="646">
+      <c r="E47" s="658">
         <f>IF(D47="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D47,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F47" s="642" t="inlineStr">
+      <c r="F47" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G47" s="648" t="inlineStr">
+      <c r="G47" s="660" t="inlineStr">
         <is>
           <t>扩展既有回归测试资产的认证、测试数据、异步回调和报告能力。</t>
         </is>
       </c>
-      <c r="H47" s="649" t="inlineStr">
+      <c r="H47" s="661" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I47" s="648" t="inlineStr"/>
-      <c r="J47" s="648" t="inlineStr"/>
-      <c r="K47" s="648" t="inlineStr">
+      <c r="I47" s="660" t="inlineStr"/>
+      <c r="J47" s="660" t="inlineStr"/>
+      <c r="K47" s="660" t="inlineStr">
         <is>
           <t>effective-start-test-assets</t>
         </is>
       </c>
-      <c r="L47" s="648" t="inlineStr">
+      <c r="L47" s="660" t="inlineStr">
         <is>
           <t>一个 API 自动化测试框架调整实例。</t>
         </is>
       </c>
-      <c r="M47" s="645">
+      <c r="M47" s="657">
         <f>IF(OR(A47="",D47="",F47=""),"",IFERROR(IF(F47="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D47,BaseUnitCatalogTable[基础单元ID],0)),IF(F47="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D47,BaseUnitCatalogTable[基础单元ID],0)),IF(F47="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D47,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N47" s="645">
+      <c r="N47" s="657">
         <f>IF(OR(A47="",H47=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H47,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O47" s="645">
+      <c r="O47" s="657">
         <f>IF(OR(A47="",NOT(ISNUMBER(M47)),NOT(ISNUMBER(N47))),"",ROUND(M47*N47,1))</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="38" customHeight="1">
-      <c r="A48" s="641" t="inlineStr">
+      <c r="A48" s="653" t="inlineStr">
         <is>
           <t>task-test-cases</t>
         </is>
       </c>
-      <c r="B48" s="641" t="inlineStr">
+      <c r="B48" s="653" t="inlineStr">
         <is>
           <t>story-test-automation</t>
         </is>
       </c>
-      <c r="C48" s="641" t="inlineStr">
+      <c r="C48" s="653" t="inlineStr">
         <is>
           <t>调整既有回归测试资产的核心自动化用例</t>
         </is>
       </c>
-      <c r="D48" s="641" t="inlineStr">
+      <c r="D48" s="653" t="inlineStr">
         <is>
           <t>BU-AUTOMATION-CASES</t>
         </is>
       </c>
-      <c r="E48" s="646">
+      <c r="E48" s="658">
         <f>IF(D48="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D48,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F48" s="642" t="inlineStr">
+      <c r="F48" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G48" s="648" t="inlineStr">
+      <c r="G48" s="660" t="inlineStr">
         <is>
           <t>在既有回归测试资产中增加订单状态、库存、退款、开票和对账自动化用例。</t>
         </is>
       </c>
-      <c r="H48" s="649" t="inlineStr">
+      <c r="H48" s="661" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I48" s="648" t="inlineStr">
+      <c r="I48" s="660" t="inlineStr">
         <is>
           <t>覆盖五条跨系统链路、异步结果、失败补偿和财务金额断言，数据组合较多。</t>
         </is>
       </c>
-      <c r="J48" s="648" t="inlineStr"/>
-      <c r="K48" s="648" t="inlineStr">
+      <c r="J48" s="660" t="inlineStr"/>
+      <c r="K48" s="660" t="inlineStr">
         <is>
           <t>effective-start-test-assets</t>
         </is>
       </c>
-      <c r="L48" s="648" t="inlineStr">
+      <c r="L48" s="660" t="inlineStr">
         <is>
           <t>一个核心业务自动化用例集实例。</t>
         </is>
       </c>
-      <c r="M48" s="645">
+      <c r="M48" s="657">
         <f>IF(OR(A48="",D48="",F48=""),"",IFERROR(IF(F48="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D48,BaseUnitCatalogTable[基础单元ID],0)),IF(F48="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D48,BaseUnitCatalogTable[基础单元ID],0)),IF(F48="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D48,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N48" s="645">
+      <c r="N48" s="657">
         <f>IF(OR(A48="",H48=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H48,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O48" s="645">
+      <c r="O48" s="657">
         <f>IF(OR(A48="",NOT(ISNUMBER(M48)),NOT(ISNUMBER(N48))),"",ROUND(M48*N48,1))</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="38" customHeight="1">
-      <c r="A49" s="641" t="inlineStr">
+      <c r="A49" s="653" t="inlineStr">
         <is>
           <t>task-compatibility-matrix</t>
         </is>
       </c>
-      <c r="B49" s="641" t="inlineStr">
+      <c r="B49" s="653" t="inlineStr">
         <is>
           <t>story-test-non-uat</t>
         </is>
       </c>
-      <c r="C49" s="641" t="inlineStr">
+      <c r="C49" s="653" t="inlineStr">
         <is>
           <t>调整既有回归测试资产的兼容矩阵</t>
         </is>
       </c>
-      <c r="D49" s="641" t="inlineStr">
+      <c r="D49" s="653" t="inlineStr">
         <is>
           <t>BU-COMPATIBILITY-ACCESSIBILITY-TESTING</t>
         </is>
       </c>
-      <c r="E49" s="646">
+      <c r="E49" s="658">
         <f>IF(D49="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D49,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F49" s="642" t="inlineStr">
+      <c r="F49" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G49" s="648" t="inlineStr">
+      <c r="G49" s="660" t="inlineStr">
         <is>
           <t>根据既有回归测试资产更新浏览器、门店设备和无障碍检查范围。</t>
         </is>
       </c>
-      <c r="H49" s="649" t="inlineStr">
+      <c r="H49" s="661" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I49" s="648" t="inlineStr">
+      <c r="I49" s="660" t="inlineStr">
         <is>
           <t>仅验证两类浏览器和一种门店设备，沿用现有脚本且无新增终端。</t>
         </is>
       </c>
-      <c r="J49" s="648" t="inlineStr"/>
-      <c r="K49" s="648" t="inlineStr">
+      <c r="J49" s="660" t="inlineStr"/>
+      <c r="K49" s="660" t="inlineStr">
         <is>
           <t>effective-start-test-assets</t>
         </is>
       </c>
-      <c r="L49" s="648" t="inlineStr">
+      <c r="L49" s="660" t="inlineStr">
         <is>
           <t>一个兼容性与无障碍测试矩阵实例。</t>
         </is>
       </c>
-      <c r="M49" s="645">
+      <c r="M49" s="657">
         <f>IF(OR(A49="",D49="",F49=""),"",IFERROR(IF(F49="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D49,BaseUnitCatalogTable[基础单元ID],0)),IF(F49="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D49,BaseUnitCatalogTable[基础单元ID],0)),IF(F49="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D49,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N49" s="645">
+      <c r="N49" s="657">
         <f>IF(OR(A49="",H49=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H49,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O49" s="645">
+      <c r="O49" s="657">
         <f>IF(OR(A49="",NOT(ISNUMBER(M49)),NOT(ISNUMBER(N49))),"",ROUND(M49*N49,1))</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="38" customHeight="1">
-      <c r="A50" s="641" t="inlineStr">
+      <c r="A50" s="653" t="inlineStr">
         <is>
           <t>task-engineering-regression</t>
         </is>
       </c>
-      <c r="B50" s="641" t="inlineStr">
+      <c r="B50" s="653" t="inlineStr">
         <is>
           <t>story-test-non-uat</t>
         </is>
       </c>
-      <c r="C50" s="641" t="inlineStr">
+      <c r="C50" s="653" t="inlineStr">
         <is>
           <t>调整既有回归测试资产的工程回归范围</t>
         </is>
       </c>
-      <c r="D50" s="641" t="inlineStr">
+      <c r="D50" s="653" t="inlineStr">
         <is>
           <t>BU-MANUAL-TESTING</t>
         </is>
       </c>
-      <c r="E50" s="646">
+      <c r="E50" s="658">
         <f>IF(D50="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(D50,BaseUnitCatalogTable[基础单元ID],0)),""))</f>
         <v/>
       </c>
-      <c r="F50" s="642" t="inlineStr">
+      <c r="F50" s="654" t="inlineStr">
         <is>
           <t>调整</t>
         </is>
       </c>
-      <c r="G50" s="648" t="inlineStr">
+      <c r="G50" s="660" t="inlineStr">
         <is>
           <t>基于既有回归测试资产补充配置、权限、作业恢复和日志审计检查。</t>
         </is>
       </c>
-      <c r="H50" s="649" t="inlineStr">
+      <c r="H50" s="661" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I50" s="648" t="inlineStr">
+      <c r="I50" s="660" t="inlineStr">
         <is>
           <t>四项工程检查均有现成步骤，只需补充新配置和日志断言。</t>
         </is>
       </c>
-      <c r="J50" s="648" t="inlineStr"/>
-      <c r="K50" s="648" t="inlineStr">
+      <c r="J50" s="660" t="inlineStr"/>
+      <c r="K50" s="660" t="inlineStr">
         <is>
           <t>effective-start-test-assets</t>
         </is>
       </c>
-      <c r="L50" s="648" t="inlineStr">
+      <c r="L50" s="660" t="inlineStr">
         <is>
           <t>一个不计入 UAT 分母的工程回归测试实例。</t>
         </is>
       </c>
-      <c r="M50" s="645">
+      <c r="M50" s="657">
         <f>IF(OR(A50="",D50="",F50=""),"",IFERROR(IF(F50="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(D50,BaseUnitCatalogTable[基础单元ID],0)),IF(F50="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(D50,BaseUnitCatalogTable[基础单元ID],0)),IF(F50="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(D50,BaseUnitCatalogTable[基础单元ID],0)),""))),""))</f>
         <v/>
       </c>
-      <c r="N50" s="645">
+      <c r="N50" s="657">
         <f>IF(OR(A50="",H50=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;H50,ProjectParameterTable[参数代码],0)),""))</f>
         <v/>
       </c>
-      <c r="O50" s="645">
+      <c r="O50" s="657">
         <f>IF(OR(A50="",NOT(ISNUMBER(M50)),NOT(ISNUMBER(N50))),"",ROUND(M50*N50,1))</f>
         <v/>
       </c>
@@ -17667,18 +17895,18 @@
           <t>集成点</t>
         </is>
       </c>
-      <c r="B1" s="635" t="n"/>
-      <c r="C1" s="635" t="n"/>
-      <c r="D1" s="635" t="n"/>
-      <c r="E1" s="635" t="n"/>
-      <c r="F1" s="635" t="n"/>
-      <c r="G1" s="635" t="n"/>
-      <c r="H1" s="635" t="n"/>
-      <c r="I1" s="635" t="n"/>
-      <c r="J1" s="635" t="n"/>
-      <c r="K1" s="635" t="n"/>
-      <c r="L1" s="635" t="n"/>
-      <c r="M1" s="635" t="n"/>
+      <c r="B1" s="647" t="n"/>
+      <c r="C1" s="647" t="n"/>
+      <c r="D1" s="647" t="n"/>
+      <c r="E1" s="647" t="n"/>
+      <c r="F1" s="647" t="n"/>
+      <c r="G1" s="647" t="n"/>
+      <c r="H1" s="647" t="n"/>
+      <c r="I1" s="647" t="n"/>
+      <c r="J1" s="647" t="n"/>
+      <c r="K1" s="647" t="n"/>
+      <c r="L1" s="647" t="n"/>
+      <c r="M1" s="647" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="400" t="inlineStr">
@@ -17686,18 +17914,18 @@
           <t>一行对应一个顶层 Integration；Integration 独立于 Story 类型；只有引用该 Integration 的内部/外部系统对接 Task 才触发 SIT。</t>
         </is>
       </c>
-      <c r="B2" s="636" t="n"/>
-      <c r="C2" s="636" t="n"/>
-      <c r="D2" s="636" t="n"/>
-      <c r="E2" s="636" t="n"/>
-      <c r="F2" s="636" t="n"/>
-      <c r="G2" s="636" t="n"/>
-      <c r="H2" s="636" t="n"/>
-      <c r="I2" s="636" t="n"/>
-      <c r="J2" s="636" t="n"/>
-      <c r="K2" s="636" t="n"/>
-      <c r="L2" s="636" t="n"/>
-      <c r="M2" s="636" t="n"/>
+      <c r="B2" s="648" t="n"/>
+      <c r="C2" s="648" t="n"/>
+      <c r="D2" s="648" t="n"/>
+      <c r="E2" s="648" t="n"/>
+      <c r="F2" s="648" t="n"/>
+      <c r="G2" s="648" t="n"/>
+      <c r="H2" s="648" t="n"/>
+      <c r="I2" s="648" t="n"/>
+      <c r="J2" s="648" t="n"/>
+      <c r="K2" s="648" t="n"/>
+      <c r="L2" s="648" t="n"/>
+      <c r="M2" s="648" t="n"/>
     </row>
     <row r="3" ht="9" customHeight="1"/>
     <row r="4" ht="38" customHeight="1">
@@ -17768,249 +17996,249 @@
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="641" t="inlineStr">
+      <c r="A5" s="653" t="inlineStr">
         <is>
           <t>integration-profile-api</t>
         </is>
       </c>
-      <c r="B5" s="641" t="inlineStr">
+      <c r="B5" s="653" t="inlineStr">
         <is>
           <t>story-profile-integration</t>
         </is>
       </c>
-      <c r="C5" s="641" t="inlineStr">
+      <c r="C5" s="653" t="inlineStr">
         <is>
           <t>星云会员门户</t>
         </is>
       </c>
-      <c r="D5" s="641" t="inlineStr">
+      <c r="D5" s="653" t="inlineStr">
         <is>
           <t>会员主数据服务</t>
         </is>
       </c>
-      <c r="E5" s="641" t="inlineStr">
+      <c r="E5" s="653" t="inlineStr">
         <is>
           <t>收到客户档案查看请求</t>
         </is>
       </c>
-      <c r="F5" s="642" t="inlineStr">
+      <c r="F5" s="654" t="inlineStr">
         <is>
           <t>OUTBOUND</t>
         </is>
       </c>
-      <c r="G5" s="641" t="inlineStr">
+      <c r="G5" s="653" t="inlineStr">
         <is>
           <t>检索统一会员号和授权范围内的客户档案</t>
         </is>
       </c>
-      <c r="H5" s="642" t="inlineStr">
+      <c r="H5" s="654" t="inlineStr">
         <is>
           <t>内部</t>
         </is>
       </c>
-      <c r="I5" s="644">
+      <c r="I5" s="656">
         <f>IF(A5="","",IFERROR(INDEX(TaskTable[Task ID],MATCH(A5,TaskTable[Integration ID],0)),""))</f>
         <v/>
       </c>
-      <c r="J5" s="650">
+      <c r="J5" s="662">
         <f>IF(I5="","",IFERROR(INDEX(TaskTable[工作模式],MATCH(I5,TaskTable[Task ID],0)),""))</f>
         <v/>
       </c>
-      <c r="K5" s="650">
+      <c r="K5" s="662">
         <f>IF(I5="","",IFERROR(INDEX(TaskTable[复杂度],MATCH(I5,TaskTable[Task ID],0)),""))</f>
         <v/>
       </c>
-      <c r="L5" s="645">
+      <c r="L5" s="657">
         <f>IF(I5="","",IF(H5="内部",INDEX(ProjectParameterTable[值],MATCH("SIT_INT_SUPPORT",ProjectParameterTable[参数代码],0)),IF(H5="外部",INDEX(ProjectParameterTable[值],MATCH("SIT_EXT_SUPPORT",ProjectParameterTable[参数代码],0)),"")))</f>
         <v/>
       </c>
-      <c r="M5" s="645">
+      <c r="M5" s="657">
         <f>IF(OR(I5="",L5=""),"",ROUND(L5*IFERROR(INDEX(TaskTable[复杂度倍率],MATCH(I5,TaskTable[Task ID],0)),0),1))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="641" t="inlineStr">
+      <c r="A6" s="653" t="inlineStr">
         <is>
           <t>integration-erp-reservation</t>
         </is>
       </c>
-      <c r="B6" s="641" t="inlineStr">
+      <c r="B6" s="653" t="inlineStr">
         <is>
           <t>story-inventory-reservation</t>
         </is>
       </c>
-      <c r="C6" s="641" t="inlineStr">
+      <c r="C6" s="653" t="inlineStr">
         <is>
           <t>订单服务</t>
         </is>
       </c>
-      <c r="D6" s="641" t="inlineStr">
+      <c r="D6" s="653" t="inlineStr">
         <is>
           <t>ERP</t>
         </is>
       </c>
-      <c r="E6" s="641" t="inlineStr">
+      <c r="E6" s="653" t="inlineStr">
         <is>
           <t>订单确认、取消或预占超时</t>
         </is>
       </c>
-      <c r="F6" s="642" t="inlineStr">
+      <c r="F6" s="654" t="inlineStr">
         <is>
           <t>OUTBOUND</t>
         </is>
       </c>
-      <c r="G6" s="641" t="inlineStr">
+      <c r="G6" s="653" t="inlineStr">
         <is>
           <t>预占或释放门店与仓库库存</t>
         </is>
       </c>
-      <c r="H6" s="642" t="inlineStr">
+      <c r="H6" s="654" t="inlineStr">
         <is>
           <t>内部</t>
         </is>
       </c>
-      <c r="I6" s="644">
+      <c r="I6" s="656">
         <f>IF(A6="","",IFERROR(INDEX(TaskTable[Task ID],MATCH(A6,TaskTable[Integration ID],0)),""))</f>
         <v/>
       </c>
-      <c r="J6" s="650">
+      <c r="J6" s="662">
         <f>IF(I6="","",IFERROR(INDEX(TaskTable[工作模式],MATCH(I6,TaskTable[Task ID],0)),""))</f>
         <v/>
       </c>
-      <c r="K6" s="650">
+      <c r="K6" s="662">
         <f>IF(I6="","",IFERROR(INDEX(TaskTable[复杂度],MATCH(I6,TaskTable[Task ID],0)),""))</f>
         <v/>
       </c>
-      <c r="L6" s="645">
+      <c r="L6" s="657">
         <f>IF(I6="","",IF(H6="内部",INDEX(ProjectParameterTable[值],MATCH("SIT_INT_SUPPORT",ProjectParameterTable[参数代码],0)),IF(H6="外部",INDEX(ProjectParameterTable[值],MATCH("SIT_EXT_SUPPORT",ProjectParameterTable[参数代码],0)),"")))</f>
         <v/>
       </c>
-      <c r="M6" s="645">
+      <c r="M6" s="657">
         <f>IF(OR(I6="",L6=""),"",ROUND(L6*IFERROR(INDEX(TaskTable[复杂度倍率],MATCH(I6,TaskTable[Task ID],0)),0),1))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="641" t="inlineStr">
+      <c r="A7" s="653" t="inlineStr">
         <is>
           <t>integration-payment-gateway</t>
         </is>
       </c>
-      <c r="B7" s="641" t="inlineStr">
+      <c r="B7" s="653" t="inlineStr">
         <is>
           <t>story-refund-payment</t>
         </is>
       </c>
-      <c r="C7" s="641" t="inlineStr">
+      <c r="C7" s="653" t="inlineStr">
         <is>
           <t>订单服务</t>
         </is>
       </c>
-      <c r="D7" s="641" t="inlineStr">
+      <c r="D7" s="653" t="inlineStr">
         <is>
           <t>支付网关</t>
         </is>
       </c>
-      <c r="E7" s="641" t="inlineStr">
+      <c r="E7" s="653" t="inlineStr">
         <is>
           <t>退货审核通过</t>
         </is>
       </c>
-      <c r="F7" s="642" t="inlineStr">
+      <c r="F7" s="654" t="inlineStr">
         <is>
           <t>OUTBOUND</t>
         </is>
       </c>
-      <c r="G7" s="641" t="inlineStr">
+      <c r="G7" s="653" t="inlineStr">
         <is>
           <t>发起退款并查询或接收退款结果</t>
         </is>
       </c>
-      <c r="H7" s="642" t="inlineStr">
+      <c r="H7" s="654" t="inlineStr">
         <is>
           <t>外部</t>
         </is>
       </c>
-      <c r="I7" s="644">
+      <c r="I7" s="656">
         <f>IF(A7="","",IFERROR(INDEX(TaskTable[Task ID],MATCH(A7,TaskTable[Integration ID],0)),""))</f>
         <v/>
       </c>
-      <c r="J7" s="650">
+      <c r="J7" s="662">
         <f>IF(I7="","",IFERROR(INDEX(TaskTable[工作模式],MATCH(I7,TaskTable[Task ID],0)),""))</f>
         <v/>
       </c>
-      <c r="K7" s="650">
+      <c r="K7" s="662">
         <f>IF(I7="","",IFERROR(INDEX(TaskTable[复杂度],MATCH(I7,TaskTable[Task ID],0)),""))</f>
         <v/>
       </c>
-      <c r="L7" s="645">
+      <c r="L7" s="657">
         <f>IF(I7="","",IF(H7="内部",INDEX(ProjectParameterTable[值],MATCH("SIT_INT_SUPPORT",ProjectParameterTable[参数代码],0)),IF(H7="外部",INDEX(ProjectParameterTable[值],MATCH("SIT_EXT_SUPPORT",ProjectParameterTable[参数代码],0)),"")))</f>
         <v/>
       </c>
-      <c r="M7" s="645">
+      <c r="M7" s="657">
         <f>IF(OR(I7="",L7=""),"",ROUND(L7*IFERROR(INDEX(TaskTable[复杂度倍率],MATCH(I7,TaskTable[Task ID],0)),0),1))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="641" t="inlineStr">
+      <c r="A8" s="653" t="inlineStr">
         <is>
           <t>integration-einvoice</t>
         </is>
       </c>
-      <c r="B8" s="641" t="inlineStr">
+      <c r="B8" s="653" t="inlineStr">
         <is>
           <t>story-einvoice</t>
         </is>
       </c>
-      <c r="C8" s="641" t="inlineStr">
+      <c r="C8" s="653" t="inlineStr">
         <is>
           <t>订单服务</t>
         </is>
       </c>
-      <c r="D8" s="641" t="inlineStr">
+      <c r="D8" s="653" t="inlineStr">
         <is>
           <t>电子发票平台</t>
         </is>
       </c>
-      <c r="E8" s="641" t="inlineStr">
+      <c r="E8" s="653" t="inlineStr">
         <is>
           <t>顾客对已完成订单提交开票申请</t>
         </is>
       </c>
-      <c r="F8" s="642" t="inlineStr">
+      <c r="F8" s="654" t="inlineStr">
         <is>
           <t>OUTBOUND</t>
         </is>
       </c>
-      <c r="G8" s="641" t="inlineStr">
+      <c r="G8" s="653" t="inlineStr">
         <is>
           <t>申请电子发票并查询开票状态</t>
         </is>
       </c>
-      <c r="H8" s="642" t="inlineStr">
+      <c r="H8" s="654" t="inlineStr">
         <is>
           <t>外部</t>
         </is>
       </c>
-      <c r="I8" s="644">
+      <c r="I8" s="656">
         <f>IF(A8="","",IFERROR(INDEX(TaskTable[Task ID],MATCH(A8,TaskTable[Integration ID],0)),""))</f>
         <v/>
       </c>
-      <c r="J8" s="650">
+      <c r="J8" s="662">
         <f>IF(I8="","",IFERROR(INDEX(TaskTable[工作模式],MATCH(I8,TaskTable[Task ID],0)),""))</f>
         <v/>
       </c>
-      <c r="K8" s="650">
+      <c r="K8" s="662">
         <f>IF(I8="","",IFERROR(INDEX(TaskTable[复杂度],MATCH(I8,TaskTable[Task ID],0)),""))</f>
         <v/>
       </c>
-      <c r="L8" s="645">
+      <c r="L8" s="657">
         <f>IF(I8="","",IF(H8="内部",INDEX(ProjectParameterTable[值],MATCH("SIT_INT_SUPPORT",ProjectParameterTable[参数代码],0)),IF(H8="外部",INDEX(ProjectParameterTable[值],MATCH("SIT_EXT_SUPPORT",ProjectParameterTable[参数代码],0)),"")))</f>
         <v/>
       </c>
-      <c r="M8" s="645">
+      <c r="M8" s="657">
         <f>IF(OR(I8="",L8=""),"",ROUND(L8*IFERROR(INDEX(TaskTable[复杂度倍率],MATCH(I8,TaskTable[Task ID],0)),0),1))</f>
         <v/>
       </c>
@@ -18160,14 +18388,14 @@
           <t>假设与风险清单</t>
         </is>
       </c>
-      <c r="B1" s="635" t="n"/>
-      <c r="C1" s="635" t="n"/>
-      <c r="D1" s="635" t="n"/>
-      <c r="E1" s="635" t="n"/>
-      <c r="F1" s="635" t="n"/>
-      <c r="G1" s="635" t="n"/>
-      <c r="H1" s="635" t="n"/>
-      <c r="I1" s="635" t="n"/>
+      <c r="B1" s="647" t="n"/>
+      <c r="C1" s="647" t="n"/>
+      <c r="D1" s="647" t="n"/>
+      <c r="E1" s="647" t="n"/>
+      <c r="F1" s="647" t="n"/>
+      <c r="G1" s="647" t="n"/>
+      <c r="H1" s="647" t="n"/>
+      <c r="I1" s="647" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="400" t="inlineStr">
@@ -18175,14 +18403,14 @@
           <t>每个假设或风险一行；关联的 Story ID 按输入顺序去重并以顿号连接；待确认项计入风险人天</t>
         </is>
       </c>
-      <c r="B2" s="636" t="n"/>
-      <c r="C2" s="636" t="n"/>
-      <c r="D2" s="636" t="n"/>
-      <c r="E2" s="636" t="n"/>
-      <c r="F2" s="636" t="n"/>
-      <c r="G2" s="636" t="n"/>
-      <c r="H2" s="636" t="n"/>
-      <c r="I2" s="636" t="n"/>
+      <c r="B2" s="648" t="n"/>
+      <c r="C2" s="648" t="n"/>
+      <c r="D2" s="648" t="n"/>
+      <c r="E2" s="648" t="n"/>
+      <c r="F2" s="648" t="n"/>
+      <c r="G2" s="648" t="n"/>
+      <c r="H2" s="648" t="n"/>
+      <c r="I2" s="648" t="n"/>
     </row>
     <row r="3" ht="9" customHeight="1"/>
     <row r="4" ht="38" customHeight="1">
@@ -18233,278 +18461,278 @@
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="641" t="inlineStr">
+      <c r="A5" s="653" t="inlineStr">
         <is>
           <t>assumption-profile-api-availability</t>
         </is>
       </c>
-      <c r="B5" s="642" t="inlineStr">
+      <c r="B5" s="654" t="inlineStr">
         <is>
           <t>假设</t>
         </is>
       </c>
-      <c r="C5" s="641" t="inlineStr">
+      <c r="C5" s="653" t="inlineStr">
         <is>
           <t>会员主数据服务在联调期间可用</t>
         </is>
       </c>
-      <c r="D5" s="641" t="inlineStr">
+      <c r="D5" s="653" t="inlineStr">
         <is>
           <t>客户档案内部集成测试开始</t>
         </is>
       </c>
-      <c r="E5" s="641" t="inlineStr">
+      <c r="E5" s="653" t="inlineStr">
         <is>
           <t>story-profile-integration、story-member-tier</t>
         </is>
       </c>
-      <c r="F5" s="641" t="inlineStr">
+      <c r="F5" s="653" t="inlineStr">
         <is>
           <t>会员主数据团队提供稳定的 SIT 端点和测试账号</t>
         </is>
       </c>
-      <c r="G5" s="642" t="inlineStr">
+      <c r="G5" s="654" t="inlineStr">
         <is>
           <t>已明确</t>
         </is>
       </c>
-      <c r="H5" s="641" t="inlineStr">
+      <c r="H5" s="653" t="inlineStr">
         <is>
           <t>按已确认的联调窗口执行系统集成测试</t>
         </is>
       </c>
-      <c r="I5" s="645">
-        <f>IF(OR(E5="",G5&lt;&gt;"待确认"),0,IFERROR(INDEX(SOWStoryTable[人天],MATCH(E5,SOWStoryTable[Story ID],0)),0))</f>
+      <c r="I5" s="657">
+        <f>IF(OR(E5="",G5&lt;&gt;"待确认"),0,SUMPRODUCT(SOWStoryTable[人天]*--ISNUMBER(SEARCH("、"&amp;SOWStoryTable[Story ID]&amp;"、","、"&amp;SUBSTITUTE(E5," ","")&amp;"、"))))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="641" t="inlineStr">
+      <c r="A6" s="653" t="inlineStr">
         <is>
           <t>assumption-risk-profile-alert-channel</t>
         </is>
       </c>
-      <c r="B6" s="642" t="inlineStr">
+      <c r="B6" s="654" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="C6" s="641" t="inlineStr">
+      <c r="C6" s="653" t="inlineStr">
         <is>
           <t>生产告警通知渠道待确认</t>
         </is>
       </c>
-      <c r="D6" s="641" t="inlineStr">
+      <c r="D6" s="653" t="inlineStr">
         <is>
           <t>生产准备评审前仍未登记最终通知渠道</t>
         </is>
       </c>
-      <c r="E6" s="641" t="inlineStr">
+      <c r="E6" s="653" t="inlineStr">
         <is>
           <t>story-profile-integration、story-observability、story-production-validation</t>
         </is>
       </c>
-      <c r="F6" s="641" t="inlineStr">
+      <c r="F6" s="653" t="inlineStr">
         <is>
           <t>运维团队确认邮件、工单或值班群以及接收人</t>
         </is>
       </c>
-      <c r="G6" s="642" t="inlineStr">
+      <c r="G6" s="654" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="H6" s="641" t="inlineStr">
+      <c r="H6" s="653" t="inlineStr">
         <is>
           <t>上线前确认渠道并写入监控配置和运维手册</t>
         </is>
       </c>
-      <c r="I6" s="645">
-        <f>IF(OR(E6="",G6&lt;&gt;"待确认"),0,IFERROR(INDEX(SOWStoryTable[人天],MATCH(E6,SOWStoryTable[Story ID],0)),0))</f>
+      <c r="I6" s="657">
+        <f>IF(OR(E6="",G6&lt;&gt;"待确认"),0,SUMPRODUCT(SOWStoryTable[人天]*--ISNUMBER(SEARCH("、"&amp;SOWStoryTable[Story ID]&amp;"、","、"&amp;SUBSTITUTE(E6," ","")&amp;"、"))))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="641" t="inlineStr">
+      <c r="A7" s="653" t="inlineStr">
         <is>
           <t>assumption-erp-sit-window</t>
         </is>
       </c>
-      <c r="B7" s="642" t="inlineStr">
+      <c r="B7" s="654" t="inlineStr">
         <is>
           <t>假设</t>
         </is>
       </c>
-      <c r="C7" s="641" t="inlineStr">
+      <c r="C7" s="653" t="inlineStr">
         <is>
           <t>ERP SIT 环境按工作日窗口开放</t>
         </is>
       </c>
-      <c r="D7" s="641" t="inlineStr">
+      <c r="D7" s="653" t="inlineStr">
         <is>
           <t>库存预占联调计划基线确认</t>
         </is>
       </c>
-      <c r="E7" s="641" t="inlineStr">
+      <c r="E7" s="653" t="inlineStr">
         <is>
           <t>story-inventory-reservation、story-production-cutover</t>
         </is>
       </c>
-      <c r="F7" s="641" t="inlineStr">
+      <c r="F7" s="653" t="inlineStr">
         <is>
           <t>ERP 团队保证工作日 09:00 至 18:00 可用并提前通知停机</t>
         </is>
       </c>
-      <c r="G7" s="642" t="inlineStr">
+      <c r="G7" s="654" t="inlineStr">
         <is>
           <t>已明确</t>
         </is>
       </c>
-      <c r="H7" s="641" t="inlineStr">
+      <c r="H7" s="653" t="inlineStr">
         <is>
           <t>联调和缺陷复测安排在已确认窗口内</t>
         </is>
       </c>
-      <c r="I7" s="645">
-        <f>IF(OR(E7="",G7&lt;&gt;"待确认"),0,IFERROR(INDEX(SOWStoryTable[人天],MATCH(E7,SOWStoryTable[Story ID],0)),0))</f>
+      <c r="I7" s="657">
+        <f>IF(OR(E7="",G7&lt;&gt;"待确认"),0,SUMPRODUCT(SOWStoryTable[人天]*--ISNUMBER(SEARCH("、"&amp;SOWStoryTable[Story ID]&amp;"、","、"&amp;SUBSTITUTE(E7," ","")&amp;"、"))))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="641" t="inlineStr">
+      <c r="A8" s="653" t="inlineStr">
         <is>
           <t>assumption-risk-payment-certification</t>
         </is>
       </c>
-      <c r="B8" s="642" t="inlineStr">
+      <c r="B8" s="654" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="C8" s="641" t="inlineStr">
+      <c r="C8" s="653" t="inlineStr">
         <is>
           <t>支付网关退款认证可能延迟</t>
         </is>
       </c>
-      <c r="D8" s="641" t="inlineStr">
+      <c r="D8" s="653" t="inlineStr">
         <is>
           <t>SIT 第 2 周开始时认证材料仍未通过</t>
         </is>
       </c>
-      <c r="E8" s="641" t="inlineStr">
+      <c r="E8" s="653" t="inlineStr">
         <is>
           <t>story-refund-payment、story-production-validation</t>
         </is>
       </c>
-      <c r="F8" s="641" t="inlineStr">
+      <c r="F8" s="653" t="inlineStr">
         <is>
           <t>资金管理部提交企业材料，项目团队提供回调地址和测试证据</t>
         </is>
       </c>
-      <c r="G8" s="642" t="inlineStr">
+      <c r="G8" s="654" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="H8" s="641" t="inlineStr">
+      <c r="H8" s="653" t="inlineStr">
         <is>
           <t>项目启动五个工作日内提交材料，延期时调整退款联调顺序</t>
         </is>
       </c>
-      <c r="I8" s="645">
-        <f>IF(OR(E8="",G8&lt;&gt;"待确认"),0,IFERROR(INDEX(SOWStoryTable[人天],MATCH(E8,SOWStoryTable[Story ID],0)),0))</f>
+      <c r="I8" s="657">
+        <f>IF(OR(E8="",G8&lt;&gt;"待确认"),0,SUMPRODUCT(SOWStoryTable[人天]*--ISNUMBER(SEARCH("、"&amp;SOWStoryTable[Story ID]&amp;"、","、"&amp;SUBSTITUTE(E8," ","")&amp;"、"))))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="641" t="inlineStr">
+      <c r="A9" s="653" t="inlineStr">
         <is>
           <t>assumption-migration-freeze-window</t>
         </is>
       </c>
-      <c r="B9" s="642" t="inlineStr">
+      <c r="B9" s="654" t="inlineStr">
         <is>
           <t>假设</t>
         </is>
       </c>
-      <c r="C9" s="641" t="inlineStr">
+      <c r="C9" s="653" t="inlineStr">
         <is>
           <t>迁移冻结窗口为周六 00:00 至 04:00</t>
         </is>
       </c>
-      <c r="D9" s="641" t="inlineStr">
+      <c r="D9" s="653" t="inlineStr">
         <is>
           <t>生产切换计划批准</t>
         </is>
       </c>
-      <c r="E9" s="641" t="inlineStr">
+      <c r="E9" s="653" t="inlineStr">
         <is>
           <t>story-data-migration、story-production-cutover</t>
         </is>
       </c>
-      <c r="F9" s="641" t="inlineStr">
+      <c r="F9" s="653" t="inlineStr">
         <is>
           <t>业务负责人批准冻结，数据负责人提供最终增量范围</t>
         </is>
       </c>
-      <c r="G9" s="642" t="inlineStr">
+      <c r="G9" s="654" t="inlineStr">
         <is>
           <t>已明确</t>
         </is>
       </c>
-      <c r="H9" s="641" t="inlineStr">
+      <c r="H9" s="653" t="inlineStr">
         <is>
           <t>按四小时窗口编排增量迁移、校验和回滚检查点</t>
         </is>
       </c>
-      <c r="I9" s="645">
-        <f>IF(OR(E9="",G9&lt;&gt;"待确认"),0,IFERROR(INDEX(SOWStoryTable[人天],MATCH(E9,SOWStoryTable[Story ID],0)),0))</f>
+      <c r="I9" s="657">
+        <f>IF(OR(E9="",G9&lt;&gt;"待确认"),0,SUMPRODUCT(SOWStoryTable[人天]*--ISNUMBER(SEARCH("、"&amp;SOWStoryTable[Story ID]&amp;"、","、"&amp;SUBSTITUTE(E9," ","")&amp;"、"))))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="641" t="inlineStr">
+      <c r="A10" s="653" t="inlineStr">
         <is>
           <t>assumption-risk-invoice-certificate</t>
         </is>
       </c>
-      <c r="B10" s="642" t="inlineStr">
+      <c r="B10" s="654" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="C10" s="641" t="inlineStr">
+      <c r="C10" s="653" t="inlineStr">
         <is>
           <t>电子发票生产证书与测试配额待确认</t>
         </is>
       </c>
-      <c r="D10" s="641" t="inlineStr">
+      <c r="D10" s="653" t="inlineStr">
         <is>
           <t>生产准备评审时证书或每日 500 张测试配额未就绪</t>
         </is>
       </c>
-      <c r="E10" s="641" t="inlineStr">
+      <c r="E10" s="653" t="inlineStr">
         <is>
           <t>story-einvoice</t>
         </is>
       </c>
-      <c r="F10" s="641" t="inlineStr">
+      <c r="F10" s="653" t="inlineStr">
         <is>
           <t>财务共享中心协调供应商下发证书并确认配额</t>
         </is>
       </c>
-      <c r="G10" s="642" t="inlineStr">
+      <c r="G10" s="654" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="H10" s="641" t="inlineStr">
+      <c r="H10" s="653" t="inlineStr">
         <is>
           <t>联调前确认测试配额，生产切换前完成证书装载和连通性检查</t>
         </is>
       </c>
-      <c r="I10" s="645">
-        <f>IF(OR(E10="",G10&lt;&gt;"待确认"),0,IFERROR(INDEX(SOWStoryTable[人天],MATCH(E10,SOWStoryTable[Story ID],0)),0))</f>
+      <c r="I10" s="657">
+        <f>IF(OR(E10="",G10&lt;&gt;"待确认"),0,SUMPRODUCT(SOWStoryTable[人天]*--ISNUMBER(SEARCH("、"&amp;SOWStoryTable[Story ID]&amp;"、","、"&amp;SUBSTITUTE(E10," ","")&amp;"、"))))</f>
         <v/>
       </c>
     </row>
@@ -18652,11 +18880,11 @@
           <t>开发交付估算汇总</t>
         </is>
       </c>
-      <c r="B1" s="635" t="n"/>
-      <c r="C1" s="635" t="n"/>
-      <c r="D1" s="635" t="n"/>
-      <c r="E1" s="635" t="n"/>
-      <c r="F1" s="635" t="n"/>
+      <c r="B1" s="647" t="n"/>
+      <c r="C1" s="647" t="n"/>
+      <c r="D1" s="647" t="n"/>
+      <c r="E1" s="647" t="n"/>
+      <c r="F1" s="647" t="n"/>
     </row>
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="400" t="inlineStr">
@@ -18664,11 +18892,11 @@
           <t>当前口径含直接Dev、SIT支持、UAT支持和待确认假设关联Story风险人天；不含人员/迭代、敏捷活动及BA/QA/TL/PM人天</t>
         </is>
       </c>
-      <c r="B2" s="636" t="n"/>
-      <c r="C2" s="636" t="n"/>
-      <c r="D2" s="636" t="n"/>
-      <c r="E2" s="636" t="n"/>
-      <c r="F2" s="636" t="n"/>
+      <c r="B2" s="648" t="n"/>
+      <c r="C2" s="648" t="n"/>
+      <c r="D2" s="648" t="n"/>
+      <c r="E2" s="648" t="n"/>
+      <c r="F2" s="648" t="n"/>
     </row>
     <row r="3" ht="9" customHeight="1"/>
     <row r="4" ht="38" customHeight="1">

--- a/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
+++ b/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C5" s="1053" t="inlineStr">
         <is>
-          <t>会员门户已有客户档案页面、字段校验和服务框架。</t>
+          <t>从现有客户档案页面、字段校验和服务框架开始。</t>
         </is>
       </c>
       <c r="D5" s="1057" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="C6" s="1053" t="inlineStr">
         <is>
-          <t>会员主数据保存统一会员号、基础属性和当前等级，但没有等级历史表。</t>
+          <t>复用统一会员号与基础属性表，新增等级历史和规则版本。</t>
         </is>
       </c>
       <c r="D6" s="1057" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="C7" s="1053" t="inlineStr">
         <is>
-          <t>订单服务支持线上订单基础状态流转，尚未覆盖门店订单和完整退货退款。</t>
+          <t>调整线上订单服务，扩展门店、退货退款和财务状态。</t>
         </is>
       </c>
       <c r="D7" s="1057" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="C8" s="1053" t="inlineStr">
         <is>
-          <t>企业服务总线已注册 ERP 库存查询和预占接口。</t>
+          <t>接口契约保持不变，本项目完成认证、映射、适配和专项验证。</t>
         </is>
       </c>
       <c r="D8" s="1057" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="C9" s="1053" t="inlineStr">
         <is>
-          <t>企业支付网关已完成签约和生产租户开通。</t>
+          <t>支付网关平台保持不变，本项目完成配置、认证、映射和专项验证。</t>
         </is>
       </c>
       <c r="D9" s="1057" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="C10" s="1053" t="inlineStr">
         <is>
-          <t>电子发票平台已签约并提供标准开票 API。</t>
+          <t>电子发票平台保持不变，本项目完成租户设置、认证、映射和适配。</t>
         </is>
       </c>
       <c r="D10" s="1057" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="C11" s="1053" t="inlineStr">
         <is>
-          <t>现有 Kubernetes 集群、制品库和 CI/CD 流水线承载会员门户与订单服务。</t>
+          <t>在现有集群与流水线中增加应用配置、发布步骤、切换和回滚清单。</t>
         </is>
       </c>
       <c r="D11" s="1057" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="C12" s="1053" t="inlineStr">
         <is>
-          <t>现有身份平台提供员工与门店角色控制，授权中心保存会员授权记录。</t>
+          <t>现有授权、撤回、查询与审计能力已完整覆盖本期目标。</t>
         </is>
       </c>
       <c r="D12" s="1057" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="C13" s="1053" t="inlineStr">
         <is>
-          <t>消息中心已消费标准订单事件并通过短信、App Push 发送通知。</t>
+          <t>标准订单事件和现有通知通道已完整覆盖本期通知目标。</t>
         </is>
       </c>
       <c r="D13" s="1057" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C14" s="1053" t="inlineStr">
         <is>
-          <t>平台已采集应用日志、指标与链路，但缺少新订单指标和财务批处理告警。</t>
+          <t>复用日志、指标和链路平台，新增订单与财务作业监控。</t>
         </is>
       </c>
       <c r="D14" s="1057" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="C15" s="1053" t="inlineStr">
         <is>
-          <t>一期已有 API 自动化框架、订单基础用例和兼容矩阵。</t>
+          <t>调整既有测试框架、测试用例、测试脚本、兼容矩阵与负载模型。</t>
         </is>
       </c>
       <c r="D15" s="1057" t="inlineStr">

--- a/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
+++ b/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
@@ -5003,10 +5003,10 @@
     <tableColumn id="3" name="故事名称"/>
     <tableColumn id="4" name="UAT适用"/>
     <tableColumn id="5" name="验收条件">
-      <calculatedColumnFormula>IF(C5="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C5,"")),""))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">IF(C5="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C5,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" name="任务明细">
-      <calculatedColumnFormula>IF(C5="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C5,"")),""))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">IF(C5="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C5,"• "&amp;TaskTable[任务名称],"")),""))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" name="人天">
       <calculatedColumnFormula>IF(C5="","",CEILING(SUMIF(TaskTable[故事名称],C5,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</calculatedColumnFormula>
@@ -11711,11 +11711,11 @@
         </is>
       </c>
       <c r="E5" s="926">
-        <f>IF(C5="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C5,"")),""))</f>
+        <f t="array" ref="E5">IF(C5="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C5,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F5" s="928">
-        <f>IF(C5="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C5,"")),""))</f>
+        <f t="array" ref="F5">IF(C5="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C5,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G5" s="929">
@@ -11749,11 +11749,11 @@
         </is>
       </c>
       <c r="E6" s="926">
-        <f>IF(C6="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C6,"")),""))</f>
+        <f t="array" ref="E6">IF(C6="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C6,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F6" s="928">
-        <f>IF(C6="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C6,"")),""))</f>
+        <f t="array" ref="F6">IF(C6="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C6,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G6" s="929">
@@ -11787,11 +11787,11 @@
         </is>
       </c>
       <c r="E7" s="926">
-        <f>IF(C7="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C7,"")),""))</f>
+        <f t="array" ref="E7">IF(C7="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C7,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F7" s="928">
-        <f>IF(C7="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C7,"")),""))</f>
+        <f t="array" ref="F7">IF(C7="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C7,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G7" s="929">
@@ -11829,11 +11829,11 @@
         </is>
       </c>
       <c r="E8" s="926">
-        <f>IF(C8="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C8,"")),""))</f>
+        <f t="array" ref="E8">IF(C8="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C8,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F8" s="928">
-        <f>IF(C8="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C8,"")),""))</f>
+        <f t="array" ref="F8">IF(C8="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C8,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G8" s="929">
@@ -11871,11 +11871,11 @@
         </is>
       </c>
       <c r="E9" s="926">
-        <f>IF(C9="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C9,"")),""))</f>
+        <f t="array" ref="E9">IF(C9="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C9,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F9" s="928">
-        <f>IF(C9="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C9,"")),""))</f>
+        <f t="array" ref="F9">IF(C9="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C9,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G9" s="929">
@@ -11909,11 +11909,11 @@
         </is>
       </c>
       <c r="E10" s="926">
-        <f>IF(C10="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C10,"")),""))</f>
+        <f t="array" ref="E10">IF(C10="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C10,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F10" s="928">
-        <f>IF(C10="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C10,"")),""))</f>
+        <f t="array" ref="F10">IF(C10="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C10,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G10" s="929">
@@ -11947,11 +11947,11 @@
         </is>
       </c>
       <c r="E11" s="926">
-        <f>IF(C11="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C11,"")),""))</f>
+        <f t="array" ref="E11">IF(C11="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C11,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F11" s="928">
-        <f>IF(C11="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C11,"")),""))</f>
+        <f t="array" ref="F11">IF(C11="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C11,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G11" s="929">
@@ -11989,11 +11989,11 @@
         </is>
       </c>
       <c r="E12" s="926">
-        <f>IF(C12="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C12,"")),""))</f>
+        <f t="array" ref="E12">IF(C12="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C12,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F12" s="928">
-        <f>IF(C12="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C12,"")),""))</f>
+        <f t="array" ref="F12">IF(C12="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C12,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G12" s="929">
@@ -12027,11 +12027,11 @@
         </is>
       </c>
       <c r="E13" s="926">
-        <f>IF(C13="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C13,"")),""))</f>
+        <f t="array" ref="E13">IF(C13="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C13,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F13" s="928">
-        <f>IF(C13="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C13,"")),""))</f>
+        <f t="array" ref="F13">IF(C13="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C13,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G13" s="929">
@@ -12069,11 +12069,11 @@
         </is>
       </c>
       <c r="E14" s="926">
-        <f>IF(C14="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C14,"")),""))</f>
+        <f t="array" ref="E14">IF(C14="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C14,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F14" s="928">
-        <f>IF(C14="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C14,"")),""))</f>
+        <f t="array" ref="F14">IF(C14="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C14,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G14" s="929">
@@ -12107,11 +12107,11 @@
         </is>
       </c>
       <c r="E15" s="926">
-        <f>IF(C15="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C15,"")),""))</f>
+        <f t="array" ref="E15">IF(C15="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C15,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F15" s="928">
-        <f>IF(C15="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C15,"")),""))</f>
+        <f t="array" ref="F15">IF(C15="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C15,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G15" s="929">
@@ -12145,11 +12145,11 @@
         </is>
       </c>
       <c r="E16" s="926">
-        <f>IF(C16="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C16,"")),""))</f>
+        <f t="array" ref="E16">IF(C16="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C16,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F16" s="928">
-        <f>IF(C16="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C16,"")),""))</f>
+        <f t="array" ref="F16">IF(C16="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C16,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G16" s="929">
@@ -12183,11 +12183,11 @@
         </is>
       </c>
       <c r="E17" s="926">
-        <f>IF(C17="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C17,"")),""))</f>
+        <f t="array" ref="E17">IF(C17="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C17,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F17" s="928">
-        <f>IF(C17="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C17,"")),""))</f>
+        <f t="array" ref="F17">IF(C17="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C17,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G17" s="929">
@@ -12225,11 +12225,11 @@
         </is>
       </c>
       <c r="E18" s="926">
-        <f>IF(C18="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C18,"")),""))</f>
+        <f t="array" ref="E18">IF(C18="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C18,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F18" s="928">
-        <f>IF(C18="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C18,"")),""))</f>
+        <f t="array" ref="F18">IF(C18="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C18,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G18" s="929">
@@ -12263,11 +12263,11 @@
         </is>
       </c>
       <c r="E19" s="926">
-        <f>IF(C19="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C19,"")),""))</f>
+        <f t="array" ref="E19">IF(C19="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C19,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F19" s="928">
-        <f>IF(C19="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C19,"")),""))</f>
+        <f t="array" ref="F19">IF(C19="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C19,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G19" s="929">
@@ -12301,11 +12301,11 @@
         </is>
       </c>
       <c r="E20" s="926">
-        <f>IF(C20="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C20,"")),""))</f>
+        <f t="array" ref="E20">IF(C20="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C20,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F20" s="928">
-        <f>IF(C20="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C20,"")),""))</f>
+        <f t="array" ref="F20">IF(C20="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C20,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G20" s="929">
@@ -12343,11 +12343,11 @@
         </is>
       </c>
       <c r="E21" s="926">
-        <f>IF(C21="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C21,"")),""))</f>
+        <f t="array" ref="E21">IF(C21="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C21,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F21" s="928">
-        <f>IF(C21="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C21,"")),""))</f>
+        <f t="array" ref="F21">IF(C21="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C21,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G21" s="929">
@@ -12385,11 +12385,11 @@
         </is>
       </c>
       <c r="E22" s="926">
-        <f>IF(C22="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C22,"")),""))</f>
+        <f t="array" ref="E22">IF(C22="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C22,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F22" s="928">
-        <f>IF(C22="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C22,"")),""))</f>
+        <f t="array" ref="F22">IF(C22="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C22,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G22" s="929">
@@ -12427,11 +12427,11 @@
         </is>
       </c>
       <c r="E23" s="926">
-        <f>IF(C23="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C23,"")),""))</f>
+        <f t="array" ref="E23">IF(C23="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C23,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F23" s="928">
-        <f>IF(C23="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C23,"")),""))</f>
+        <f t="array" ref="F23">IF(C23="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C23,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G23" s="929">
@@ -12469,11 +12469,11 @@
         </is>
       </c>
       <c r="E24" s="926">
-        <f>IF(C24="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C24,"")),""))</f>
+        <f t="array" ref="E24">IF(C24="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C24,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F24" s="928">
-        <f>IF(C24="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C24,"")),""))</f>
+        <f t="array" ref="F24">IF(C24="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C24,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G24" s="929">
@@ -12507,11 +12507,11 @@
         </is>
       </c>
       <c r="E25" s="926">
-        <f>IF(C25="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C25,"")),""))</f>
+        <f t="array" ref="E25">IF(C25="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C25,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F25" s="928">
-        <f>IF(C25="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C25,"")),""))</f>
+        <f t="array" ref="F25">IF(C25="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C25,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G25" s="929">
@@ -12545,11 +12545,11 @@
         </is>
       </c>
       <c r="E26" s="926">
-        <f>IF(C26="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C26,"")),""))</f>
+        <f t="array" ref="E26">IF(C26="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C26,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F26" s="928">
-        <f>IF(C26="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C26,"")),""))</f>
+        <f t="array" ref="F26">IF(C26="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C26,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G26" s="929">
@@ -12583,11 +12583,11 @@
         </is>
       </c>
       <c r="E27" s="926">
-        <f>IF(C27="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER(AcceptanceCriterionTable[验收条件名称],AcceptanceCriterionTable[故事名称]=C27,"")),""))</f>
+        <f t="array" ref="E27">IF(C27="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C27,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
         <v/>
       </c>
       <c r="F27" s="928">
-        <f>IF(C27="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,_xlfn._xlws.FILTER("• "&amp;TaskTable[任务名称],TaskTable[故事名称]=C27,"")),""))</f>
+        <f t="array" ref="F27">IF(C27="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C27,"• "&amp;TaskTable[任务名称],"")),""))</f>
         <v/>
       </c>
       <c r="G27" s="929">
@@ -13679,7 +13679,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -14463,7 +14463,7 @@
     <row r="103" s="1025"/>
     <row r="104" s="1025"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -18163,7 +18163,7 @@
     <row r="503" s="1025"/>
     <row r="504" s="1025"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
@@ -18710,7 +18710,7 @@
     <row r="103" s="1025"/>
     <row r="104" s="1025"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -20557,7 +20557,7 @@
       <c r="F100" s="948" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
+++ b/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
@@ -13679,7 +13679,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -14463,7 +14463,7 @@
     <row r="103" s="1025"/>
     <row r="104" s="1025"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -18163,7 +18163,7 @@
     <row r="503" s="1025"/>
     <row r="504" s="1025"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
@@ -18710,7 +18710,7 @@
     <row r="103" s="1025"/>
     <row r="104" s="1025"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -20557,7 +20557,7 @@
       <c r="F100" s="948" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
+++ b/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
@@ -6202,7 +6202,7 @@
       </c>
       <c r="B45" s="1040" t="inlineStr">
         <is>
-          <t>e82bed56bfdeef7657145d894f813eec584179277812152eaa0b93cf36cf26ce</t>
+          <t>f53080d649a2f8d30feb355c7054ee39b5db643556d769be9fa9019700aae0ee</t>
         </is>
       </c>
       <c r="C45" s="1041" t="n"/>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="B48" s="1040" t="inlineStr">
         <is>
-          <t>0aeb3baff7024ba001b3206c687c3f35bb09436c579f4be4de14cd178d3271ed</t>
+          <t>aac75df69d3dbcc48e4a15a9cf3dee699c95246b9ff062e662d93aaf69218228</t>
         </is>
       </c>
       <c r="C48" s="1041" t="n"/>

--- a/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
+++ b/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
@@ -10482,7 +10482,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1" s="1025">
+    <row r="5" ht="49" customHeight="1" s="1025">
       <c r="A5" s="1058" t="inlineStr">
         <is>
           <t>会员与客户管理</t>
@@ -10514,7 +10514,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1" s="1025">
+    <row r="6" ht="49" customHeight="1" s="1025">
       <c r="A6" s="1058" t="inlineStr">
         <is>
           <t>订单与履约</t>
@@ -10546,7 +10546,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1" s="1025">
+    <row r="7" ht="49" customHeight="1" s="1025">
       <c r="A7" s="1058" t="inlineStr">
         <is>
           <t>全渠道运营</t>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1" s="1025">
+    <row r="8" ht="34" customHeight="1" s="1025">
       <c r="A8" s="1058" t="inlineStr">
         <is>
           <t>财务结算与经营分析</t>
@@ -10610,7 +10610,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1" s="1025">
+    <row r="9" ht="34" customHeight="1" s="1025">
       <c r="A9" s="1058" t="inlineStr">
         <is>
           <t>平台与服务边界</t>
@@ -10642,7 +10642,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1" s="1025">
+    <row r="10" ht="34" customHeight="1" s="1025">
       <c r="A10" s="1058" t="inlineStr">
         <is>
           <t>上线与质量保障</t>
@@ -10912,7 +10912,7 @@
       </c>
       <c r="G5" s="1058" t="inlineStr"/>
     </row>
-    <row r="6" ht="34" customHeight="1" s="1025">
+    <row r="6" ht="49" customHeight="1" s="1025">
       <c r="A6" s="1058" t="inlineStr">
         <is>
           <t>会员与客户管理</t>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="G13" s="1058" t="inlineStr"/>
     </row>
-    <row r="14" ht="34" customHeight="1" s="1025">
+    <row r="14" ht="49" customHeight="1" s="1025">
       <c r="A14" s="1058" t="inlineStr">
         <is>
           <t>财务结算与经营分析</t>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="G16" s="1058" t="inlineStr"/>
     </row>
-    <row r="17" ht="34" customHeight="1" s="1025">
+    <row r="17" ht="94" customHeight="1" s="1025">
       <c r="A17" s="1058" t="inlineStr">
         <is>
           <t>平台与服务边界</t>
@@ -11728,7 +11728,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1" s="1025">
+    <row r="6" ht="49" customHeight="1" s="1025">
       <c r="A6" s="926">
         <f>IF(B6="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B6,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
         <v/>
@@ -12162,7 +12162,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="42" customHeight="1" s="1025">
+    <row r="17" ht="49" customHeight="1" s="1025">
       <c r="A17" s="926">
         <f>IF(B17="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B17,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
         <v/>
@@ -12242,7 +12242,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="42" customHeight="1" s="1025">
+    <row r="19" ht="49" customHeight="1" s="1025">
       <c r="A19" s="926">
         <f>IF(B19="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B19,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
         <v/>
@@ -12322,7 +12322,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="42" customHeight="1" s="1025">
+    <row r="21" ht="49" customHeight="1" s="1025">
       <c r="A21" s="926">
         <f>IF(B21="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B21,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
         <v/>
@@ -12364,7 +12364,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1" s="1025">
+    <row r="22" ht="49" customHeight="1" s="1025">
       <c r="A22" s="926">
         <f>IF(B22="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B22,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
         <v/>
@@ -14646,7 +14646,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="38" customHeight="1" s="1025">
+    <row r="5" ht="49" customHeight="1" s="1025">
       <c r="A5" s="944">
         <f>IF(C5="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C5,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -14717,7 +14717,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="38" customHeight="1" s="1025">
+    <row r="6" ht="49" customHeight="1" s="1025">
       <c r="A6" s="944">
         <f>IF(C6="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C6,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -14784,7 +14784,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="38" customHeight="1" s="1025">
+    <row r="7" ht="49" customHeight="1" s="1025">
       <c r="A7" s="944">
         <f>IF(C7="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C7,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -15052,7 +15052,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1" s="1025">
+    <row r="11" ht="49" customHeight="1" s="1025">
       <c r="A11" s="944">
         <f>IF(C11="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C11,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -15186,7 +15186,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="38" customHeight="1" s="1025">
+    <row r="13" ht="49" customHeight="1" s="1025">
       <c r="A13" s="944">
         <f>IF(C13="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C13,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -15320,7 +15320,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="38" customHeight="1" s="1025">
+    <row r="15" ht="49" customHeight="1" s="1025">
       <c r="A15" s="944">
         <f>IF(C15="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C15,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -15387,7 +15387,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="38" customHeight="1" s="1025">
+    <row r="16" ht="49" customHeight="1" s="1025">
       <c r="A16" s="944">
         <f>IF(C16="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C16,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -15454,7 +15454,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="38" customHeight="1" s="1025">
+    <row r="17" ht="49" customHeight="1" s="1025">
       <c r="A17" s="944">
         <f>IF(C17="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C17,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -15651,7 +15651,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="38" customHeight="1" s="1025">
+    <row r="20" ht="49" customHeight="1" s="1025">
       <c r="A20" s="944">
         <f>IF(C20="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C20,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -15848,7 +15848,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="38" customHeight="1" s="1025">
+    <row r="23" ht="49" customHeight="1" s="1025">
       <c r="A23" s="944">
         <f>IF(C23="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C23,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -16171,7 +16171,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="38" customHeight="1" s="1025">
+    <row r="28" ht="49" customHeight="1" s="1025">
       <c r="A28" s="944">
         <f>IF(C28="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C28,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -16301,7 +16301,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="38" customHeight="1" s="1025">
+    <row r="30" ht="49" customHeight="1" s="1025">
       <c r="A30" s="944">
         <f>IF(C30="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C30,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -16431,7 +16431,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="38" customHeight="1" s="1025">
+    <row r="32" ht="49" customHeight="1" s="1025">
       <c r="A32" s="944">
         <f>IF(C32="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C32,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -16498,7 +16498,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="38" customHeight="1" s="1025">
+    <row r="33" ht="49" customHeight="1" s="1025">
       <c r="A33" s="944">
         <f>IF(C33="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C33,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -16565,7 +16565,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="38" customHeight="1" s="1025">
+    <row r="34" ht="49" customHeight="1" s="1025">
       <c r="A34" s="944">
         <f>IF(C34="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C34,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -16636,7 +16636,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="38" customHeight="1" s="1025">
+    <row r="35" ht="49" customHeight="1" s="1025">
       <c r="A35" s="944">
         <f>IF(C35="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C35,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -16707,7 +16707,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="38" customHeight="1" s="1025">
+    <row r="36" ht="49" customHeight="1" s="1025">
       <c r="A36" s="944">
         <f>IF(C36="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C36,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -16774,7 +16774,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="38" customHeight="1" s="1025">
+    <row r="37" ht="49" customHeight="1" s="1025">
       <c r="A37" s="944">
         <f>IF(C37="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C37,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -16967,7 +16967,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="38" customHeight="1" s="1025">
+    <row r="40" ht="49" customHeight="1" s="1025">
       <c r="A40" s="944">
         <f>IF(C40="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C40,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -17038,7 +17038,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="38" customHeight="1" s="1025">
+    <row r="41" ht="49" customHeight="1" s="1025">
       <c r="A41" s="944">
         <f>IF(C41="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C41,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -17168,7 +17168,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="38" customHeight="1" s="1025">
+    <row r="43" ht="49" customHeight="1" s="1025">
       <c r="A43" s="944">
         <f>IF(C43="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C43,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -17298,7 +17298,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="38" customHeight="1" s="1025">
+    <row r="45" ht="49" customHeight="1" s="1025">
       <c r="A45" s="944">
         <f>IF(C45="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C45,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -17495,7 +17495,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="38" customHeight="1" s="1025">
+    <row r="48" ht="49" customHeight="1" s="1025">
       <c r="A48" s="944">
         <f>IF(C48="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C48,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -17566,7 +17566,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="38" customHeight="1" s="1025">
+    <row r="49" ht="49" customHeight="1" s="1025">
       <c r="A49" s="944">
         <f>IF(C49="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C49,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -18920,7 +18920,7 @@
       <c r="H7" s="1049" t="n"/>
       <c r="I7" s="1049" t="n"/>
     </row>
-    <row r="8" ht="38" customHeight="1" s="1025">
+    <row r="8" ht="49" customHeight="1" s="1025">
       <c r="A8" s="1060" t="inlineStr">
         <is>
           <t>支付网关退款认证可能延迟</t>

--- a/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
+++ b/plugins/ai-sow/docs/reference/SOW估算与生成示例_v1.3.xlsx
@@ -4926,8 +4926,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EpicTable" displayName="EpicTable" ref="A4:F10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A4:F10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EpicTable" displayName="EpicTable" ref="A4:F5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A4:F5"/>
   <tableColumns count="6">
     <tableColumn id="1" name="需求名称"/>
     <tableColumn id="2" name="需求类型"/>
@@ -4977,8 +4977,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="FeatureTable" displayName="FeatureTable" ref="A4:G22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A4:G22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="FeatureTable" displayName="FeatureTable" ref="A4:G6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A4:G6"/>
   <tableColumns count="7">
     <tableColumn id="1" name="需求名称"/>
     <tableColumn id="2" name="子需求名称"/>
@@ -4993,8 +4993,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SOWStoryTable" displayName="SOWStoryTable" ref="A4:I27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A4:I27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SOWStoryTable" displayName="SOWStoryTable" ref="A4:I5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A4:I5"/>
   <tableColumns count="9">
     <tableColumn id="1" name="需求名称">
       <calculatedColumnFormula>IF(B5="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B5,FeatureTable[子需求名称],0)),"来源未匹配"))</calculatedColumnFormula>
@@ -5021,8 +5021,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="AcceptanceCriterionTable" displayName="AcceptanceCriterionTable" ref="A4:D35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A4:D35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="AcceptanceCriterionTable" displayName="AcceptanceCriterionTable" ref="A4:D5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A4:D5"/>
   <tableColumns count="4">
     <tableColumn id="1" name="需求名称">
       <calculatedColumnFormula>IF(C5="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C5,SOWStoryTable[故事名称],0)),"来源未匹配"))</calculatedColumnFormula>
@@ -5038,7 +5038,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TaskTable" displayName="TaskTable" ref="A4:O50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TaskTable" displayName="TaskTable" ref="A4:O7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="15">
     <tableColumn id="1" name="需求名称">
       <calculatedColumnFormula>IF(C5="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C5,SOWStoryTable[故事名称],0)),"来源未匹配"))</calculatedColumnFormula>
@@ -5073,7 +5073,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="IntegrationTable" displayName="IntegrationTable" ref="A4:N8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="IntegrationTable" displayName="IntegrationTable" ref="A4:N5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="14">
     <tableColumn id="1" name="需求名称">
       <calculatedColumnFormula>IF(C5="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C5,SOWStoryTable[故事名称],0)),"来源未匹配"))</calculatedColumnFormula>
@@ -5107,7 +5107,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="AssumptionRiskTable" displayName="AssumptionRiskTable" ref="A4:F10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="AssumptionRiskTable" displayName="AssumptionRiskTable" ref="A4:F5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" name="假设/风险名称"/>
     <tableColumn id="2" name="类型"/>
@@ -5136,8 +5136,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="AsIsDetailTable" displayName="AsIsDetailTable" ref="A4:D15" headerRowCount="1">
-  <autoFilter ref="A4:D15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="AsIsDetailTable" displayName="AsIsDetailTable" ref="A4:D5" headerRowCount="1">
+  <autoFilter ref="A4:D5"/>
   <tableColumns count="4">
     <tableColumn id="1" name="主题名称"/>
     <tableColumn id="2" name="现状条目名称"/>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="B44" s="1040" t="inlineStr">
         <is>
-          <t>0d2185e21964766b07adf5925e809d63bd32cb07f9e47d4a8a0cf499d41a5de4</t>
+          <t>ee806b28729ff8b4ecb4cd020d31b1f016c84d382d4a5f601d92cf5ff382a7ed</t>
         </is>
       </c>
       <c r="C44" s="1041" t="n"/>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="B45" s="1040" t="inlineStr">
         <is>
-          <t>f53080d649a2f8d30feb355c7054ee39b5db643556d769be9fa9019700aae0ee</t>
+          <t>7d125349439fe1439e226ec1ad7187585171f5d82bdf9d947112342fe425d506</t>
         </is>
       </c>
       <c r="C45" s="1041" t="n"/>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="B46" s="1040" t="inlineStr">
         <is>
-          <t>72412b3c186a51a55879a592e2e74bd4ad234710052502718de5ada36c94b16c</t>
+          <t>7d125349439fe1439e226ec1ad7187585171f5d82bdf9d947112342fe425d506</t>
         </is>
       </c>
       <c r="C46" s="1041" t="n"/>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="B47" s="1040" t="inlineStr">
         <is>
-          <t>16d678a745213634f4b9e0b027e9b271233f60af4c91e27b25dd1b14cae002a3</t>
+          <t>7d125349439fe1439e226ec1ad7187585171f5d82bdf9d947112342fe425d506</t>
         </is>
       </c>
       <c r="C47" s="1041" t="n"/>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="B48" s="1040" t="inlineStr">
         <is>
-          <t>aac75df69d3dbcc48e4a15a9cf3dee699c95246b9ff062e662d93aaf69218228</t>
+          <t>0349220808ff3bb520b25dc0a0acf1a5171637847613a38a7e0dc4f36b1e7c58</t>
         </is>
       </c>
       <c r="C48" s="1041" t="n"/>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="B49" s="1040" t="inlineStr">
         <is>
-          <t>982f42b43a059f66a9b506e20205ea14070345e493891396dc380b091381c9e6</t>
+          <t>0349220808ff3bb520b25dc0a0acf1a5171637847613a38a7e0dc4f36b1e7c58</t>
         </is>
       </c>
       <c r="C49" s="1041" t="n"/>
@@ -6327,7 +6327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.79999923706055"/>
   <cols>
     <col width="24" customWidth="1" style="1025" min="1" max="1"/>
@@ -6355,7 +6355,7 @@
     <row r="2" ht="32" customHeight="1" s="1025">
       <c r="A2" s="1055" t="inlineStr">
         <is>
-          <t>模式：存量改造 | 截止日期：2026-08-19 | 代码仓库：客户门户仓库@0123456789ab | 排除范围：上线后驻场支持、旧系统退役、ERP 库存核算改造、总账系统改造</t>
+          <t>有效起点：1 项 | 往期承诺沿用：1 项 | 排除：0 项</t>
         </is>
       </c>
       <c r="B2" s="1056" t="n"/>
@@ -6397,17 +6397,17 @@
     <row r="5" ht="36" customHeight="1" s="1025">
       <c r="A5" s="1057" t="inlineStr">
         <is>
-          <t>应用与组件</t>
+          <t>能力与流程</t>
         </is>
       </c>
       <c r="B5" s="1053" t="inlineStr">
         <is>
-          <t>可复用的客户档案框架</t>
+          <t>既有退款接口</t>
         </is>
       </c>
       <c r="C5" s="1053" t="inlineStr">
         <is>
-          <t>从现有客户档案页面、字段校验和服务框架开始。</t>
+          <t>项目启动时已有可调用的退款申请和状态查询接口。</t>
         </is>
       </c>
       <c r="D5" s="1057" t="inlineStr">
@@ -6416,226 +6416,15 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1" s="1025">
-      <c r="A6" s="1057" t="inlineStr">
-        <is>
-          <t>数据与存储</t>
-        </is>
-      </c>
-      <c r="B6" s="1053" t="inlineStr">
-        <is>
-          <t>既有会员主数据模型</t>
-        </is>
-      </c>
-      <c r="C6" s="1053" t="inlineStr">
-        <is>
-          <t>复用统一会员号与基础属性表，新增等级历史和规则版本。</t>
-        </is>
-      </c>
-      <c r="D6" s="1057" t="inlineStr">
-        <is>
-          <t>当前已存在</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" s="1025">
-      <c r="A7" s="1057" t="inlineStr">
-        <is>
-          <t>应用与组件</t>
-        </is>
-      </c>
-      <c r="B7" s="1053" t="inlineStr">
-        <is>
-          <t>既有订单服务与状态机</t>
-        </is>
-      </c>
-      <c r="C7" s="1053" t="inlineStr">
-        <is>
-          <t>调整线上订单服务，扩展门店、退货退款和财务状态。</t>
-        </is>
-      </c>
-      <c r="D7" s="1057" t="inlineStr">
-        <is>
-          <t>当前已存在</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1" s="1025">
-      <c r="A8" s="1057" t="inlineStr">
-        <is>
-          <t>集成与外部依赖</t>
-        </is>
-      </c>
-      <c r="B8" s="1053" t="inlineStr">
-        <is>
-          <t>既有 ERP 库存接口</t>
-        </is>
-      </c>
-      <c r="C8" s="1053" t="inlineStr">
-        <is>
-          <t>接口契约保持不变，本项目完成认证、映射、适配和专项验证。</t>
-        </is>
-      </c>
-      <c r="D8" s="1057" t="inlineStr">
-        <is>
-          <t>当前已存在</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1" s="1025">
-      <c r="A9" s="1057" t="inlineStr">
-        <is>
-          <t>集成与外部依赖</t>
-        </is>
-      </c>
-      <c r="B9" s="1053" t="inlineStr">
-        <is>
-          <t>既有支付网关租户</t>
-        </is>
-      </c>
-      <c r="C9" s="1053" t="inlineStr">
-        <is>
-          <t>支付网关平台保持不变，本项目完成配置、认证、映射和专项验证。</t>
-        </is>
-      </c>
-      <c r="D9" s="1057" t="inlineStr">
-        <is>
-          <t>当前已存在</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1" s="1025">
-      <c r="A10" s="1057" t="inlineStr">
-        <is>
-          <t>集成与外部依赖</t>
-        </is>
-      </c>
-      <c r="B10" s="1053" t="inlineStr">
-        <is>
-          <t>既有电子发票通道</t>
-        </is>
-      </c>
-      <c r="C10" s="1053" t="inlineStr">
-        <is>
-          <t>电子发票平台保持不变，本项目完成租户设置、认证、映射和适配。</t>
-        </is>
-      </c>
-      <c r="D10" s="1057" t="inlineStr">
-        <is>
-          <t>当前已存在</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1" s="1025">
-      <c r="A11" s="1057" t="inlineStr">
-        <is>
-          <t>平台、环境与部署</t>
-        </is>
-      </c>
-      <c r="B11" s="1053" t="inlineStr">
-        <is>
-          <t>既有生产环境与发布流水线</t>
-        </is>
-      </c>
-      <c r="C11" s="1053" t="inlineStr">
-        <is>
-          <t>在现有集群与流水线中增加应用配置、发布步骤、切换和回滚清单。</t>
-        </is>
-      </c>
-      <c r="D11" s="1057" t="inlineStr">
-        <is>
-          <t>当前已存在</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1" s="1025">
-      <c r="A12" s="1057" t="inlineStr">
-        <is>
-          <t>安全与合规</t>
-        </is>
-      </c>
-      <c r="B12" s="1053" t="inlineStr">
-        <is>
-          <t>既有会员授权中心</t>
-        </is>
-      </c>
-      <c r="C12" s="1053" t="inlineStr">
-        <is>
-          <t>现有授权、撤回、查询与审计能力已完整覆盖本期目标。</t>
-        </is>
-      </c>
-      <c r="D12" s="1057" t="inlineStr">
-        <is>
-          <t>当前已存在</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" s="1025">
-      <c r="A13" s="1057" t="inlineStr">
-        <is>
-          <t>能力与流程</t>
-        </is>
-      </c>
-      <c r="B13" s="1053" t="inlineStr">
-        <is>
-          <t>既有订单消息通知服务</t>
-        </is>
-      </c>
-      <c r="C13" s="1053" t="inlineStr">
-        <is>
-          <t>标准订单事件和现有通知通道已完整覆盖本期通知目标。</t>
-        </is>
-      </c>
-      <c r="D13" s="1057" t="inlineStr">
-        <is>
-          <t>当前已存在</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1" s="1025">
-      <c r="A14" s="1057" t="inlineStr">
-        <is>
-          <t>运维与质量</t>
-        </is>
-      </c>
-      <c r="B14" s="1053" t="inlineStr">
-        <is>
-          <t>既有统一监控平台</t>
-        </is>
-      </c>
-      <c r="C14" s="1053" t="inlineStr">
-        <is>
-          <t>复用日志、指标和链路平台，新增订单与财务作业监控。</t>
-        </is>
-      </c>
-      <c r="D14" s="1057" t="inlineStr">
-        <is>
-          <t>当前已存在</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1" s="1025">
-      <c r="A15" s="1057" t="inlineStr">
-        <is>
-          <t>运维与质量</t>
-        </is>
-      </c>
-      <c r="B15" s="1053" t="inlineStr">
-        <is>
-          <t>既有回归测试资产</t>
-        </is>
-      </c>
-      <c r="C15" s="1053" t="inlineStr">
-        <is>
-          <t>调整既有测试框架、测试用例、测试脚本、兼容矩阵与负载模型。</t>
-        </is>
-      </c>
-      <c r="D15" s="1057" t="inlineStr">
-        <is>
-          <t>当前已存在</t>
-        </is>
-      </c>
-    </row>
+    <row r="6" ht="28" customHeight="1" s="1025"/>
+    <row r="7" ht="28" customHeight="1" s="1025"/>
+    <row r="8" ht="28" customHeight="1" s="1025"/>
+    <row r="9" ht="28" customHeight="1" s="1025"/>
+    <row r="10" ht="28" customHeight="1" s="1025"/>
+    <row r="11" ht="28" customHeight="1" s="1025"/>
+    <row r="12" ht="28" customHeight="1" s="1025"/>
+    <row r="13" ht="28" customHeight="1" s="1025"/>
+    <row r="14" ht="44" customHeight="1" s="1025"/>
     <row r="17" ht="38" customHeight="1" s="1025"/>
     <row r="18" ht="36" customHeight="1" s="1025"/>
     <row r="19" ht="36" customHeight="1" s="1025"/>
@@ -10485,7 +10274,7 @@
     <row r="5" ht="49" customHeight="1" s="1025">
       <c r="A5" s="1058" t="inlineStr">
         <is>
-          <t>会员与客户管理</t>
+          <t>退款能力升级</t>
         </is>
       </c>
       <c r="B5" s="1059" t="inlineStr">
@@ -10495,185 +10284,26 @@
       </c>
       <c r="C5" s="1058" t="inlineStr">
         <is>
-          <t>统一会员身份、档案、等级与授权边界。</t>
+          <t>升级退款处理并保持状态通知一致。</t>
         </is>
       </c>
       <c r="D5" s="1058" t="inlineStr">
         <is>
-          <t>会员门户、会员主数据、授权中心 / customer_profile、member_tier</t>
+          <t>退款编排流程</t>
         </is>
       </c>
       <c r="E5" s="1058" t="inlineStr">
         <is>
-          <t>会员信息跨渠道一致，等级与授权过程可追溯</t>
-        </is>
-      </c>
-      <c r="F5" s="1058" t="inlineStr">
-        <is>
-          <t>不迁移授权主数据，不改造现有授权中心</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="49" customHeight="1" s="1025">
-      <c r="A6" s="1058" t="inlineStr">
-        <is>
-          <t>订单与履约</t>
-        </is>
-      </c>
-      <c r="B6" s="1059" t="inlineStr">
-        <is>
-          <t>业务</t>
-        </is>
-      </c>
-      <c r="C6" s="1058" t="inlineStr">
-        <is>
-          <t>统一订单受理、库存预占、状态流转与退货退款。</t>
-        </is>
-      </c>
-      <c r="D6" s="1058" t="inlineStr">
-        <is>
-          <t>订单服务、ERP、支付网关 / order、inventory_reservation、refund</t>
-        </is>
-      </c>
-      <c r="E6" s="1058" t="inlineStr">
-        <is>
-          <t>门店与线上订单按同一规则履约且异常可恢复</t>
-        </is>
-      </c>
-      <c r="F6" s="1058" t="inlineStr">
-        <is>
-          <t>不替换 ERP 库存核算与支付清算能力</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="49" customHeight="1" s="1025">
-      <c r="A7" s="1058" t="inlineStr">
-        <is>
-          <t>全渠道运营</t>
-        </is>
-      </c>
-      <c r="B7" s="1059" t="inlineStr">
-        <is>
-          <t>业务</t>
-        </is>
-      </c>
-      <c r="C7" s="1058" t="inlineStr">
-        <is>
-          <t>为门店、顾客和客服提供一致的订单操作与信息。</t>
-        </is>
-      </c>
-      <c r="D7" s="1058" t="inlineStr">
-        <is>
-          <t>门店工作台、会员门户、消息中心 / store_order、order_timeline</t>
-        </is>
-      </c>
-      <c r="E7" s="1058" t="inlineStr">
-        <is>
-          <t>门店处理效率与顾客订单可视性提升</t>
-        </is>
-      </c>
-      <c r="F7" s="1058" t="inlineStr">
-        <is>
-          <t>不改造消息中心通道策略与营销触达规则</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1" s="1025">
-      <c r="A8" s="1058" t="inlineStr">
-        <is>
-          <t>财务结算与经营分析</t>
-        </is>
-      </c>
-      <c r="B8" s="1059" t="inlineStr">
-        <is>
-          <t>业务</t>
-        </is>
-      </c>
-      <c r="C8" s="1058" t="inlineStr">
-        <is>
-          <t>建立支付、退款、发票和经营指标的日结闭环。</t>
-        </is>
-      </c>
-      <c r="D8" s="1058" t="inlineStr">
-        <is>
-          <t>订单服务、支付网关、电子发票平台、财务数据集市</t>
-        </is>
-      </c>
-      <c r="E8" s="1058" t="inlineStr">
-        <is>
-          <t>财务差异可定位、发票可追踪、经营指标口径一致</t>
-        </is>
-      </c>
-      <c r="F8" s="1058" t="inlineStr">
-        <is>
-          <t>不改造总账系统，不包含税务筹划与历史会计调整</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1" s="1025">
-      <c r="A9" s="1058" t="inlineStr">
-        <is>
-          <t>平台与服务边界</t>
-        </is>
-      </c>
-      <c r="B9" s="1059" t="inlineStr">
-        <is>
-          <t>技术</t>
-        </is>
-      </c>
-      <c r="C9" s="1058" t="inlineStr">
-        <is>
-          <t>明确会员、订单与生产发布所需的稳定技术边界。</t>
-        </is>
-      </c>
-      <c r="D9" s="1058" t="inlineStr">
-        <is>
-          <t>会员门户、订单服务、API 网关、生产平台</t>
-        </is>
-      </c>
-      <c r="E9" s="1058" t="inlineStr">
-        <is>
-          <t>服务职责清晰、发布可回滚、生产范围可签署</t>
-        </is>
-      </c>
-      <c r="F9" s="1058" t="inlineStr">
-        <is>
-          <t>不替换企业级网关、Kubernetes 平台与 CI/CD 产品</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1" s="1025">
-      <c r="A10" s="1058" t="inlineStr">
-        <is>
-          <t>上线与质量保障</t>
-        </is>
-      </c>
-      <c r="B10" s="1059" t="inlineStr">
-        <is>
-          <t>技术</t>
-        </is>
-      </c>
-      <c r="C10" s="1058" t="inlineStr">
-        <is>
-          <t>将数据迁移、监控运维、质量验证和责任边界纳入可估算交付。</t>
-        </is>
-      </c>
-      <c r="D10" s="1058" t="inlineStr">
-        <is>
-          <t>迁移作业、统一监控平台、测试资产、运维知识库</t>
-        </is>
-      </c>
-      <c r="E10" s="1058" t="inlineStr">
-        <is>
-          <t>上线过程可验证、可回退、可运维并可审计</t>
-        </is>
-      </c>
-      <c r="F10" s="1058" t="inlineStr">
-        <is>
-          <t>不包含上线后驻场支持和旧系统退役实施</t>
-        </is>
-      </c>
-    </row>
+          <t>在既有退款能力上增加自动审核并保持可追踪结果。、退款状态变化后向用户提供一致的通知结果。</t>
+        </is>
+      </c>
+      <c r="F5" s="1058" t="inlineStr"/>
+    </row>
+    <row r="6" s="1025"/>
+    <row r="7" s="1025"/>
+    <row r="8" s="1025"/>
+    <row r="9" s="1025"/>
+    <row r="10" s="1025"/>
     <row r="11" s="1025"/>
     <row r="12" s="1025"/>
     <row r="13" s="1025"/>
@@ -10882,27 +10512,27 @@
     <row r="5" ht="34" customHeight="1" s="1025">
       <c r="A5" s="1058" t="inlineStr">
         <is>
-          <t>会员与客户管理</t>
+          <t>退款能力升级</t>
         </is>
       </c>
       <c r="B5" s="1058" t="inlineStr">
         <is>
-          <t>创建并查看客户档案</t>
+          <t>退款处理升级</t>
         </is>
       </c>
       <c r="C5" s="1058" t="inlineStr">
         <is>
-          <t>用户创建或维护客户档案后，各渠道可查看授权范围内的最新信息。</t>
+          <t>在既有退款能力上增加自动审核并保持可追踪结果。</t>
         </is>
       </c>
       <c r="D5" s="1058" t="inlineStr">
         <is>
-          <t>会员门户、会员主数据 / customer_profile</t>
+          <t>退款编排流程、支付平台退款</t>
         </is>
       </c>
       <c r="E5" s="1058" t="inlineStr">
         <is>
-          <t>档案查询 P95 小于 300ms；敏感字段按角色脱敏</t>
+          <t>退款流程恢复目标</t>
         </is>
       </c>
       <c r="F5" s="1059" t="inlineStr">
@@ -10910,32 +10540,36 @@
           <t>来源输入</t>
         </is>
       </c>
-      <c r="G5" s="1058" t="inlineStr"/>
-    </row>
-    <row r="6" ht="49" customHeight="1" s="1025">
+      <c r="G5" s="1058" t="inlineStr">
+        <is>
+          <t>本期需要在既有退款服务上交付自动审核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" s="1025">
       <c r="A6" s="1058" t="inlineStr">
         <is>
-          <t>会员与客户管理</t>
+          <t>退款能力升级</t>
         </is>
       </c>
       <c r="B6" s="1058" t="inlineStr">
         <is>
-          <t>会员等级计算与版本</t>
+          <t>退款状态通知</t>
         </is>
       </c>
       <c r="C6" s="1058" t="inlineStr">
         <is>
-          <t>按有效消费额计算等级，并记录规则版本、生效日和调整原因。</t>
+          <t>退款状态变化后向用户提供一致的通知结果。</t>
         </is>
       </c>
       <c r="D6" s="1058" t="inlineStr">
         <is>
-          <t>会员主数据、订单服务 / member_tier_rule、member_tier_history</t>
+          <t>退款编排流程、支付平台退款</t>
         </is>
       </c>
       <c r="E6" s="1058" t="inlineStr">
         <is>
-          <t>同一会员同一时点仅有一个生效等级</t>
+          <t>退款流程恢复目标</t>
         </is>
       </c>
       <c r="F6" s="1059" t="inlineStr">
@@ -10943,540 +10577,28 @@
           <t>来源输入</t>
         </is>
       </c>
-      <c r="G6" s="1058" t="inlineStr"/>
-    </row>
-    <row r="7" ht="34" customHeight="1" s="1025">
-      <c r="A7" s="1058" t="inlineStr">
-        <is>
-          <t>会员与客户管理</t>
-        </is>
-      </c>
-      <c r="B7" s="1058" t="inlineStr">
-        <is>
-          <t>会员授权与撤回复用</t>
-        </is>
-      </c>
-      <c r="C7" s="1058" t="inlineStr">
-        <is>
-          <t>复用授权中心的授权、撤回与查询能力。</t>
-        </is>
-      </c>
-      <c r="D7" s="1058" t="inlineStr">
-        <is>
-          <t>授权中心 / consent_record、consent_audit</t>
-        </is>
-      </c>
-      <c r="E7" s="1058" t="inlineStr">
-        <is>
-          <t>渠道不复制授权主数据，查询留痕保存 36 个月</t>
-        </is>
-      </c>
-      <c r="F7" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G7" s="1058" t="inlineStr"/>
-    </row>
-    <row r="8" ht="34" customHeight="1" s="1025">
-      <c r="A8" s="1058" t="inlineStr">
-        <is>
-          <t>订单与履约</t>
-        </is>
-      </c>
-      <c r="B8" s="1058" t="inlineStr">
-        <is>
-          <t>统一订单编排与状态机</t>
-        </is>
-      </c>
-      <c r="C8" s="1058" t="inlineStr">
-        <is>
-          <t>接收门店与线上订单，执行价格、权益和履约校验并驱动状态流转。</t>
-        </is>
-      </c>
-      <c r="D8" s="1058" t="inlineStr">
-        <is>
-          <t>订单服务、门店工作台、会员门户 / order、order_state</t>
-        </is>
-      </c>
-      <c r="E8" s="1058" t="inlineStr">
-        <is>
-          <t>订单状态变更幂等且全链路可追踪</t>
-        </is>
-      </c>
-      <c r="F8" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G8" s="1058" t="inlineStr"/>
-    </row>
-    <row r="9" ht="34" customHeight="1" s="1025">
-      <c r="A9" s="1058" t="inlineStr">
-        <is>
-          <t>订单与履约</t>
-        </is>
-      </c>
-      <c r="B9" s="1058" t="inlineStr">
-        <is>
-          <t>库存预占与释放</t>
-        </is>
-      </c>
-      <c r="C9" s="1058" t="inlineStr">
-        <is>
-          <t>订单确认前通过 ERP 预占库存，取消或超时后释放。</t>
-        </is>
-      </c>
-      <c r="D9" s="1058" t="inlineStr">
-        <is>
-          <t>订单服务、ERP / inventory_reservation</t>
-        </is>
-      </c>
-      <c r="E9" s="1058" t="inlineStr">
-        <is>
-          <t>接口重试不得重复预占；调用超时 3 秒</t>
-        </is>
-      </c>
-      <c r="F9" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G9" s="1058" t="inlineStr"/>
-    </row>
-    <row r="10" ht="34" customHeight="1" s="1025">
-      <c r="A10" s="1058" t="inlineStr">
-        <is>
-          <t>订单与履约</t>
-        </is>
-      </c>
-      <c r="B10" s="1058" t="inlineStr">
-        <is>
-          <t>退货退款闭环</t>
-        </is>
-      </c>
-      <c r="C10" s="1058" t="inlineStr">
-        <is>
-          <t>核验可退数量，生成退货单并调用支付网关退款。</t>
-        </is>
-      </c>
-      <c r="D10" s="1058" t="inlineStr">
-        <is>
-          <t>门店工作台、订单服务、支付网关 / return_order、refund</t>
-        </is>
-      </c>
-      <c r="E10" s="1058" t="inlineStr">
-        <is>
-          <t>退款请求幂等，支付结果与订单差异可审计</t>
-        </is>
-      </c>
-      <c r="F10" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G10" s="1058" t="inlineStr"/>
-    </row>
-    <row r="11" ht="34" customHeight="1" s="1025">
-      <c r="A11" s="1058" t="inlineStr">
-        <is>
-          <t>全渠道运营</t>
-        </is>
-      </c>
-      <c r="B11" s="1058" t="inlineStr">
-        <is>
-          <t>门店接单工作台</t>
-        </is>
-      </c>
-      <c r="C11" s="1058" t="inlineStr">
-        <is>
-          <t>展示待处理订单、缺货替代与交接信息并按门店权限操作。</t>
-        </is>
-      </c>
-      <c r="D11" s="1058" t="inlineStr">
-        <is>
-          <t>门店工作台、订单服务 / store_order_queue</t>
-        </is>
-      </c>
-      <c r="E11" s="1058" t="inlineStr">
-        <is>
-          <t>仅授权门店可查看和操作本店订单</t>
-        </is>
-      </c>
-      <c r="F11" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G11" s="1058" t="inlineStr"/>
-    </row>
-    <row r="12" ht="34" customHeight="1" s="1025">
-      <c r="A12" s="1058" t="inlineStr">
-        <is>
-          <t>全渠道运营</t>
-        </is>
-      </c>
-      <c r="B12" s="1058" t="inlineStr">
-        <is>
-          <t>订单状态与履约轨迹</t>
-        </is>
-      </c>
-      <c r="C12" s="1058" t="inlineStr">
-        <is>
-          <t>顾客和客服查看一致的状态、履约节点与异常原因。</t>
-        </is>
-      </c>
-      <c r="D12" s="1058" t="inlineStr">
-        <is>
-          <t>会员门户、客服工作台、订单服务 / order_timeline</t>
-        </is>
-      </c>
-      <c r="E12" s="1058" t="inlineStr">
-        <is>
-          <t>关键状态变更 60 秒内可见</t>
-        </is>
-      </c>
-      <c r="F12" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G12" s="1058" t="inlineStr"/>
-    </row>
-    <row r="13" ht="34" customHeight="1" s="1025">
-      <c r="A13" s="1058" t="inlineStr">
-        <is>
-          <t>全渠道运营</t>
-        </is>
-      </c>
-      <c r="B13" s="1058" t="inlineStr">
-        <is>
-          <t>订单节点通知复用</t>
-        </is>
-      </c>
-      <c r="C13" s="1058" t="inlineStr">
-        <is>
-          <t>复用消息中心消费标准订单事件并发送通知。</t>
-        </is>
-      </c>
-      <c r="D13" s="1058" t="inlineStr">
-        <is>
-          <t>消息中心、订单事件总线 / notification_event</t>
-        </is>
-      </c>
-      <c r="E13" s="1058" t="inlineStr">
-        <is>
-          <t>不新增通知渠道和营销模板</t>
-        </is>
-      </c>
-      <c r="F13" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G13" s="1058" t="inlineStr"/>
-    </row>
-    <row r="14" ht="49" customHeight="1" s="1025">
-      <c r="A14" s="1058" t="inlineStr">
-        <is>
-          <t>财务结算与经营分析</t>
-        </is>
-      </c>
-      <c r="B14" s="1058" t="inlineStr">
-        <is>
-          <t>支付退款日结对账</t>
-        </is>
-      </c>
-      <c r="C14" s="1058" t="inlineStr">
-        <is>
-          <t>按渠道、门店和订单核对实收、退款与手续费差异。</t>
-        </is>
-      </c>
-      <c r="D14" s="1058" t="inlineStr">
-        <is>
-          <t>订单服务、支付网关、财务数据集市 / payment_reconciliation</t>
-        </is>
-      </c>
-      <c r="E14" s="1058" t="inlineStr">
-        <is>
-          <t>每日 07:00 前完成前一自然日对账</t>
-        </is>
-      </c>
-      <c r="F14" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G14" s="1058" t="inlineStr"/>
-    </row>
-    <row r="15" ht="34" customHeight="1" s="1025">
-      <c r="A15" s="1058" t="inlineStr">
-        <is>
-          <t>财务结算与经营分析</t>
-        </is>
-      </c>
-      <c r="B15" s="1058" t="inlineStr">
-        <is>
-          <t>电子发票申请与状态</t>
-        </is>
-      </c>
-      <c r="C15" s="1058" t="inlineStr">
-        <is>
-          <t>调用电子发票平台开票并保存号码、状态和失败原因。</t>
-        </is>
-      </c>
-      <c r="D15" s="1058" t="inlineStr">
-        <is>
-          <t>订单服务、电子发票平台 / invoice_application</t>
-        </is>
-      </c>
-      <c r="E15" s="1058" t="inlineStr">
-        <is>
-          <t>开票失败可重试且不得重复开票</t>
-        </is>
-      </c>
-      <c r="F15" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G15" s="1058" t="inlineStr"/>
-    </row>
-    <row r="16" ht="34" customHeight="1" s="1025">
-      <c r="A16" s="1058" t="inlineStr">
-        <is>
-          <t>财务结算与经营分析</t>
-        </is>
-      </c>
-      <c r="B16" s="1058" t="inlineStr">
-        <is>
-          <t>财务经营报表</t>
-        </is>
-      </c>
-      <c r="C16" s="1058" t="inlineStr">
-        <is>
-          <t>按日、区域和渠道展示销售、退款、优惠与未对账金额。</t>
-        </is>
-      </c>
-      <c r="D16" s="1058" t="inlineStr">
-        <is>
-          <t>财务数据集市 / finance_daily_metric</t>
-        </is>
-      </c>
-      <c r="E16" s="1058" t="inlineStr">
-        <is>
-          <t>指标与对账规则同源，支持追溯到订单</t>
-        </is>
-      </c>
-      <c r="F16" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G16" s="1058" t="inlineStr"/>
-    </row>
-    <row r="17" ht="94" customHeight="1" s="1025">
-      <c r="A17" s="1058" t="inlineStr">
-        <is>
-          <t>平台与服务边界</t>
-        </is>
-      </c>
-      <c r="B17" s="1058" t="inlineStr">
-        <is>
-          <t>客户档案操作 API</t>
-        </is>
-      </c>
-      <c r="C17" s="1058" t="inlineStr">
-        <is>
-          <t>通过稳定 API 创建、维护和检索客户档案，并隔离渠道与会员主数据。</t>
-        </is>
-      </c>
-      <c r="D17" s="1058" t="inlineStr">
-        <is>
-          <t>会员门户、会员主数据 / customer-profile-api</t>
-        </is>
-      </c>
-      <c r="E17" s="1058" t="inlineStr">
-        <is>
-          <t>API P95 小于 300ms；写操作使用幂等键；敏感字段按权限返回</t>
-        </is>
-      </c>
-      <c r="F17" s="1059" t="inlineStr">
-        <is>
-          <t>设计派生</t>
-        </is>
-      </c>
-      <c r="G17" s="1058" t="inlineStr">
-        <is>
-          <t>设计决策/Decision: 公开客户档案 API 使用专用 API 边界处理客户档案操作；产生原因/Cause: 客户档案操作 API 需要为会员门户与未来渠道提供统一操作边界；不交付影响/Non-delivery impact: 接口/API | 星云会员门户 -&gt; 无法通过统一边界创建或检索客户档案</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="34" customHeight="1" s="1025">
-      <c r="A18" s="1058" t="inlineStr">
-        <is>
-          <t>平台与服务边界</t>
-        </is>
-      </c>
-      <c r="B18" s="1058" t="inlineStr">
-        <is>
-          <t>生产准备、切换与验证</t>
-        </is>
-      </c>
-      <c r="C18" s="1058" t="inlineStr">
-        <is>
-          <t>完成环境配置、发布清单、切换回滚和生产验证，并形成签署证据。</t>
-        </is>
-      </c>
-      <c r="D18" s="1058" t="inlineStr">
-        <is>
-          <t>Kubernetes 生产环境、CI/CD、功能开关、发布清单</t>
-        </is>
-      </c>
-      <c r="E18" s="1058" t="inlineStr">
-        <is>
-          <t>业务中断不超过 15 分钟；回滚路径在切换前完成演练</t>
-        </is>
-      </c>
-      <c r="F18" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G18" s="1058" t="inlineStr"/>
-    </row>
-    <row r="19" ht="34" customHeight="1" s="1025">
-      <c r="A19" s="1058" t="inlineStr">
-        <is>
-          <t>平台与服务边界</t>
-        </is>
-      </c>
-      <c r="B19" s="1058" t="inlineStr">
-        <is>
-          <t>上线后支持与旧系统退役边界</t>
-        </is>
-      </c>
-      <c r="C19" s="1058" t="inlineStr">
-        <is>
-          <t>明确上线后驻场支持和旧系统退役不在本期固定范围内。</t>
-        </is>
-      </c>
-      <c r="D19" s="1058" t="inlineStr">
-        <is>
-          <t>旧会员门户、旧订单查询服务</t>
-        </is>
-      </c>
-      <c r="E19" s="1058" t="inlineStr">
-        <is>
-          <t>如需实施必须单独立项并重新确认基线</t>
-        </is>
-      </c>
-      <c r="F19" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G19" s="1058" t="inlineStr"/>
-    </row>
-    <row r="20" ht="34" customHeight="1" s="1025">
-      <c r="A20" s="1058" t="inlineStr">
-        <is>
-          <t>上线与质量保障</t>
-        </is>
-      </c>
-      <c r="B20" s="1058" t="inlineStr">
-        <is>
-          <t>会员与订单数据迁移</t>
-        </is>
-      </c>
-      <c r="C20" s="1058" t="inlineStr">
-        <is>
-          <t>迁移会员扩展字段与两年内历史订单，执行校验、补偿与留痕。</t>
-        </is>
-      </c>
-      <c r="D20" s="1058" t="inlineStr">
-        <is>
-          <t>会员主数据、订单库 / customer_profile、order、order_item</t>
-        </is>
-      </c>
-      <c r="E20" s="1058" t="inlineStr">
-        <is>
-          <t>迁移前后关键字段一致率 100%，业务主键重复为 0</t>
-        </is>
-      </c>
-      <c r="F20" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G20" s="1058" t="inlineStr"/>
-    </row>
-    <row r="21" ht="34" customHeight="1" s="1025">
-      <c r="A21" s="1058" t="inlineStr">
-        <is>
-          <t>上线与质量保障</t>
-        </is>
-      </c>
-      <c r="B21" s="1058" t="inlineStr">
-        <is>
-          <t>监控、运维交接与用户赋能</t>
-        </is>
-      </c>
-      <c r="C21" s="1058" t="inlineStr">
-        <is>
-          <t>建设关键指标和告警，完成运维手册、交接演练与业务用户培训。</t>
-        </is>
-      </c>
-      <c r="D21" s="1058" t="inlineStr">
-        <is>
-          <t>统一监控平台、运维知识库、培训材料</t>
-        </is>
-      </c>
-      <c r="E21" s="1058" t="inlineStr">
-        <is>
-          <t>核心交易告警 5 分钟内触发；交接与培训均需签到和验收记录</t>
-        </is>
-      </c>
-      <c r="F21" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G21" s="1058" t="inlineStr"/>
-    </row>
-    <row r="22" ht="34" customHeight="1" s="1025">
-      <c r="A22" s="1058" t="inlineStr">
-        <is>
-          <t>上线与质量保障</t>
-        </is>
-      </c>
-      <c r="B22" s="1058" t="inlineStr">
-        <is>
-          <t>自动化、性能与生产质量验证</t>
-        </is>
-      </c>
-      <c r="C22" s="1058" t="inlineStr">
-        <is>
-          <t>调整既有测试资产，覆盖回归、性能、安全、兼容性和生产烟测。</t>
-        </is>
-      </c>
-      <c r="D22" s="1058" t="inlineStr">
-        <is>
-          <t>API 自动化框架、测试用例库、负载模型、兼容矩阵</t>
-        </is>
-      </c>
-      <c r="E22" s="1058" t="inlineStr">
-        <is>
-          <t>P0/P1 用例通过率 100%，核心查询峰值 500 TPS</t>
-        </is>
-      </c>
-      <c r="F22" s="1059" t="inlineStr">
-        <is>
-          <t>来源输入</t>
-        </is>
-      </c>
-      <c r="G22" s="1058" t="inlineStr"/>
-    </row>
+      <c r="G6" s="1058" t="inlineStr">
+        <is>
+          <t>退款状态通知是本期用户可见结果。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" s="1025"/>
+    <row r="8" s="1025"/>
+    <row r="9" s="1025"/>
+    <row r="10" s="1025"/>
+    <row r="11" s="1025"/>
+    <row r="12" s="1025"/>
+    <row r="13" s="1025"/>
+    <row r="14" s="1025"/>
+    <row r="15" s="1025"/>
+    <row r="16" s="1025"/>
+    <row r="17" s="1025"/>
+    <row r="18" s="1025"/>
+    <row r="19" s="1025"/>
+    <row r="20" s="1025"/>
+    <row r="21" s="1025"/>
+    <row r="22" s="1025"/>
     <row r="23" s="1025"/>
     <row r="24" s="1025"/>
     <row r="25" s="1025"/>
@@ -11690,19 +10812,19 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1" s="1025">
+    <row r="5" ht="49" customHeight="1" s="1025">
       <c r="A5" s="926">
         <f>IF(B5="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B5,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
         <v/>
       </c>
       <c r="B5" s="1058" t="inlineStr">
         <is>
-          <t>创建并查看客户档案</t>
+          <t>退款处理升级</t>
         </is>
       </c>
       <c r="C5" s="1058" t="inlineStr">
         <is>
-          <t>创建并查看客户档案</t>
+          <t>完成退款自动审核与状态通知</t>
         </is>
       </c>
       <c r="D5" s="1059" t="inlineStr">
@@ -11722,880 +10844,320 @@
         <f>IF(C5="","",CEILING(SUMIF(TaskTable[故事名称],C5,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
         <v/>
       </c>
-      <c r="H5" s="1058" t="inlineStr"/>
+      <c r="H5" s="1058" t="inlineStr">
+        <is>
+          <t>支付沙箱按时可用</t>
+        </is>
+      </c>
       <c r="I5" s="930">
         <f>IF(H5="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H5,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="49" customHeight="1" s="1025">
-      <c r="A6" s="926">
-        <f>IF(B6="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B6,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B6" s="1058" t="inlineStr">
-        <is>
-          <t>客户档案操作 API</t>
-        </is>
-      </c>
-      <c r="C6" s="1058" t="inlineStr">
-        <is>
-          <t>提供客户档案操作</t>
-        </is>
-      </c>
-      <c r="D6" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E6" s="926">
-        <f t="array" ref="E6">IF(C6="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C6,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F6" s="928">
-        <f t="array" ref="F6">IF(C6="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C6,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G6" s="929">
-        <f>IF(C6="","",CEILING(SUMIF(TaskTable[故事名称],C6,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H6" s="1058" t="inlineStr"/>
-      <c r="I6" s="930">
+    <row r="6" ht="42" customHeight="1" s="1025">
+      <c r="A6" s="926" t="n"/>
+      <c r="B6" s="1043" t="n"/>
+      <c r="C6" s="1043" t="n"/>
+      <c r="D6" s="1044" t="n"/>
+      <c r="E6" s="926" t="n"/>
+      <c r="F6" s="926" t="n"/>
+      <c r="G6" s="930" t="n"/>
+      <c r="H6" s="1043" t="n"/>
+      <c r="I6" s="929">
         <f>IF(H6="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H6,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" s="1025">
-      <c r="A7" s="926">
-        <f>IF(B7="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B7,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B7" s="1058" t="inlineStr">
-        <is>
-          <t>客户档案操作 API</t>
-        </is>
-      </c>
-      <c r="C7" s="1058" t="inlineStr">
-        <is>
-          <t>集成会员主数据查询</t>
-        </is>
-      </c>
-      <c r="D7" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E7" s="926">
-        <f t="array" ref="E7">IF(C7="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C7,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F7" s="928">
-        <f t="array" ref="F7">IF(C7="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C7,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G7" s="929">
-        <f>IF(C7="","",CEILING(SUMIF(TaskTable[故事名称],C7,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H7" s="1058" t="inlineStr">
-        <is>
-          <t>会员主数据服务在联调期间可用</t>
-        </is>
-      </c>
-      <c r="I7" s="930">
+      <c r="A7" s="926" t="n"/>
+      <c r="B7" s="1043" t="n"/>
+      <c r="C7" s="1043" t="n"/>
+      <c r="D7" s="1044" t="n"/>
+      <c r="E7" s="926" t="n"/>
+      <c r="F7" s="926" t="n"/>
+      <c r="G7" s="930" t="n"/>
+      <c r="H7" s="1043" t="n"/>
+      <c r="I7" s="929">
         <f>IF(H7="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H7,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" s="1025">
-      <c r="A8" s="926">
-        <f>IF(B8="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B8,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B8" s="1058" t="inlineStr">
-        <is>
-          <t>会员等级计算与版本</t>
-        </is>
-      </c>
-      <c r="C8" s="1058" t="inlineStr">
-        <is>
-          <t>计算并追溯会员等级</t>
-        </is>
-      </c>
-      <c r="D8" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E8" s="926">
-        <f t="array" ref="E8">IF(C8="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C8,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F8" s="928">
-        <f t="array" ref="F8">IF(C8="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C8,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G8" s="929">
-        <f>IF(C8="","",CEILING(SUMIF(TaskTable[故事名称],C8,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H8" s="1058" t="inlineStr">
-        <is>
-          <t>会员主数据服务在联调期间可用</t>
-        </is>
-      </c>
-      <c r="I8" s="930">
+      <c r="A8" s="926" t="n"/>
+      <c r="B8" s="1043" t="n"/>
+      <c r="C8" s="1043" t="n"/>
+      <c r="D8" s="1044" t="n"/>
+      <c r="E8" s="926" t="n"/>
+      <c r="F8" s="926" t="n"/>
+      <c r="G8" s="930" t="n"/>
+      <c r="H8" s="1043" t="n"/>
+      <c r="I8" s="929">
         <f>IF(H8="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H8,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" s="1025">
-      <c r="A9" s="926">
-        <f>IF(B9="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B9,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B9" s="1058" t="inlineStr">
-        <is>
-          <t>统一订单编排与状态机</t>
-        </is>
-      </c>
-      <c r="C9" s="1058" t="inlineStr">
-        <is>
-          <t>统一创建全渠道订单</t>
-        </is>
-      </c>
-      <c r="D9" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E9" s="926">
-        <f t="array" ref="E9">IF(C9="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C9,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F9" s="928">
-        <f t="array" ref="F9">IF(C9="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C9,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G9" s="929">
-        <f>IF(C9="","",CEILING(SUMIF(TaskTable[故事名称],C9,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H9" s="1058" t="inlineStr"/>
-      <c r="I9" s="930">
+      <c r="A9" s="926" t="n"/>
+      <c r="B9" s="1043" t="n"/>
+      <c r="C9" s="1043" t="n"/>
+      <c r="D9" s="1044" t="n"/>
+      <c r="E9" s="926" t="n"/>
+      <c r="F9" s="926" t="n"/>
+      <c r="G9" s="930" t="n"/>
+      <c r="H9" s="1043" t="n"/>
+      <c r="I9" s="929">
         <f>IF(H9="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H9,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" s="1025">
-      <c r="A10" s="926">
-        <f>IF(B10="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B10,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B10" s="1058" t="inlineStr">
-        <is>
-          <t>统一订单编排与状态机</t>
-        </is>
-      </c>
-      <c r="C10" s="1058" t="inlineStr">
-        <is>
-          <t>驱动订单状态与事件</t>
-        </is>
-      </c>
-      <c r="D10" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E10" s="926">
-        <f t="array" ref="E10">IF(C10="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C10,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F10" s="928">
-        <f t="array" ref="F10">IF(C10="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C10,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G10" s="929">
-        <f>IF(C10="","",CEILING(SUMIF(TaskTable[故事名称],C10,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H10" s="1058" t="inlineStr"/>
-      <c r="I10" s="930">
+      <c r="A10" s="926" t="n"/>
+      <c r="B10" s="1043" t="n"/>
+      <c r="C10" s="1043" t="n"/>
+      <c r="D10" s="1044" t="n"/>
+      <c r="E10" s="926" t="n"/>
+      <c r="F10" s="926" t="n"/>
+      <c r="G10" s="930" t="n"/>
+      <c r="H10" s="1043" t="n"/>
+      <c r="I10" s="929">
         <f>IF(H10="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H10,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" s="1025">
-      <c r="A11" s="926">
-        <f>IF(B11="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B11,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B11" s="1058" t="inlineStr">
-        <is>
-          <t>库存预占与释放</t>
-        </is>
-      </c>
-      <c r="C11" s="1058" t="inlineStr">
-        <is>
-          <t>预占和释放 ERP 库存</t>
-        </is>
-      </c>
-      <c r="D11" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E11" s="926">
-        <f t="array" ref="E11">IF(C11="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C11,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F11" s="928">
-        <f t="array" ref="F11">IF(C11="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C11,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G11" s="929">
-        <f>IF(C11="","",CEILING(SUMIF(TaskTable[故事名称],C11,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H11" s="1058" t="inlineStr">
-        <is>
-          <t>ERP SIT 环境按工作日窗口开放</t>
-        </is>
-      </c>
-      <c r="I11" s="930">
+      <c r="A11" s="926" t="n"/>
+      <c r="B11" s="1043" t="n"/>
+      <c r="C11" s="1043" t="n"/>
+      <c r="D11" s="1044" t="n"/>
+      <c r="E11" s="926" t="n"/>
+      <c r="F11" s="926" t="n"/>
+      <c r="G11" s="930" t="n"/>
+      <c r="H11" s="1043" t="n"/>
+      <c r="I11" s="929">
         <f>IF(H11="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H11,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" s="1025">
-      <c r="A12" s="926">
-        <f>IF(B12="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B12,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B12" s="1058" t="inlineStr">
-        <is>
-          <t>退货退款闭环</t>
-        </is>
-      </c>
-      <c r="C12" s="1058" t="inlineStr">
-        <is>
-          <t>提交并审核退货申请</t>
-        </is>
-      </c>
-      <c r="D12" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E12" s="926">
-        <f t="array" ref="E12">IF(C12="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C12,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F12" s="928">
-        <f t="array" ref="F12">IF(C12="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C12,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G12" s="929">
-        <f>IF(C12="","",CEILING(SUMIF(TaskTable[故事名称],C12,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H12" s="1058" t="inlineStr"/>
-      <c r="I12" s="930">
+      <c r="A12" s="926" t="n"/>
+      <c r="B12" s="1043" t="n"/>
+      <c r="C12" s="1043" t="n"/>
+      <c r="D12" s="1044" t="n"/>
+      <c r="E12" s="926" t="n"/>
+      <c r="F12" s="926" t="n"/>
+      <c r="G12" s="930" t="n"/>
+      <c r="H12" s="1043" t="n"/>
+      <c r="I12" s="929">
         <f>IF(H12="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H12,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" s="1025">
-      <c r="A13" s="926">
-        <f>IF(B13="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B13,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B13" s="1058" t="inlineStr">
-        <is>
-          <t>退货退款闭环</t>
-        </is>
-      </c>
-      <c r="C13" s="1058" t="inlineStr">
-        <is>
-          <t>发起退款并回写结果</t>
-        </is>
-      </c>
-      <c r="D13" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E13" s="926">
-        <f t="array" ref="E13">IF(C13="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C13,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F13" s="928">
-        <f t="array" ref="F13">IF(C13="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C13,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G13" s="929">
-        <f>IF(C13="","",CEILING(SUMIF(TaskTable[故事名称],C13,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H13" s="1058" t="inlineStr">
-        <is>
-          <t>支付网关退款认证可能延迟</t>
-        </is>
-      </c>
-      <c r="I13" s="930">
+      <c r="A13" s="926" t="n"/>
+      <c r="B13" s="1043" t="n"/>
+      <c r="C13" s="1043" t="n"/>
+      <c r="D13" s="1044" t="n"/>
+      <c r="E13" s="926" t="n"/>
+      <c r="F13" s="926" t="n"/>
+      <c r="G13" s="930" t="n"/>
+      <c r="H13" s="1043" t="n"/>
+      <c r="I13" s="929">
         <f>IF(H13="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H13,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" s="1025">
-      <c r="A14" s="926">
-        <f>IF(B14="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B14,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B14" s="1058" t="inlineStr">
-        <is>
-          <t>门店接单工作台</t>
-        </is>
-      </c>
-      <c r="C14" s="1058" t="inlineStr">
-        <is>
-          <t>门店处理订单与交接</t>
-        </is>
-      </c>
-      <c r="D14" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E14" s="926">
-        <f t="array" ref="E14">IF(C14="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C14,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F14" s="928">
-        <f t="array" ref="F14">IF(C14="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C14,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G14" s="929">
-        <f>IF(C14="","",CEILING(SUMIF(TaskTable[故事名称],C14,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H14" s="1058" t="inlineStr"/>
-      <c r="I14" s="930">
+      <c r="A14" s="926" t="n"/>
+      <c r="B14" s="1043" t="n"/>
+      <c r="C14" s="1043" t="n"/>
+      <c r="D14" s="1044" t="n"/>
+      <c r="E14" s="926" t="n"/>
+      <c r="F14" s="926" t="n"/>
+      <c r="G14" s="930" t="n"/>
+      <c r="H14" s="1043" t="n"/>
+      <c r="I14" s="929">
         <f>IF(H14="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H14,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" s="1025">
-      <c r="A15" s="926">
-        <f>IF(B15="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B15,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B15" s="1058" t="inlineStr">
-        <is>
-          <t>订单状态与履约轨迹</t>
-        </is>
-      </c>
-      <c r="C15" s="1058" t="inlineStr">
-        <is>
-          <t>查看统一履约轨迹</t>
-        </is>
-      </c>
-      <c r="D15" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E15" s="926">
-        <f t="array" ref="E15">IF(C15="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C15,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F15" s="928">
-        <f t="array" ref="F15">IF(C15="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C15,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G15" s="929">
-        <f>IF(C15="","",CEILING(SUMIF(TaskTable[故事名称],C15,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H15" s="1058" t="inlineStr"/>
-      <c r="I15" s="930">
+      <c r="A15" s="926" t="n"/>
+      <c r="B15" s="1043" t="n"/>
+      <c r="C15" s="1043" t="n"/>
+      <c r="D15" s="1044" t="n"/>
+      <c r="E15" s="926" t="n"/>
+      <c r="F15" s="926" t="n"/>
+      <c r="G15" s="930" t="n"/>
+      <c r="H15" s="1043" t="n"/>
+      <c r="I15" s="929">
         <f>IF(H15="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H15,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" s="1025">
-      <c r="A16" s="926">
-        <f>IF(B16="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B16,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B16" s="1058" t="inlineStr">
-        <is>
-          <t>支付退款日结对账</t>
-        </is>
-      </c>
-      <c r="C16" s="1058" t="inlineStr">
-        <is>
-          <t>执行支付退款日结对账</t>
-        </is>
-      </c>
-      <c r="D16" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E16" s="926">
-        <f t="array" ref="E16">IF(C16="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C16,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F16" s="928">
-        <f t="array" ref="F16">IF(C16="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C16,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G16" s="929">
-        <f>IF(C16="","",CEILING(SUMIF(TaskTable[故事名称],C16,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H16" s="1058" t="inlineStr"/>
-      <c r="I16" s="930">
+      <c r="A16" s="926" t="n"/>
+      <c r="B16" s="1043" t="n"/>
+      <c r="C16" s="1043" t="n"/>
+      <c r="D16" s="1044" t="n"/>
+      <c r="E16" s="926" t="n"/>
+      <c r="F16" s="926" t="n"/>
+      <c r="G16" s="930" t="n"/>
+      <c r="H16" s="1043" t="n"/>
+      <c r="I16" s="929">
         <f>IF(H16="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H16,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="49" customHeight="1" s="1025">
-      <c r="A17" s="926">
-        <f>IF(B17="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B17,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B17" s="1058" t="inlineStr">
-        <is>
-          <t>电子发票申请与状态</t>
-        </is>
-      </c>
-      <c r="C17" s="1058" t="inlineStr">
-        <is>
-          <t>申请并追踪电子发票</t>
-        </is>
-      </c>
-      <c r="D17" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E17" s="926">
-        <f t="array" ref="E17">IF(C17="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C17,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F17" s="928">
-        <f t="array" ref="F17">IF(C17="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C17,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G17" s="929">
-        <f>IF(C17="","",CEILING(SUMIF(TaskTable[故事名称],C17,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H17" s="1058" t="inlineStr">
-        <is>
-          <t>电子发票生产证书与测试配额待确认</t>
-        </is>
-      </c>
-      <c r="I17" s="930">
+    <row r="17" ht="42" customHeight="1" s="1025">
+      <c r="A17" s="926" t="n"/>
+      <c r="B17" s="1043" t="n"/>
+      <c r="C17" s="1043" t="n"/>
+      <c r="D17" s="1044" t="n"/>
+      <c r="E17" s="926" t="n"/>
+      <c r="F17" s="926" t="n"/>
+      <c r="G17" s="930" t="n"/>
+      <c r="H17" s="1043" t="n"/>
+      <c r="I17" s="929">
         <f>IF(H17="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H17,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" s="1025">
-      <c r="A18" s="926">
-        <f>IF(B18="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B18,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B18" s="1058" t="inlineStr">
-        <is>
-          <t>财务经营报表</t>
-        </is>
-      </c>
-      <c r="C18" s="1058" t="inlineStr">
-        <is>
-          <t>查看财务经营日报</t>
-        </is>
-      </c>
-      <c r="D18" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E18" s="926">
-        <f t="array" ref="E18">IF(C18="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C18,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F18" s="928">
-        <f t="array" ref="F18">IF(C18="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C18,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G18" s="929">
-        <f>IF(C18="","",CEILING(SUMIF(TaskTable[故事名称],C18,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H18" s="1058" t="inlineStr"/>
-      <c r="I18" s="930">
+      <c r="A18" s="926" t="n"/>
+      <c r="B18" s="1043" t="n"/>
+      <c r="C18" s="1043" t="n"/>
+      <c r="D18" s="1044" t="n"/>
+      <c r="E18" s="926" t="n"/>
+      <c r="F18" s="926" t="n"/>
+      <c r="G18" s="930" t="n"/>
+      <c r="H18" s="1043" t="n"/>
+      <c r="I18" s="929">
         <f>IF(H18="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H18,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="49" customHeight="1" s="1025">
-      <c r="A19" s="926">
-        <f>IF(B19="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B19,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B19" s="1058" t="inlineStr">
-        <is>
-          <t>生产准备、切换与验证</t>
-        </is>
-      </c>
-      <c r="C19" s="1058" t="inlineStr">
-        <is>
-          <t>准备生产环境和发布流水线</t>
-        </is>
-      </c>
-      <c r="D19" s="1059" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E19" s="926">
-        <f t="array" ref="E19">IF(C19="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C19,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F19" s="928">
-        <f t="array" ref="F19">IF(C19="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C19,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G19" s="929">
-        <f>IF(C19="","",CEILING(SUMIF(TaskTable[故事名称],C19,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H19" s="1058" t="inlineStr"/>
-      <c r="I19" s="930">
+    <row r="19" ht="42" customHeight="1" s="1025">
+      <c r="A19" s="926" t="n"/>
+      <c r="B19" s="1043" t="n"/>
+      <c r="C19" s="1043" t="n"/>
+      <c r="D19" s="1044" t="n"/>
+      <c r="E19" s="926" t="n"/>
+      <c r="F19" s="926" t="n"/>
+      <c r="G19" s="930" t="n"/>
+      <c r="H19" s="1043" t="n"/>
+      <c r="I19" s="929">
         <f>IF(H19="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H19,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1" s="1025">
-      <c r="A20" s="926">
-        <f>IF(B20="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B20,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B20" s="1058" t="inlineStr">
-        <is>
-          <t>生产准备、切换与验证</t>
-        </is>
-      </c>
-      <c r="C20" s="1058" t="inlineStr">
-        <is>
-          <t>执行生产切换与回滚演练</t>
-        </is>
-      </c>
-      <c r="D20" s="1059" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E20" s="926">
-        <f t="array" ref="E20">IF(C20="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C20,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F20" s="928">
-        <f t="array" ref="F20">IF(C20="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C20,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G20" s="929">
-        <f>IF(C20="","",CEILING(SUMIF(TaskTable[故事名称],C20,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H20" s="1058" t="inlineStr">
-        <is>
-          <t>迁移冻结窗口为周六 00:00 至 04:00</t>
-        </is>
-      </c>
-      <c r="I20" s="930">
+      <c r="A20" s="926" t="n"/>
+      <c r="B20" s="1043" t="n"/>
+      <c r="C20" s="1043" t="n"/>
+      <c r="D20" s="1044" t="n"/>
+      <c r="E20" s="926" t="n"/>
+      <c r="F20" s="926" t="n"/>
+      <c r="G20" s="930" t="n"/>
+      <c r="H20" s="1043" t="n"/>
+      <c r="I20" s="929">
         <f>IF(H20="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H20,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="49" customHeight="1" s="1025">
-      <c r="A21" s="926">
-        <f>IF(B21="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B21,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B21" s="1058" t="inlineStr">
-        <is>
-          <t>生产准备、切换与验证</t>
-        </is>
-      </c>
-      <c r="C21" s="1058" t="inlineStr">
-        <is>
-          <t>完成生产烟测与业务确认</t>
-        </is>
-      </c>
-      <c r="D21" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E21" s="926">
-        <f t="array" ref="E21">IF(C21="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C21,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F21" s="928">
-        <f t="array" ref="F21">IF(C21="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C21,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G21" s="929">
-        <f>IF(C21="","",CEILING(SUMIF(TaskTable[故事名称],C21,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H21" s="1058" t="inlineStr">
-        <is>
-          <t>生产告警通知渠道待确认</t>
-        </is>
-      </c>
-      <c r="I21" s="930">
+    <row r="21" ht="42" customHeight="1" s="1025">
+      <c r="A21" s="926" t="n"/>
+      <c r="B21" s="1043" t="n"/>
+      <c r="C21" s="1043" t="n"/>
+      <c r="D21" s="1044" t="n"/>
+      <c r="E21" s="926" t="n"/>
+      <c r="F21" s="926" t="n"/>
+      <c r="G21" s="930" t="n"/>
+      <c r="H21" s="1043" t="n"/>
+      <c r="I21" s="929">
         <f>IF(H21="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H21,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="49" customHeight="1" s="1025">
-      <c r="A22" s="926">
-        <f>IF(B22="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B22,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B22" s="1058" t="inlineStr">
-        <is>
-          <t>会员与订单数据迁移</t>
-        </is>
-      </c>
-      <c r="C22" s="1058" t="inlineStr">
-        <is>
-          <t>迁移会员与历史订单数据</t>
-        </is>
-      </c>
-      <c r="D22" s="1059" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E22" s="926">
-        <f t="array" ref="E22">IF(C22="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C22,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F22" s="928">
-        <f t="array" ref="F22">IF(C22="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C22,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G22" s="929">
-        <f>IF(C22="","",CEILING(SUMIF(TaskTable[故事名称],C22,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H22" s="1058" t="inlineStr">
-        <is>
-          <t>迁移冻结窗口为周六 00:00 至 04:00</t>
-        </is>
-      </c>
-      <c r="I22" s="930">
+    <row r="22" ht="42" customHeight="1" s="1025">
+      <c r="A22" s="926" t="n"/>
+      <c r="B22" s="1043" t="n"/>
+      <c r="C22" s="1043" t="n"/>
+      <c r="D22" s="1044" t="n"/>
+      <c r="E22" s="926" t="n"/>
+      <c r="F22" s="926" t="n"/>
+      <c r="G22" s="930" t="n"/>
+      <c r="H22" s="1043" t="n"/>
+      <c r="I22" s="929">
         <f>IF(H22="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H22,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1" s="1025">
-      <c r="A23" s="926">
-        <f>IF(B23="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B23,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B23" s="1058" t="inlineStr">
-        <is>
-          <t>监控、运维交接与用户赋能</t>
-        </is>
-      </c>
-      <c r="C23" s="1058" t="inlineStr">
-        <is>
-          <t>监控核心交易与财务作业</t>
-        </is>
-      </c>
-      <c r="D23" s="1059" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E23" s="926">
-        <f t="array" ref="E23">IF(C23="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C23,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F23" s="928">
-        <f t="array" ref="F23">IF(C23="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C23,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G23" s="929">
-        <f>IF(C23="","",CEILING(SUMIF(TaskTable[故事名称],C23,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H23" s="1058" t="inlineStr">
-        <is>
-          <t>生产告警通知渠道待确认</t>
-        </is>
-      </c>
-      <c r="I23" s="930">
+      <c r="A23" s="926" t="n"/>
+      <c r="B23" s="1043" t="n"/>
+      <c r="C23" s="1043" t="n"/>
+      <c r="D23" s="1044" t="n"/>
+      <c r="E23" s="926" t="n"/>
+      <c r="F23" s="926" t="n"/>
+      <c r="G23" s="930" t="n"/>
+      <c r="H23" s="1043" t="n"/>
+      <c r="I23" s="929">
         <f>IF(H23="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H23,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1" s="1025">
-      <c r="A24" s="926">
-        <f>IF(B24="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B24,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B24" s="1058" t="inlineStr">
-        <is>
-          <t>监控、运维交接与用户赋能</t>
-        </is>
-      </c>
-      <c r="C24" s="1058" t="inlineStr">
-        <is>
-          <t>完成运维交接与演练</t>
-        </is>
-      </c>
-      <c r="D24" s="1059" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E24" s="926">
-        <f t="array" ref="E24">IF(C24="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C24,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F24" s="928">
-        <f t="array" ref="F24">IF(C24="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C24,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G24" s="929">
-        <f>IF(C24="","",CEILING(SUMIF(TaskTable[故事名称],C24,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H24" s="1058" t="inlineStr"/>
-      <c r="I24" s="930">
+      <c r="A24" s="926" t="n"/>
+      <c r="B24" s="1043" t="n"/>
+      <c r="C24" s="1043" t="n"/>
+      <c r="D24" s="1044" t="n"/>
+      <c r="E24" s="926" t="n"/>
+      <c r="F24" s="926" t="n"/>
+      <c r="G24" s="930" t="n"/>
+      <c r="H24" s="1043" t="n"/>
+      <c r="I24" s="929">
         <f>IF(H24="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H24,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1" s="1025">
-      <c r="A25" s="926">
-        <f>IF(B25="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B25,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B25" s="1058" t="inlineStr">
-        <is>
-          <t>监控、运维交接与用户赋能</t>
-        </is>
-      </c>
-      <c r="C25" s="1058" t="inlineStr">
-        <is>
-          <t>培训门店、客服和财务用户</t>
-        </is>
-      </c>
-      <c r="D25" s="1059" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E25" s="926">
-        <f t="array" ref="E25">IF(C25="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C25,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F25" s="928">
-        <f t="array" ref="F25">IF(C25="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C25,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G25" s="929">
-        <f>IF(C25="","",CEILING(SUMIF(TaskTable[故事名称],C25,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H25" s="1058" t="inlineStr"/>
-      <c r="I25" s="930">
+      <c r="A25" s="926" t="n"/>
+      <c r="B25" s="1043" t="n"/>
+      <c r="C25" s="1043" t="n"/>
+      <c r="D25" s="1044" t="n"/>
+      <c r="E25" s="926" t="n"/>
+      <c r="F25" s="926" t="n"/>
+      <c r="G25" s="930" t="n"/>
+      <c r="H25" s="1043" t="n"/>
+      <c r="I25" s="929">
         <f>IF(H25="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H25,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1" s="1025">
-      <c r="A26" s="926">
-        <f>IF(B26="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B26,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B26" s="1058" t="inlineStr">
-        <is>
-          <t>自动化、性能与生产质量验证</t>
-        </is>
-      </c>
-      <c r="C26" s="1058" t="inlineStr">
-        <is>
-          <t>扩展自动化与性能验证</t>
-        </is>
-      </c>
-      <c r="D26" s="1059" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E26" s="926">
-        <f t="array" ref="E26">IF(C26="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C26,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F26" s="928">
-        <f t="array" ref="F26">IF(C26="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C26,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G26" s="929">
-        <f>IF(C26="","",CEILING(SUMIF(TaskTable[故事名称],C26,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H26" s="1058" t="inlineStr"/>
-      <c r="I26" s="930">
+      <c r="A26" s="926" t="n"/>
+      <c r="B26" s="1043" t="n"/>
+      <c r="C26" s="1043" t="n"/>
+      <c r="D26" s="1044" t="n"/>
+      <c r="E26" s="926" t="n"/>
+      <c r="F26" s="926" t="n"/>
+      <c r="G26" s="930" t="n"/>
+      <c r="H26" s="1043" t="n"/>
+      <c r="I26" s="929">
         <f>IF(H26="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H26,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1" s="1025">
-      <c r="A27" s="926">
-        <f>IF(B27="","",IFERROR(INDEX(FeatureTable[需求名称],MATCH(B27,FeatureTable[子需求名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B27" s="1058" t="inlineStr">
-        <is>
-          <t>自动化、性能与生产质量验证</t>
-        </is>
-      </c>
-      <c r="C27" s="1058" t="inlineStr">
-        <is>
-          <t>执行兼容性与工程回归</t>
-        </is>
-      </c>
-      <c r="D27" s="1059" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E27" s="926">
-        <f t="array" ref="E27">IF(C27="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AcceptanceCriterionTable[故事名称]=C27,"• "&amp;AcceptanceCriterionTable[验收条件名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="F27" s="928">
-        <f t="array" ref="F27">IF(C27="","",IFERROR(_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(TaskTable[故事名称]=C27,"• "&amp;TaskTable[任务名称],"")),""))</f>
-        <v/>
-      </c>
-      <c r="G27" s="929">
-        <f>IF(C27="","",CEILING(SUMIF(TaskTable[故事名称],C27,TaskTable[人天小计]),INDEX(ProjectParameterTable[值],MATCH("ROUND_STORY",ProjectParameterTable[参数代码],0))))</f>
-        <v/>
-      </c>
-      <c r="H27" s="1058" t="inlineStr"/>
-      <c r="I27" s="930">
+      <c r="A27" s="926" t="n"/>
+      <c r="B27" s="1043" t="n"/>
+      <c r="C27" s="1043" t="n"/>
+      <c r="D27" s="1044" t="n"/>
+      <c r="E27" s="926" t="n"/>
+      <c r="F27" s="926" t="n"/>
+      <c r="G27" s="930" t="n"/>
+      <c r="H27" s="1043" t="n"/>
+      <c r="I27" s="929">
         <f>IF(H27="","",IFERROR(INDEX(AssumptionRiskTable[状态],MATCH(H27,AssumptionRiskTable[假设/风险名称],0)),"名称未匹配"))</f>
         <v/>
       </c>
@@ -13784,615 +12346,45 @@
       </c>
       <c r="C5" s="1058" t="inlineStr">
         <is>
-          <t>创建并查看客户档案</t>
+          <t>完成退款自动审核与状态通知</t>
         </is>
       </c>
       <c r="D5" s="1058" t="inlineStr">
         <is>
-          <t>用户保存档案后可以查看授权范围内的最新字段。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" s="1025">
-      <c r="A6" s="926">
-        <f>IF(C6="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C6,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B6" s="926">
-        <f>IF(C6="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C6,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C6" s="1058" t="inlineStr">
-        <is>
-          <t>创建并查看客户档案</t>
-        </is>
-      </c>
-      <c r="D6" s="1058" t="inlineStr">
-        <is>
-          <t>档案变更记录包含操作者、时间和变更字段。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1" s="1025">
-      <c r="A7" s="926">
-        <f>IF(C7="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C7,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B7" s="926">
-        <f>IF(C7="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C7,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C7" s="1058" t="inlineStr">
-        <is>
-          <t>提供客户档案操作</t>
-        </is>
-      </c>
-      <c r="D7" s="1058" t="inlineStr">
-        <is>
-          <t>渠道可以通过已发布 API 创建、维护和检索客户档案。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1" s="1025">
-      <c r="A8" s="926">
-        <f>IF(C8="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C8,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B8" s="926">
-        <f>IF(C8="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C8,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C8" s="1058" t="inlineStr">
-        <is>
-          <t>提供客户档案操作</t>
-        </is>
-      </c>
-      <c r="D8" s="1058" t="inlineStr">
-        <is>
-          <t>未授权角色无法读取敏感字段且访问留痕。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1" s="1025">
-      <c r="A9" s="926">
-        <f>IF(C9="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C9,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B9" s="926">
-        <f>IF(C9="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C9,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C9" s="1058" t="inlineStr">
-        <is>
-          <t>集成会员主数据查询</t>
-        </is>
-      </c>
-      <c r="D9" s="1058" t="inlineStr">
-        <is>
-          <t>星云会员门户可以通过内部接口检索统一会员号和档案。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1" s="1025">
-      <c r="A10" s="926">
-        <f>IF(C10="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C10,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B10" s="926">
-        <f>IF(C10="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C10,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C10" s="1058" t="inlineStr">
-        <is>
-          <t>计算并追溯会员等级</t>
-        </is>
-      </c>
-      <c r="D10" s="1058" t="inlineStr">
-        <is>
-          <t>会员等级按生效规则计算且可以追溯规则版本。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1" s="1025">
-      <c r="A11" s="926">
-        <f>IF(C11="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C11,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B11" s="926">
-        <f>IF(C11="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C11,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C11" s="1058" t="inlineStr">
-        <is>
-          <t>计算并追溯会员等级</t>
-        </is>
-      </c>
-      <c r="D11" s="1058" t="inlineStr">
-        <is>
-          <t>等级调整后保留原等级、生效时间和调整原因。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1" s="1025">
-      <c r="A12" s="926">
-        <f>IF(C12="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C12,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B12" s="926">
-        <f>IF(C12="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C12,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C12" s="1058" t="inlineStr">
-        <is>
-          <t>统一创建全渠道订单</t>
-        </is>
-      </c>
-      <c r="D12" s="1058" t="inlineStr">
-        <is>
-          <t>门店和线上渠道通过相同校验规则创建订单。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1" s="1025">
-      <c r="A13" s="926">
-        <f>IF(C13="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C13,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B13" s="926">
-        <f>IF(C13="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C13,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C13" s="1058" t="inlineStr">
-        <is>
-          <t>统一创建全渠道订单</t>
-        </is>
-      </c>
-      <c r="D13" s="1058" t="inlineStr">
-        <is>
-          <t>相同幂等键的重复请求不产生重复订单。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1" s="1025">
-      <c r="A14" s="926">
-        <f>IF(C14="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C14,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B14" s="926">
-        <f>IF(C14="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C14,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C14" s="1058" t="inlineStr">
-        <is>
-          <t>驱动订单状态与事件</t>
-        </is>
-      </c>
-      <c r="D14" s="1058" t="inlineStr">
-        <is>
-          <t>合法命令驱动状态变化并记录来源、时间和事件编号。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1" s="1025">
-      <c r="A15" s="926">
-        <f>IF(C15="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C15,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B15" s="926">
-        <f>IF(C15="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C15,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C15" s="1058" t="inlineStr">
-        <is>
-          <t>预占和释放 ERP 库存</t>
-        </is>
-      </c>
-      <c r="D15" s="1058" t="inlineStr">
-        <is>
-          <t>订单确认和取消分别完成库存预占与释放。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1" s="1025">
-      <c r="A16" s="926">
-        <f>IF(C16="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C16,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B16" s="926">
-        <f>IF(C16="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C16,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C16" s="1058" t="inlineStr">
-        <is>
-          <t>预占和释放 ERP 库存</t>
-        </is>
-      </c>
-      <c r="D16" s="1058" t="inlineStr">
-        <is>
-          <t>ERP 超时重试不会产生重复预占。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1" s="1025">
-      <c r="A17" s="926">
-        <f>IF(C17="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C17,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B17" s="926">
-        <f>IF(C17="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C17,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C17" s="1058" t="inlineStr">
-        <is>
-          <t>提交并审核退货申请</t>
-        </is>
-      </c>
-      <c r="D17" s="1058" t="inlineStr">
-        <is>
-          <t>系统拒绝超过可退数量的申请并记录审核结果。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="34" customHeight="1" s="1025">
-      <c r="A18" s="926">
-        <f>IF(C18="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C18,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B18" s="926">
-        <f>IF(C18="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C18,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C18" s="1058" t="inlineStr">
-        <is>
-          <t>发起退款并回写结果</t>
-        </is>
-      </c>
-      <c r="D18" s="1058" t="inlineStr">
-        <is>
-          <t>退款结果回写订单且同一退货单不重复退款。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="34" customHeight="1" s="1025">
-      <c r="A19" s="926">
-        <f>IF(C19="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C19,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B19" s="926">
-        <f>IF(C19="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C19,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C19" s="1058" t="inlineStr">
-        <is>
-          <t>门店处理订单与交接</t>
-        </is>
-      </c>
-      <c r="D19" s="1058" t="inlineStr">
-        <is>
-          <t>授权门店可以处理本店订单并完成交接记录。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="34" customHeight="1" s="1025">
-      <c r="A20" s="926">
-        <f>IF(C20="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C20,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B20" s="926">
-        <f>IF(C20="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C20,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C20" s="1058" t="inlineStr">
-        <is>
-          <t>查看统一履约轨迹</t>
-        </is>
-      </c>
-      <c r="D20" s="1058" t="inlineStr">
-        <is>
-          <t>顾客和客服看到一致的履约节点与异常原因。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="34" customHeight="1" s="1025">
-      <c r="A21" s="926">
-        <f>IF(C21="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C21,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B21" s="926">
-        <f>IF(C21="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C21,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C21" s="1058" t="inlineStr">
-        <is>
-          <t>执行支付退款日结对账</t>
-        </is>
-      </c>
-      <c r="D21" s="1058" t="inlineStr">
-        <is>
-          <t>前一自然日交易在 07:00 前完成对账并标识差异。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="34" customHeight="1" s="1025">
-      <c r="A22" s="926">
-        <f>IF(C22="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C22,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B22" s="926">
-        <f>IF(C22="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C22,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C22" s="1058" t="inlineStr">
-        <is>
-          <t>执行支付退款日结对账</t>
-        </is>
-      </c>
-      <c r="D22" s="1058" t="inlineStr">
-        <is>
-          <t>每个差异项可以追溯到订单、支付交易和退款记录。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1" s="1025">
-      <c r="A23" s="926">
-        <f>IF(C23="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C23,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B23" s="926">
-        <f>IF(C23="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C23,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C23" s="1058" t="inlineStr">
-        <is>
-          <t>申请并追踪电子发票</t>
-        </is>
-      </c>
-      <c r="D23" s="1058" t="inlineStr">
-        <is>
-          <t>开票成功后保存发票号码和下载地址，失败时保存失败码。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="34" customHeight="1" s="1025">
-      <c r="A24" s="926">
-        <f>IF(C24="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C24,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B24" s="926">
-        <f>IF(C24="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C24,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C24" s="1058" t="inlineStr">
-        <is>
-          <t>申请并追踪电子发票</t>
-        </is>
-      </c>
-      <c r="D24" s="1058" t="inlineStr">
-        <is>
-          <t>重复提交相同开票申请不会重复开票。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="34" customHeight="1" s="1025">
-      <c r="A25" s="926">
-        <f>IF(C25="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C25,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B25" s="926">
-        <f>IF(C25="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C25,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C25" s="1058" t="inlineStr">
-        <is>
-          <t>查看财务经营日报</t>
-        </is>
-      </c>
-      <c r="D25" s="1058" t="inlineStr">
-        <is>
-          <t>财务可按日期、区域和渠道查看已定义经营指标。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1" s="1025">
-      <c r="A26" s="926">
-        <f>IF(C26="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C26,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B26" s="926">
-        <f>IF(C26="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C26,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C26" s="1058" t="inlineStr">
-        <is>
-          <t>查看财务经营日报</t>
-        </is>
-      </c>
-      <c r="D26" s="1058" t="inlineStr">
-        <is>
-          <t>报表金额可下钻到构成订单和对账状态。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1" s="1025">
-      <c r="A27" s="926">
-        <f>IF(C27="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C27,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B27" s="926">
-        <f>IF(C27="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C27,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C27" s="1058" t="inlineStr">
-        <is>
-          <t>准备生产环境和发布流水线</t>
-        </is>
-      </c>
-      <c r="D27" s="1058" t="inlineStr">
-        <is>
-          <t>生产参数、权限、制品和功能开关通过准备检查。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="34" customHeight="1" s="1025">
-      <c r="A28" s="926">
-        <f>IF(C28="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C28,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B28" s="926">
-        <f>IF(C28="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C28,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C28" s="1058" t="inlineStr">
-        <is>
-          <t>执行生产切换与回滚演练</t>
-        </is>
-      </c>
-      <c r="D28" s="1058" t="inlineStr">
-        <is>
-          <t>切换清单在批准窗口内完成且回滚演练有记录。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="34" customHeight="1" s="1025">
-      <c r="A29" s="926">
-        <f>IF(C29="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C29,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B29" s="926">
-        <f>IF(C29="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C29,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C29" s="1058" t="inlineStr">
-        <is>
-          <t>完成生产烟测与业务确认</t>
-        </is>
-      </c>
-      <c r="D29" s="1058" t="inlineStr">
-        <is>
-          <t>五条关键业务链路烟测通过并由业务负责人确认。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1" s="1025">
-      <c r="A30" s="926">
-        <f>IF(C30="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C30,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B30" s="926">
-        <f>IF(C30="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C30,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C30" s="1058" t="inlineStr">
-        <is>
-          <t>迁移会员与历史订单数据</t>
-        </is>
-      </c>
-      <c r="D30" s="1058" t="inlineStr">
-        <is>
-          <t>关键字段迁移前后一致率为 100%，重复业务主键为 0。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="34" customHeight="1" s="1025">
-      <c r="A31" s="926">
-        <f>IF(C31="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C31,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B31" s="926">
-        <f>IF(C31="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C31,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C31" s="1058" t="inlineStr">
-        <is>
-          <t>监控核心交易与财务作业</t>
-        </is>
-      </c>
-      <c r="D31" s="1058" t="inlineStr">
-        <is>
-          <t>核心交易和财务作业指标均配置阈值、渠道与接收人。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="34" customHeight="1" s="1025">
-      <c r="A32" s="926">
-        <f>IF(C32="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C32,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B32" s="926">
-        <f>IF(C32="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C32,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C32" s="1058" t="inlineStr">
-        <is>
-          <t>完成运维交接与演练</t>
-        </is>
-      </c>
-      <c r="D32" s="1058" t="inlineStr">
-        <is>
-          <t>运维手册、联系人和故障演练由运维经理签收。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="34" customHeight="1" s="1025">
-      <c r="A33" s="926">
-        <f>IF(C33="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C33,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B33" s="926">
-        <f>IF(C33="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C33,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C33" s="1058" t="inlineStr">
-        <is>
-          <t>培训门店、客服和财务用户</t>
-        </is>
-      </c>
-      <c r="D33" s="1058" t="inlineStr">
-        <is>
-          <t>门店、客服和财务培训完成并保留材料、签到和反馈。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="34" customHeight="1" s="1025">
-      <c r="A34" s="926">
-        <f>IF(C34="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C34,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B34" s="926">
-        <f>IF(C34="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C34,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C34" s="1058" t="inlineStr">
-        <is>
-          <t>扩展自动化与性能验证</t>
-        </is>
-      </c>
-      <c r="D34" s="1058" t="inlineStr">
-        <is>
-          <t>P0/P1 自动化用例全部通过且核心查询达到 500 TPS。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="34" customHeight="1" s="1025">
-      <c r="A35" s="926">
-        <f>IF(C35="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C35,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B35" s="926">
-        <f>IF(C35="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C35,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C35" s="1058" t="inlineStr">
-        <is>
-          <t>执行兼容性与工程回归</t>
-        </is>
-      </c>
-      <c r="D35" s="1058" t="inlineStr">
-        <is>
-          <t>支持的浏览器和设备矩阵通过工程回归且无阻断缺陷。</t>
-        </is>
-      </c>
-    </row>
+          <t>通过审核的退款获得支付结果和用户通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" s="1025"/>
+    <row r="7" s="1025"/>
+    <row r="8" s="1025"/>
+    <row r="9" s="1025"/>
+    <row r="10" s="1025"/>
+    <row r="11" s="1025"/>
+    <row r="12" s="1025"/>
+    <row r="13" s="1025"/>
+    <row r="14" s="1025"/>
+    <row r="15" s="1025"/>
+    <row r="16" s="1025"/>
+    <row r="17" s="1025"/>
+    <row r="18" s="1025"/>
+    <row r="19" s="1025"/>
+    <row r="20" s="1025"/>
+    <row r="21" s="1025"/>
+    <row r="22" s="1025"/>
+    <row r="23" s="1025"/>
+    <row r="24" s="1025"/>
+    <row r="25" s="1025"/>
+    <row r="26" s="1025"/>
+    <row r="27" s="1025"/>
+    <row r="28" s="1025"/>
+    <row r="29" s="1025"/>
+    <row r="30" s="1025"/>
+    <row r="31" s="1025"/>
+    <row r="32" s="1025"/>
+    <row r="33" s="1025"/>
+    <row r="34" s="1025"/>
+    <row r="35" s="1025"/>
     <row r="36" s="1025"/>
     <row r="37" s="1025"/>
     <row r="38" s="1025"/>
@@ -14646,7 +12638,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="49" customHeight="1" s="1025">
+    <row r="5" ht="38" customHeight="1" s="1025">
       <c r="A5" s="944">
         <f>IF(C5="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C5,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -14657,17 +12649,17 @@
       </c>
       <c r="C5" s="1060" t="inlineStr">
         <is>
-          <t>创建并查看客户档案</t>
+          <t>完成退款自动审核与状态通知</t>
         </is>
       </c>
       <c r="D5" s="1060" t="inlineStr">
         <is>
-          <t>调整客户档案页面和状态</t>
+          <t>设计退款流程恢复目标与方案</t>
         </is>
       </c>
       <c r="E5" s="1060" t="inlineStr">
         <is>
-          <t>界面与交互</t>
+          <t>架构方案设计</t>
         </is>
       </c>
       <c r="F5" s="945">
@@ -14676,32 +12668,24 @@
       </c>
       <c r="G5" s="1061" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>新建</t>
         </is>
       </c>
       <c r="H5" s="1060" t="inlineStr">
         <is>
-          <t>沿用可复用的客户档案框架及其页面入口，修改本次交付范围内的界面状态和校验。</t>
+          <t>往期 SOW 未包含退款流程恢复目标设计。</t>
         </is>
       </c>
       <c r="I5" s="1061" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="J5" s="1060" t="inlineStr">
-        <is>
-          <t>仅一个界面和单一路径，使用成熟组件，无复杂权限或跨界面状态恢复。</t>
-        </is>
-      </c>
-      <c r="K5" s="1060" t="inlineStr">
-        <is>
-          <t>可复用的客户档案框架</t>
-        </is>
-      </c>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J5" s="1060" t="inlineStr"/>
+      <c r="K5" s="1060" t="inlineStr"/>
       <c r="L5" s="1060" t="inlineStr">
         <is>
-          <t>调整一个可独立验收的客户档案界面实例。</t>
+          <t>以一项待明确恢复目标的方案设计实例计价。</t>
         </is>
       </c>
       <c r="M5" s="945">
@@ -14717,7 +12701,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="49" customHeight="1" s="1025">
+    <row r="6" ht="38" customHeight="1" s="1025">
       <c r="A6" s="944">
         <f>IF(C6="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C6,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -14728,12 +12712,12 @@
       </c>
       <c r="C6" s="1060" t="inlineStr">
         <is>
-          <t>提供客户档案操作</t>
+          <t>完成退款自动审核与状态通知</t>
         </is>
       </c>
       <c r="D6" s="1060" t="inlineStr">
         <is>
-          <t>调整客户档案业务服务与接口</t>
+          <t>调整退款编排流程</t>
         </is>
       </c>
       <c r="E6" s="1060" t="inlineStr">
@@ -14752,7 +12736,7 @@
       </c>
       <c r="H6" s="1060" t="inlineStr">
         <is>
-          <t>保留可复用的客户档案框架对应的服务边界，扩展创建和检索规则及接口。</t>
+          <t>在既有退款接口基础上调整退款编排流程。</t>
         </is>
       </c>
       <c r="I6" s="1061" t="inlineStr">
@@ -14763,12 +12747,12 @@
       <c r="J6" s="1060" t="inlineStr"/>
       <c r="K6" s="1060" t="inlineStr">
         <is>
-          <t>可复用的客户档案框架</t>
+          <t>既有退款接口</t>
         </is>
       </c>
       <c r="L6" s="1060" t="inlineStr">
         <is>
-          <t>一组围绕客户档案操作的紧密相关接口，符合单实例计数口径。</t>
+          <t>按一个既有退款业务操作调整实例计价。</t>
         </is>
       </c>
       <c r="M6" s="945">
@@ -14784,7 +12768,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="49" customHeight="1" s="1025">
+    <row r="7" ht="38" customHeight="1" s="1025">
       <c r="A7" s="944">
         <f>IF(C7="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C7,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
         <v/>
@@ -14795,17 +12779,17 @@
       </c>
       <c r="C7" s="1060" t="inlineStr">
         <is>
-          <t>集成会员主数据查询</t>
+          <t>完成退款自动审核与状态通知</t>
         </is>
       </c>
       <c r="D7" s="1060" t="inlineStr">
         <is>
-          <t>接入内部客户档案 API</t>
+          <t>接入支付平台退款接口</t>
         </is>
       </c>
       <c r="E7" s="1060" t="inlineStr">
         <is>
-          <t>内部系统对接</t>
+          <t>外部系统对接</t>
         </is>
       </c>
       <c r="F7" s="945">
@@ -14814,32 +12798,24 @@
       </c>
       <c r="G7" s="1061" t="inlineStr">
         <is>
-          <t>接入复用</t>
+          <t>新建</t>
         </is>
       </c>
       <c r="H7" s="1060" t="inlineStr">
         <is>
-          <t>可复用的客户档案框架保持不变；本项目负责并交付：认证、映射、适配。</t>
+          <t>本期首次交付支付平台退款集成。</t>
         </is>
       </c>
       <c r="I7" s="1061" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="J7" s="1060" t="inlineStr">
-        <is>
-          <t>同组织稳定接口、单向查询和简单字段映射，不涉及对端改造。</t>
-        </is>
-      </c>
-      <c r="K7" s="1060" t="inlineStr">
-        <is>
-          <t>可复用的客户档案框架</t>
-        </is>
-      </c>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J7" s="1060" t="inlineStr"/>
+      <c r="K7" s="1060" t="inlineStr"/>
       <c r="L7" s="1060" t="inlineStr">
         <is>
-          <t>实现一个已登记的内部出站集成，不包含另行开展的 SIT。</t>
+          <t>按一个外部支付平台退款对接实例计价。</t>
         </is>
       </c>
       <c r="M7" s="945">
@@ -14855,2859 +12831,49 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="38" customHeight="1" s="1025">
-      <c r="A8" s="944">
-        <f>IF(C8="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C8,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B8" s="944">
-        <f>IF(C8="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C8,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C8" s="1060" t="inlineStr">
-        <is>
-          <t>创建并查看客户档案</t>
-        </is>
-      </c>
-      <c r="D8" s="1060" t="inlineStr">
-        <is>
-          <t>调整可复用的客户档案框架字段模型</t>
-        </is>
-      </c>
-      <c r="E8" s="1060" t="inlineStr">
-        <is>
-          <t>数据模型与存储结构</t>
-        </is>
-      </c>
-      <c r="F8" s="945">
-        <f>IF(E8="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E8,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G8" s="1061" t="inlineStr">
-        <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="H8" s="1060" t="inlineStr">
-        <is>
-          <t>在可复用的客户档案框架中增加一期顺延字段、授权标识和变更审计列。</t>
-        </is>
-      </c>
-      <c r="I8" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J8" s="1060" t="inlineStr"/>
-      <c r="K8" s="1060" t="inlineStr">
-        <is>
-          <t>可复用的客户档案框架</t>
-        </is>
-      </c>
-      <c r="L8" s="1060" t="inlineStr">
-        <is>
-          <t>一个客户档案数据模型实例，覆盖字段、约束和审计列。</t>
-        </is>
-      </c>
-      <c r="M8" s="945">
-        <f>IF(OR(D8="",E8="",G8=""),"",IFERROR(IF(G8="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E8,BaseUnitCatalogTable[基础单元名称],0)),IF(G8="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E8,BaseUnitCatalogTable[基础单元名称],0)),IF(G8="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E8,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N8" s="945">
-        <f>IF(OR(D8="",I8=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I8,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O8" s="945">
-        <f>IF(OR(D8="",NOT(ISNUMBER(M8)),NOT(ISNUMBER(N8))),"",ROUND(M8*N8,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1" s="1025">
-      <c r="A9" s="944">
-        <f>IF(C9="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C9,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B9" s="944">
-        <f>IF(C9="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C9,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C9" s="1060" t="inlineStr">
-        <is>
-          <t>提供客户档案操作</t>
-        </is>
-      </c>
-      <c r="D9" s="1060" t="inlineStr">
-        <is>
-          <t>建立档案 API 身份与字段权限</t>
-        </is>
-      </c>
-      <c r="E9" s="1060" t="inlineStr">
-        <is>
-          <t>身份与权限管理</t>
-        </is>
-      </c>
-      <c r="F9" s="945">
-        <f>IF(E9="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E9,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G9" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H9" s="1060" t="inlineStr">
-        <is>
-          <t>为档案 API 新增角色、权限范围和敏感字段过滤规则。</t>
-        </is>
-      </c>
-      <c r="I9" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J9" s="1060" t="inlineStr"/>
-      <c r="K9" s="1060" t="inlineStr"/>
-      <c r="L9" s="1060" t="inlineStr">
-        <is>
-          <t>一个档案 API 权限控制实例，覆盖门店、客服和会员三类主体。</t>
-        </is>
-      </c>
-      <c r="M9" s="945">
-        <f>IF(OR(D9="",E9="",G9=""),"",IFERROR(IF(G9="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E9,BaseUnitCatalogTable[基础单元名称],0)),IF(G9="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E9,BaseUnitCatalogTable[基础单元名称],0)),IF(G9="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E9,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N9" s="945">
-        <f>IF(OR(D9="",I9=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I9,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O9" s="945">
-        <f>IF(OR(D9="",NOT(ISNUMBER(M9)),NOT(ISNUMBER(N9))),"",ROUND(M9*N9,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="38" customHeight="1" s="1025">
-      <c r="A10" s="944">
-        <f>IF(C10="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C10,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B10" s="944">
-        <f>IF(C10="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C10,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C10" s="1060" t="inlineStr">
-        <is>
-          <t>计算并追溯会员等级</t>
-        </is>
-      </c>
-      <c r="D10" s="1060" t="inlineStr">
-        <is>
-          <t>调整既有会员主数据模型的等级计算服务</t>
-        </is>
-      </c>
-      <c r="E10" s="1060" t="inlineStr">
-        <is>
-          <t>业务服务与接口</t>
-        </is>
-      </c>
-      <c r="F10" s="945">
-        <f>IF(E10="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E10,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G10" s="1061" t="inlineStr">
-        <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="H10" s="1060" t="inlineStr">
-        <is>
-          <t>基于既有会员主数据模型新增等级试算、生效和查询操作。</t>
-        </is>
-      </c>
-      <c r="I10" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J10" s="1060" t="inlineStr"/>
-      <c r="K10" s="1060" t="inlineStr">
-        <is>
-          <t>既有会员主数据模型</t>
-        </is>
-      </c>
-      <c r="L10" s="1060" t="inlineStr">
-        <is>
-          <t>一组围绕等级规则生效的紧密相关业务操作。</t>
-        </is>
-      </c>
-      <c r="M10" s="945">
-        <f>IF(OR(D10="",E10="",G10=""),"",IFERROR(IF(G10="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E10,BaseUnitCatalogTable[基础单元名称],0)),IF(G10="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E10,BaseUnitCatalogTable[基础单元名称],0)),IF(G10="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E10,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N10" s="945">
-        <f>IF(OR(D10="",I10=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I10,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O10" s="945">
-        <f>IF(OR(D10="",NOT(ISNUMBER(M10)),NOT(ISNUMBER(N10))),"",ROUND(M10*N10,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="49" customHeight="1" s="1025">
-      <c r="A11" s="944">
-        <f>IF(C11="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C11,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B11" s="944">
-        <f>IF(C11="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C11,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C11" s="1060" t="inlineStr">
-        <is>
-          <t>计算并追溯会员等级</t>
-        </is>
-      </c>
-      <c r="D11" s="1060" t="inlineStr">
-        <is>
-          <t>调整既有会员主数据模型的等级历史</t>
-        </is>
-      </c>
-      <c r="E11" s="1060" t="inlineStr">
-        <is>
-          <t>数据模型与存储结构</t>
-        </is>
-      </c>
-      <c r="F11" s="945">
-        <f>IF(E11="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E11,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G11" s="1061" t="inlineStr">
-        <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="H11" s="1060" t="inlineStr">
-        <is>
-          <t>扩展既有会员主数据模型，增加规则版本、生效区间和等级变更历史。</t>
-        </is>
-      </c>
-      <c r="I11" s="1061" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="J11" s="1060" t="inlineStr">
-        <is>
-          <t>新增两张关系清晰的历史表和唯一性约束，不涉及分区或跨库事务。</t>
-        </is>
-      </c>
-      <c r="K11" s="1060" t="inlineStr">
-        <is>
-          <t>既有会员主数据模型</t>
-        </is>
-      </c>
-      <c r="L11" s="1060" t="inlineStr">
-        <is>
-          <t>一个会员等级数据模型实例。</t>
-        </is>
-      </c>
-      <c r="M11" s="945">
-        <f>IF(OR(D11="",E11="",G11=""),"",IFERROR(IF(G11="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E11,BaseUnitCatalogTable[基础单元名称],0)),IF(G11="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E11,BaseUnitCatalogTable[基础单元名称],0)),IF(G11="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E11,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N11" s="945">
-        <f>IF(OR(D11="",I11=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I11,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O11" s="945">
-        <f>IF(OR(D11="",NOT(ISNUMBER(M11)),NOT(ISNUMBER(N11))),"",ROUND(M11*N11,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1" s="1025">
-      <c r="A12" s="944">
-        <f>IF(C12="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C12,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B12" s="944">
-        <f>IF(C12="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C12,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C12" s="1060" t="inlineStr">
-        <is>
-          <t>统一创建全渠道订单</t>
-        </is>
-      </c>
-      <c r="D12" s="1060" t="inlineStr">
-        <is>
-          <t>新建全渠道订单创建交互</t>
-        </is>
-      </c>
-      <c r="E12" s="1060" t="inlineStr">
-        <is>
-          <t>界面与交互</t>
-        </is>
-      </c>
-      <c r="F12" s="945">
-        <f>IF(E12="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E12,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G12" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H12" s="1060" t="inlineStr">
-        <is>
-          <t>新增门店与线上共用的价格、权益和履约方式校验交互。</t>
-        </is>
-      </c>
-      <c r="I12" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J12" s="1060" t="inlineStr"/>
-      <c r="K12" s="1060" t="inlineStr"/>
-      <c r="L12" s="1060" t="inlineStr">
-        <is>
-          <t>一个订单创建主流程界面实例，包含统一校验和错误反馈。</t>
-        </is>
-      </c>
-      <c r="M12" s="945">
-        <f>IF(OR(D12="",E12="",G12=""),"",IFERROR(IF(G12="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E12,BaseUnitCatalogTable[基础单元名称],0)),IF(G12="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E12,BaseUnitCatalogTable[基础单元名称],0)),IF(G12="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E12,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N12" s="945">
-        <f>IF(OR(D12="",I12=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I12,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O12" s="945">
-        <f>IF(OR(D12="",NOT(ISNUMBER(M12)),NOT(ISNUMBER(N12))),"",ROUND(M12*N12,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="49" customHeight="1" s="1025">
-      <c r="A13" s="944">
-        <f>IF(C13="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C13,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B13" s="944">
-        <f>IF(C13="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C13,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C13" s="1060" t="inlineStr">
-        <is>
-          <t>统一创建全渠道订单</t>
-        </is>
-      </c>
-      <c r="D13" s="1060" t="inlineStr">
-        <is>
-          <t>新建全渠道订单创建服务</t>
-        </is>
-      </c>
-      <c r="E13" s="1060" t="inlineStr">
-        <is>
-          <t>业务服务与接口</t>
-        </is>
-      </c>
-      <c r="F13" s="945">
-        <f>IF(E13="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E13,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G13" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H13" s="1060" t="inlineStr">
-        <is>
-          <t>新增跨渠道订单创建、价格快照、权益核验和幂等控制。</t>
-        </is>
-      </c>
-      <c r="I13" s="1061" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J13" s="1060" t="inlineStr">
-        <is>
-          <t>涉及门店与线上两类渠道、四项业务校验、跨域价格权益快照和并发幂等。</t>
-        </is>
-      </c>
-      <c r="K13" s="1060" t="inlineStr"/>
-      <c r="L13" s="1060" t="inlineStr">
-        <is>
-          <t>一个全渠道订单创建服务实例。</t>
-        </is>
-      </c>
-      <c r="M13" s="945">
-        <f>IF(OR(D13="",E13="",G13=""),"",IFERROR(IF(G13="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E13,BaseUnitCatalogTable[基础单元名称],0)),IF(G13="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E13,BaseUnitCatalogTable[基础单元名称],0)),IF(G13="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E13,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N13" s="945">
-        <f>IF(OR(D13="",I13=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I13,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O13" s="945">
-        <f>IF(OR(D13="",NOT(ISNUMBER(M13)),NOT(ISNUMBER(N13))),"",ROUND(M13*N13,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="38" customHeight="1" s="1025">
-      <c r="A14" s="944">
-        <f>IF(C14="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C14,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B14" s="944">
-        <f>IF(C14="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C14,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C14" s="1060" t="inlineStr">
-        <is>
-          <t>驱动订单状态与事件</t>
-        </is>
-      </c>
-      <c r="D14" s="1060" t="inlineStr">
-        <is>
-          <t>调整既有订单服务与状态机</t>
-        </is>
-      </c>
-      <c r="E14" s="1060" t="inlineStr">
-        <is>
-          <t>业务服务与接口</t>
-        </is>
-      </c>
-      <c r="F14" s="945">
-        <f>IF(E14="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E14,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G14" s="1061" t="inlineStr">
-        <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="H14" s="1060" t="inlineStr">
-        <is>
-          <t>扩展既有订单服务与状态机，增加门店接单、退货、退款和开票状态。</t>
-        </is>
-      </c>
-      <c r="I14" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J14" s="1060" t="inlineStr"/>
-      <c r="K14" s="1060" t="inlineStr">
-        <is>
-          <t>既有订单服务与状态机</t>
-        </is>
-      </c>
-      <c r="L14" s="1060" t="inlineStr">
-        <is>
-          <t>一个订单状态机调整实例，包含新增状态、命令和合法迁移。</t>
-        </is>
-      </c>
-      <c r="M14" s="945">
-        <f>IF(OR(D14="",E14="",G14=""),"",IFERROR(IF(G14="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E14,BaseUnitCatalogTable[基础单元名称],0)),IF(G14="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E14,BaseUnitCatalogTable[基础单元名称],0)),IF(G14="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E14,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N14" s="945">
-        <f>IF(OR(D14="",I14=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I14,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O14" s="945">
-        <f>IF(OR(D14="",NOT(ISNUMBER(M14)),NOT(ISNUMBER(N14))),"",ROUND(M14*N14,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="49" customHeight="1" s="1025">
-      <c r="A15" s="944">
-        <f>IF(C15="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C15,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B15" s="944">
-        <f>IF(C15="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C15,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C15" s="1060" t="inlineStr">
-        <is>
-          <t>驱动订单状态与事件</t>
-        </is>
-      </c>
-      <c r="D15" s="1060" t="inlineStr">
-        <is>
-          <t>新建订单状态事件处理</t>
-        </is>
-      </c>
-      <c r="E15" s="1060" t="inlineStr">
-        <is>
-          <t>事件与消息处理</t>
-        </is>
-      </c>
-      <c r="F15" s="945">
-        <f>IF(E15="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E15,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G15" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H15" s="1060" t="inlineStr">
-        <is>
-          <t>新增带事件编号、业务键和重放保护的订单状态事件。</t>
-        </is>
-      </c>
-      <c r="I15" s="1061" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J15" s="1060" t="inlineStr">
-        <is>
-          <t>覆盖九类状态事件、顺序保证、重复消费和失败重放，并被多个下游订阅。</t>
-        </is>
-      </c>
-      <c r="K15" s="1060" t="inlineStr"/>
-      <c r="L15" s="1060" t="inlineStr">
-        <is>
-          <t>一个订单状态事件主题及其生产消费处理实例。</t>
-        </is>
-      </c>
-      <c r="M15" s="945">
-        <f>IF(OR(D15="",E15="",G15=""),"",IFERROR(IF(G15="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E15,BaseUnitCatalogTable[基础单元名称],0)),IF(G15="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E15,BaseUnitCatalogTable[基础单元名称],0)),IF(G15="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E15,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N15" s="945">
-        <f>IF(OR(D15="",I15=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I15,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O15" s="945">
-        <f>IF(OR(D15="",NOT(ISNUMBER(M15)),NOT(ISNUMBER(N15))),"",ROUND(M15*N15,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="49" customHeight="1" s="1025">
-      <c r="A16" s="944">
-        <f>IF(C16="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C16,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B16" s="944">
-        <f>IF(C16="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C16,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C16" s="1060" t="inlineStr">
-        <is>
-          <t>预占和释放 ERP 库存</t>
-        </is>
-      </c>
-      <c r="D16" s="1060" t="inlineStr">
-        <is>
-          <t>接入既有 ERP 库存接口</t>
-        </is>
-      </c>
-      <c r="E16" s="1060" t="inlineStr">
-        <is>
-          <t>内部系统对接</t>
-        </is>
-      </c>
-      <c r="F16" s="945">
-        <f>IF(E16="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E16,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G16" s="1061" t="inlineStr">
-        <is>
-          <t>接入复用</t>
-        </is>
-      </c>
-      <c r="H16" s="1060" t="inlineStr">
-        <is>
-          <t>既有 ERP 库存接口保持不变；本项目负责并交付：映射、适配、认证、专项验证。</t>
-        </is>
-      </c>
-      <c r="I16" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J16" s="1060" t="inlineStr"/>
-      <c r="K16" s="1060" t="inlineStr">
-        <is>
-          <t>既有 ERP 库存接口</t>
-        </is>
-      </c>
-      <c r="L16" s="1060" t="inlineStr">
-        <is>
-          <t>实现一个已登记的内部 ERP 库存集成，SIT 人天由集成表公式另计。</t>
-        </is>
-      </c>
-      <c r="M16" s="945">
-        <f>IF(OR(D16="",E16="",G16=""),"",IFERROR(IF(G16="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E16,BaseUnitCatalogTable[基础单元名称],0)),IF(G16="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E16,BaseUnitCatalogTable[基础单元名称],0)),IF(G16="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E16,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N16" s="945">
-        <f>IF(OR(D16="",I16=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I16,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O16" s="945">
-        <f>IF(OR(D16="",NOT(ISNUMBER(M16)),NOT(ISNUMBER(N16))),"",ROUND(M16*N16,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="49" customHeight="1" s="1025">
-      <c r="A17" s="944">
-        <f>IF(C17="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C17,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B17" s="944">
-        <f>IF(C17="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C17,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C17" s="1060" t="inlineStr">
-        <is>
-          <t>预占和释放 ERP 库存</t>
-        </is>
-      </c>
-      <c r="D17" s="1060" t="inlineStr">
-        <is>
-          <t>验证库存预占幂等与补偿</t>
-        </is>
-      </c>
-      <c r="E17" s="1060" t="inlineStr">
-        <is>
-          <t>人工测试</t>
-        </is>
-      </c>
-      <c r="F17" s="945">
-        <f>IF(E17="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E17,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G17" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H17" s="1060" t="inlineStr">
-        <is>
-          <t>新增 ERP 超时、重试、重复请求和释放失败的人工验证场景。</t>
-        </is>
-      </c>
-      <c r="I17" s="1061" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="J17" s="1060" t="inlineStr">
-        <is>
-          <t>集中验证四个已定义异常场景，数据准备简单且无需跨设备矩阵。</t>
-        </is>
-      </c>
-      <c r="K17" s="1060" t="inlineStr"/>
-      <c r="L17" s="1060" t="inlineStr">
-        <is>
-          <t>一个库存集成专项人工测试实例，不替代集成支持 SIT 公式。</t>
-        </is>
-      </c>
-      <c r="M17" s="945">
-        <f>IF(OR(D17="",E17="",G17=""),"",IFERROR(IF(G17="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E17,BaseUnitCatalogTable[基础单元名称],0)),IF(G17="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E17,BaseUnitCatalogTable[基础单元名称],0)),IF(G17="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E17,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N17" s="945">
-        <f>IF(OR(D17="",I17=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I17,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O17" s="945">
-        <f>IF(OR(D17="",NOT(ISNUMBER(M17)),NOT(ISNUMBER(N17))),"",ROUND(M17*N17,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="38" customHeight="1" s="1025">
-      <c r="A18" s="944">
-        <f>IF(C18="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C18,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B18" s="944">
-        <f>IF(C18="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C18,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C18" s="1060" t="inlineStr">
-        <is>
-          <t>提交并审核退货申请</t>
-        </is>
-      </c>
-      <c r="D18" s="1060" t="inlineStr">
-        <is>
-          <t>新建退货申请与审核交互</t>
-        </is>
-      </c>
-      <c r="E18" s="1060" t="inlineStr">
-        <is>
-          <t>界面与交互</t>
-        </is>
-      </c>
-      <c r="F18" s="945">
-        <f>IF(E18="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E18,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G18" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H18" s="1060" t="inlineStr">
-        <is>
-          <t>新增门店和客服使用的退货明细、可退校验和审核反馈。</t>
-        </is>
-      </c>
-      <c r="I18" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J18" s="1060" t="inlineStr"/>
-      <c r="K18" s="1060" t="inlineStr"/>
-      <c r="L18" s="1060" t="inlineStr">
-        <is>
-          <t>一个退货申请与审核主流程界面实例。</t>
-        </is>
-      </c>
-      <c r="M18" s="945">
-        <f>IF(OR(D18="",E18="",G18=""),"",IFERROR(IF(G18="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E18,BaseUnitCatalogTable[基础单元名称],0)),IF(G18="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E18,BaseUnitCatalogTable[基础单元名称],0)),IF(G18="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E18,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N18" s="945">
-        <f>IF(OR(D18="",I18=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I18,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O18" s="945">
-        <f>IF(OR(D18="",NOT(ISNUMBER(M18)),NOT(ISNUMBER(N18))),"",ROUND(M18*N18,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="38" customHeight="1" s="1025">
-      <c r="A19" s="944">
-        <f>IF(C19="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C19,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B19" s="944">
-        <f>IF(C19="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C19,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C19" s="1060" t="inlineStr">
-        <is>
-          <t>提交并审核退货申请</t>
-        </is>
-      </c>
-      <c r="D19" s="1060" t="inlineStr">
-        <is>
-          <t>调整既有订单服务与状态机的退货规则</t>
-        </is>
-      </c>
-      <c r="E19" s="1060" t="inlineStr">
-        <is>
-          <t>业务服务与接口</t>
-        </is>
-      </c>
-      <c r="F19" s="945">
-        <f>IF(E19="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E19,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G19" s="1061" t="inlineStr">
-        <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="H19" s="1060" t="inlineStr">
-        <is>
-          <t>在既有订单服务与状态机中增加可退数量、退货审核和退货单状态。</t>
-        </is>
-      </c>
-      <c r="I19" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J19" s="1060" t="inlineStr"/>
-      <c r="K19" s="1060" t="inlineStr">
-        <is>
-          <t>既有订单服务与状态机</t>
-        </is>
-      </c>
-      <c r="L19" s="1060" t="inlineStr">
-        <is>
-          <t>一个退货领域服务调整实例。</t>
-        </is>
-      </c>
-      <c r="M19" s="945">
-        <f>IF(OR(D19="",E19="",G19=""),"",IFERROR(IF(G19="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E19,BaseUnitCatalogTable[基础单元名称],0)),IF(G19="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E19,BaseUnitCatalogTable[基础单元名称],0)),IF(G19="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E19,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N19" s="945">
-        <f>IF(OR(D19="",I19=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I19,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O19" s="945">
-        <f>IF(OR(D19="",NOT(ISNUMBER(M19)),NOT(ISNUMBER(N19))),"",ROUND(M19*N19,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="49" customHeight="1" s="1025">
-      <c r="A20" s="944">
-        <f>IF(C20="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C20,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B20" s="944">
-        <f>IF(C20="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C20,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C20" s="1060" t="inlineStr">
-        <is>
-          <t>发起退款并回写结果</t>
-        </is>
-      </c>
-      <c r="D20" s="1060" t="inlineStr">
-        <is>
-          <t>接入既有支付网关租户</t>
-        </is>
-      </c>
-      <c r="E20" s="1060" t="inlineStr">
-        <is>
-          <t>外部系统对接</t>
-        </is>
-      </c>
-      <c r="F20" s="945">
-        <f>IF(E20="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E20,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G20" s="1061" t="inlineStr">
-        <is>
-          <t>接入复用</t>
-        </is>
-      </c>
-      <c r="H20" s="1060" t="inlineStr">
-        <is>
-          <t>既有支付网关租户保持不变；本项目负责并交付：配置、映射、适配、认证、专项验证。</t>
-        </is>
-      </c>
-      <c r="I20" s="1061" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J20" s="1060" t="inlineStr">
-        <is>
-          <t>涉及外部认证、同步申请与异步回调、金额幂等、供应商错误码和认证窗口。</t>
-        </is>
-      </c>
-      <c r="K20" s="1060" t="inlineStr">
-        <is>
-          <t>既有支付网关租户</t>
-        </is>
-      </c>
-      <c r="L20" s="1060" t="inlineStr">
-        <is>
-          <t>实现一个已登记的外部支付退款集成，外部支持成本在集成表单列展示。</t>
-        </is>
-      </c>
-      <c r="M20" s="945">
-        <f>IF(OR(D20="",E20="",G20=""),"",IFERROR(IF(G20="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E20,BaseUnitCatalogTable[基础单元名称],0)),IF(G20="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E20,BaseUnitCatalogTable[基础单元名称],0)),IF(G20="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E20,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N20" s="945">
-        <f>IF(OR(D20="",I20=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I20,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O20" s="945">
-        <f>IF(OR(D20="",NOT(ISNUMBER(M20)),NOT(ISNUMBER(N20))),"",ROUND(M20*N20,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="38" customHeight="1" s="1025">
-      <c r="A21" s="944">
-        <f>IF(C21="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C21,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B21" s="944">
-        <f>IF(C21="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C21,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C21" s="1060" t="inlineStr">
-        <is>
-          <t>发起退款并回写结果</t>
-        </is>
-      </c>
-      <c r="D21" s="1060" t="inlineStr">
-        <is>
-          <t>验证退款签名与隐私保护</t>
-        </is>
-      </c>
-      <c r="E21" s="1060" t="inlineStr">
-        <is>
-          <t>安全与隐私测试</t>
-        </is>
-      </c>
-      <c r="F21" s="945">
-        <f>IF(E21="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E21,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G21" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H21" s="1060" t="inlineStr">
-        <is>
-          <t>新增退款回调签名、重放攻击、敏感字段和越权场景验证。</t>
-        </is>
-      </c>
-      <c r="I21" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J21" s="1060" t="inlineStr"/>
-      <c r="K21" s="1060" t="inlineStr"/>
-      <c r="L21" s="1060" t="inlineStr">
-        <is>
-          <t>一个退款链路安全与隐私测试实例。</t>
-        </is>
-      </c>
-      <c r="M21" s="945">
-        <f>IF(OR(D21="",E21="",G21=""),"",IFERROR(IF(G21="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E21,BaseUnitCatalogTable[基础单元名称],0)),IF(G21="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E21,BaseUnitCatalogTable[基础单元名称],0)),IF(G21="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E21,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N21" s="945">
-        <f>IF(OR(D21="",I21=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I21,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O21" s="945">
-        <f>IF(OR(D21="",NOT(ISNUMBER(M21)),NOT(ISNUMBER(N21))),"",ROUND(M21*N21,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="38" customHeight="1" s="1025">
-      <c r="A22" s="944">
-        <f>IF(C22="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C22,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B22" s="944">
-        <f>IF(C22="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C22,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C22" s="1060" t="inlineStr">
-        <is>
-          <t>门店处理订单与交接</t>
-        </is>
-      </c>
-      <c r="D22" s="1060" t="inlineStr">
-        <is>
-          <t>新建门店订单队列与交接界面</t>
-        </is>
-      </c>
-      <c r="E22" s="1060" t="inlineStr">
-        <is>
-          <t>界面与交互</t>
-        </is>
-      </c>
-      <c r="F22" s="945">
-        <f>IF(E22="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E22,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G22" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H22" s="1060" t="inlineStr">
-        <is>
-          <t>新增门店待处理队列、缺货替代、备注和班次交接交互。</t>
-        </is>
-      </c>
-      <c r="I22" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J22" s="1060" t="inlineStr"/>
-      <c r="K22" s="1060" t="inlineStr"/>
-      <c r="L22" s="1060" t="inlineStr">
-        <is>
-          <t>一个门店接单工作台主界面实例。</t>
-        </is>
-      </c>
-      <c r="M22" s="945">
-        <f>IF(OR(D22="",E22="",G22=""),"",IFERROR(IF(G22="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E22,BaseUnitCatalogTable[基础单元名称],0)),IF(G22="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E22,BaseUnitCatalogTable[基础单元名称],0)),IF(G22="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E22,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N22" s="945">
-        <f>IF(OR(D22="",I22=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I22,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O22" s="945">
-        <f>IF(OR(D22="",NOT(ISNUMBER(M22)),NOT(ISNUMBER(N22))),"",ROUND(M22*N22,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="49" customHeight="1" s="1025">
-      <c r="A23" s="944">
-        <f>IF(C23="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C23,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B23" s="944">
-        <f>IF(C23="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C23,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C23" s="1060" t="inlineStr">
-        <is>
-          <t>门店处理订单与交接</t>
-        </is>
-      </c>
-      <c r="D23" s="1060" t="inlineStr">
-        <is>
-          <t>新建门店接单与交接服务</t>
-        </is>
-      </c>
-      <c r="E23" s="1060" t="inlineStr">
-        <is>
-          <t>业务服务与接口</t>
-        </is>
-      </c>
-      <c r="F23" s="945">
-        <f>IF(E23="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E23,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G23" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H23" s="1060" t="inlineStr">
-        <is>
-          <t>交付一期顺延的门店接单、缺货替代、权限校验和交接操作。</t>
-        </is>
-      </c>
-      <c r="I23" s="1061" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J23" s="1060" t="inlineStr">
-        <is>
-          <t>涉及门店数据隔离、并发抢单、缺货替代和跨班次交接四类复杂规则。</t>
-        </is>
-      </c>
-      <c r="K23" s="1060" t="inlineStr"/>
-      <c r="L23" s="1060" t="inlineStr">
-        <is>
-          <t>一个门店接单领域服务实例。</t>
-        </is>
-      </c>
-      <c r="M23" s="945">
-        <f>IF(OR(D23="",E23="",G23=""),"",IFERROR(IF(G23="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E23,BaseUnitCatalogTable[基础单元名称],0)),IF(G23="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E23,BaseUnitCatalogTable[基础单元名称],0)),IF(G23="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E23,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N23" s="945">
-        <f>IF(OR(D23="",I23=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I23,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O23" s="945">
-        <f>IF(OR(D23="",NOT(ISNUMBER(M23)),NOT(ISNUMBER(N23))),"",ROUND(M23*N23,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="38" customHeight="1" s="1025">
-      <c r="A24" s="944">
-        <f>IF(C24="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C24,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B24" s="944">
-        <f>IF(C24="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C24,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C24" s="1060" t="inlineStr">
-        <is>
-          <t>查看统一履约轨迹</t>
-        </is>
-      </c>
-      <c r="D24" s="1060" t="inlineStr">
-        <is>
-          <t>新建统一订单履约轨迹</t>
-        </is>
-      </c>
-      <c r="E24" s="1060" t="inlineStr">
-        <is>
-          <t>界面与交互</t>
-        </is>
-      </c>
-      <c r="F24" s="945">
-        <f>IF(E24="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E24,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G24" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H24" s="1060" t="inlineStr">
-        <is>
-          <t>新增顾客与客服共用的状态、履约节点和异常原因时间轴。</t>
-        </is>
-      </c>
-      <c r="I24" s="1061" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="J24" s="1060" t="inlineStr">
-        <is>
-          <t>单一只读时间轴，复用现有列表组件且无复杂编辑状态。</t>
-        </is>
-      </c>
-      <c r="K24" s="1060" t="inlineStr"/>
-      <c r="L24" s="1060" t="inlineStr">
-        <is>
-          <t>一个订单履约轨迹界面实例。</t>
-        </is>
-      </c>
-      <c r="M24" s="945">
-        <f>IF(OR(D24="",E24="",G24=""),"",IFERROR(IF(G24="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E24,BaseUnitCatalogTable[基础单元名称],0)),IF(G24="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E24,BaseUnitCatalogTable[基础单元名称],0)),IF(G24="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E24,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N24" s="945">
-        <f>IF(OR(D24="",I24=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I24,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O24" s="945">
-        <f>IF(OR(D24="",NOT(ISNUMBER(M24)),NOT(ISNUMBER(N24))),"",ROUND(M24*N24,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="38" customHeight="1" s="1025">
-      <c r="A25" s="944">
-        <f>IF(C25="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C25,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B25" s="944">
-        <f>IF(C25="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C25,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C25" s="1060" t="inlineStr">
-        <is>
-          <t>查看统一履约轨迹</t>
-        </is>
-      </c>
-      <c r="D25" s="1060" t="inlineStr">
-        <is>
-          <t>新建履约轨迹事件投影</t>
-        </is>
-      </c>
-      <c r="E25" s="1060" t="inlineStr">
-        <is>
-          <t>事件与消息处理</t>
-        </is>
-      </c>
-      <c r="F25" s="945">
-        <f>IF(E25="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E25,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G25" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H25" s="1060" t="inlineStr">
-        <is>
-          <t>新增订单状态事件到渠道可读轨迹的投影与延迟补偿。</t>
-        </is>
-      </c>
-      <c r="I25" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J25" s="1060" t="inlineStr"/>
-      <c r="K25" s="1060" t="inlineStr"/>
-      <c r="L25" s="1060" t="inlineStr">
-        <is>
-          <t>一个履约轨迹事件消费和投影实例。</t>
-        </is>
-      </c>
-      <c r="M25" s="945">
-        <f>IF(OR(D25="",E25="",G25=""),"",IFERROR(IF(G25="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E25,BaseUnitCatalogTable[基础单元名称],0)),IF(G25="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E25,BaseUnitCatalogTable[基础单元名称],0)),IF(G25="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E25,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N25" s="945">
-        <f>IF(OR(D25="",I25=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I25,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O25" s="945">
-        <f>IF(OR(D25="",NOT(ISNUMBER(M25)),NOT(ISNUMBER(N25))),"",ROUND(M25*N25,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="38" customHeight="1" s="1025">
-      <c r="A26" s="944">
-        <f>IF(C26="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C26,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B26" s="944">
-        <f>IF(C26="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C26,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C26" s="1060" t="inlineStr">
-        <is>
-          <t>执行支付退款日结对账</t>
-        </is>
-      </c>
-      <c r="D26" s="1060" t="inlineStr">
-        <is>
-          <t>新建支付退款日结作业</t>
-        </is>
-      </c>
-      <c r="E26" s="1060" t="inlineStr">
-        <is>
-          <t>后台任务</t>
-        </is>
-      </c>
-      <c r="F26" s="945">
-        <f>IF(E26="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E26,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G26" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H26" s="1060" t="inlineStr">
-        <is>
-          <t>新增每日交易归集、手续费计算、差异识别和失败重跑作业。</t>
-        </is>
-      </c>
-      <c r="I26" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J26" s="1060" t="inlineStr"/>
-      <c r="K26" s="1060" t="inlineStr"/>
-      <c r="L26" s="1060" t="inlineStr">
-        <is>
-          <t>一个按自然日调度的支付对账后台作业实例。</t>
-        </is>
-      </c>
-      <c r="M26" s="945">
-        <f>IF(OR(D26="",E26="",G26=""),"",IFERROR(IF(G26="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E26,BaseUnitCatalogTable[基础单元名称],0)),IF(G26="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E26,BaseUnitCatalogTable[基础单元名称],0)),IF(G26="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E26,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N26" s="945">
-        <f>IF(OR(D26="",I26=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I26,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O26" s="945">
-        <f>IF(OR(D26="",NOT(ISNUMBER(M26)),NOT(ISNUMBER(N26))),"",ROUND(M26*N26,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="38" customHeight="1" s="1025">
-      <c r="A27" s="944">
-        <f>IF(C27="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C27,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B27" s="944">
-        <f>IF(C27="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C27,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C27" s="1060" t="inlineStr">
-        <is>
-          <t>执行支付退款日结对账</t>
-        </is>
-      </c>
-      <c r="D27" s="1060" t="inlineStr">
-        <is>
-          <t>新建支付差异复核视图</t>
-        </is>
-      </c>
-      <c r="E27" s="1060" t="inlineStr">
-        <is>
-          <t>报表与指标</t>
-        </is>
-      </c>
-      <c r="F27" s="945">
-        <f>IF(E27="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E27,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G27" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H27" s="1060" t="inlineStr">
-        <is>
-          <t>新增按渠道、门店和订单查看实收、退款与手续费差异的财务视图。</t>
-        </is>
-      </c>
-      <c r="I27" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J27" s="1060" t="inlineStr"/>
-      <c r="K27" s="1060" t="inlineStr"/>
-      <c r="L27" s="1060" t="inlineStr">
-        <is>
-          <t>一个支付日结差异报表实例。</t>
-        </is>
-      </c>
-      <c r="M27" s="945">
-        <f>IF(OR(D27="",E27="",G27=""),"",IFERROR(IF(G27="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E27,BaseUnitCatalogTable[基础单元名称],0)),IF(G27="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E27,BaseUnitCatalogTable[基础单元名称],0)),IF(G27="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E27,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N27" s="945">
-        <f>IF(OR(D27="",I27=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I27,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O27" s="945">
-        <f>IF(OR(D27="",NOT(ISNUMBER(M27)),NOT(ISNUMBER(N27))),"",ROUND(M27*N27,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="49" customHeight="1" s="1025">
-      <c r="A28" s="944">
-        <f>IF(C28="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C28,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B28" s="944">
-        <f>IF(C28="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C28,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C28" s="1060" t="inlineStr">
-        <is>
-          <t>申请并追踪电子发票</t>
-        </is>
-      </c>
-      <c r="D28" s="1060" t="inlineStr">
-        <is>
-          <t>接入既有电子发票通道</t>
-        </is>
-      </c>
-      <c r="E28" s="1060" t="inlineStr">
-        <is>
-          <t>外部系统对接</t>
-        </is>
-      </c>
-      <c r="F28" s="945">
-        <f>IF(E28="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E28,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G28" s="1061" t="inlineStr">
-        <is>
-          <t>接入复用</t>
-        </is>
-      </c>
-      <c r="H28" s="1060" t="inlineStr">
-        <is>
-          <t>既有电子发票通道保持不变；本项目负责并交付：配置、映射、适配、认证、租户设置、专项验证。</t>
-        </is>
-      </c>
-      <c r="I28" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J28" s="1060" t="inlineStr"/>
-      <c r="K28" s="1060" t="inlineStr">
-        <is>
-          <t>既有电子发票通道</t>
-        </is>
-      </c>
-      <c r="L28" s="1060" t="inlineStr">
-        <is>
-          <t>实现一个已登记的外部电子发票集成，并单列外部支持成本。</t>
-        </is>
-      </c>
-      <c r="M28" s="945">
-        <f>IF(OR(D28="",E28="",G28=""),"",IFERROR(IF(G28="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E28,BaseUnitCatalogTable[基础单元名称],0)),IF(G28="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E28,BaseUnitCatalogTable[基础单元名称],0)),IF(G28="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E28,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N28" s="945">
-        <f>IF(OR(D28="",I28=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I28,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O28" s="945">
-        <f>IF(OR(D28="",NOT(ISNUMBER(M28)),NOT(ISNUMBER(N28))),"",ROUND(M28*N28,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="38" customHeight="1" s="1025">
-      <c r="A29" s="944">
-        <f>IF(C29="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C29,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B29" s="944">
-        <f>IF(C29="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C29,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C29" s="1060" t="inlineStr">
-        <is>
-          <t>申请并追踪电子发票</t>
-        </is>
-      </c>
-      <c r="D29" s="1060" t="inlineStr">
-        <is>
-          <t>新建发票状态补偿作业</t>
-        </is>
-      </c>
-      <c r="E29" s="1060" t="inlineStr">
-        <is>
-          <t>后台任务</t>
-        </is>
-      </c>
-      <c r="F29" s="945">
-        <f>IF(E29="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E29,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G29" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H29" s="1060" t="inlineStr">
-        <is>
-          <t>新增开票状态轮询、失败重试、重复申请拦截和结果回写作业。</t>
-        </is>
-      </c>
-      <c r="I29" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J29" s="1060" t="inlineStr"/>
-      <c r="K29" s="1060" t="inlineStr"/>
-      <c r="L29" s="1060" t="inlineStr">
-        <is>
-          <t>一个电子发票状态补偿后台作业实例。</t>
-        </is>
-      </c>
-      <c r="M29" s="945">
-        <f>IF(OR(D29="",E29="",G29=""),"",IFERROR(IF(G29="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E29,BaseUnitCatalogTable[基础单元名称],0)),IF(G29="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E29,BaseUnitCatalogTable[基础单元名称],0)),IF(G29="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E29,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N29" s="945">
-        <f>IF(OR(D29="",I29=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I29,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O29" s="945">
-        <f>IF(OR(D29="",NOT(ISNUMBER(M29)),NOT(ISNUMBER(N29))),"",ROUND(M29*N29,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="49" customHeight="1" s="1025">
-      <c r="A30" s="944">
-        <f>IF(C30="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C30,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B30" s="944">
-        <f>IF(C30="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C30,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C30" s="1060" t="inlineStr">
-        <is>
-          <t>查看财务经营日报</t>
-        </is>
-      </c>
-      <c r="D30" s="1060" t="inlineStr">
-        <is>
-          <t>新建财务经营日报</t>
-        </is>
-      </c>
-      <c r="E30" s="1060" t="inlineStr">
-        <is>
-          <t>报表与指标</t>
-        </is>
-      </c>
-      <c r="F30" s="945">
-        <f>IF(E30="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E30,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G30" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H30" s="1060" t="inlineStr">
-        <is>
-          <t>新增销售、退款、优惠和未对账金额的多维指标与下钻。</t>
-        </is>
-      </c>
-      <c r="I30" s="1061" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J30" s="1060" t="inlineStr">
-        <is>
-          <t>包含四类金额、日期区域渠道三维切片、逐笔下钻和财务口径校验。</t>
-        </is>
-      </c>
-      <c r="K30" s="1060" t="inlineStr"/>
-      <c r="L30" s="1060" t="inlineStr">
-        <is>
-          <t>一个财务经营日报与指标集合实例。</t>
-        </is>
-      </c>
-      <c r="M30" s="945">
-        <f>IF(OR(D30="",E30="",G30=""),"",IFERROR(IF(G30="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E30,BaseUnitCatalogTable[基础单元名称],0)),IF(G30="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E30,BaseUnitCatalogTable[基础单元名称],0)),IF(G30="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E30,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N30" s="945">
-        <f>IF(OR(D30="",I30=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I30,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O30" s="945">
-        <f>IF(OR(D30="",NOT(ISNUMBER(M30)),NOT(ISNUMBER(N30))),"",ROUND(M30*N30,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="38" customHeight="1" s="1025">
-      <c r="A31" s="944">
-        <f>IF(C31="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C31,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B31" s="944">
-        <f>IF(C31="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C31,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C31" s="1060" t="inlineStr">
-        <is>
-          <t>查看财务经营日报</t>
-        </is>
-      </c>
-      <c r="D31" s="1060" t="inlineStr">
-        <is>
-          <t>新建财务指标处理流程</t>
-        </is>
-      </c>
-      <c r="E31" s="1060" t="inlineStr">
-        <is>
-          <t>数据处理流程</t>
-        </is>
-      </c>
-      <c r="F31" s="945">
-        <f>IF(E31="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E31,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G31" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H31" s="1060" t="inlineStr">
-        <is>
-          <t>新增订单、支付、退款和发票明细的清洗、关联与日汇总流程。</t>
-        </is>
-      </c>
-      <c r="I31" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J31" s="1060" t="inlineStr"/>
-      <c r="K31" s="1060" t="inlineStr"/>
-      <c r="L31" s="1060" t="inlineStr">
-        <is>
-          <t>一个财务指标数据处理流程实例。</t>
-        </is>
-      </c>
-      <c r="M31" s="945">
-        <f>IF(OR(D31="",E31="",G31=""),"",IFERROR(IF(G31="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E31,BaseUnitCatalogTable[基础单元名称],0)),IF(G31="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E31,BaseUnitCatalogTable[基础单元名称],0)),IF(G31="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E31,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N31" s="945">
-        <f>IF(OR(D31="",I31=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I31,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O31" s="945">
-        <f>IF(OR(D31="",NOT(ISNUMBER(M31)),NOT(ISNUMBER(N31))),"",ROUND(M31*N31,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="49" customHeight="1" s="1025">
-      <c r="A32" s="944">
-        <f>IF(C32="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C32,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B32" s="944">
-        <f>IF(C32="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C32,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C32" s="1060" t="inlineStr">
-        <is>
-          <t>准备生产环境和发布流水线</t>
-        </is>
-      </c>
-      <c r="D32" s="1060" t="inlineStr">
-        <is>
-          <t>调整既有生产环境与发布流水线的运行配置</t>
-        </is>
-      </c>
-      <c r="E32" s="1060" t="inlineStr">
-        <is>
-          <t>运行环境</t>
-        </is>
-      </c>
-      <c r="F32" s="945">
-        <f>IF(E32="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E32,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G32" s="1061" t="inlineStr">
-        <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="H32" s="1060" t="inlineStr">
-        <is>
-          <t>在既有生产环境与发布流水线中增加会员、订单、批处理和外部证书配置。</t>
-        </is>
-      </c>
-      <c r="I32" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J32" s="1060" t="inlineStr"/>
-      <c r="K32" s="1060" t="inlineStr">
-        <is>
-          <t>既有生产环境与发布流水线</t>
-        </is>
-      </c>
-      <c r="L32" s="1060" t="inlineStr">
-        <is>
-          <t>一个生产运行环境配置实例。</t>
-        </is>
-      </c>
-      <c r="M32" s="945">
-        <f>IF(OR(D32="",E32="",G32=""),"",IFERROR(IF(G32="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E32,BaseUnitCatalogTable[基础单元名称],0)),IF(G32="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E32,BaseUnitCatalogTable[基础单元名称],0)),IF(G32="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E32,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N32" s="945">
-        <f>IF(OR(D32="",I32=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I32,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O32" s="945">
-        <f>IF(OR(D32="",NOT(ISNUMBER(M32)),NOT(ISNUMBER(N32))),"",ROUND(M32*N32,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="49" customHeight="1" s="1025">
-      <c r="A33" s="944">
-        <f>IF(C33="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C33,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B33" s="944">
-        <f>IF(C33="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C33,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C33" s="1060" t="inlineStr">
-        <is>
-          <t>准备生产环境和发布流水线</t>
-        </is>
-      </c>
-      <c r="D33" s="1060" t="inlineStr">
-        <is>
-          <t>调整既有生产环境与发布流水线的部署步骤</t>
-        </is>
-      </c>
-      <c r="E33" s="1060" t="inlineStr">
-        <is>
-          <t>构建与部署流水线</t>
-        </is>
-      </c>
-      <c r="F33" s="945">
-        <f>IF(E33="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E33,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G33" s="1061" t="inlineStr">
-        <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="H33" s="1060" t="inlineStr">
-        <is>
-          <t>扩展既有生产环境与发布流水线，增加迁移前检查、分步发布和验证门禁。</t>
-        </is>
-      </c>
-      <c r="I33" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J33" s="1060" t="inlineStr"/>
-      <c r="K33" s="1060" t="inlineStr">
-        <is>
-          <t>既有生产环境与发布流水线</t>
-        </is>
-      </c>
-      <c r="L33" s="1060" t="inlineStr">
-        <is>
-          <t>一个应用构建与部署流水线调整实例。</t>
-        </is>
-      </c>
-      <c r="M33" s="945">
-        <f>IF(OR(D33="",E33="",G33=""),"",IFERROR(IF(G33="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E33,BaseUnitCatalogTable[基础单元名称],0)),IF(G33="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E33,BaseUnitCatalogTable[基础单元名称],0)),IF(G33="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E33,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N33" s="945">
-        <f>IF(OR(D33="",I33=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I33,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O33" s="945">
-        <f>IF(OR(D33="",NOT(ISNUMBER(M33)),NOT(ISNUMBER(N33))),"",ROUND(M33*N33,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="49" customHeight="1" s="1025">
-      <c r="A34" s="944">
-        <f>IF(C34="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C34,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B34" s="944">
-        <f>IF(C34="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C34,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C34" s="1060" t="inlineStr">
-        <is>
-          <t>准备生产环境和发布流水线</t>
-        </is>
-      </c>
-      <c r="D34" s="1060" t="inlineStr">
-        <is>
-          <t>调整既有生产环境与发布流水线的功能开关</t>
-        </is>
-      </c>
-      <c r="E34" s="1060" t="inlineStr">
-        <is>
-          <t>配置与功能开关</t>
-        </is>
-      </c>
-      <c r="F34" s="945">
-        <f>IF(E34="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E34,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G34" s="1061" t="inlineStr">
-        <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="H34" s="1060" t="inlineStr">
-        <is>
-          <t>在既有生产环境与发布流水线中配置渠道切流、退款和开票功能开关。</t>
-        </is>
-      </c>
-      <c r="I34" s="1061" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="J34" s="1060" t="inlineStr">
-        <is>
-          <t>三个独立布尔开关及默认值，沿用现有配置中心且无复杂灰度算法。</t>
-        </is>
-      </c>
-      <c r="K34" s="1060" t="inlineStr">
-        <is>
-          <t>既有生产环境与发布流水线</t>
-        </is>
-      </c>
-      <c r="L34" s="1060" t="inlineStr">
-        <is>
-          <t>一个上线功能开关配置实例。</t>
-        </is>
-      </c>
-      <c r="M34" s="945">
-        <f>IF(OR(D34="",E34="",G34=""),"",IFERROR(IF(G34="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E34,BaseUnitCatalogTable[基础单元名称],0)),IF(G34="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E34,BaseUnitCatalogTable[基础单元名称],0)),IF(G34="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E34,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N34" s="945">
-        <f>IF(OR(D34="",I34=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I34,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O34" s="945">
-        <f>IF(OR(D34="",NOT(ISNUMBER(M34)),NOT(ISNUMBER(N34))),"",ROUND(M34*N34,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="49" customHeight="1" s="1025">
-      <c r="A35" s="944">
-        <f>IF(C35="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C35,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B35" s="944">
-        <f>IF(C35="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C35,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C35" s="1060" t="inlineStr">
-        <is>
-          <t>执行生产切换与回滚演练</t>
-        </is>
-      </c>
-      <c r="D35" s="1060" t="inlineStr">
-        <is>
-          <t>执行生产切换与回滚</t>
-        </is>
-      </c>
-      <c r="E35" s="1060" t="inlineStr">
-        <is>
-          <t>发布切换</t>
-        </is>
-      </c>
-      <c r="F35" s="945">
-        <f>IF(E35="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E35,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G35" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H35" s="1060" t="inlineStr">
-        <is>
-          <t>基于既有生产环境与发布流水线编制并执行分步切流、检查点和回滚清单。</t>
-        </is>
-      </c>
-      <c r="I35" s="1061" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J35" s="1060" t="inlineStr">
-        <is>
-          <t>涉及会员、订单、四个集成链路、迁移窗口、三次继续回滚决策和多团队协同。</t>
-        </is>
-      </c>
-      <c r="K35" s="1060" t="inlineStr">
-        <is>
-          <t>既有生产环境与发布流水线</t>
-        </is>
-      </c>
-      <c r="L35" s="1060" t="inlineStr">
-        <is>
-          <t>一个批准上线窗口内的生产发布切换实例。</t>
-        </is>
-      </c>
-      <c r="M35" s="945">
-        <f>IF(OR(D35="",E35="",G35=""),"",IFERROR(IF(G35="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E35,BaseUnitCatalogTable[基础单元名称],0)),IF(G35="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E35,BaseUnitCatalogTable[基础单元名称],0)),IF(G35="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E35,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N35" s="945">
-        <f>IF(OR(D35="",I35=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I35,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O35" s="945">
-        <f>IF(OR(D35="",NOT(ISNUMBER(M35)),NOT(ISNUMBER(N35))),"",ROUND(M35*N35,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="49" customHeight="1" s="1025">
-      <c r="A36" s="944">
-        <f>IF(C36="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C36,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B36" s="944">
-        <f>IF(C36="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C36,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C36" s="1060" t="inlineStr">
-        <is>
-          <t>执行生产切换与回滚演练</t>
-        </is>
-      </c>
-      <c r="D36" s="1060" t="inlineStr">
-        <is>
-          <t>验证切换与回滚检查清单</t>
-        </is>
-      </c>
-      <c r="E36" s="1060" t="inlineStr">
-        <is>
-          <t>人工测试</t>
-        </is>
-      </c>
-      <c r="F36" s="945">
-        <f>IF(E36="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E36,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G36" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H36" s="1060" t="inlineStr">
-        <is>
-          <t>新增切换前置条件、检查点、回滚触发器和联系人桌面演练。</t>
-        </is>
-      </c>
-      <c r="I36" s="1061" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="J36" s="1060" t="inlineStr">
-        <is>
-          <t>一次桌面演练和一套固定清单，不涉及额外环境或大规模数据准备。</t>
-        </is>
-      </c>
-      <c r="K36" s="1060" t="inlineStr"/>
-      <c r="L36" s="1060" t="inlineStr">
-        <is>
-          <t>一个切换回滚清单验证实例。</t>
-        </is>
-      </c>
-      <c r="M36" s="945">
-        <f>IF(OR(D36="",E36="",G36=""),"",IFERROR(IF(G36="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E36,BaseUnitCatalogTable[基础单元名称],0)),IF(G36="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E36,BaseUnitCatalogTable[基础单元名称],0)),IF(G36="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E36,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N36" s="945">
-        <f>IF(OR(D36="",I36=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I36,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O36" s="945">
-        <f>IF(OR(D36="",NOT(ISNUMBER(M36)),NOT(ISNUMBER(N36))),"",ROUND(M36*N36,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="49" customHeight="1" s="1025">
-      <c r="A37" s="944">
-        <f>IF(C37="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C37,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B37" s="944">
-        <f>IF(C37="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C37,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C37" s="1060" t="inlineStr">
-        <is>
-          <t>完成生产烟测与业务确认</t>
-        </is>
-      </c>
-      <c r="D37" s="1060" t="inlineStr">
-        <is>
-          <t>执行核心查询性能验证</t>
-        </is>
-      </c>
-      <c r="E37" s="1060" t="inlineStr">
-        <is>
-          <t>性能与容量测试</t>
-        </is>
-      </c>
-      <c r="F37" s="945">
-        <f>IF(E37="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E37,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G37" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H37" s="1060" t="inlineStr">
-        <is>
-          <t>新增档案查询、订单创建和轨迹查询的峰值负载与稳定性验证。</t>
-        </is>
-      </c>
-      <c r="I37" s="1061" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J37" s="1060" t="inlineStr">
-        <is>
-          <t>三条核心链路、500 TPS 峰值、两小时稳定性和容量拐点分析需要多轮调优。</t>
-        </is>
-      </c>
-      <c r="K37" s="1060" t="inlineStr"/>
-      <c r="L37" s="1060" t="inlineStr">
-        <is>
-          <t>一个生产前性能与容量测试实例。</t>
-        </is>
-      </c>
-      <c r="M37" s="945">
-        <f>IF(OR(D37="",E37="",G37=""),"",IFERROR(IF(G37="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E37,BaseUnitCatalogTable[基础单元名称],0)),IF(G37="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E37,BaseUnitCatalogTable[基础单元名称],0)),IF(G37="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E37,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N37" s="945">
-        <f>IF(OR(D37="",I37=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I37,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O37" s="945">
-        <f>IF(OR(D37="",NOT(ISNUMBER(M37)),NOT(ISNUMBER(N37))),"",ROUND(M37*N37,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="38" customHeight="1" s="1025">
-      <c r="A38" s="944">
-        <f>IF(C38="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C38,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B38" s="944">
-        <f>IF(C38="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C38,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C38" s="1060" t="inlineStr">
-        <is>
-          <t>完成生产烟测与业务确认</t>
-        </is>
-      </c>
-      <c r="D38" s="1060" t="inlineStr">
-        <is>
-          <t>执行生产权限与证书验证</t>
-        </is>
-      </c>
-      <c r="E38" s="1060" t="inlineStr">
-        <is>
-          <t>安全与隐私测试</t>
-        </is>
-      </c>
-      <c r="F38" s="945">
-        <f>IF(E38="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E38,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G38" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H38" s="1060" t="inlineStr">
-        <is>
-          <t>新增生产角色最小权限、外部证书、密钥轮换和敏感字段脱敏检查。</t>
-        </is>
-      </c>
-      <c r="I38" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J38" s="1060" t="inlineStr"/>
-      <c r="K38" s="1060" t="inlineStr"/>
-      <c r="L38" s="1060" t="inlineStr">
-        <is>
-          <t>一个生产安全与隐私验证实例。</t>
-        </is>
-      </c>
-      <c r="M38" s="945">
-        <f>IF(OR(D38="",E38="",G38=""),"",IFERROR(IF(G38="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E38,BaseUnitCatalogTable[基础单元名称],0)),IF(G38="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E38,BaseUnitCatalogTable[基础单元名称],0)),IF(G38="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E38,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N38" s="945">
-        <f>IF(OR(D38="",I38=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I38,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O38" s="945">
-        <f>IF(OR(D38="",NOT(ISNUMBER(M38)),NOT(ISNUMBER(N38))),"",ROUND(M38*N38,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="38" customHeight="1" s="1025">
-      <c r="A39" s="944">
-        <f>IF(C39="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C39,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B39" s="944">
-        <f>IF(C39="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C39,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C39" s="1060" t="inlineStr">
-        <is>
-          <t>完成生产烟测与业务确认</t>
-        </is>
-      </c>
-      <c r="D39" s="1060" t="inlineStr">
-        <is>
-          <t>执行五条生产业务烟测</t>
-        </is>
-      </c>
-      <c r="E39" s="1060" t="inlineStr">
-        <is>
-          <t>人工测试</t>
-        </is>
-      </c>
-      <c r="F39" s="945">
-        <f>IF(E39="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E39,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G39" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H39" s="1060" t="inlineStr">
-        <is>
-          <t>新增档案、下单、退款、开票和对账五条生产烟测并留存证据。</t>
-        </is>
-      </c>
-      <c r="I39" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J39" s="1060" t="inlineStr"/>
-      <c r="K39" s="1060" t="inlineStr"/>
-      <c r="L39" s="1060" t="inlineStr">
-        <is>
-          <t>一个生产关键业务链路烟测实例。</t>
-        </is>
-      </c>
-      <c r="M39" s="945">
-        <f>IF(OR(D39="",E39="",G39=""),"",IFERROR(IF(G39="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E39,BaseUnitCatalogTable[基础单元名称],0)),IF(G39="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E39,BaseUnitCatalogTable[基础单元名称],0)),IF(G39="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E39,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N39" s="945">
-        <f>IF(OR(D39="",I39=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I39,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O39" s="945">
-        <f>IF(OR(D39="",NOT(ISNUMBER(M39)),NOT(ISNUMBER(N39))),"",ROUND(M39*N39,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="49" customHeight="1" s="1025">
-      <c r="A40" s="944">
-        <f>IF(C40="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C40,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B40" s="944">
-        <f>IF(C40="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C40,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C40" s="1060" t="inlineStr">
-        <is>
-          <t>迁移会员与历史订单数据</t>
-        </is>
-      </c>
-      <c r="D40" s="1060" t="inlineStr">
-        <is>
-          <t>迁移会员与两年历史订单</t>
-        </is>
-      </c>
-      <c r="E40" s="1060" t="inlineStr">
-        <is>
-          <t>数据迁移</t>
-        </is>
-      </c>
-      <c r="F40" s="945">
-        <f>IF(E40="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E40,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G40" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H40" s="1060" t="inlineStr">
-        <is>
-          <t>从既有会员主数据模型和既有订单服务与状态机抽取数据，执行映射、加载、校验和补偿。</t>
-        </is>
-      </c>
-      <c r="I40" s="1061" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J40" s="1060" t="inlineStr">
-        <is>
-          <t>涉及两类源数据、约 1200 万订单行、历史状态映射、增量窗口和失败补偿。</t>
-        </is>
-      </c>
-      <c r="K40" s="1060" t="inlineStr">
-        <is>
-          <t>既有会员主数据模型</t>
-        </is>
-      </c>
-      <c r="L40" s="1060" t="inlineStr">
-        <is>
-          <t>一个会员与订单迁移批次方案实例，与发布切换分别估算。</t>
-        </is>
-      </c>
-      <c r="M40" s="945">
-        <f>IF(OR(D40="",E40="",G40=""),"",IFERROR(IF(G40="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E40,BaseUnitCatalogTable[基础单元名称],0)),IF(G40="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E40,BaseUnitCatalogTable[基础单元名称],0)),IF(G40="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E40,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N40" s="945">
-        <f>IF(OR(D40="",I40=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I40,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O40" s="945">
-        <f>IF(OR(D40="",NOT(ISNUMBER(M40)),NOT(ISNUMBER(N40))),"",ROUND(M40*N40,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="49" customHeight="1" s="1025">
-      <c r="A41" s="944">
-        <f>IF(C41="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C41,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B41" s="944">
-        <f>IF(C41="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C41,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C41" s="1060" t="inlineStr">
-        <is>
-          <t>迁移会员与历史订单数据</t>
-        </is>
-      </c>
-      <c r="D41" s="1060" t="inlineStr">
-        <is>
-          <t>新建迁移抽取转换流程</t>
-        </is>
-      </c>
-      <c r="E41" s="1060" t="inlineStr">
-        <is>
-          <t>数据处理流程</t>
-        </is>
-      </c>
-      <c r="F41" s="945">
-        <f>IF(E41="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E41,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G41" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H41" s="1060" t="inlineStr">
-        <is>
-          <t>新增全量与增量抽取、字段标准化、状态映射和失败重放流程。</t>
-        </is>
-      </c>
-      <c r="I41" s="1061" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J41" s="1060" t="inlineStr">
-        <is>
-          <t>包含全量与增量两条路径、跨版本状态映射、断点续传和可重复执行控制。</t>
-        </is>
-      </c>
-      <c r="K41" s="1060" t="inlineStr"/>
-      <c r="L41" s="1060" t="inlineStr">
-        <is>
-          <t>一个可重复执行的数据迁移处理流程实例。</t>
-        </is>
-      </c>
-      <c r="M41" s="945">
-        <f>IF(OR(D41="",E41="",G41=""),"",IFERROR(IF(G41="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E41,BaseUnitCatalogTable[基础单元名称],0)),IF(G41="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E41,BaseUnitCatalogTable[基础单元名称],0)),IF(G41="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E41,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N41" s="945">
-        <f>IF(OR(D41="",I41=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I41,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O41" s="945">
-        <f>IF(OR(D41="",NOT(ISNUMBER(M41)),NOT(ISNUMBER(N41))),"",ROUND(M41*N41,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="38" customHeight="1" s="1025">
-      <c r="A42" s="944">
-        <f>IF(C42="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C42,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B42" s="944">
-        <f>IF(C42="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C42,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C42" s="1060" t="inlineStr">
-        <is>
-          <t>迁移会员与历史订单数据</t>
-        </is>
-      </c>
-      <c r="D42" s="1060" t="inlineStr">
-        <is>
-          <t>验证迁移数量与关键字段</t>
-        </is>
-      </c>
-      <c r="E42" s="1060" t="inlineStr">
-        <is>
-          <t>人工测试</t>
-        </is>
-      </c>
-      <c r="F42" s="945">
-        <f>IF(E42="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E42,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G42" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H42" s="1060" t="inlineStr">
-        <is>
-          <t>新增数量、金额、业务主键、抽样字段和失败补偿核对场景。</t>
-        </is>
-      </c>
-      <c r="I42" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J42" s="1060" t="inlineStr"/>
-      <c r="K42" s="1060" t="inlineStr"/>
-      <c r="L42" s="1060" t="inlineStr">
-        <is>
-          <t>一个迁移核对与业务签署测试实例。</t>
-        </is>
-      </c>
-      <c r="M42" s="945">
-        <f>IF(OR(D42="",E42="",G42=""),"",IFERROR(IF(G42="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E42,BaseUnitCatalogTable[基础单元名称],0)),IF(G42="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E42,BaseUnitCatalogTable[基础单元名称],0)),IF(G42="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E42,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N42" s="945">
-        <f>IF(OR(D42="",I42=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I42,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O42" s="945">
-        <f>IF(OR(D42="",NOT(ISNUMBER(M42)),NOT(ISNUMBER(N42))),"",ROUND(M42*N42,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="49" customHeight="1" s="1025">
-      <c r="A43" s="944">
-        <f>IF(C43="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C43,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B43" s="944">
-        <f>IF(C43="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C43,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C43" s="1060" t="inlineStr">
-        <is>
-          <t>监控核心交易与财务作业</t>
-        </is>
-      </c>
-      <c r="D43" s="1060" t="inlineStr">
-        <is>
-          <t>调整既有统一监控平台的交易与财务看板</t>
-        </is>
-      </c>
-      <c r="E43" s="1060" t="inlineStr">
-        <is>
-          <t>监控、追踪与审计</t>
-        </is>
-      </c>
-      <c r="F43" s="945">
-        <f>IF(E43="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E43,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G43" s="1061" t="inlineStr">
-        <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="H43" s="1060" t="inlineStr">
-        <is>
-          <t>在既有统一监控平台新增订单成功率、退款失败、开票积压和对账延迟指标。</t>
-        </is>
-      </c>
-      <c r="I43" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J43" s="1060" t="inlineStr"/>
-      <c r="K43" s="1060" t="inlineStr">
-        <is>
-          <t>既有统一监控平台</t>
-        </is>
-      </c>
-      <c r="L43" s="1060" t="inlineStr">
-        <is>
-          <t>一个核心交易与财务作业可观测性实例。</t>
-        </is>
-      </c>
-      <c r="M43" s="945">
-        <f>IF(OR(D43="",E43="",G43=""),"",IFERROR(IF(G43="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E43,BaseUnitCatalogTable[基础单元名称],0)),IF(G43="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E43,BaseUnitCatalogTable[基础单元名称],0)),IF(G43="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E43,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N43" s="945">
-        <f>IF(OR(D43="",I43=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I43,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O43" s="945">
-        <f>IF(OR(D43="",NOT(ISNUMBER(M43)),NOT(ISNUMBER(N43))),"",ROUND(M43*N43,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="38" customHeight="1" s="1025">
-      <c r="A44" s="944">
-        <f>IF(C44="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C44,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B44" s="944">
-        <f>IF(C44="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C44,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C44" s="1060" t="inlineStr">
-        <is>
-          <t>监控核心交易与财务作业</t>
-        </is>
-      </c>
-      <c r="D44" s="1060" t="inlineStr">
-        <is>
-          <t>新建关键链路稳定性控制</t>
-        </is>
-      </c>
-      <c r="E44" s="1060" t="inlineStr">
-        <is>
-          <t>性能与稳定性保障</t>
-        </is>
-      </c>
-      <c r="F44" s="945">
-        <f>IF(E44="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E44,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G44" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H44" s="1060" t="inlineStr">
-        <is>
-          <t>新增 ERP、支付和发票调用的超时、限流、重试与熔断配置。</t>
-        </is>
-      </c>
-      <c r="I44" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J44" s="1060" t="inlineStr"/>
-      <c r="K44" s="1060" t="inlineStr"/>
-      <c r="L44" s="1060" t="inlineStr">
-        <is>
-          <t>一个跨外部依赖的性能与稳定性保障实例。</t>
-        </is>
-      </c>
-      <c r="M44" s="945">
-        <f>IF(OR(D44="",E44="",G44=""),"",IFERROR(IF(G44="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E44,BaseUnitCatalogTable[基础单元名称],0)),IF(G44="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E44,BaseUnitCatalogTable[基础单元名称],0)),IF(G44="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E44,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N44" s="945">
-        <f>IF(OR(D44="",I44=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I44,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O44" s="945">
-        <f>IF(OR(D44="",NOT(ISNUMBER(M44)),NOT(ISNUMBER(N44))),"",ROUND(M44*N44,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="49" customHeight="1" s="1025">
-      <c r="A45" s="944">
-        <f>IF(C45="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C45,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B45" s="944">
-        <f>IF(C45="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C45,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C45" s="1060" t="inlineStr">
-        <is>
-          <t>完成运维交接与演练</t>
-        </is>
-      </c>
-      <c r="D45" s="1060" t="inlineStr">
-        <is>
-          <t>调整既有统一监控平台的运维手册与交接</t>
-        </is>
-      </c>
-      <c r="E45" s="1060" t="inlineStr">
-        <is>
-          <t>运维交接与操作手册</t>
-        </is>
-      </c>
-      <c r="F45" s="945">
-        <f>IF(E45="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E45,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G45" s="1061" t="inlineStr">
-        <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="H45" s="1060" t="inlineStr">
-        <is>
-          <t>基于既有统一监控平台补齐指标说明、责任人、通知渠道、排障和升级流程。</t>
-        </is>
-      </c>
-      <c r="I45" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J45" s="1060" t="inlineStr"/>
-      <c r="K45" s="1060" t="inlineStr">
-        <is>
-          <t>既有统一监控平台</t>
-        </is>
-      </c>
-      <c r="L45" s="1060" t="inlineStr">
-        <is>
-          <t>一个运维交接包和一次故障演练实例。</t>
-        </is>
-      </c>
-      <c r="M45" s="945">
-        <f>IF(OR(D45="",E45="",G45=""),"",IFERROR(IF(G45="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E45,BaseUnitCatalogTable[基础单元名称],0)),IF(G45="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E45,BaseUnitCatalogTable[基础单元名称],0)),IF(G45="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E45,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N45" s="945">
-        <f>IF(OR(D45="",I45=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I45,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O45" s="945">
-        <f>IF(OR(D45="",NOT(ISNUMBER(M45)),NOT(ISNUMBER(N45))),"",ROUND(M45*N45,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="38" customHeight="1" s="1025">
-      <c r="A46" s="944">
-        <f>IF(C46="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C46,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B46" s="944">
-        <f>IF(C46="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C46,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C46" s="1060" t="inlineStr">
-        <is>
-          <t>培训门店、客服和财务用户</t>
-        </is>
-      </c>
-      <c r="D46" s="1060" t="inlineStr">
-        <is>
-          <t>交付门店客服财务培训</t>
-        </is>
-      </c>
-      <c r="E46" s="1060" t="inlineStr">
-        <is>
-          <t>用户培训与使用材料</t>
-        </is>
-      </c>
-      <c r="F46" s="945">
-        <f>IF(E46="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E46,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G46" s="1061" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H46" s="1060" t="inlineStr">
-        <is>
-          <t>新增门店、客服和财务三类角色材料，并组织两场培训和反馈收集。</t>
-        </is>
-      </c>
-      <c r="I46" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J46" s="1060" t="inlineStr"/>
-      <c r="K46" s="1060" t="inlineStr"/>
-      <c r="L46" s="1060" t="inlineStr">
-        <is>
-          <t>一个角色化用户培训与使用材料交付实例。</t>
-        </is>
-      </c>
-      <c r="M46" s="945">
-        <f>IF(OR(D46="",E46="",G46=""),"",IFERROR(IF(G46="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E46,BaseUnitCatalogTable[基础单元名称],0)),IF(G46="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E46,BaseUnitCatalogTable[基础单元名称],0)),IF(G46="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E46,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N46" s="945">
-        <f>IF(OR(D46="",I46=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I46,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O46" s="945">
-        <f>IF(OR(D46="",NOT(ISNUMBER(M46)),NOT(ISNUMBER(N46))),"",ROUND(M46*N46,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="38" customHeight="1" s="1025">
-      <c r="A47" s="944">
-        <f>IF(C47="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C47,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B47" s="944">
-        <f>IF(C47="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C47,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C47" s="1060" t="inlineStr">
-        <is>
-          <t>扩展自动化与性能验证</t>
-        </is>
-      </c>
-      <c r="D47" s="1060" t="inlineStr">
-        <is>
-          <t>调整既有回归测试资产的自动化框架</t>
-        </is>
-      </c>
-      <c r="E47" s="1060" t="inlineStr">
-        <is>
-          <t>自动化测试框架</t>
-        </is>
-      </c>
-      <c r="F47" s="945">
-        <f>IF(E47="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E47,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G47" s="1061" t="inlineStr">
-        <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="H47" s="1060" t="inlineStr">
-        <is>
-          <t>扩展既有回归测试资产的认证、测试数据、异步回调和报告能力。</t>
-        </is>
-      </c>
-      <c r="I47" s="1061" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J47" s="1060" t="inlineStr"/>
-      <c r="K47" s="1060" t="inlineStr">
-        <is>
-          <t>既有回归测试资产</t>
-        </is>
-      </c>
-      <c r="L47" s="1060" t="inlineStr">
-        <is>
-          <t>一个 API 自动化测试框架调整实例。</t>
-        </is>
-      </c>
-      <c r="M47" s="945">
-        <f>IF(OR(D47="",E47="",G47=""),"",IFERROR(IF(G47="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E47,BaseUnitCatalogTable[基础单元名称],0)),IF(G47="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E47,BaseUnitCatalogTable[基础单元名称],0)),IF(G47="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E47,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N47" s="945">
-        <f>IF(OR(D47="",I47=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I47,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O47" s="945">
-        <f>IF(OR(D47="",NOT(ISNUMBER(M47)),NOT(ISNUMBER(N47))),"",ROUND(M47*N47,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="49" customHeight="1" s="1025">
-      <c r="A48" s="944">
-        <f>IF(C48="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C48,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B48" s="944">
-        <f>IF(C48="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C48,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C48" s="1060" t="inlineStr">
-        <is>
-          <t>扩展自动化与性能验证</t>
-        </is>
-      </c>
-      <c r="D48" s="1060" t="inlineStr">
-        <is>
-          <t>调整既有回归测试资产的核心自动化用例</t>
-        </is>
-      </c>
-      <c r="E48" s="1060" t="inlineStr">
-        <is>
-          <t>自动化测试用例</t>
-        </is>
-      </c>
-      <c r="F48" s="945">
-        <f>IF(E48="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E48,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G48" s="1061" t="inlineStr">
-        <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="H48" s="1060" t="inlineStr">
-        <is>
-          <t>在既有回归测试资产中增加订单状态、库存、退款、开票和对账自动化用例。</t>
-        </is>
-      </c>
-      <c r="I48" s="1061" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J48" s="1060" t="inlineStr">
-        <is>
-          <t>覆盖五条跨系统链路、异步结果、失败补偿和财务金额断言，数据组合较多。</t>
-        </is>
-      </c>
-      <c r="K48" s="1060" t="inlineStr">
-        <is>
-          <t>既有回归测试资产</t>
-        </is>
-      </c>
-      <c r="L48" s="1060" t="inlineStr">
-        <is>
-          <t>一个核心业务自动化用例集实例。</t>
-        </is>
-      </c>
-      <c r="M48" s="945">
-        <f>IF(OR(D48="",E48="",G48=""),"",IFERROR(IF(G48="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E48,BaseUnitCatalogTable[基础单元名称],0)),IF(G48="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E48,BaseUnitCatalogTable[基础单元名称],0)),IF(G48="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E48,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N48" s="945">
-        <f>IF(OR(D48="",I48=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I48,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O48" s="945">
-        <f>IF(OR(D48="",NOT(ISNUMBER(M48)),NOT(ISNUMBER(N48))),"",ROUND(M48*N48,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="49" customHeight="1" s="1025">
-      <c r="A49" s="944">
-        <f>IF(C49="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C49,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B49" s="944">
-        <f>IF(C49="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C49,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C49" s="1060" t="inlineStr">
-        <is>
-          <t>执行兼容性与工程回归</t>
-        </is>
-      </c>
-      <c r="D49" s="1060" t="inlineStr">
-        <is>
-          <t>调整既有回归测试资产的兼容矩阵</t>
-        </is>
-      </c>
-      <c r="E49" s="1060" t="inlineStr">
-        <is>
-          <t>兼容性与无障碍测试</t>
-        </is>
-      </c>
-      <c r="F49" s="945">
-        <f>IF(E49="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E49,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G49" s="1061" t="inlineStr">
-        <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="H49" s="1060" t="inlineStr">
-        <is>
-          <t>根据既有回归测试资产更新浏览器、门店设备和无障碍检查范围。</t>
-        </is>
-      </c>
-      <c r="I49" s="1061" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="J49" s="1060" t="inlineStr">
-        <is>
-          <t>仅验证两类浏览器和一种门店设备，沿用现有脚本且无新增终端。</t>
-        </is>
-      </c>
-      <c r="K49" s="1060" t="inlineStr">
-        <is>
-          <t>既有回归测试资产</t>
-        </is>
-      </c>
-      <c r="L49" s="1060" t="inlineStr">
-        <is>
-          <t>一个兼容性与无障碍测试矩阵实例。</t>
-        </is>
-      </c>
-      <c r="M49" s="945">
-        <f>IF(OR(D49="",E49="",G49=""),"",IFERROR(IF(G49="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E49,BaseUnitCatalogTable[基础单元名称],0)),IF(G49="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E49,BaseUnitCatalogTable[基础单元名称],0)),IF(G49="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E49,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N49" s="945">
-        <f>IF(OR(D49="",I49=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I49,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O49" s="945">
-        <f>IF(OR(D49="",NOT(ISNUMBER(M49)),NOT(ISNUMBER(N49))),"",ROUND(M49*N49,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="38" customHeight="1" s="1025">
-      <c r="A50" s="944">
-        <f>IF(C50="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C50,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B50" s="944">
-        <f>IF(C50="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C50,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C50" s="1060" t="inlineStr">
-        <is>
-          <t>执行兼容性与工程回归</t>
-        </is>
-      </c>
-      <c r="D50" s="1060" t="inlineStr">
-        <is>
-          <t>调整既有回归测试资产的工程回归范围</t>
-        </is>
-      </c>
-      <c r="E50" s="1060" t="inlineStr">
-        <is>
-          <t>人工测试</t>
-        </is>
-      </c>
-      <c r="F50" s="945">
-        <f>IF(E50="","",IFERROR(INDEX(BaseUnitCatalogTable[任务族名称],MATCH(E50,BaseUnitCatalogTable[基础单元名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="G50" s="1061" t="inlineStr">
-        <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="H50" s="1060" t="inlineStr">
-        <is>
-          <t>基于既有回归测试资产补充配置、权限、作业恢复和日志审计检查。</t>
-        </is>
-      </c>
-      <c r="I50" s="1061" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="J50" s="1060" t="inlineStr">
-        <is>
-          <t>四项工程检查均有现成步骤，只需补充新配置和日志断言。</t>
-        </is>
-      </c>
-      <c r="K50" s="1060" t="inlineStr">
-        <is>
-          <t>既有回归测试资产</t>
-        </is>
-      </c>
-      <c r="L50" s="1060" t="inlineStr">
-        <is>
-          <t>一个不计入 UAT 分母的工程回归测试实例。</t>
-        </is>
-      </c>
-      <c r="M50" s="945">
-        <f>IF(OR(D50="",E50="",G50=""),"",IFERROR(IF(G50="新建",INDEX(BaseUnitCatalogTable[新建M档人天],MATCH(E50,BaseUnitCatalogTable[基础单元名称],0)),IF(G50="调整",INDEX(BaseUnitCatalogTable[调整M档人天],MATCH(E50,BaseUnitCatalogTable[基础单元名称],0)),IF(G50="接入复用",INDEX(BaseUnitCatalogTable[接入复用M档人天],MATCH(E50,BaseUnitCatalogTable[基础单元名称],0)),""))),""))</f>
-        <v/>
-      </c>
-      <c r="N50" s="945">
-        <f>IF(OR(D50="",I50=""),"",IFERROR(INDEX(ProjectParameterTable[值],MATCH("K_COMPLEXITY_"&amp;I50,ProjectParameterTable[参数代码],0)),""))</f>
-        <v/>
-      </c>
-      <c r="O50" s="945">
-        <f>IF(OR(D50="",NOT(ISNUMBER(M50)),NOT(ISNUMBER(N50))),"",ROUND(M50*N50,1))</f>
-        <v/>
-      </c>
-    </row>
+    <row r="8" s="1025"/>
+    <row r="9" s="1025"/>
+    <row r="10" s="1025"/>
+    <row r="11" s="1025"/>
+    <row r="12" s="1025"/>
+    <row r="13" s="1025"/>
+    <row r="14" s="1025"/>
+    <row r="15" s="1025"/>
+    <row r="16" s="1025"/>
+    <row r="17" s="1025"/>
+    <row r="18" s="1025"/>
+    <row r="19" s="1025"/>
+    <row r="20" s="1025"/>
+    <row r="21" s="1025"/>
+    <row r="22" s="1025"/>
+    <row r="23" s="1025"/>
+    <row r="24" s="1025"/>
+    <row r="25" s="1025"/>
+    <row r="26" s="1025"/>
+    <row r="27" s="1025"/>
+    <row r="28" s="1025"/>
+    <row r="29" s="1025"/>
+    <row r="30" s="1025"/>
+    <row r="31" s="1025"/>
+    <row r="32" s="1025"/>
+    <row r="33" s="1025"/>
+    <row r="34" s="1025"/>
+    <row r="35" s="1025"/>
+    <row r="36" s="1025"/>
+    <row r="37" s="1025"/>
+    <row r="38" s="1025"/>
+    <row r="39" s="1025"/>
+    <row r="40" s="1025"/>
+    <row r="41" s="1025"/>
+    <row r="42" s="1025"/>
+    <row r="43" s="1025"/>
+    <row r="44" s="1025"/>
+    <row r="45" s="1025"/>
+    <row r="46" s="1025"/>
+    <row r="47" s="1025"/>
+    <row r="48" s="1025"/>
+    <row r="49" s="1025"/>
+    <row r="50" s="1025"/>
     <row r="51" s="1025"/>
     <row r="52" s="1025"/>
     <row r="53" s="1025"/>
@@ -18360,27 +13526,27 @@
       </c>
       <c r="C5" s="944" t="inlineStr">
         <is>
-          <t>集成会员主数据查询</t>
+          <t>完成退款自动审核与状态通知</t>
         </is>
       </c>
       <c r="D5" s="944" t="inlineStr">
         <is>
-          <t>接入内部客户档案 API</t>
+          <t>接入支付平台退款接口</t>
         </is>
       </c>
       <c r="E5" s="1060" t="inlineStr">
         <is>
-          <t>星云会员门户</t>
+          <t>退款编排服务</t>
         </is>
       </c>
       <c r="F5" s="1060" t="inlineStr">
         <is>
-          <t>会员主数据服务</t>
+          <t>支付平台</t>
         </is>
       </c>
       <c r="G5" s="1060" t="inlineStr">
         <is>
-          <t>收到客户档案查看请求</t>
+          <t>退款申请通过审核</t>
         </is>
       </c>
       <c r="H5" s="1061" t="inlineStr">
@@ -18390,12 +13556,12 @@
       </c>
       <c r="I5" s="1060" t="inlineStr">
         <is>
-          <t>检索统一会员号和授权范围内的客户档案</t>
+          <t>发起退款并取得最终支付状态。</t>
         </is>
       </c>
       <c r="J5" s="1061" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>支付平台责任</t>
         </is>
       </c>
       <c r="K5" s="945">
@@ -18415,204 +13581,9 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="38" customHeight="1" s="1025">
-      <c r="A6" s="944">
-        <f>IF(C6="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C6,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B6" s="944">
-        <f>IF(C6="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C6,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C6" s="944" t="inlineStr">
-        <is>
-          <t>预占和释放 ERP 库存</t>
-        </is>
-      </c>
-      <c r="D6" s="944" t="inlineStr">
-        <is>
-          <t>接入既有 ERP 库存接口</t>
-        </is>
-      </c>
-      <c r="E6" s="1060" t="inlineStr">
-        <is>
-          <t>订单服务</t>
-        </is>
-      </c>
-      <c r="F6" s="1060" t="inlineStr">
-        <is>
-          <t>ERP</t>
-        </is>
-      </c>
-      <c r="G6" s="1060" t="inlineStr">
-        <is>
-          <t>订单确认、取消或预占超时</t>
-        </is>
-      </c>
-      <c r="H6" s="1061" t="inlineStr">
-        <is>
-          <t>出站</t>
-        </is>
-      </c>
-      <c r="I6" s="1060" t="inlineStr">
-        <is>
-          <t>预占或释放门店与仓库库存</t>
-        </is>
-      </c>
-      <c r="J6" s="1061" t="inlineStr">
-        <is>
-          <t>内部</t>
-        </is>
-      </c>
-      <c r="K6" s="945">
-        <f>IF(D6="","",IFERROR(INDEX(TaskTable[工作模式],MATCH(D6,TaskTable[任务名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="L6" s="945">
-        <f>IF(D6="","",IFERROR(INDEX(TaskTable[复杂度],MATCH(D6,TaskTable[任务名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="M6" s="945">
-        <f>IF(D6="","",IF(J6="内部",INDEX(ProjectParameterTable[值],MATCH("SIT_INT_SUPPORT",ProjectParameterTable[参数代码],0)),IF(J6="外部",INDEX(ProjectParameterTable[值],MATCH("SIT_EXT_SUPPORT",ProjectParameterTable[参数代码],0)),"")))</f>
-        <v/>
-      </c>
-      <c r="N6" s="945">
-        <f>IF(OR(D6="",M6=""),"",ROUND(M6*IFERROR(INDEX(TaskTable[复杂度倍率],MATCH(D6,TaskTable[任务名称],0)),0),1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="38" customHeight="1" s="1025">
-      <c r="A7" s="944">
-        <f>IF(C7="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C7,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B7" s="944">
-        <f>IF(C7="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C7,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C7" s="944" t="inlineStr">
-        <is>
-          <t>发起退款并回写结果</t>
-        </is>
-      </c>
-      <c r="D7" s="944" t="inlineStr">
-        <is>
-          <t>接入既有支付网关租户</t>
-        </is>
-      </c>
-      <c r="E7" s="1060" t="inlineStr">
-        <is>
-          <t>订单服务</t>
-        </is>
-      </c>
-      <c r="F7" s="1060" t="inlineStr">
-        <is>
-          <t>支付网关</t>
-        </is>
-      </c>
-      <c r="G7" s="1060" t="inlineStr">
-        <is>
-          <t>退货审核通过</t>
-        </is>
-      </c>
-      <c r="H7" s="1061" t="inlineStr">
-        <is>
-          <t>出站</t>
-        </is>
-      </c>
-      <c r="I7" s="1060" t="inlineStr">
-        <is>
-          <t>发起退款并查询或接收退款结果</t>
-        </is>
-      </c>
-      <c r="J7" s="1061" t="inlineStr">
-        <is>
-          <t>外部</t>
-        </is>
-      </c>
-      <c r="K7" s="945">
-        <f>IF(D7="","",IFERROR(INDEX(TaskTable[工作模式],MATCH(D7,TaskTable[任务名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="L7" s="945">
-        <f>IF(D7="","",IFERROR(INDEX(TaskTable[复杂度],MATCH(D7,TaskTable[任务名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="M7" s="945">
-        <f>IF(D7="","",IF(J7="内部",INDEX(ProjectParameterTable[值],MATCH("SIT_INT_SUPPORT",ProjectParameterTable[参数代码],0)),IF(J7="外部",INDEX(ProjectParameterTable[值],MATCH("SIT_EXT_SUPPORT",ProjectParameterTable[参数代码],0)),"")))</f>
-        <v/>
-      </c>
-      <c r="N7" s="945">
-        <f>IF(OR(D7="",M7=""),"",ROUND(M7*IFERROR(INDEX(TaskTable[复杂度倍率],MATCH(D7,TaskTable[任务名称],0)),0),1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1" s="1025">
-      <c r="A8" s="944">
-        <f>IF(C8="","",IFERROR(INDEX(SOWStoryTable[需求名称],MATCH(C8,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="B8" s="944">
-        <f>IF(C8="","",IFERROR(INDEX(SOWStoryTable[子需求名称],MATCH(C8,SOWStoryTable[故事名称],0)),"来源未匹配"))</f>
-        <v/>
-      </c>
-      <c r="C8" s="944" t="inlineStr">
-        <is>
-          <t>申请并追踪电子发票</t>
-        </is>
-      </c>
-      <c r="D8" s="944" t="inlineStr">
-        <is>
-          <t>接入既有电子发票通道</t>
-        </is>
-      </c>
-      <c r="E8" s="1060" t="inlineStr">
-        <is>
-          <t>订单服务</t>
-        </is>
-      </c>
-      <c r="F8" s="1060" t="inlineStr">
-        <is>
-          <t>电子发票平台</t>
-        </is>
-      </c>
-      <c r="G8" s="1060" t="inlineStr">
-        <is>
-          <t>顾客对已完成订单提交开票申请</t>
-        </is>
-      </c>
-      <c r="H8" s="1061" t="inlineStr">
-        <is>
-          <t>出站</t>
-        </is>
-      </c>
-      <c r="I8" s="1060" t="inlineStr">
-        <is>
-          <t>申请电子发票并查询开票状态</t>
-        </is>
-      </c>
-      <c r="J8" s="1061" t="inlineStr">
-        <is>
-          <t>外部</t>
-        </is>
-      </c>
-      <c r="K8" s="945">
-        <f>IF(D8="","",IFERROR(INDEX(TaskTable[工作模式],MATCH(D8,TaskTable[任务名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="L8" s="945">
-        <f>IF(D8="","",IFERROR(INDEX(TaskTable[复杂度],MATCH(D8,TaskTable[任务名称],0)),""))</f>
-        <v/>
-      </c>
-      <c r="M8" s="945">
-        <f>IF(D8="","",IF(J8="内部",INDEX(ProjectParameterTable[值],MATCH("SIT_INT_SUPPORT",ProjectParameterTable[参数代码],0)),IF(J8="外部",INDEX(ProjectParameterTable[值],MATCH("SIT_EXT_SUPPORT",ProjectParameterTable[参数代码],0)),"")))</f>
-        <v/>
-      </c>
-      <c r="N8" s="945">
-        <f>IF(OR(D8="",M8=""),"",ROUND(M8*IFERROR(INDEX(TaskTable[复杂度倍率],MATCH(D8,TaskTable[任务名称],0)),0),1))</f>
-        <v/>
-      </c>
-    </row>
+    <row r="6" s="1025"/>
+    <row r="7" s="1025"/>
+    <row r="8" s="1025"/>
     <row r="9" s="1025"/>
     <row r="10" s="1025"/>
     <row r="11" s="1025"/>
@@ -18818,7 +13789,7 @@
     <row r="5" ht="38" customHeight="1" s="1025">
       <c r="A5" s="1060" t="inlineStr">
         <is>
-          <t>会员主数据服务在联调期间可用</t>
+          <t>支付沙箱按时可用</t>
         </is>
       </c>
       <c r="B5" s="1061" t="inlineStr">
@@ -18828,12 +13799,12 @@
       </c>
       <c r="C5" s="1060" t="inlineStr">
         <is>
-          <t>客户档案内部集成测试开始</t>
+          <t>支付平台未在联调开始前提供沙箱</t>
         </is>
       </c>
       <c r="D5" s="1060" t="inlineStr">
         <is>
-          <t>会员主数据团队提供稳定的 SIT 端点和测试账号</t>
+          <t>支付平台责任</t>
         </is>
       </c>
       <c r="E5" s="1061" t="inlineStr">
@@ -18843,184 +13814,34 @@
       </c>
       <c r="F5" s="1060" t="inlineStr">
         <is>
-          <t>按已确认的联调窗口执行系统集成测试</t>
+          <t>沙箱延迟按项目变更控制调整联调计划。</t>
         </is>
       </c>
       <c r="G5" s="1049" t="n"/>
       <c r="H5" s="1049" t="n"/>
       <c r="I5" s="1049" t="n"/>
     </row>
-    <row r="6" ht="38" customHeight="1" s="1025">
-      <c r="A6" s="1060" t="inlineStr">
-        <is>
-          <t>生产告警通知渠道待确认</t>
-        </is>
-      </c>
-      <c r="B6" s="1061" t="inlineStr">
-        <is>
-          <t>风险</t>
-        </is>
-      </c>
-      <c r="C6" s="1060" t="inlineStr">
-        <is>
-          <t>生产准备评审前仍未登记最终通知渠道</t>
-        </is>
-      </c>
-      <c r="D6" s="1060" t="inlineStr">
-        <is>
-          <t>运维团队确认邮件、工单或值班群以及接收人</t>
-        </is>
-      </c>
-      <c r="E6" s="1061" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="F6" s="1060" t="inlineStr">
-        <is>
-          <t>上线前确认渠道并写入监控配置和运维手册</t>
-        </is>
-      </c>
+    <row r="6" s="1025">
       <c r="G6" s="1049" t="n"/>
       <c r="H6" s="1049" t="n"/>
       <c r="I6" s="1049" t="n"/>
     </row>
-    <row r="7" ht="38" customHeight="1" s="1025">
-      <c r="A7" s="1060" t="inlineStr">
-        <is>
-          <t>ERP SIT 环境按工作日窗口开放</t>
-        </is>
-      </c>
-      <c r="B7" s="1061" t="inlineStr">
-        <is>
-          <t>假设</t>
-        </is>
-      </c>
-      <c r="C7" s="1060" t="inlineStr">
-        <is>
-          <t>库存预占联调计划基线确认</t>
-        </is>
-      </c>
-      <c r="D7" s="1060" t="inlineStr">
-        <is>
-          <t>ERP 团队保证工作日 09:00 至 18:00 可用并提前通知停机</t>
-        </is>
-      </c>
-      <c r="E7" s="1061" t="inlineStr">
-        <is>
-          <t>已明确</t>
-        </is>
-      </c>
-      <c r="F7" s="1060" t="inlineStr">
-        <is>
-          <t>联调和缺陷复测安排在已确认窗口内</t>
-        </is>
-      </c>
+    <row r="7" s="1025">
       <c r="G7" s="1049" t="n"/>
       <c r="H7" s="1049" t="n"/>
       <c r="I7" s="1049" t="n"/>
     </row>
-    <row r="8" ht="49" customHeight="1" s="1025">
-      <c r="A8" s="1060" t="inlineStr">
-        <is>
-          <t>支付网关退款认证可能延迟</t>
-        </is>
-      </c>
-      <c r="B8" s="1061" t="inlineStr">
-        <is>
-          <t>风险</t>
-        </is>
-      </c>
-      <c r="C8" s="1060" t="inlineStr">
-        <is>
-          <t>SIT 第 2 周开始时认证材料仍未通过</t>
-        </is>
-      </c>
-      <c r="D8" s="1060" t="inlineStr">
-        <is>
-          <t>资金管理部提交企业材料，项目团队提供回调地址和测试证据</t>
-        </is>
-      </c>
-      <c r="E8" s="1061" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="F8" s="1060" t="inlineStr">
-        <is>
-          <t>项目启动五个工作日内提交材料，延期时调整退款联调顺序</t>
-        </is>
-      </c>
+    <row r="8" s="1025">
       <c r="G8" s="1049" t="n"/>
       <c r="H8" s="1049" t="n"/>
       <c r="I8" s="1049" t="n"/>
     </row>
-    <row r="9" ht="38" customHeight="1" s="1025">
-      <c r="A9" s="1060" t="inlineStr">
-        <is>
-          <t>迁移冻结窗口为周六 00:00 至 04:00</t>
-        </is>
-      </c>
-      <c r="B9" s="1061" t="inlineStr">
-        <is>
-          <t>假设</t>
-        </is>
-      </c>
-      <c r="C9" s="1060" t="inlineStr">
-        <is>
-          <t>生产切换计划批准</t>
-        </is>
-      </c>
-      <c r="D9" s="1060" t="inlineStr">
-        <is>
-          <t>业务负责人批准冻结，数据负责人提供最终增量范围</t>
-        </is>
-      </c>
-      <c r="E9" s="1061" t="inlineStr">
-        <is>
-          <t>已明确</t>
-        </is>
-      </c>
-      <c r="F9" s="1060" t="inlineStr">
-        <is>
-          <t>按四小时窗口编排增量迁移、校验和回滚检查点</t>
-        </is>
-      </c>
+    <row r="9" s="1025">
       <c r="G9" s="1049" t="n"/>
       <c r="H9" s="1049" t="n"/>
       <c r="I9" s="1049" t="n"/>
     </row>
-    <row r="10" ht="38" customHeight="1" s="1025">
-      <c r="A10" s="1060" t="inlineStr">
-        <is>
-          <t>电子发票生产证书与测试配额待确认</t>
-        </is>
-      </c>
-      <c r="B10" s="1061" t="inlineStr">
-        <is>
-          <t>风险</t>
-        </is>
-      </c>
-      <c r="C10" s="1060" t="inlineStr">
-        <is>
-          <t>生产准备评审时证书或每日 500 张测试配额未就绪</t>
-        </is>
-      </c>
-      <c r="D10" s="1060" t="inlineStr">
-        <is>
-          <t>财务共享中心协调供应商下发证书并确认配额</t>
-        </is>
-      </c>
-      <c r="E10" s="1061" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="F10" s="1060" t="inlineStr">
-        <is>
-          <t>联调前确认测试配额，生产切换前完成证书装载和连通性检查</t>
-        </is>
-      </c>
+    <row r="10" s="1025">
       <c r="G10" s="1049" t="n"/>
       <c r="H10" s="1049" t="n"/>
       <c r="I10" s="1049" t="n"/>
